--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="1067">
   <si>
     <t>id</t>
   </si>
@@ -3277,6 +3277,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/74291074815b</t>
+  </si>
+  <si>
+    <t>花牌情缘</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e53c5370ea1c</t>
   </si>
 </sst>
 </file>
@@ -3952,7 +3958,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4005,6 +4011,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4325,8 +4334,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F482"/>
+  <sheetPr/>
+  <dimension ref="A1:F483"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
@@ -4355,7 +4364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:6">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4372,7 +4381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5089,7 +5098,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:6">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5106,7 +5115,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:6">
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5123,7 +5132,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:6">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5140,7 +5149,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:6">
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:6">
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5174,7 +5183,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:6">
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5191,7 +5200,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:6">
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5208,7 +5217,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:6">
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5225,7 +5234,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:6">
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5242,7 +5251,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:6">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5259,7 +5268,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:6">
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5276,7 +5285,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:6">
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5293,7 +5302,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:6">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5310,7 +5319,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:6">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5327,7 +5336,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:6">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5344,7 +5353,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:6">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5361,7 +5370,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:6">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5378,7 +5387,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:6">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5395,7 +5404,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:6">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5412,7 +5421,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:6">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5429,7 +5438,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:6">
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5446,7 +5455,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:6">
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5463,7 +5472,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:6">
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5480,7 +5489,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:6">
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5497,7 +5506,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5514,7 +5523,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:6">
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5531,7 +5540,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:6">
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5548,7 +5557,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:6">
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5565,7 +5574,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:6">
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5582,7 +5591,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:6">
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5599,7 +5608,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:6">
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5616,7 +5625,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:6">
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5633,7 +5642,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:6">
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5650,7 +5659,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:6">
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5667,7 +5676,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:6">
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5684,7 +5693,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:6">
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5718,7 +5727,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:6">
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5803,7 +5812,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:6">
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5820,7 +5829,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:6">
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5837,7 +5846,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:6">
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5854,7 +5863,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:6">
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5888,7 +5897,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:6">
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5908,7 +5917,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:6">
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5925,7 +5934,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:6">
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5942,7 +5951,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:6">
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5959,7 +5968,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" ht="15" hidden="1" spans="1:6">
+    <row r="96" ht="15" spans="1:6">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5977,7 +5986,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="97" ht="15" hidden="1" spans="1:6">
+    <row r="97" ht="15" spans="1:6">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5995,7 +6004,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="98" ht="15" hidden="1" spans="1:6">
+    <row r="98" ht="15" spans="1:6">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6015,7 +6024,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="99" ht="15" hidden="1" spans="1:6">
+    <row r="99" ht="15" spans="1:6">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6035,7 +6044,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="100" ht="15" hidden="1" spans="1:6">
+    <row r="100" ht="15" spans="1:6">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6053,7 +6062,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="101" ht="15" hidden="1" spans="1:6">
+    <row r="101" ht="15" spans="1:6">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6071,7 +6080,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" ht="15" hidden="1" spans="1:6">
+    <row r="102" ht="15" spans="1:6">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6089,7 +6098,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="103" ht="15" hidden="1" spans="1:6">
+    <row r="103" ht="15" spans="1:6">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6107,7 +6116,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="104" ht="15" hidden="1" spans="1:6">
+    <row r="104" ht="15" spans="1:6">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6125,7 +6134,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="105" ht="15" hidden="1" spans="1:6">
+    <row r="105" ht="15" spans="1:6">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6143,7 +6152,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" ht="15" hidden="1" spans="1:6">
+    <row r="106" ht="15" spans="1:6">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6161,7 +6170,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="107" ht="15" hidden="1" spans="1:6">
+    <row r="107" ht="15" spans="1:6">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6179,7 +6188,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" ht="15" hidden="1" spans="1:6">
+    <row r="108" ht="15" spans="1:6">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6197,7 +6206,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="109" ht="15" hidden="1" spans="1:6">
+    <row r="109" ht="15" spans="1:6">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6215,7 +6224,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="110" ht="15" hidden="1" spans="1:6">
+    <row r="110" ht="15" spans="1:6">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6233,7 +6242,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" ht="15" hidden="1" spans="1:6">
+    <row r="111" ht="15" spans="1:6">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6251,7 +6260,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="112" ht="15" hidden="1" spans="1:6">
+    <row r="112" ht="15" spans="1:6">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6269,7 +6278,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="113" ht="15" hidden="1" spans="1:6">
+    <row r="113" ht="15" spans="1:6">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6287,7 +6296,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" ht="15" hidden="1" spans="1:6">
+    <row r="114" ht="15" spans="1:6">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6305,7 +6314,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" ht="15" hidden="1" spans="1:6">
+    <row r="115" ht="15" spans="1:6">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6323,7 +6332,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" ht="15" hidden="1" spans="1:6">
+    <row r="116" ht="15" spans="1:6">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6341,7 +6350,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" ht="15" hidden="1" spans="1:6">
+    <row r="117" ht="15" spans="1:6">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6359,7 +6368,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" ht="15" hidden="1" spans="1:6">
+    <row r="118" ht="15" spans="1:6">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6377,7 +6386,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="119" ht="15" hidden="1" spans="1:6">
+    <row r="119" ht="15" spans="1:6">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6395,7 +6404,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="120" ht="15" hidden="1" spans="1:6">
+    <row r="120" ht="15" spans="1:6">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6413,7 +6422,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="121" ht="15" hidden="1" spans="1:6">
+    <row r="121" ht="15" spans="1:6">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6431,7 +6440,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="122" ht="15" hidden="1" spans="1:6">
+    <row r="122" ht="15" spans="1:6">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6449,7 +6458,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="123" ht="15" hidden="1" spans="1:6">
+    <row r="123" ht="15" spans="1:6">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6467,7 +6476,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="124" ht="15" hidden="1" spans="1:6">
+    <row r="124" ht="15" spans="1:6">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6485,7 +6494,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125" ht="15" hidden="1" spans="1:6">
+    <row r="125" ht="15" spans="1:6">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6503,7 +6512,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" ht="15" hidden="1" spans="1:6">
+    <row r="126" ht="15" spans="1:6">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6521,7 +6530,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="127" ht="15" hidden="1" spans="1:6">
+    <row r="127" ht="15" spans="1:6">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6539,7 +6548,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="128" ht="15" hidden="1" spans="1:6">
+    <row r="128" ht="15" spans="1:6">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6557,7 +6566,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="129" ht="15" hidden="1" spans="1:6">
+    <row r="129" ht="15" spans="1:6">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6575,7 +6584,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="130" ht="15" hidden="1" spans="1:6">
+    <row r="130" ht="15" spans="1:6">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6593,7 +6602,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="131" ht="15" hidden="1" spans="1:6">
+    <row r="131" ht="15" spans="1:6">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6611,7 +6620,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="132" ht="15" hidden="1" spans="1:6">
+    <row r="132" ht="15" spans="1:6">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6629,7 +6638,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="133" ht="15" hidden="1" spans="1:6">
+    <row r="133" ht="15" spans="1:6">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6647,7 +6656,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="134" ht="15" hidden="1" spans="1:6">
+    <row r="134" ht="15" spans="1:6">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6665,7 +6674,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="135" ht="15" hidden="1" spans="1:6">
+    <row r="135" ht="15" spans="1:6">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6683,7 +6692,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="136" ht="15" hidden="1" spans="1:6">
+    <row r="136" ht="15" spans="1:6">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6701,7 +6710,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="137" ht="15" hidden="1" spans="1:6">
+    <row r="137" ht="15" spans="1:6">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6719,7 +6728,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="138" ht="15" hidden="1" spans="1:6">
+    <row r="138" ht="15" spans="1:6">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6737,7 +6746,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="139" ht="15" hidden="1" spans="1:6">
+    <row r="139" ht="15" spans="1:6">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6755,7 +6764,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" ht="15" hidden="1" spans="1:6">
+    <row r="140" ht="15" spans="1:6">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6773,7 +6782,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="141" ht="15" hidden="1" spans="1:6">
+    <row r="141" ht="15" spans="1:6">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6791,7 +6800,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="142" ht="15" hidden="1" spans="1:6">
+    <row r="142" ht="15" spans="1:6">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6809,7 +6818,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="143" ht="15" hidden="1" spans="1:6">
+    <row r="143" ht="15" spans="1:6">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6827,7 +6836,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="144" ht="15" hidden="1" spans="1:6">
+    <row r="144" ht="15" spans="1:6">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6845,7 +6854,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="145" ht="15" hidden="1" spans="1:6">
+    <row r="145" ht="15" spans="1:6">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6863,7 +6872,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="146" ht="15" hidden="1" spans="1:6">
+    <row r="146" ht="15" spans="1:6">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6881,7 +6890,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" ht="15" hidden="1" spans="1:6">
+    <row r="147" ht="15" spans="1:6">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6899,7 +6908,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="148" ht="15" hidden="1" spans="1:6">
+    <row r="148" ht="15" spans="1:6">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6917,7 +6926,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="149" ht="15" hidden="1" spans="1:6">
+    <row r="149" ht="15" spans="1:6">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6935,7 +6944,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="150" ht="15" hidden="1" spans="1:6">
+    <row r="150" ht="15" spans="1:6">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6953,7 +6962,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="151" ht="15" hidden="1" spans="1:6">
+    <row r="151" ht="15" spans="1:6">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6971,7 +6980,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="152" ht="15" hidden="1" spans="1:6">
+    <row r="152" ht="15" spans="1:6">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6989,7 +6998,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="153" ht="15" hidden="1" spans="1:6">
+    <row r="153" ht="15" spans="1:6">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7007,7 +7016,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="154" ht="15" hidden="1" spans="1:6">
+    <row r="154" ht="15" spans="1:6">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7025,7 +7034,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="155" ht="15" hidden="1" spans="1:6">
+    <row r="155" ht="15" spans="1:6">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7043,7 +7052,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="156" ht="15" hidden="1" spans="1:6">
+    <row r="156" ht="15" spans="1:6">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7061,7 +7070,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="157" ht="15" hidden="1" spans="1:6">
+    <row r="157" ht="15" spans="1:6">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7079,7 +7088,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="158" ht="15" hidden="1" spans="1:6">
+    <row r="158" ht="15" spans="1:6">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7097,7 +7106,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="159" ht="15" hidden="1" spans="1:6">
+    <row r="159" ht="15" spans="1:6">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7115,7 +7124,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="160" ht="15" hidden="1" spans="1:6">
+    <row r="160" ht="15" spans="1:6">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7133,7 +7142,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" ht="15" hidden="1" spans="1:6">
+    <row r="161" ht="15" spans="1:6">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7151,7 +7160,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" ht="15" hidden="1" spans="1:6">
+    <row r="162" ht="15" spans="1:6">
       <c r="A162">
         <v>161</v>
       </c>
@@ -7169,7 +7178,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" ht="15" hidden="1" spans="1:6">
+    <row r="163" ht="15" spans="1:6">
       <c r="A163">
         <v>162</v>
       </c>
@@ -7187,7 +7196,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="164" ht="15" hidden="1" spans="1:6">
+    <row r="164" ht="15" spans="1:6">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7205,7 +7214,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="165" ht="15" hidden="1" spans="1:6">
+    <row r="165" ht="15" spans="1:6">
       <c r="A165">
         <v>164</v>
       </c>
@@ -7223,7 +7232,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="166" ht="15" hidden="1" spans="1:6">
+    <row r="166" ht="15" spans="1:6">
       <c r="A166">
         <v>165</v>
       </c>
@@ -7241,7 +7250,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="167" ht="15" hidden="1" spans="1:6">
+    <row r="167" ht="15" spans="1:6">
       <c r="A167">
         <v>166</v>
       </c>
@@ -7259,7 +7268,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="168" ht="15" hidden="1" spans="1:6">
+    <row r="168" ht="15" spans="1:6">
       <c r="A168">
         <v>167</v>
       </c>
@@ -7277,7 +7286,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="169" ht="15" hidden="1" spans="1:6">
+    <row r="169" ht="15" spans="1:6">
       <c r="A169">
         <v>168</v>
       </c>
@@ -7295,7 +7304,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="170" ht="15" hidden="1" spans="1:6">
+    <row r="170" ht="15" spans="1:6">
       <c r="A170">
         <v>169</v>
       </c>
@@ -7313,7 +7322,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="171" ht="15" hidden="1" spans="1:6">
+    <row r="171" ht="15" spans="1:6">
       <c r="A171">
         <v>170</v>
       </c>
@@ -7331,7 +7340,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="172" ht="15" hidden="1" spans="1:6">
+    <row r="172" ht="15" spans="1:6">
       <c r="A172">
         <v>171</v>
       </c>
@@ -7349,7 +7358,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="173" ht="15" hidden="1" spans="1:6">
+    <row r="173" ht="15" spans="1:6">
       <c r="A173">
         <v>172</v>
       </c>
@@ -7367,7 +7376,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="174" ht="15" hidden="1" spans="1:6">
+    <row r="174" ht="15" spans="1:6">
       <c r="A174">
         <v>173</v>
       </c>
@@ -7385,7 +7394,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="175" ht="15" hidden="1" spans="1:6">
+    <row r="175" ht="15" spans="1:6">
       <c r="A175">
         <v>174</v>
       </c>
@@ -7403,7 +7412,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="176" ht="15" hidden="1" spans="1:6">
+    <row r="176" ht="15" spans="1:6">
       <c r="A176">
         <v>175</v>
       </c>
@@ -7421,7 +7430,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="177" ht="15" hidden="1" spans="1:6">
+    <row r="177" ht="15" spans="1:6">
       <c r="A177">
         <v>176</v>
       </c>
@@ -7439,7 +7448,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="178" ht="15" hidden="1" spans="1:6">
+    <row r="178" ht="15" spans="1:6">
       <c r="A178">
         <v>177</v>
       </c>
@@ -7457,7 +7466,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="179" ht="15" hidden="1" spans="1:6">
+    <row r="179" ht="15" spans="1:6">
       <c r="A179">
         <v>178</v>
       </c>
@@ -7475,7 +7484,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="180" ht="15" hidden="1" spans="1:6">
+    <row r="180" ht="15" spans="1:6">
       <c r="A180">
         <v>179</v>
       </c>
@@ -7493,7 +7502,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="181" ht="15" hidden="1" spans="1:6">
+    <row r="181" ht="15" spans="1:6">
       <c r="A181">
         <v>180</v>
       </c>
@@ -7511,7 +7520,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182" ht="15" hidden="1" spans="1:6">
+    <row r="182" ht="15" spans="1:6">
       <c r="A182">
         <v>181</v>
       </c>
@@ -7529,7 +7538,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="183" ht="15" hidden="1" spans="1:6">
+    <row r="183" ht="15" spans="1:6">
       <c r="A183">
         <v>182</v>
       </c>
@@ -7547,7 +7556,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="184" ht="15" hidden="1" spans="1:6">
+    <row r="184" ht="15" spans="1:6">
       <c r="A184">
         <v>183</v>
       </c>
@@ -7565,7 +7574,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="185" ht="15" hidden="1" spans="1:6">
+    <row r="185" ht="15" spans="1:6">
       <c r="A185">
         <v>184</v>
       </c>
@@ -7583,7 +7592,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="186" ht="15" hidden="1" spans="1:6">
+    <row r="186" ht="15" spans="1:6">
       <c r="A186">
         <v>185</v>
       </c>
@@ -7601,7 +7610,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="187" ht="15" hidden="1" spans="1:6">
+    <row r="187" ht="15" spans="1:6">
       <c r="A187">
         <v>186</v>
       </c>
@@ -7619,7 +7628,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="188" ht="15" hidden="1" spans="1:6">
+    <row r="188" ht="15" spans="1:6">
       <c r="A188">
         <v>187</v>
       </c>
@@ -7637,7 +7646,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="189" ht="15" hidden="1" spans="1:6">
+    <row r="189" ht="15" spans="1:6">
       <c r="A189">
         <v>188</v>
       </c>
@@ -7655,7 +7664,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="190" ht="15.5" hidden="1" spans="1:6">
+    <row r="190" ht="15.5" spans="1:6">
       <c r="A190">
         <v>189</v>
       </c>
@@ -7673,7 +7682,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="191" ht="15.5" hidden="1" spans="1:6">
+    <row r="191" ht="15.5" spans="1:6">
       <c r="A191">
         <v>190</v>
       </c>
@@ -7691,7 +7700,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="192" ht="15.5" hidden="1" spans="1:6">
+    <row r="192" ht="15.5" spans="1:6">
       <c r="A192">
         <v>191</v>
       </c>
@@ -7709,7 +7718,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="193" ht="15.5" hidden="1" spans="1:6">
+    <row r="193" ht="15.5" spans="1:6">
       <c r="A193">
         <v>192</v>
       </c>
@@ -7727,7 +7736,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="194" ht="15.5" hidden="1" spans="1:6">
+    <row r="194" ht="15.5" spans="1:6">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7745,7 +7754,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="195" ht="15.5" hidden="1" spans="1:6">
+    <row r="195" ht="15.5" spans="1:6">
       <c r="A195">
         <v>194</v>
       </c>
@@ -7763,7 +7772,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="196" ht="15.5" hidden="1" spans="1:6">
+    <row r="196" ht="15.5" spans="1:6">
       <c r="A196">
         <v>195</v>
       </c>
@@ -7781,7 +7790,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="197" ht="15.5" hidden="1" spans="1:6">
+    <row r="197" ht="15.5" spans="1:6">
       <c r="A197">
         <v>196</v>
       </c>
@@ -7799,7 +7808,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="198" ht="15.5" hidden="1" spans="1:6">
+    <row r="198" ht="15.5" spans="1:6">
       <c r="A198">
         <v>197</v>
       </c>
@@ -7817,7 +7826,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="199" ht="15.5" hidden="1" spans="1:6">
+    <row r="199" ht="15.5" spans="1:6">
       <c r="A199">
         <v>198</v>
       </c>
@@ -7835,7 +7844,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="200" ht="15.5" hidden="1" spans="1:6">
+    <row r="200" ht="15.5" spans="1:6">
       <c r="A200">
         <v>199</v>
       </c>
@@ -7855,7 +7864,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="201" ht="15.5" hidden="1" spans="1:6">
+    <row r="201" ht="15.5" spans="1:6">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7873,7 +7882,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="202" ht="15.5" hidden="1" spans="1:6">
+    <row r="202" ht="15.5" spans="1:6">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7891,7 +7900,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="203" ht="15.5" hidden="1" spans="1:6">
+    <row r="203" ht="15.5" spans="1:6">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7909,7 +7918,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="204" ht="15.5" hidden="1" spans="1:6">
+    <row r="204" ht="15.5" spans="1:6">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7927,7 +7936,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="205" ht="15.5" hidden="1" spans="1:6">
+    <row r="205" ht="15.5" spans="1:6">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7945,7 +7954,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="206" ht="15.5" hidden="1" spans="1:6">
+    <row r="206" ht="15.5" spans="1:6">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7963,7 +7972,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="207" ht="15.5" hidden="1" spans="1:6">
+    <row r="207" ht="15.5" spans="1:6">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7981,7 +7990,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="208" ht="15.5" hidden="1" spans="1:6">
+    <row r="208" ht="15.5" spans="1:6">
       <c r="A208">
         <v>207</v>
       </c>
@@ -7999,7 +8008,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="209" ht="15.5" hidden="1" spans="1:6">
+    <row r="209" ht="15.5" spans="1:6">
       <c r="A209">
         <v>208</v>
       </c>
@@ -8019,7 +8028,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="210" ht="15.5" hidden="1" spans="1:6">
+    <row r="210" ht="15.5" spans="1:6">
       <c r="A210">
         <v>209</v>
       </c>
@@ -8037,7 +8046,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="211" ht="15.5" hidden="1" spans="1:6">
+    <row r="211" ht="15.5" spans="1:6">
       <c r="A211">
         <v>210</v>
       </c>
@@ -8055,7 +8064,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="212" ht="15.5" hidden="1" spans="1:6">
+    <row r="212" ht="15.5" spans="1:6">
       <c r="A212">
         <v>211</v>
       </c>
@@ -8073,7 +8082,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="213" ht="15.5" hidden="1" spans="1:6">
+    <row r="213" ht="15.5" spans="1:6">
       <c r="A213">
         <v>212</v>
       </c>
@@ -8091,7 +8100,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="214" ht="15.5" hidden="1" spans="1:6">
+    <row r="214" ht="15.5" spans="1:6">
       <c r="A214">
         <v>213</v>
       </c>
@@ -8109,7 +8118,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="215" ht="15.5" hidden="1" spans="1:6">
+    <row r="215" ht="15.5" spans="1:6">
       <c r="A215">
         <v>214</v>
       </c>
@@ -8127,7 +8136,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="216" ht="15.5" hidden="1" spans="1:6">
+    <row r="216" ht="15.5" spans="1:6">
       <c r="A216">
         <v>215</v>
       </c>
@@ -8145,7 +8154,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="217" ht="15.5" hidden="1" spans="1:6">
+    <row r="217" ht="15.5" spans="1:6">
       <c r="A217">
         <v>216</v>
       </c>
@@ -8163,7 +8172,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="218" ht="15.5" hidden="1" spans="1:6">
+    <row r="218" ht="15.5" spans="1:6">
       <c r="A218">
         <v>217</v>
       </c>
@@ -8181,7 +8190,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="219" ht="15.5" hidden="1" spans="1:6">
+    <row r="219" ht="15.5" spans="1:6">
       <c r="A219">
         <v>218</v>
       </c>
@@ -8199,7 +8208,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="220" ht="15.5" hidden="1" spans="1:6">
+    <row r="220" ht="15.5" spans="1:6">
       <c r="A220">
         <v>219</v>
       </c>
@@ -8217,7 +8226,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="221" ht="15.5" hidden="1" spans="1:6">
+    <row r="221" ht="15.5" spans="1:6">
       <c r="A221">
         <v>220</v>
       </c>
@@ -8235,7 +8244,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="222" ht="15.5" hidden="1" spans="1:6">
+    <row r="222" ht="15.5" spans="1:6">
       <c r="A222">
         <v>221</v>
       </c>
@@ -8253,7 +8262,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="223" ht="15.5" hidden="1" spans="1:6">
+    <row r="223" ht="15.5" spans="1:6">
       <c r="A223">
         <v>222</v>
       </c>
@@ -8271,7 +8280,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="224" ht="15.5" hidden="1" spans="1:6">
+    <row r="224" ht="15.5" spans="1:6">
       <c r="A224">
         <v>223</v>
       </c>
@@ -8289,7 +8298,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="225" ht="15.5" hidden="1" spans="1:6">
+    <row r="225" ht="15.5" spans="1:6">
       <c r="A225">
         <v>224</v>
       </c>
@@ -8307,7 +8316,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="226" ht="15.5" hidden="1" spans="1:6">
+    <row r="226" ht="15.5" spans="1:6">
       <c r="A226">
         <v>225</v>
       </c>
@@ -8325,7 +8334,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="227" ht="15.5" hidden="1" spans="1:6">
+    <row r="227" ht="15.5" spans="1:6">
       <c r="A227">
         <v>226</v>
       </c>
@@ -8343,7 +8352,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="228" ht="15.5" hidden="1" spans="1:6">
+    <row r="228" ht="15.5" spans="1:6">
       <c r="A228">
         <v>227</v>
       </c>
@@ -8361,7 +8370,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="229" ht="15.5" hidden="1" spans="1:6">
+    <row r="229" ht="15.5" spans="1:6">
       <c r="A229">
         <v>228</v>
       </c>
@@ -8379,7 +8388,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="230" ht="15.5" hidden="1" spans="1:6">
+    <row r="230" ht="15.5" spans="1:6">
       <c r="A230">
         <v>229</v>
       </c>
@@ -8397,7 +8406,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="231" ht="15.5" hidden="1" spans="1:6">
+    <row r="231" ht="15.5" spans="1:6">
       <c r="A231">
         <v>230</v>
       </c>
@@ -8415,7 +8424,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="232" ht="15.5" hidden="1" spans="1:6">
+    <row r="232" ht="15.5" spans="1:6">
       <c r="A232">
         <v>231</v>
       </c>
@@ -8433,7 +8442,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="233" ht="15.5" hidden="1" spans="1:6">
+    <row r="233" ht="15.5" spans="1:6">
       <c r="A233">
         <v>232</v>
       </c>
@@ -8453,7 +8462,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="234" ht="15.5" hidden="1" spans="1:6">
+    <row r="234" ht="15.5" spans="1:6">
       <c r="A234">
         <v>233</v>
       </c>
@@ -8471,7 +8480,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="235" ht="15.5" hidden="1" spans="1:6">
+    <row r="235" ht="15.5" spans="1:6">
       <c r="A235">
         <v>234</v>
       </c>
@@ -8489,7 +8498,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="236" ht="15.5" hidden="1" spans="1:6">
+    <row r="236" ht="15.5" spans="1:6">
       <c r="A236">
         <v>235</v>
       </c>
@@ -8507,7 +8516,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="237" ht="15.5" hidden="1" spans="1:6">
+    <row r="237" ht="15.5" spans="1:6">
       <c r="A237">
         <v>236</v>
       </c>
@@ -8525,7 +8534,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="238" ht="15.5" hidden="1" spans="1:6">
+    <row r="238" ht="15.5" spans="1:6">
       <c r="A238">
         <v>237</v>
       </c>
@@ -8543,7 +8552,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="239" ht="15.5" hidden="1" spans="1:6">
+    <row r="239" ht="15.5" spans="1:6">
       <c r="A239">
         <v>238</v>
       </c>
@@ -8561,7 +8570,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="240" ht="15.5" hidden="1" spans="1:6">
+    <row r="240" ht="15.5" spans="1:6">
       <c r="A240">
         <v>239</v>
       </c>
@@ -8579,7 +8588,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="241" ht="15.5" hidden="1" spans="1:6">
+    <row r="241" ht="15.5" spans="1:6">
       <c r="A241">
         <v>240</v>
       </c>
@@ -8597,7 +8606,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="242" ht="15.5" hidden="1" spans="1:6">
+    <row r="242" ht="15.5" spans="1:6">
       <c r="A242">
         <v>241</v>
       </c>
@@ -8632,7 +8641,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:6">
+    <row r="244" spans="1:6">
       <c r="A244">
         <v>243</v>
       </c>
@@ -8649,7 +8658,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="245" ht="15.5" hidden="1" spans="1:6">
+    <row r="245" ht="15.5" spans="1:6">
       <c r="A245">
         <v>244</v>
       </c>
@@ -8667,7 +8676,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="246" ht="15.5" hidden="1" spans="1:6">
+    <row r="246" ht="15.5" spans="1:6">
       <c r="A246">
         <v>245</v>
       </c>
@@ -8685,7 +8694,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="247" ht="15.5" hidden="1" spans="1:6">
+    <row r="247" ht="15.5" spans="1:6">
       <c r="A247">
         <v>246</v>
       </c>
@@ -8703,7 +8712,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="248" ht="15.5" hidden="1" spans="1:6">
+    <row r="248" ht="15.5" spans="1:6">
       <c r="A248">
         <v>247</v>
       </c>
@@ -8721,7 +8730,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="249" ht="15.5" hidden="1" spans="1:6">
+    <row r="249" ht="15.5" spans="1:6">
       <c r="A249">
         <v>248</v>
       </c>
@@ -8739,7 +8748,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="250" ht="15.5" hidden="1" spans="1:6">
+    <row r="250" ht="15.5" spans="1:6">
       <c r="A250">
         <v>249</v>
       </c>
@@ -8757,7 +8766,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="251" ht="15.5" hidden="1" spans="1:6">
+    <row r="251" ht="15.5" spans="1:6">
       <c r="A251">
         <v>250</v>
       </c>
@@ -8775,7 +8784,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="252" ht="15.5" hidden="1" spans="1:6">
+    <row r="252" ht="15.5" spans="1:6">
       <c r="A252">
         <v>251</v>
       </c>
@@ -8793,7 +8802,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="253" ht="15.5" hidden="1" spans="1:6">
+    <row r="253" ht="15.5" spans="1:6">
       <c r="A253">
         <v>252</v>
       </c>
@@ -8811,7 +8820,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="254" ht="15.5" hidden="1" spans="1:6">
+    <row r="254" ht="15.5" spans="1:6">
       <c r="A254">
         <v>253</v>
       </c>
@@ -8829,7 +8838,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="255" ht="15.5" hidden="1" spans="1:6">
+    <row r="255" ht="15.5" spans="1:6">
       <c r="A255">
         <v>254</v>
       </c>
@@ -8849,7 +8858,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="256" ht="15.5" hidden="1" spans="1:6">
+    <row r="256" ht="15.5" spans="1:6">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8867,7 +8876,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="257" ht="15.5" hidden="1" spans="1:6">
+    <row r="257" ht="15.5" spans="1:6">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8885,7 +8894,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="258" ht="15.5" hidden="1" spans="1:6">
+    <row r="258" ht="15.5" spans="1:6">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8903,7 +8912,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="259" ht="15.5" hidden="1" spans="1:6">
+    <row r="259" ht="15.5" spans="1:6">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8921,7 +8930,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="260" ht="15.5" hidden="1" spans="1:6">
+    <row r="260" ht="15.5" spans="1:6">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8939,7 +8948,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="261" ht="15.5" hidden="1" spans="1:6">
+    <row r="261" ht="15.5" spans="1:6">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8957,7 +8966,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="262" ht="15.5" hidden="1" spans="1:6">
+    <row r="262" ht="15.5" spans="1:6">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8975,7 +8984,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="263" ht="15.5" hidden="1" spans="1:6">
+    <row r="263" ht="15.5" spans="1:6">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8993,7 +9002,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="264" ht="15.5" hidden="1" spans="1:6">
+    <row r="264" ht="15.5" spans="1:6">
       <c r="A264">
         <v>263</v>
       </c>
@@ -9011,7 +9020,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="265" ht="15.5" hidden="1" spans="1:6">
+    <row r="265" ht="15.5" spans="1:6">
       <c r="A265">
         <v>264</v>
       </c>
@@ -9029,7 +9038,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="266" ht="15.5" hidden="1" spans="1:6">
+    <row r="266" ht="15.5" spans="1:6">
       <c r="A266">
         <v>265</v>
       </c>
@@ -9047,7 +9056,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="267" ht="15.5" hidden="1" spans="1:6">
+    <row r="267" ht="15.5" spans="1:6">
       <c r="A267">
         <v>266</v>
       </c>
@@ -9067,7 +9076,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="268" ht="15.5" hidden="1" spans="1:6">
+    <row r="268" ht="15.5" spans="1:6">
       <c r="A268">
         <v>267</v>
       </c>
@@ -9085,7 +9094,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="269" ht="15.5" hidden="1" spans="1:6">
+    <row r="269" ht="15.5" spans="1:6">
       <c r="A269">
         <v>268</v>
       </c>
@@ -9103,7 +9112,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="270" ht="15.5" hidden="1" spans="1:6">
+    <row r="270" ht="15.5" spans="1:6">
       <c r="A270">
         <v>269</v>
       </c>
@@ -9121,7 +9130,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="271" ht="15.5" hidden="1" spans="1:6">
+    <row r="271" ht="15.5" spans="1:6">
       <c r="A271">
         <v>270</v>
       </c>
@@ -9139,7 +9148,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="272" ht="15.5" hidden="1" spans="1:6">
+    <row r="272" ht="15.5" spans="1:6">
       <c r="A272">
         <v>271</v>
       </c>
@@ -9159,7 +9168,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="273" ht="15.5" hidden="1" spans="1:6">
+    <row r="273" ht="15.5" spans="1:6">
       <c r="A273">
         <v>272</v>
       </c>
@@ -9177,7 +9186,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="274" ht="15.5" hidden="1" spans="1:6">
+    <row r="274" ht="15.5" spans="1:6">
       <c r="A274">
         <v>273</v>
       </c>
@@ -9195,7 +9204,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="275" ht="15.5" hidden="1" spans="1:6">
+    <row r="275" ht="15.5" spans="1:6">
       <c r="A275">
         <v>274</v>
       </c>
@@ -9213,7 +9222,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="276" ht="15.5" hidden="1" spans="1:6">
+    <row r="276" ht="15.5" spans="1:6">
       <c r="A276">
         <v>275</v>
       </c>
@@ -9231,7 +9240,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="277" ht="15.5" hidden="1" spans="1:6">
+    <row r="277" ht="15.5" spans="1:6">
       <c r="A277">
         <v>276</v>
       </c>
@@ -9249,7 +9258,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="278" ht="15.5" hidden="1" spans="1:6">
+    <row r="278" ht="15.5" spans="1:6">
       <c r="A278">
         <v>277</v>
       </c>
@@ -9267,7 +9276,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="279" ht="15.5" hidden="1" spans="1:6">
+    <row r="279" ht="15.5" spans="1:6">
       <c r="A279">
         <v>278</v>
       </c>
@@ -9285,7 +9294,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="280" ht="15.5" hidden="1" spans="1:6">
+    <row r="280" ht="15.5" spans="1:6">
       <c r="A280">
         <v>279</v>
       </c>
@@ -9303,7 +9312,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="281" ht="15.5" hidden="1" spans="1:6">
+    <row r="281" ht="15.5" spans="1:6">
       <c r="A281">
         <v>280</v>
       </c>
@@ -9321,7 +9330,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="282" ht="15.5" hidden="1" spans="1:6">
+    <row r="282" ht="15.5" spans="1:6">
       <c r="A282">
         <v>281</v>
       </c>
@@ -9339,7 +9348,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="283" ht="15.5" hidden="1" spans="1:6">
+    <row r="283" ht="15.5" spans="1:6">
       <c r="A283">
         <v>282</v>
       </c>
@@ -9357,7 +9366,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="284" ht="15.5" hidden="1" spans="1:6">
+    <row r="284" ht="15.5" spans="1:6">
       <c r="A284">
         <v>283</v>
       </c>
@@ -9375,7 +9384,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="285" ht="15.5" hidden="1" spans="1:6">
+    <row r="285" ht="15.5" spans="1:6">
       <c r="A285">
         <v>284</v>
       </c>
@@ -9393,7 +9402,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="286" ht="15.5" hidden="1" spans="1:6">
+    <row r="286" ht="15.5" spans="1:6">
       <c r="A286">
         <v>285</v>
       </c>
@@ -9411,7 +9420,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="287" ht="15.5" hidden="1" spans="1:6">
+    <row r="287" ht="15.5" spans="1:6">
       <c r="A287">
         <v>286</v>
       </c>
@@ -9429,7 +9438,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="288" ht="15.5" hidden="1" spans="1:6">
+    <row r="288" ht="15.5" spans="1:6">
       <c r="A288">
         <v>287</v>
       </c>
@@ -9447,7 +9456,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="289" ht="15.5" hidden="1" spans="1:6">
+    <row r="289" ht="15.5" spans="1:6">
       <c r="A289">
         <v>288</v>
       </c>
@@ -9465,7 +9474,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="290" ht="15.5" hidden="1" spans="1:6">
+    <row r="290" ht="15.5" spans="1:6">
       <c r="A290">
         <v>289</v>
       </c>
@@ -9483,7 +9492,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="291" ht="15.5" hidden="1" spans="1:6">
+    <row r="291" ht="15.5" spans="1:6">
       <c r="A291">
         <v>290</v>
       </c>
@@ -9503,7 +9512,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="292" ht="15.5" hidden="1" spans="1:6">
+    <row r="292" ht="15.5" spans="1:6">
       <c r="A292">
         <v>291</v>
       </c>
@@ -9521,7 +9530,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="293" ht="15.5" hidden="1" spans="1:6">
+    <row r="293" ht="15.5" spans="1:6">
       <c r="A293">
         <v>292</v>
       </c>
@@ -9538,7 +9547,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="294" ht="15.5" hidden="1" spans="1:6">
+    <row r="294" ht="15.5" spans="1:6">
       <c r="A294">
         <v>293</v>
       </c>
@@ -9555,7 +9564,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="295" ht="15.5" hidden="1" spans="1:6">
+    <row r="295" ht="15.5" spans="1:6">
       <c r="A295">
         <v>294</v>
       </c>
@@ -9572,7 +9581,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="296" ht="15.5" hidden="1" spans="1:6">
+    <row r="296" ht="15.5" spans="1:6">
       <c r="A296">
         <v>295</v>
       </c>
@@ -9589,7 +9598,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="297" ht="15.5" hidden="1" spans="1:6">
+    <row r="297" ht="15.5" spans="1:6">
       <c r="A297">
         <v>296</v>
       </c>
@@ -9607,7 +9616,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="298" ht="15.5" hidden="1" spans="1:6">
+    <row r="298" ht="15.5" spans="1:6">
       <c r="A298">
         <v>297</v>
       </c>
@@ -9625,7 +9634,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="299" ht="15.5" hidden="1" spans="1:6">
+    <row r="299" ht="15.5" spans="1:6">
       <c r="A299">
         <v>298</v>
       </c>
@@ -9643,7 +9652,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="300" ht="15.5" hidden="1" spans="1:6">
+    <row r="300" ht="15.5" spans="1:6">
       <c r="A300">
         <v>299</v>
       </c>
@@ -9661,7 +9670,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="301" ht="15.5" hidden="1" spans="1:6">
+    <row r="301" ht="15.5" spans="1:6">
       <c r="A301">
         <v>300</v>
       </c>
@@ -9679,7 +9688,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="302" ht="15.5" hidden="1" spans="1:6">
+    <row r="302" ht="15.5" spans="1:6">
       <c r="A302">
         <v>301</v>
       </c>
@@ -9697,7 +9706,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="303" ht="15.5" hidden="1" spans="1:6">
+    <row r="303" ht="15.5" spans="1:6">
       <c r="A303">
         <v>302</v>
       </c>
@@ -9717,7 +9726,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="304" ht="15.5" hidden="1" spans="1:6">
+    <row r="304" ht="15.5" spans="1:6">
       <c r="A304">
         <v>303</v>
       </c>
@@ -9735,7 +9744,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="305" ht="15.5" hidden="1" spans="1:6">
+    <row r="305" ht="15.5" spans="1:6">
       <c r="A305">
         <v>304</v>
       </c>
@@ -9753,7 +9762,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="306" ht="15.5" hidden="1" spans="1:6">
+    <row r="306" ht="15.5" spans="1:6">
       <c r="A306">
         <v>305</v>
       </c>
@@ -9771,7 +9780,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="307" ht="15.5" hidden="1" spans="1:6">
+    <row r="307" ht="15.5" spans="1:6">
       <c r="A307">
         <v>306</v>
       </c>
@@ -9789,7 +9798,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="308" ht="15.5" hidden="1" spans="1:6">
+    <row r="308" ht="15.5" spans="1:6">
       <c r="A308">
         <v>307</v>
       </c>
@@ -9807,7 +9816,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="309" ht="15.5" hidden="1" spans="1:6">
+    <row r="309" ht="15.5" spans="1:6">
       <c r="A309">
         <v>308</v>
       </c>
@@ -9825,7 +9834,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="310" ht="15.5" hidden="1" spans="1:6">
+    <row r="310" ht="15.5" spans="1:6">
       <c r="A310">
         <v>309</v>
       </c>
@@ -9843,7 +9852,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="311" ht="15.5" hidden="1" spans="1:6">
+    <row r="311" ht="15.5" spans="1:6">
       <c r="A311">
         <v>310</v>
       </c>
@@ -9861,7 +9870,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="312" ht="15.5" hidden="1" spans="1:6">
+    <row r="312" ht="15.5" spans="1:6">
       <c r="A312">
         <v>311</v>
       </c>
@@ -9879,7 +9888,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="313" ht="15.5" hidden="1" spans="1:6">
+    <row r="313" ht="15.5" spans="1:6">
       <c r="A313">
         <v>312</v>
       </c>
@@ -9896,7 +9905,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="314" ht="15.5" hidden="1" spans="1:6">
+    <row r="314" ht="15.5" spans="1:6">
       <c r="A314">
         <v>313</v>
       </c>
@@ -9913,7 +9922,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="315" ht="15.5" hidden="1" spans="1:6">
+    <row r="315" ht="15.5" spans="1:6">
       <c r="A315">
         <v>314</v>
       </c>
@@ -9930,7 +9939,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="316" ht="15.5" hidden="1" spans="1:6">
+    <row r="316" ht="15.5" spans="1:6">
       <c r="A316">
         <v>315</v>
       </c>
@@ -9947,7 +9956,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="317" ht="15" hidden="1" spans="1:6">
+    <row r="317" ht="15" spans="1:6">
       <c r="A317">
         <v>316</v>
       </c>
@@ -9965,7 +9974,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="318" ht="15" hidden="1" spans="1:6">
+    <row r="318" ht="15" spans="1:6">
       <c r="A318">
         <v>317</v>
       </c>
@@ -9983,7 +9992,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="319" ht="15" hidden="1" spans="1:6">
+    <row r="319" ht="15" spans="1:6">
       <c r="A319">
         <v>318</v>
       </c>
@@ -10001,7 +10010,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="320" ht="15" hidden="1" spans="1:6">
+    <row r="320" ht="15" spans="1:6">
       <c r="A320">
         <v>319</v>
       </c>
@@ -10019,7 +10028,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="321" ht="15" hidden="1" spans="1:6">
+    <row r="321" ht="15" spans="1:6">
       <c r="A321">
         <v>320</v>
       </c>
@@ -10037,7 +10046,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="322" ht="15" hidden="1" spans="1:6">
+    <row r="322" ht="15" spans="1:6">
       <c r="A322">
         <v>321</v>
       </c>
@@ -10055,7 +10064,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="323" ht="15" hidden="1" spans="1:6">
+    <row r="323" ht="15" spans="1:6">
       <c r="A323">
         <v>322</v>
       </c>
@@ -10073,7 +10082,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="324" ht="15" hidden="1" spans="1:6">
+    <row r="324" ht="15" spans="1:6">
       <c r="A324">
         <v>323</v>
       </c>
@@ -10091,7 +10100,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="325" ht="15" hidden="1" spans="1:6">
+    <row r="325" ht="15" spans="1:6">
       <c r="A325">
         <v>324</v>
       </c>
@@ -10109,7 +10118,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="326" ht="15" hidden="1" spans="1:6">
+    <row r="326" ht="15" spans="1:6">
       <c r="A326">
         <v>325</v>
       </c>
@@ -10127,7 +10136,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="327" ht="15" hidden="1" spans="1:6">
+    <row r="327" ht="15" spans="1:6">
       <c r="A327">
         <v>326</v>
       </c>
@@ -10145,7 +10154,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="328" ht="15" hidden="1" spans="1:6">
+    <row r="328" ht="15" spans="1:6">
       <c r="A328">
         <v>327</v>
       </c>
@@ -10163,7 +10172,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="329" ht="15" hidden="1" spans="1:6">
+    <row r="329" ht="15" spans="1:6">
       <c r="A329">
         <v>328</v>
       </c>
@@ -10181,7 +10190,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="330" ht="15" hidden="1" spans="1:6">
+    <row r="330" ht="15" spans="1:6">
       <c r="A330">
         <v>329</v>
       </c>
@@ -10199,7 +10208,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="331" ht="15" hidden="1" spans="1:6">
+    <row r="331" ht="15" spans="1:6">
       <c r="A331">
         <v>330</v>
       </c>
@@ -10217,7 +10226,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="332" ht="15" hidden="1" spans="1:6">
+    <row r="332" ht="15" spans="1:6">
       <c r="A332">
         <v>331</v>
       </c>
@@ -10235,7 +10244,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="333" ht="15" hidden="1" spans="1:6">
+    <row r="333" ht="15" spans="1:6">
       <c r="A333">
         <v>332</v>
       </c>
@@ -10253,7 +10262,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="334" ht="15" hidden="1" spans="1:6">
+    <row r="334" ht="15" spans="1:6">
       <c r="A334">
         <v>333</v>
       </c>
@@ -10271,7 +10280,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="335" ht="15" hidden="1" spans="1:6">
+    <row r="335" ht="15" spans="1:6">
       <c r="A335">
         <v>334</v>
       </c>
@@ -10289,7 +10298,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="336" ht="15" hidden="1" spans="1:6">
+    <row r="336" ht="15" spans="1:6">
       <c r="A336">
         <v>335</v>
       </c>
@@ -10307,7 +10316,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="337" ht="15" hidden="1" spans="1:6">
+    <row r="337" ht="15" spans="1:6">
       <c r="A337">
         <v>336</v>
       </c>
@@ -10325,7 +10334,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="338" ht="15" hidden="1" spans="1:6">
+    <row r="338" ht="15" spans="1:6">
       <c r="A338">
         <v>337</v>
       </c>
@@ -10343,7 +10352,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="339" ht="15" hidden="1" spans="1:6">
+    <row r="339" ht="15" spans="1:6">
       <c r="A339">
         <v>338</v>
       </c>
@@ -10361,7 +10370,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="340" ht="15" hidden="1" spans="1:6">
+    <row r="340" ht="15" spans="1:6">
       <c r="A340">
         <v>339</v>
       </c>
@@ -10379,7 +10388,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="341" ht="15" hidden="1" spans="1:6">
+    <row r="341" ht="15" spans="1:6">
       <c r="A341">
         <v>340</v>
       </c>
@@ -10397,7 +10406,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="342" ht="15" hidden="1" spans="1:6">
+    <row r="342" ht="15" spans="1:6">
       <c r="A342">
         <v>341</v>
       </c>
@@ -10415,7 +10424,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="343" ht="15" hidden="1" spans="1:6">
+    <row r="343" ht="15" spans="1:6">
       <c r="A343">
         <v>342</v>
       </c>
@@ -10433,7 +10442,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="344" ht="15" hidden="1" spans="1:6">
+    <row r="344" ht="15" spans="1:6">
       <c r="A344">
         <v>343</v>
       </c>
@@ -10453,7 +10462,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="345" ht="15" hidden="1" spans="1:6">
+    <row r="345" ht="15" spans="1:6">
       <c r="A345">
         <v>344</v>
       </c>
@@ -10470,7 +10479,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="346" ht="15" hidden="1" spans="1:6">
+    <row r="346" ht="15" spans="1:6">
       <c r="A346">
         <v>345</v>
       </c>
@@ -10490,7 +10499,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="347" ht="15" hidden="1" spans="1:6">
+    <row r="347" ht="15" spans="1:6">
       <c r="A347">
         <v>346</v>
       </c>
@@ -10508,7 +10517,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="348" ht="15" hidden="1" spans="1:6">
+    <row r="348" ht="15" spans="1:6">
       <c r="A348">
         <v>347</v>
       </c>
@@ -10526,7 +10535,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="349" ht="15" hidden="1" spans="1:6">
+    <row r="349" ht="15" spans="1:6">
       <c r="A349">
         <v>348</v>
       </c>
@@ -10544,7 +10553,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="350" ht="15" hidden="1" spans="1:6">
+    <row r="350" ht="15" spans="1:6">
       <c r="A350">
         <v>349</v>
       </c>
@@ -10562,7 +10571,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="351" ht="15" hidden="1" spans="1:6">
+    <row r="351" ht="15" spans="1:6">
       <c r="A351">
         <v>350</v>
       </c>
@@ -10580,7 +10589,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="352" ht="15" hidden="1" spans="1:6">
+    <row r="352" ht="15" spans="1:6">
       <c r="A352">
         <v>351</v>
       </c>
@@ -10598,7 +10607,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="353" ht="15" hidden="1" spans="1:6">
+    <row r="353" ht="15" spans="1:6">
       <c r="A353">
         <v>352</v>
       </c>
@@ -10616,7 +10625,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="354" ht="15" hidden="1" spans="1:6">
+    <row r="354" ht="15" spans="1:6">
       <c r="A354">
         <v>353</v>
       </c>
@@ -10634,7 +10643,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="355" ht="15" hidden="1" spans="1:6">
+    <row r="355" ht="15" spans="1:6">
       <c r="A355">
         <v>354</v>
       </c>
@@ -10652,7 +10661,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="356" ht="15" hidden="1" spans="1:6">
+    <row r="356" ht="15" spans="1:6">
       <c r="A356">
         <v>355</v>
       </c>
@@ -10670,7 +10679,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="357" ht="15" hidden="1" spans="1:6">
+    <row r="357" ht="15" spans="1:6">
       <c r="A357">
         <v>356</v>
       </c>
@@ -10688,7 +10697,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="358" ht="15" hidden="1" spans="1:6">
+    <row r="358" ht="15" spans="1:6">
       <c r="A358">
         <v>357</v>
       </c>
@@ -10706,7 +10715,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="359" ht="15" hidden="1" spans="1:6">
+    <row r="359" ht="15" spans="1:6">
       <c r="A359">
         <v>358</v>
       </c>
@@ -10724,7 +10733,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="360" ht="15" hidden="1" spans="1:6">
+    <row r="360" ht="15" spans="1:6">
       <c r="A360">
         <v>359</v>
       </c>
@@ -10742,7 +10751,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="361" ht="15" hidden="1" spans="1:6">
+    <row r="361" ht="15" spans="1:6">
       <c r="A361">
         <v>360</v>
       </c>
@@ -10760,7 +10769,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="362" ht="15" hidden="1" spans="1:6">
+    <row r="362" ht="15" spans="1:6">
       <c r="A362">
         <v>361</v>
       </c>
@@ -10778,7 +10787,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="363" ht="15" hidden="1" spans="1:6">
+    <row r="363" ht="15" spans="1:6">
       <c r="A363">
         <v>362</v>
       </c>
@@ -10796,7 +10805,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="364" ht="15" hidden="1" spans="1:6">
+    <row r="364" ht="15" spans="1:6">
       <c r="A364">
         <v>363</v>
       </c>
@@ -10814,7 +10823,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="365" ht="15" hidden="1" spans="1:6">
+    <row r="365" ht="15" spans="1:6">
       <c r="A365">
         <v>364</v>
       </c>
@@ -10832,7 +10841,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="366" ht="15" hidden="1" spans="1:6">
+    <row r="366" ht="15" spans="1:6">
       <c r="A366">
         <v>365</v>
       </c>
@@ -10850,7 +10859,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="367" ht="15" hidden="1" spans="1:6">
+    <row r="367" ht="15" spans="1:6">
       <c r="A367">
         <v>366</v>
       </c>
@@ -10868,7 +10877,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="368" ht="15" hidden="1" spans="1:6">
+    <row r="368" ht="15" spans="1:6">
       <c r="A368">
         <v>367</v>
       </c>
@@ -10886,7 +10895,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="369" ht="15" hidden="1" spans="1:6">
+    <row r="369" ht="15" spans="1:6">
       <c r="A369">
         <v>368</v>
       </c>
@@ -10904,7 +10913,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="370" ht="15" hidden="1" spans="1:6">
+    <row r="370" ht="15" spans="1:6">
       <c r="A370">
         <v>369</v>
       </c>
@@ -10922,7 +10931,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="371" ht="15" hidden="1" spans="1:6">
+    <row r="371" ht="15" spans="1:6">
       <c r="A371">
         <v>370</v>
       </c>
@@ -10940,7 +10949,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="372" ht="15" hidden="1" spans="1:6">
+    <row r="372" ht="15" spans="1:6">
       <c r="A372">
         <v>371</v>
       </c>
@@ -10958,7 +10967,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="373" ht="15" hidden="1" spans="1:6">
+    <row r="373" ht="15" spans="1:6">
       <c r="A373">
         <v>372</v>
       </c>
@@ -10976,7 +10985,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="374" ht="15" hidden="1" spans="1:6">
+    <row r="374" ht="15" spans="1:6">
       <c r="A374">
         <v>373</v>
       </c>
@@ -10994,7 +11003,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="375" ht="15" hidden="1" spans="1:6">
+    <row r="375" ht="15" spans="1:6">
       <c r="A375">
         <v>374</v>
       </c>
@@ -11012,7 +11021,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="376" ht="15" hidden="1" spans="1:6">
+    <row r="376" ht="15" spans="1:6">
       <c r="A376">
         <v>375</v>
       </c>
@@ -11030,7 +11039,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="377" ht="15" hidden="1" spans="1:6">
+    <row r="377" ht="15" spans="1:6">
       <c r="A377">
         <v>376</v>
       </c>
@@ -11048,7 +11057,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="378" ht="15" hidden="1" spans="1:6">
+    <row r="378" ht="15" spans="1:6">
       <c r="A378">
         <v>377</v>
       </c>
@@ -11066,7 +11075,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="379" ht="15" hidden="1" spans="1:6">
+    <row r="379" ht="15" spans="1:6">
       <c r="A379">
         <v>378</v>
       </c>
@@ -11084,7 +11093,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="380" ht="15" hidden="1" spans="1:6">
+    <row r="380" ht="15" spans="1:6">
       <c r="A380">
         <v>379</v>
       </c>
@@ -11102,7 +11111,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="381" ht="15" hidden="1" spans="1:6">
+    <row r="381" ht="15" spans="1:6">
       <c r="A381">
         <v>380</v>
       </c>
@@ -11120,7 +11129,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="382" ht="15" hidden="1" spans="1:6">
+    <row r="382" ht="15" spans="1:6">
       <c r="A382">
         <v>381</v>
       </c>
@@ -11138,7 +11147,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="383" ht="15" hidden="1" spans="1:6">
+    <row r="383" ht="15" spans="1:6">
       <c r="A383">
         <v>382</v>
       </c>
@@ -11156,7 +11165,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="384" ht="15" hidden="1" spans="1:6">
+    <row r="384" ht="15" spans="1:6">
       <c r="A384">
         <v>383</v>
       </c>
@@ -11174,7 +11183,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="385" ht="15" hidden="1" spans="1:6">
+    <row r="385" ht="15" spans="1:6">
       <c r="A385">
         <v>384</v>
       </c>
@@ -11192,7 +11201,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="386" ht="15" hidden="1" spans="1:6">
+    <row r="386" ht="15" spans="1:6">
       <c r="A386">
         <v>385</v>
       </c>
@@ -11210,7 +11219,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="387" ht="15" hidden="1" spans="1:6">
+    <row r="387" ht="15" spans="1:6">
       <c r="A387">
         <v>386</v>
       </c>
@@ -11228,7 +11237,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="388" ht="15" hidden="1" spans="1:6">
+    <row r="388" ht="15" spans="1:6">
       <c r="A388">
         <v>387</v>
       </c>
@@ -11246,7 +11255,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="389" ht="15" hidden="1" spans="1:6">
+    <row r="389" ht="15" spans="1:6">
       <c r="A389">
         <v>388</v>
       </c>
@@ -11264,7 +11273,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="390" ht="15" hidden="1" spans="1:6">
+    <row r="390" ht="15" spans="1:6">
       <c r="A390">
         <v>389</v>
       </c>
@@ -11282,7 +11291,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="391" ht="15" hidden="1" spans="1:6">
+    <row r="391" ht="15" spans="1:6">
       <c r="A391">
         <v>390</v>
       </c>
@@ -11300,7 +11309,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="392" ht="15" hidden="1" spans="1:6">
+    <row r="392" ht="15" spans="1:6">
       <c r="A392">
         <v>391</v>
       </c>
@@ -11318,7 +11327,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="393" ht="15" hidden="1" spans="1:6">
+    <row r="393" ht="15" spans="1:6">
       <c r="A393">
         <v>392</v>
       </c>
@@ -11336,7 +11345,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="394" ht="15" hidden="1" spans="1:6">
+    <row r="394" ht="15" spans="1:6">
       <c r="A394">
         <v>393</v>
       </c>
@@ -11354,7 +11363,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="395" ht="15" hidden="1" spans="1:6">
+    <row r="395" ht="15" spans="1:6">
       <c r="A395">
         <v>394</v>
       </c>
@@ -11372,7 +11381,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="396" ht="15" hidden="1" spans="1:6">
+    <row r="396" ht="15" spans="1:6">
       <c r="A396">
         <v>395</v>
       </c>
@@ -11390,7 +11399,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="397" ht="15" hidden="1" spans="1:6">
+    <row r="397" ht="15" spans="1:6">
       <c r="A397">
         <v>396</v>
       </c>
@@ -11408,7 +11417,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="398" ht="15" hidden="1" spans="1:6">
+    <row r="398" ht="15" spans="1:6">
       <c r="A398">
         <v>397</v>
       </c>
@@ -11426,7 +11435,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="399" ht="15" hidden="1" spans="1:6">
+    <row r="399" ht="15" spans="1:6">
       <c r="A399">
         <v>398</v>
       </c>
@@ -11444,7 +11453,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="400" ht="15" hidden="1" spans="1:6">
+    <row r="400" ht="15" spans="1:6">
       <c r="A400">
         <v>399</v>
       </c>
@@ -11462,7 +11471,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="401" ht="15" hidden="1" spans="1:6">
+    <row r="401" ht="15" spans="1:6">
       <c r="A401">
         <v>400</v>
       </c>
@@ -11480,7 +11489,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="402" ht="15" hidden="1" spans="1:6">
+    <row r="402" ht="15" spans="1:6">
       <c r="A402">
         <v>401</v>
       </c>
@@ -11498,7 +11507,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="403" ht="15" hidden="1" spans="1:6">
+    <row r="403" ht="15" spans="1:6">
       <c r="A403">
         <v>402</v>
       </c>
@@ -11516,7 +11525,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="404" ht="15" hidden="1" spans="1:6">
+    <row r="404" ht="15" spans="1:6">
       <c r="A404">
         <v>403</v>
       </c>
@@ -11534,7 +11543,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="405" ht="15" hidden="1" spans="1:6">
+    <row r="405" ht="15" spans="1:6">
       <c r="A405">
         <v>404</v>
       </c>
@@ -11552,7 +11561,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="406" ht="15" hidden="1" spans="1:6">
+    <row r="406" ht="15" spans="1:6">
       <c r="A406">
         <v>405</v>
       </c>
@@ -11570,7 +11579,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="407" ht="15" hidden="1" spans="1:6">
+    <row r="407" ht="15" spans="1:6">
       <c r="A407">
         <v>406</v>
       </c>
@@ -11588,7 +11597,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="408" ht="15" hidden="1" spans="1:6">
+    <row r="408" ht="15" spans="1:6">
       <c r="A408">
         <v>407</v>
       </c>
@@ -11606,7 +11615,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="409" ht="15" hidden="1" spans="1:6">
+    <row r="409" ht="15" spans="1:6">
       <c r="A409">
         <v>408</v>
       </c>
@@ -11624,7 +11633,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="410" ht="15" hidden="1" spans="1:6">
+    <row r="410" ht="15" spans="1:6">
       <c r="A410">
         <v>409</v>
       </c>
@@ -11642,7 +11651,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="411" ht="15" hidden="1" spans="1:6">
+    <row r="411" ht="15" spans="1:6">
       <c r="A411">
         <v>410</v>
       </c>
@@ -11660,7 +11669,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="412" ht="15" hidden="1" spans="1:6">
+    <row r="412" ht="15" spans="1:6">
       <c r="A412">
         <v>411</v>
       </c>
@@ -11678,7 +11687,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="413" ht="15" hidden="1" spans="1:6">
+    <row r="413" ht="15" spans="1:6">
       <c r="A413">
         <v>412</v>
       </c>
@@ -11696,7 +11705,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="414" ht="15" hidden="1" spans="1:6">
+    <row r="414" ht="15" spans="1:6">
       <c r="A414">
         <v>413</v>
       </c>
@@ -11714,7 +11723,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="415" ht="15" hidden="1" spans="1:6">
+    <row r="415" ht="15" spans="1:6">
       <c r="A415">
         <v>414</v>
       </c>
@@ -11732,7 +11741,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="416" ht="15" hidden="1" spans="1:6">
+    <row r="416" ht="15" spans="1:6">
       <c r="A416">
         <v>415</v>
       </c>
@@ -11750,7 +11759,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="417" ht="15" hidden="1" spans="1:6">
+    <row r="417" ht="15" spans="1:6">
       <c r="A417">
         <v>416</v>
       </c>
@@ -11768,7 +11777,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="418" ht="15" hidden="1" spans="1:6">
+    <row r="418" ht="15" spans="1:6">
       <c r="A418">
         <v>417</v>
       </c>
@@ -11786,7 +11795,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="419" ht="15" hidden="1" spans="1:6">
+    <row r="419" ht="15" spans="1:6">
       <c r="A419">
         <v>418</v>
       </c>
@@ -11804,7 +11813,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="420" ht="15" hidden="1" spans="1:6">
+    <row r="420" ht="15" spans="1:6">
       <c r="A420">
         <v>419</v>
       </c>
@@ -11822,7 +11831,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="421" ht="15" hidden="1" spans="1:6">
+    <row r="421" ht="15" spans="1:6">
       <c r="A421">
         <v>420</v>
       </c>
@@ -11840,7 +11849,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="422" ht="15" hidden="1" spans="1:6">
+    <row r="422" ht="15" spans="1:6">
       <c r="A422">
         <v>421</v>
       </c>
@@ -11858,7 +11867,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="423" ht="15" hidden="1" spans="1:6">
+    <row r="423" ht="15" spans="1:6">
       <c r="A423">
         <v>422</v>
       </c>
@@ -11876,7 +11885,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="424" ht="15" hidden="1" spans="1:6">
+    <row r="424" ht="15" spans="1:6">
       <c r="A424">
         <v>423</v>
       </c>
@@ -11894,7 +11903,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="425" ht="15" hidden="1" spans="1:6">
+    <row r="425" ht="15" spans="1:6">
       <c r="A425">
         <v>424</v>
       </c>
@@ -11912,7 +11921,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="426" ht="15" hidden="1" spans="1:6">
+    <row r="426" ht="15" spans="1:6">
       <c r="A426">
         <v>425</v>
       </c>
@@ -11930,7 +11939,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="427" ht="15" hidden="1" spans="1:6">
+    <row r="427" ht="15" spans="1:6">
       <c r="A427">
         <v>426</v>
       </c>
@@ -11948,7 +11957,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="428" ht="15" hidden="1" spans="1:6">
+    <row r="428" ht="15" spans="1:6">
       <c r="A428">
         <v>427</v>
       </c>
@@ -11966,7 +11975,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="429" ht="15" hidden="1" spans="1:6">
+    <row r="429" ht="15" spans="1:6">
       <c r="A429">
         <v>428</v>
       </c>
@@ -11984,7 +11993,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="430" ht="15" hidden="1" spans="1:6">
+    <row r="430" ht="15" spans="1:6">
       <c r="A430">
         <v>429</v>
       </c>
@@ -12002,7 +12011,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="431" ht="15" hidden="1" spans="1:6">
+    <row r="431" ht="15" spans="1:6">
       <c r="A431">
         <v>430</v>
       </c>
@@ -12020,7 +12029,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="432" ht="15" hidden="1" spans="1:6">
+    <row r="432" ht="15" spans="1:6">
       <c r="A432">
         <v>431</v>
       </c>
@@ -12038,7 +12047,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="433" ht="15" hidden="1" spans="1:6">
+    <row r="433" ht="15" spans="1:6">
       <c r="A433">
         <v>432</v>
       </c>
@@ -12056,7 +12065,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="434" ht="15" hidden="1" spans="1:6">
+    <row r="434" ht="15" spans="1:6">
       <c r="A434">
         <v>433</v>
       </c>
@@ -12074,7 +12083,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="435" ht="15" hidden="1" spans="1:6">
+    <row r="435" ht="15" spans="1:6">
       <c r="A435">
         <v>434</v>
       </c>
@@ -12092,7 +12101,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="436" ht="15" hidden="1" spans="1:6">
+    <row r="436" ht="15" spans="1:6">
       <c r="A436">
         <v>435</v>
       </c>
@@ -12110,7 +12119,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="437" ht="15" hidden="1" spans="1:6">
+    <row r="437" ht="15" spans="1:6">
       <c r="A437">
         <v>436</v>
       </c>
@@ -12128,7 +12137,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="438" ht="15" hidden="1" spans="1:6">
+    <row r="438" ht="15" spans="1:6">
       <c r="A438">
         <v>437</v>
       </c>
@@ -12146,7 +12155,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="439" ht="15" hidden="1" spans="1:6">
+    <row r="439" ht="15" spans="1:6">
       <c r="A439">
         <v>438</v>
       </c>
@@ -12164,7 +12173,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="440" ht="15" hidden="1" spans="1:6">
+    <row r="440" ht="15" spans="1:6">
       <c r="A440">
         <v>439</v>
       </c>
@@ -12182,7 +12191,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="441" ht="15" hidden="1" spans="1:6">
+    <row r="441" ht="15" spans="1:6">
       <c r="A441">
         <v>440</v>
       </c>
@@ -12200,7 +12209,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="442" ht="15" hidden="1" spans="1:6">
+    <row r="442" ht="15" spans="1:6">
       <c r="A442">
         <v>441</v>
       </c>
@@ -12218,7 +12227,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="443" ht="15" hidden="1" spans="1:6">
+    <row r="443" ht="15" spans="1:6">
       <c r="A443">
         <v>442</v>
       </c>
@@ -12236,7 +12245,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="444" ht="15" hidden="1" spans="1:6">
+    <row r="444" ht="15" spans="1:6">
       <c r="A444">
         <v>443</v>
       </c>
@@ -12254,7 +12263,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="445" ht="15" hidden="1" spans="1:6">
+    <row r="445" ht="15" spans="1:6">
       <c r="A445">
         <v>444</v>
       </c>
@@ -12272,7 +12281,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="446" ht="15" hidden="1" spans="1:6">
+    <row r="446" ht="15" spans="1:6">
       <c r="A446">
         <v>445</v>
       </c>
@@ -12290,7 +12299,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="447" ht="15" hidden="1" spans="1:6">
+    <row r="447" ht="15" spans="1:6">
       <c r="A447">
         <v>446</v>
       </c>
@@ -12308,7 +12317,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="448" ht="15" hidden="1" spans="1:6">
+    <row r="448" ht="15" spans="1:6">
       <c r="A448">
         <v>447</v>
       </c>
@@ -12326,7 +12335,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="449" ht="15" hidden="1" spans="1:6">
+    <row r="449" ht="15" spans="1:6">
       <c r="A449">
         <v>448</v>
       </c>
@@ -12344,7 +12353,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="450" ht="15" hidden="1" spans="1:6">
+    <row r="450" ht="15" spans="1:6">
       <c r="A450">
         <v>449</v>
       </c>
@@ -12362,7 +12371,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="451" ht="15" hidden="1" spans="1:6">
+    <row r="451" ht="15" spans="1:6">
       <c r="A451">
         <v>450</v>
       </c>
@@ -12400,7 +12409,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="453" hidden="1" spans="1:6">
+    <row r="453" spans="1:6">
       <c r="A453">
         <v>452</v>
       </c>
@@ -12417,7 +12426,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="454" hidden="1" spans="1:6">
+    <row r="454" spans="1:6">
       <c r="A454">
         <v>453</v>
       </c>
@@ -12437,7 +12446,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="455" ht="15" hidden="1" spans="1:6">
+    <row r="455" ht="15" spans="1:6">
       <c r="A455">
         <v>454</v>
       </c>
@@ -12455,7 +12464,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="456" ht="15" hidden="1" spans="1:6">
+    <row r="456" ht="15" spans="1:6">
       <c r="A456">
         <v>455</v>
       </c>
@@ -12490,7 +12499,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="458" ht="15" hidden="1" spans="1:6">
+    <row r="458" ht="15" spans="1:6">
       <c r="A458">
         <v>457</v>
       </c>
@@ -12508,7 +12517,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="459" ht="15" hidden="1" spans="1:6">
+    <row r="459" ht="15" spans="1:6">
       <c r="A459">
         <v>458</v>
       </c>
@@ -12526,7 +12535,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="460" ht="15" hidden="1" spans="1:6">
+    <row r="460" ht="15" spans="1:6">
       <c r="A460">
         <v>459</v>
       </c>
@@ -12543,7 +12552,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="461" ht="15" hidden="1" spans="1:6">
+    <row r="461" ht="15" spans="1:6">
       <c r="A461">
         <v>460</v>
       </c>
@@ -12560,7 +12569,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="462" ht="15" hidden="1" spans="1:6">
+    <row r="462" ht="15" spans="1:6">
       <c r="A462">
         <v>461</v>
       </c>
@@ -12577,7 +12586,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="463" ht="15" hidden="1" spans="1:6">
+    <row r="463" ht="15" spans="1:6">
       <c r="A463">
         <v>462</v>
       </c>
@@ -12594,7 +12603,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="464" ht="15" hidden="1" spans="1:6">
+    <row r="464" ht="15" spans="1:6">
       <c r="A464">
         <v>463</v>
       </c>
@@ -12611,7 +12620,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:6">
+    <row r="465" spans="1:6">
       <c r="A465">
         <v>464</v>
       </c>
@@ -12628,7 +12637,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:6">
+    <row r="466" spans="1:6">
       <c r="A466">
         <v>465</v>
       </c>
@@ -12645,7 +12654,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="467" ht="15" hidden="1" spans="1:6">
+    <row r="467" ht="15" spans="1:6">
       <c r="A467">
         <v>466</v>
       </c>
@@ -12663,7 +12672,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="468" ht="15" hidden="1" spans="1:6">
+    <row r="468" ht="15" spans="1:6">
       <c r="A468">
         <v>467</v>
       </c>
@@ -12681,7 +12690,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="469" ht="15" hidden="1" spans="1:6">
+    <row r="469" ht="15" spans="1:6">
       <c r="A469">
         <v>468</v>
       </c>
@@ -12698,7 +12707,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="470" ht="15" hidden="1" spans="1:6">
+    <row r="470" ht="15" spans="1:6">
       <c r="A470">
         <v>469</v>
       </c>
@@ -12715,7 +12724,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="471" ht="15" hidden="1" spans="1:6">
+    <row r="471" ht="15" spans="1:6">
       <c r="A471">
         <v>470</v>
       </c>
@@ -12732,7 +12741,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="472" ht="15" hidden="1" spans="1:6">
+    <row r="472" ht="15" spans="1:6">
       <c r="A472">
         <v>471</v>
       </c>
@@ -12749,7 +12758,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="473" ht="15" hidden="1" spans="1:6">
+    <row r="473" ht="15" spans="1:6">
       <c r="A473">
         <v>472</v>
       </c>
@@ -12766,7 +12775,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="474" ht="15" hidden="1" spans="1:6">
+    <row r="474" ht="15" spans="1:6">
       <c r="A474">
         <v>473</v>
       </c>
@@ -12783,7 +12792,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="475" ht="15" hidden="1" spans="1:6">
+    <row r="475" ht="15" spans="1:6">
       <c r="A475">
         <v>474</v>
       </c>
@@ -12800,7 +12809,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="476" ht="15" hidden="1" spans="1:6">
+    <row r="476" ht="15" spans="1:6">
       <c r="A476">
         <v>475</v>
       </c>
@@ -12817,7 +12826,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="477" ht="15" hidden="1" spans="1:6">
+    <row r="477" ht="15" spans="1:6">
       <c r="A477">
         <v>476</v>
       </c>
@@ -12834,7 +12843,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="478" ht="15" hidden="1" spans="1:6">
+    <row r="478" ht="15" spans="1:6">
       <c r="A478">
         <v>477</v>
       </c>
@@ -12851,7 +12860,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="479" ht="15" hidden="1" spans="1:6">
+    <row r="479" ht="15" spans="1:6">
       <c r="A479">
         <v>478</v>
       </c>
@@ -12868,7 +12877,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="480" ht="15" hidden="1" spans="1:6">
+    <row r="480" ht="15" spans="1:6">
       <c r="A480">
         <v>479</v>
       </c>
@@ -12885,7 +12894,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="481" ht="15" hidden="1" spans="1:6">
+    <row r="481" ht="15" spans="1:6">
       <c r="A481">
         <v>480</v>
       </c>
@@ -12902,7 +12911,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="482" ht="15" hidden="1" spans="1:6">
+    <row r="482" ht="15" spans="1:6">
       <c r="A482">
         <v>481</v>
       </c>
@@ -12919,13 +12928,25 @@
         <v>1064</v>
       </c>
     </row>
+    <row r="483" spans="1:6">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483" s="22" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D483" t="s">
+        <v>139</v>
+      </c>
+      <c r="E483" t="s">
+        <v>139</v>
+      </c>
+      <c r="F483" s="22" t="s">
+        <v>1066</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F482" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="剧集"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$483</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="1068">
   <si>
     <t>id</t>
   </si>
@@ -585,6 +585,9 @@
   </si>
   <si>
     <t>离婚吧！赶紧的</t>
+  </si>
+  <si>
+    <t>离婚吧！赶紧的,离婚吧赶紧的</t>
   </si>
   <si>
     <t>剧本杀</t>
@@ -5377,14 +5380,17 @@
       <c r="B61" s="3" t="s">
         <v>184</v>
       </c>
+      <c r="C61" t="s">
+        <v>185</v>
+      </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5392,16 +5398,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5409,16 +5415,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E63" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5426,16 +5432,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5443,16 +5449,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5460,16 +5466,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5477,16 +5483,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5494,16 +5500,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5511,16 +5517,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E69" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5528,16 +5534,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -5545,16 +5551,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5562,16 +5568,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -5579,16 +5585,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5596,16 +5602,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5613,16 +5619,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5630,16 +5636,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5647,16 +5653,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5664,16 +5670,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5681,16 +5687,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E79" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5698,16 +5704,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D80" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5715,16 +5721,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D81" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E81" t="s">
         <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5732,16 +5738,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5749,16 +5755,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D83" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E83" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5766,16 +5772,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D84" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E84" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5783,16 +5789,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E85" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5800,16 +5806,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D86" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E86" t="s">
         <v>14</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5817,16 +5823,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5834,16 +5840,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5851,16 +5857,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D89" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E89" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5868,16 +5874,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5885,16 +5891,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E91" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5902,19 +5908,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5922,16 +5928,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5939,16 +5945,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5956,16 +5962,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D95" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E95" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" ht="15" spans="1:6">
@@ -5973,17 +5979,17 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E96" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" ht="15" spans="1:6">
@@ -5991,17 +5997,17 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" ht="15" spans="1:6">
@@ -6009,19 +6015,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" ht="15" spans="1:6">
@@ -6029,19 +6035,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" ht="15" spans="1:6">
@@ -6049,17 +6055,17 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" ht="15" spans="1:6">
@@ -6067,17 +6073,17 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" ht="15" spans="1:6">
@@ -6085,17 +6091,17 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" ht="15" spans="1:6">
@@ -6103,17 +6109,17 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="104" ht="15" spans="1:6">
@@ -6121,17 +6127,17 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E104" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" ht="15" spans="1:6">
@@ -6139,17 +6145,17 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="106" ht="15" spans="1:6">
@@ -6157,17 +6163,17 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="107" ht="15" spans="1:6">
@@ -6175,17 +6181,17 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" ht="15" spans="1:6">
@@ -6193,17 +6199,17 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="109" ht="15" spans="1:6">
@@ -6211,17 +6217,17 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E109" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110" ht="15" spans="1:6">
@@ -6229,17 +6235,17 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E110" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="111" ht="15" spans="1:6">
@@ -6247,17 +6253,17 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="112" ht="15" spans="1:6">
@@ -6265,17 +6271,17 @@
         <v>111</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E112" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="113" ht="15" spans="1:6">
@@ -6283,17 +6289,17 @@
         <v>112</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E113" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114" ht="15" spans="1:6">
@@ -6301,17 +6307,17 @@
         <v>113</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="115" ht="15" spans="1:6">
@@ -6319,17 +6325,17 @@
         <v>114</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E115" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="116" ht="15" spans="1:6">
@@ -6337,17 +6343,17 @@
         <v>115</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E116" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" ht="15" spans="1:6">
@@ -6355,17 +6361,17 @@
         <v>116</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E117" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="118" ht="15" spans="1:6">
@@ -6373,17 +6379,17 @@
         <v>117</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E118" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="119" ht="15" spans="1:6">
@@ -6391,17 +6397,17 @@
         <v>118</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E119" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="120" ht="15" spans="1:6">
@@ -6409,17 +6415,17 @@
         <v>119</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C120" s="8"/>
       <c r="D120" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E120" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="121" ht="15" spans="1:6">
@@ -6427,17 +6433,17 @@
         <v>120</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E121" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="122" ht="15" spans="1:6">
@@ -6445,17 +6451,17 @@
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E122" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="123" ht="15" spans="1:6">
@@ -6463,17 +6469,17 @@
         <v>122</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E123" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="124" ht="15" spans="1:6">
@@ -6481,17 +6487,17 @@
         <v>123</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C124" s="8"/>
       <c r="D124" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E124" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="125" ht="15" spans="1:6">
@@ -6499,17 +6505,17 @@
         <v>124</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E125" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" ht="15" spans="1:6">
@@ -6517,17 +6523,17 @@
         <v>125</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C126" s="8"/>
       <c r="D126" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E126" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="127" ht="15" spans="1:6">
@@ -6535,17 +6541,17 @@
         <v>126</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E127" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="128" ht="15" spans="1:6">
@@ -6553,17 +6559,17 @@
         <v>127</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E128" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="129" ht="15" spans="1:6">
@@ -6571,17 +6577,17 @@
         <v>128</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E129" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="130" ht="15" spans="1:6">
@@ -6589,17 +6595,17 @@
         <v>129</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="131" ht="15" spans="1:6">
@@ -6607,17 +6613,17 @@
         <v>130</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="132" ht="15" spans="1:6">
@@ -6625,17 +6631,17 @@
         <v>131</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E132" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="133" ht="15" spans="1:6">
@@ -6643,17 +6649,17 @@
         <v>132</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" ht="15" spans="1:6">
@@ -6661,17 +6667,17 @@
         <v>133</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" ht="15" spans="1:6">
@@ -6679,17 +6685,17 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E135" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="136" ht="15" spans="1:6">
@@ -6697,17 +6703,17 @@
         <v>135</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E136" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" ht="15" spans="1:6">
@@ -6715,17 +6721,17 @@
         <v>136</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C137" s="8"/>
       <c r="D137" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="138" ht="15" spans="1:6">
@@ -6733,17 +6739,17 @@
         <v>137</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="139" ht="15" spans="1:6">
@@ -6751,17 +6757,17 @@
         <v>138</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C139" s="8"/>
       <c r="D139" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="140" ht="15" spans="1:6">
@@ -6769,17 +6775,17 @@
         <v>139</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="141" ht="15" spans="1:6">
@@ -6787,17 +6793,17 @@
         <v>140</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="142" ht="15" spans="1:6">
@@ -6805,17 +6811,17 @@
         <v>141</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="143" ht="15" spans="1:6">
@@ -6823,17 +6829,17 @@
         <v>142</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C143" s="8"/>
       <c r="D143" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="144" ht="15" spans="1:6">
@@ -6841,17 +6847,17 @@
         <v>143</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="145" ht="15" spans="1:6">
@@ -6859,17 +6865,17 @@
         <v>144</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C145" s="8"/>
       <c r="D145" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E145" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="146" ht="15" spans="1:6">
@@ -6877,17 +6883,17 @@
         <v>145</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E146" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="147" ht="15" spans="1:6">
@@ -6895,17 +6901,17 @@
         <v>146</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C147" s="8"/>
       <c r="D147" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="148" ht="15" spans="1:6">
@@ -6913,17 +6919,17 @@
         <v>147</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="149" ht="15" spans="1:6">
@@ -6931,17 +6937,17 @@
         <v>148</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="150" ht="15" spans="1:6">
@@ -6949,17 +6955,17 @@
         <v>149</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="151" ht="15" spans="1:6">
@@ -6967,17 +6973,17 @@
         <v>150</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="152" ht="15" spans="1:6">
@@ -6985,17 +6991,17 @@
         <v>151</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="153" ht="15" spans="1:6">
@@ -7003,17 +7009,17 @@
         <v>152</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E153" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" ht="15" spans="1:6">
@@ -7021,17 +7027,17 @@
         <v>153</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E154" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="155" ht="15" spans="1:6">
@@ -7039,17 +7045,17 @@
         <v>154</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C155" s="8"/>
       <c r="D155" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E155" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="156" ht="15" spans="1:6">
@@ -7057,17 +7063,17 @@
         <v>155</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" ht="15" spans="1:6">
@@ -7075,17 +7081,17 @@
         <v>156</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E157" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" ht="15" spans="1:6">
@@ -7093,17 +7099,17 @@
         <v>157</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C158" s="8"/>
       <c r="D158" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E158" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="159" ht="15" spans="1:6">
@@ -7111,17 +7117,17 @@
         <v>158</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E159" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" ht="15" spans="1:6">
@@ -7129,17 +7135,17 @@
         <v>159</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E160" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" ht="15" spans="1:6">
@@ -7147,17 +7153,17 @@
         <v>160</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E161" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" ht="15" spans="1:6">
@@ -7165,17 +7171,17 @@
         <v>161</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C162" s="8"/>
       <c r="D162" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E162" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" ht="15" spans="1:6">
@@ -7183,17 +7189,17 @@
         <v>162</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C163" s="8"/>
       <c r="D163" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E163" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" ht="15" spans="1:6">
@@ -7201,17 +7207,17 @@
         <v>163</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E164" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" ht="15" spans="1:6">
@@ -7219,17 +7225,17 @@
         <v>164</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" ht="15" spans="1:6">
@@ -7237,17 +7243,17 @@
         <v>165</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C166" s="8"/>
       <c r="D166" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E166" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" ht="15" spans="1:6">
@@ -7255,17 +7261,17 @@
         <v>166</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C167" s="8"/>
       <c r="D167" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" ht="15" spans="1:6">
@@ -7273,17 +7279,17 @@
         <v>167</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C168" s="8"/>
       <c r="D168" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E168" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" ht="15" spans="1:6">
@@ -7291,17 +7297,17 @@
         <v>168</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C169" s="8"/>
       <c r="D169" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" ht="15" spans="1:6">
@@ -7309,17 +7315,17 @@
         <v>169</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C170" s="8"/>
       <c r="D170" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E170" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="171" ht="15" spans="1:6">
@@ -7327,17 +7333,17 @@
         <v>170</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E171" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" ht="15" spans="1:6">
@@ -7345,17 +7351,17 @@
         <v>171</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="173" ht="15" spans="1:6">
@@ -7363,17 +7369,17 @@
         <v>172</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C173" s="8"/>
       <c r="D173" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E173" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="174" ht="15" spans="1:6">
@@ -7381,17 +7387,17 @@
         <v>173</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C174" s="8"/>
       <c r="D174" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E174" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="175" ht="15" spans="1:6">
@@ -7399,17 +7405,17 @@
         <v>174</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C175" s="8"/>
       <c r="D175" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E175" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="176" ht="15" spans="1:6">
@@ -7417,17 +7423,17 @@
         <v>175</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C176" s="8"/>
       <c r="D176" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="177" ht="15" spans="1:6">
@@ -7435,17 +7441,17 @@
         <v>176</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C177" s="8"/>
       <c r="D177" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E177" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="178" ht="15" spans="1:6">
@@ -7453,17 +7459,17 @@
         <v>177</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E178" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" ht="15" spans="1:6">
@@ -7471,17 +7477,17 @@
         <v>178</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E179" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" ht="15" spans="1:6">
@@ -7489,17 +7495,17 @@
         <v>179</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E180" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" ht="15" spans="1:6">
@@ -7507,17 +7513,17 @@
         <v>180</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C181" s="8"/>
       <c r="D181" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" ht="15" spans="1:6">
@@ -7525,17 +7531,17 @@
         <v>181</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C182" s="8"/>
       <c r="D182" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" ht="15" spans="1:6">
@@ -7543,17 +7549,17 @@
         <v>182</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C183" s="8"/>
       <c r="D183" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" ht="15" spans="1:6">
@@ -7561,17 +7567,17 @@
         <v>183</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C184" s="8"/>
       <c r="D184" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" ht="15" spans="1:6">
@@ -7579,17 +7585,17 @@
         <v>184</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C185" s="8"/>
       <c r="D185" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F185" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" ht="15" spans="1:6">
@@ -7597,17 +7603,17 @@
         <v>185</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" ht="15" spans="1:6">
@@ -7615,17 +7621,17 @@
         <v>186</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C187" s="8"/>
       <c r="D187" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E187" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" ht="15" spans="1:6">
@@ -7633,17 +7639,17 @@
         <v>187</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C188" s="8"/>
       <c r="D188" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E188" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="189" ht="15" spans="1:6">
@@ -7651,17 +7657,17 @@
         <v>188</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C189" s="8"/>
       <c r="D189" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F189" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="190" ht="15.5" spans="1:6">
@@ -7669,17 +7675,17 @@
         <v>189</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C190" s="11"/>
       <c r="D190" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E190" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="191" ht="15.5" spans="1:6">
@@ -7687,17 +7693,17 @@
         <v>190</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C191" s="11"/>
       <c r="D191" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="192" ht="15.5" spans="1:6">
@@ -7705,17 +7711,17 @@
         <v>191</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C192" s="11"/>
       <c r="D192" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E192" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="193" ht="15.5" spans="1:6">
@@ -7723,17 +7729,17 @@
         <v>192</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C193" s="11"/>
       <c r="D193" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="194" ht="15.5" spans="1:6">
@@ -7741,17 +7747,17 @@
         <v>193</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C194" s="11"/>
       <c r="D194" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" ht="15.5" spans="1:6">
@@ -7759,17 +7765,17 @@
         <v>194</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C195" s="11"/>
       <c r="D195" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E195" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="196" ht="15.5" spans="1:6">
@@ -7777,17 +7783,17 @@
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C196" s="11"/>
       <c r="D196" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="197" ht="15.5" spans="1:6">
@@ -7795,17 +7801,17 @@
         <v>196</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C197" s="11"/>
       <c r="D197" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="198" ht="15.5" spans="1:6">
@@ -7813,17 +7819,17 @@
         <v>197</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C198" s="11"/>
       <c r="D198" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E198" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="199" ht="15.5" spans="1:6">
@@ -7831,17 +7837,17 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C199" s="11"/>
       <c r="D199" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E199" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="200" ht="15.5" spans="1:6">
@@ -7849,19 +7855,19 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E200" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="201" ht="15.5" spans="1:6">
@@ -7869,17 +7875,17 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C201" s="11"/>
       <c r="D201" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="202" ht="15.5" spans="1:6">
@@ -7887,17 +7893,17 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C202" s="11"/>
       <c r="D202" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E202" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="203" ht="15.5" spans="1:6">
@@ -7905,17 +7911,17 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C203" s="11"/>
       <c r="D203" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E203" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204" ht="15.5" spans="1:6">
@@ -7923,17 +7929,17 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E204" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F204" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="205" ht="15.5" spans="1:6">
@@ -7941,17 +7947,17 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E205" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" ht="15.5" spans="1:6">
@@ -7959,17 +7965,17 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C206" s="11"/>
       <c r="D206" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E206" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="207" ht="15.5" spans="1:6">
@@ -7977,17 +7983,17 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C207" s="11"/>
       <c r="D207" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E207" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="208" ht="15.5" spans="1:6">
@@ -7995,17 +8001,17 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C208" s="11"/>
       <c r="D208" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E208" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="209" ht="15.5" spans="1:6">
@@ -8013,19 +8019,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E209" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="210" ht="15.5" spans="1:6">
@@ -8033,17 +8039,17 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C210" s="11"/>
       <c r="D210" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E210" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="211" ht="15.5" spans="1:6">
@@ -8051,17 +8057,17 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C211" s="11"/>
       <c r="D211" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E211" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="212" ht="15.5" spans="1:6">
@@ -8069,17 +8075,17 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C212" s="11"/>
       <c r="D212" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E212" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="213" ht="15.5" spans="1:6">
@@ -8087,17 +8093,17 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C213" s="11"/>
       <c r="D213" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E213" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F213" s="12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" ht="15.5" spans="1:6">
@@ -8105,17 +8111,17 @@
         <v>213</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C214" s="11"/>
       <c r="D214" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E214" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F214" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" ht="15.5" spans="1:6">
@@ -8123,17 +8129,17 @@
         <v>214</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C215" s="11"/>
       <c r="D215" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E215" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F215" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" ht="15.5" spans="1:6">
@@ -8141,17 +8147,17 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C216" s="11"/>
       <c r="D216" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F216" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="217" ht="15.5" spans="1:6">
@@ -8159,17 +8165,17 @@
         <v>216</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C217" s="11"/>
       <c r="D217" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F217" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" ht="15.5" spans="1:6">
@@ -8177,17 +8183,17 @@
         <v>217</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C218" s="11"/>
       <c r="D218" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E218" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" ht="15.5" spans="1:6">
@@ -8195,17 +8201,17 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C219" s="11"/>
       <c r="D219" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E219" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F219" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="220" ht="15.5" spans="1:6">
@@ -8213,17 +8219,17 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C220" s="11"/>
       <c r="D220" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E220" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F220" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="221" ht="15.5" spans="1:6">
@@ -8231,17 +8237,17 @@
         <v>220</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C221" s="11"/>
       <c r="D221" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E221" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="222" ht="15.5" spans="1:6">
@@ -8249,17 +8255,17 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C222" s="11"/>
       <c r="D222" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="223" ht="15.5" spans="1:6">
@@ -8267,17 +8273,17 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C223" s="11"/>
       <c r="D223" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="224" ht="15.5" spans="1:6">
@@ -8285,17 +8291,17 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C224" s="11"/>
       <c r="D224" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E224" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="225" ht="15.5" spans="1:6">
@@ -8303,17 +8309,17 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C225" s="11"/>
       <c r="D225" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="226" ht="15.5" spans="1:6">
@@ -8321,17 +8327,17 @@
         <v>225</v>
       </c>
       <c r="B226" s="16" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C226" s="11"/>
       <c r="D226" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F226" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="227" ht="15.5" spans="1:6">
@@ -8339,17 +8345,17 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C227" s="11"/>
       <c r="D227" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="228" ht="15.5" spans="1:6">
@@ -8357,17 +8363,17 @@
         <v>227</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C228" s="11"/>
       <c r="D228" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F228" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="229" ht="15.5" spans="1:6">
@@ -8375,17 +8381,17 @@
         <v>228</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C229" s="11"/>
       <c r="D229" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E229" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F229" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="230" ht="15.5" spans="1:6">
@@ -8393,17 +8399,17 @@
         <v>229</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C230" s="11"/>
       <c r="D230" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E230" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F230" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="231" ht="15.5" spans="1:6">
@@ -8411,17 +8417,17 @@
         <v>230</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C231" s="11"/>
       <c r="D231" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E231" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="232" ht="15.5" spans="1:6">
@@ -8429,17 +8435,17 @@
         <v>231</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C232" s="11"/>
       <c r="D232" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F232" s="13" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="233" ht="15.5" spans="1:6">
@@ -8447,19 +8453,19 @@
         <v>232</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C233" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E233" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F233" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="234" ht="15.5" spans="1:6">
@@ -8467,17 +8473,17 @@
         <v>233</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C234" s="11"/>
       <c r="D234" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E234" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F234" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="235" ht="15.5" spans="1:6">
@@ -8485,17 +8491,17 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C235" s="11"/>
       <c r="D235" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E235" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" ht="15.5" spans="1:6">
@@ -8503,17 +8509,17 @@
         <v>235</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C236" s="11"/>
       <c r="D236" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E236" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F236" s="13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="237" ht="15.5" spans="1:6">
@@ -8521,17 +8527,17 @@
         <v>236</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C237" s="11"/>
       <c r="D237" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="238" ht="15.5" spans="1:6">
@@ -8539,17 +8545,17 @@
         <v>237</v>
       </c>
       <c r="B238" s="14" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C238" s="11"/>
       <c r="D238" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E238" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F238" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="239" ht="15.5" spans="1:6">
@@ -8557,17 +8563,17 @@
         <v>238</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C239" s="11"/>
       <c r="D239" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E239" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F239" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="240" ht="15.5" spans="1:6">
@@ -8575,17 +8581,17 @@
         <v>239</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C240" s="11"/>
       <c r="D240" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E240" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F240" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="241" ht="15.5" spans="1:6">
@@ -8593,17 +8599,17 @@
         <v>240</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C241" s="11"/>
       <c r="D241" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E241" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F241" s="14" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="242" ht="15.5" spans="1:6">
@@ -8611,17 +8617,17 @@
         <v>241</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C242" s="11"/>
       <c r="D242" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E242" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F242" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -8629,16 +8635,16 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D243" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E243" t="s">
         <v>14</v>
       </c>
       <c r="F243" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -8646,16 +8652,16 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D244" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E244" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F244" s="14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="245" ht="15.5" spans="1:6">
@@ -8663,17 +8669,17 @@
         <v>244</v>
       </c>
       <c r="B245" s="14" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C245" s="11"/>
       <c r="D245" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E245" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F245" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="246" ht="15.5" spans="1:6">
@@ -8681,17 +8687,17 @@
         <v>245</v>
       </c>
       <c r="B246" s="14" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C246" s="11"/>
       <c r="D246" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E246" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F246" s="13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="247" ht="15.5" spans="1:6">
@@ -8699,17 +8705,17 @@
         <v>246</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C247" s="11"/>
       <c r="D247" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E247" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F247" s="13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="248" ht="15.5" spans="1:6">
@@ -8717,17 +8723,17 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C248" s="11"/>
       <c r="D248" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E248" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F248" s="13" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="249" ht="15.5" spans="1:6">
@@ -8735,17 +8741,17 @@
         <v>248</v>
       </c>
       <c r="B249" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C249" s="11"/>
       <c r="D249" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E249" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F249" s="13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="250" ht="15.5" spans="1:6">
@@ -8753,17 +8759,17 @@
         <v>249</v>
       </c>
       <c r="B250" s="20" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C250" s="11"/>
       <c r="D250" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E250" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="251" ht="15.5" spans="1:6">
@@ -8771,17 +8777,17 @@
         <v>250</v>
       </c>
       <c r="B251" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C251" s="11"/>
       <c r="D251" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E251" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F251" s="13" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="252" ht="15.5" spans="1:6">
@@ -8789,17 +8795,17 @@
         <v>251</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C252" s="11"/>
       <c r="D252" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E252" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F252" s="14" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="253" ht="15.5" spans="1:6">
@@ -8807,17 +8813,17 @@
         <v>252</v>
       </c>
       <c r="B253" s="14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C253" s="11"/>
       <c r="D253" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E253" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F253" s="13" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="254" ht="15.5" spans="1:6">
@@ -8825,17 +8831,17 @@
         <v>253</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C254" s="11"/>
       <c r="D254" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E254" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F254" s="13" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="255" ht="15.5" spans="1:6">
@@ -8843,19 +8849,19 @@
         <v>254</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D255" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E255" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="256" ht="15.5" spans="1:6">
@@ -8863,17 +8869,17 @@
         <v>255</v>
       </c>
       <c r="B256" s="21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C256" s="11"/>
       <c r="D256" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F256" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="257" ht="15.5" spans="1:6">
@@ -8881,17 +8887,17 @@
         <v>256</v>
       </c>
       <c r="B257" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C257" s="11"/>
       <c r="D257" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="258" ht="15.5" spans="1:6">
@@ -8899,17 +8905,17 @@
         <v>257</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C258" s="11"/>
       <c r="D258" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="259" ht="15.5" spans="1:6">
@@ -8917,17 +8923,17 @@
         <v>258</v>
       </c>
       <c r="B259" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C259" s="11"/>
       <c r="D259" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F259" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="260" ht="15.5" spans="1:6">
@@ -8935,17 +8941,17 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C260" s="11"/>
       <c r="D260" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F260" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="261" ht="15.5" spans="1:6">
@@ -8953,17 +8959,17 @@
         <v>260</v>
       </c>
       <c r="B261" s="21" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C261" s="11"/>
       <c r="D261" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F261" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="262" ht="15.5" spans="1:6">
@@ -8971,17 +8977,17 @@
         <v>261</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C262" s="11"/>
       <c r="D262" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F262" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="263" ht="15.5" spans="1:6">
@@ -8989,17 +8995,17 @@
         <v>262</v>
       </c>
       <c r="B263" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C263" s="11"/>
       <c r="D263" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E263" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F263" s="13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="264" ht="15.5" spans="1:6">
@@ -9007,17 +9013,17 @@
         <v>263</v>
       </c>
       <c r="B264" s="14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C264" s="11"/>
       <c r="D264" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E264" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F264" s="14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="265" ht="15.5" spans="1:6">
@@ -9025,17 +9031,17 @@
         <v>264</v>
       </c>
       <c r="B265" s="14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C265" s="11"/>
       <c r="D265" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F265" s="14" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="266" ht="15.5" spans="1:6">
@@ -9043,17 +9049,17 @@
         <v>265</v>
       </c>
       <c r="B266" s="18" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C266" s="11"/>
       <c r="D266" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F266" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="267" ht="15.5" spans="1:6">
@@ -9061,19 +9067,19 @@
         <v>266</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E267" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F267" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="268" ht="15.5" spans="1:6">
@@ -9081,17 +9087,17 @@
         <v>267</v>
       </c>
       <c r="B268" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C268" s="11"/>
       <c r="D268" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F268" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="269" ht="15.5" spans="1:6">
@@ -9099,17 +9105,17 @@
         <v>268</v>
       </c>
       <c r="B269" s="14" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C269" s="11"/>
       <c r="D269" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E269" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F269" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="270" ht="15.5" spans="1:6">
@@ -9117,17 +9123,17 @@
         <v>269</v>
       </c>
       <c r="B270" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C270" s="11"/>
       <c r="D270" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E270" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F270" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="271" ht="15.5" spans="1:6">
@@ -9135,17 +9141,17 @@
         <v>270</v>
       </c>
       <c r="B271" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C271" s="11"/>
       <c r="D271" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E271" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F271" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="272" ht="15.5" spans="1:6">
@@ -9153,19 +9159,19 @@
         <v>271</v>
       </c>
       <c r="B272" s="18" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F272" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="273" ht="15.5" spans="1:6">
@@ -9173,17 +9179,17 @@
         <v>272</v>
       </c>
       <c r="B273" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C273" s="11"/>
       <c r="D273" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E273" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F273" s="14" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="274" ht="15.5" spans="1:6">
@@ -9191,17 +9197,17 @@
         <v>273</v>
       </c>
       <c r="B274" s="14" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C274" s="11"/>
       <c r="D274" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F274" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="275" ht="15.5" spans="1:6">
@@ -9209,17 +9215,17 @@
         <v>274</v>
       </c>
       <c r="B275" s="14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C275" s="11"/>
       <c r="D275" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E275" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F275" s="14" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" ht="15.5" spans="1:6">
@@ -9227,17 +9233,17 @@
         <v>275</v>
       </c>
       <c r="B276" s="14" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C276" s="11"/>
       <c r="D276" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F276" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="277" ht="15.5" spans="1:6">
@@ -9245,17 +9251,17 @@
         <v>276</v>
       </c>
       <c r="B277" s="14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C277" s="11"/>
       <c r="D277" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E277" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F277" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="278" ht="15.5" spans="1:6">
@@ -9263,17 +9269,17 @@
         <v>277</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C278" s="11"/>
       <c r="D278" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F278" s="14" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="279" ht="15.5" spans="1:6">
@@ -9281,17 +9287,17 @@
         <v>278</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C279" s="11"/>
       <c r="D279" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E279" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F279" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="280" ht="15.5" spans="1:6">
@@ -9299,17 +9305,17 @@
         <v>279</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C280" s="11"/>
       <c r="D280" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F280" s="14" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="281" ht="15.5" spans="1:6">
@@ -9317,17 +9323,17 @@
         <v>280</v>
       </c>
       <c r="B281" s="14" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C281" s="11"/>
       <c r="D281" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E281" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F281" s="14" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="282" ht="15.5" spans="1:6">
@@ -9335,17 +9341,17 @@
         <v>281</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C282" s="11"/>
       <c r="D282" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E282" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F282" s="14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="283" ht="15.5" spans="1:6">
@@ -9353,17 +9359,17 @@
         <v>282</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C283" s="11"/>
       <c r="D283" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E283" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F283" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="284" ht="15.5" spans="1:6">
@@ -9371,17 +9377,17 @@
         <v>283</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C284" s="11"/>
       <c r="D284" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F284" s="14" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="285" ht="15.5" spans="1:6">
@@ -9389,17 +9395,17 @@
         <v>284</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C285" s="11"/>
       <c r="D285" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E285" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F285" s="14" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="286" ht="15.5" spans="1:6">
@@ -9407,17 +9413,17 @@
         <v>285</v>
       </c>
       <c r="B286" s="18" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C286" s="11"/>
       <c r="D286" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F286" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="287" ht="15.5" spans="1:6">
@@ -9425,17 +9431,17 @@
         <v>286</v>
       </c>
       <c r="B287" s="14" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C287" s="11"/>
       <c r="D287" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E287" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F287" s="14" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="288" ht="15.5" spans="1:6">
@@ -9443,17 +9449,17 @@
         <v>287</v>
       </c>
       <c r="B288" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C288" s="11"/>
       <c r="D288" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F288" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="289" ht="15.5" spans="1:6">
@@ -9461,17 +9467,17 @@
         <v>288</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C289" s="8"/>
       <c r="D289" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E289" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="290" ht="15.5" spans="1:6">
@@ -9479,17 +9485,17 @@
         <v>289</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C290" s="8"/>
       <c r="D290" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F290" s="8" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="291" ht="15.5" spans="1:6">
@@ -9497,19 +9503,19 @@
         <v>290</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E291" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F291" s="8" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="292" ht="15.5" spans="1:6">
@@ -9517,17 +9523,17 @@
         <v>291</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C292" s="8"/>
       <c r="D292" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E292" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F292" s="8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="293" ht="15.5" spans="1:6">
@@ -9535,16 +9541,16 @@
         <v>292</v>
       </c>
       <c r="B293" s="14" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E293" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F293" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="294" ht="15.5" spans="1:6">
@@ -9552,16 +9558,16 @@
         <v>293</v>
       </c>
       <c r="B294" s="14" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F294" s="14" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="295" ht="15.5" spans="1:6">
@@ -9569,16 +9575,16 @@
         <v>294</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E295" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F295" s="14" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="296" ht="15.5" spans="1:6">
@@ -9586,16 +9592,16 @@
         <v>295</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F296" s="13" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="297" ht="15.5" spans="1:6">
@@ -9603,17 +9609,17 @@
         <v>296</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C297" s="8"/>
       <c r="D297" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E297" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F297" s="8" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="298" ht="15.5" spans="1:6">
@@ -9621,17 +9627,17 @@
         <v>297</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E298" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="299" ht="15.5" spans="1:6">
@@ -9639,17 +9645,17 @@
         <v>298</v>
       </c>
       <c r="B299" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C299" s="8"/>
       <c r="D299" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E299" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F299" s="8" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="300" ht="15.5" spans="1:6">
@@ -9657,17 +9663,17 @@
         <v>299</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C300" s="8"/>
       <c r="D300" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F300" s="8" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="301" ht="15.5" spans="1:6">
@@ -9675,17 +9681,17 @@
         <v>300</v>
       </c>
       <c r="B301" s="8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C301" s="8"/>
       <c r="D301" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E301" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F301" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="302" ht="15.5" spans="1:6">
@@ -9693,17 +9699,17 @@
         <v>301</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C302" s="8"/>
       <c r="D302" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E302" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F302" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="303" ht="15.5" spans="1:6">
@@ -9711,19 +9717,19 @@
         <v>302</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E303" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F303" s="8" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="304" ht="15.5" spans="1:6">
@@ -9731,17 +9737,17 @@
         <v>303</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C304" s="8"/>
       <c r="D304" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E304" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F304" s="8" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="305" ht="15.5" spans="1:6">
@@ -9749,17 +9755,17 @@
         <v>304</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C305" s="8"/>
       <c r="D305" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E305" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F305" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="306" ht="15.5" spans="1:6">
@@ -9767,17 +9773,17 @@
         <v>305</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C306" s="8"/>
       <c r="D306" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E306" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F306" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="307" ht="15.5" spans="1:6">
@@ -9785,17 +9791,17 @@
         <v>306</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C307" s="8"/>
       <c r="D307" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E307" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F307" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="308" ht="15.5" spans="1:6">
@@ -9803,17 +9809,17 @@
         <v>307</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C308" s="8"/>
       <c r="D308" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E308" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F308" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="309" ht="15.5" spans="1:6">
@@ -9821,17 +9827,17 @@
         <v>308</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C309" s="8"/>
       <c r="D309" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E309" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F309" s="8" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="310" ht="15.5" spans="1:6">
@@ -9839,17 +9845,17 @@
         <v>309</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C310" s="8"/>
       <c r="D310" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E310" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F310" s="8" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="311" ht="15.5" spans="1:6">
@@ -9857,17 +9863,17 @@
         <v>310</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C311" s="8"/>
       <c r="D311" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E311" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F311" s="8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="312" ht="15.5" spans="1:6">
@@ -9875,17 +9881,17 @@
         <v>311</v>
       </c>
       <c r="B312" s="8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C312" s="8"/>
       <c r="D312" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E312" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F312" s="8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="313" ht="15.5" spans="1:6">
@@ -9893,16 +9899,16 @@
         <v>312</v>
       </c>
       <c r="B313" s="14" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D313" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E313" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F313" s="14" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="314" ht="15.5" spans="1:6">
@@ -9910,16 +9916,16 @@
         <v>313</v>
       </c>
       <c r="B314" s="18" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D314" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E314" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F314" s="13" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="315" ht="15.5" spans="1:6">
@@ -9927,16 +9933,16 @@
         <v>314</v>
       </c>
       <c r="B315" s="18" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E315" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F315" s="14" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="316" ht="15.5" spans="1:6">
@@ -9944,16 +9950,16 @@
         <v>315</v>
       </c>
       <c r="B316" s="18" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D316" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E316" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F316" s="14" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="317" ht="15" spans="1:6">
@@ -9961,17 +9967,17 @@
         <v>316</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E317" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F317" s="8" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="318" ht="15" spans="1:6">
@@ -9979,17 +9985,17 @@
         <v>317</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E318" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="319" ht="15" spans="1:6">
@@ -9997,17 +10003,17 @@
         <v>318</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E319" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F319" s="8" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="320" ht="15" spans="1:6">
@@ -10015,17 +10021,17 @@
         <v>319</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C320" s="8"/>
       <c r="D320" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E320" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F320" s="8" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="321" ht="15" spans="1:6">
@@ -10033,17 +10039,17 @@
         <v>320</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E321" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F321" s="8" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="322" ht="15" spans="1:6">
@@ -10051,17 +10057,17 @@
         <v>321</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C322" s="8"/>
       <c r="D322" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E322" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F322" s="8" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="323" ht="15" spans="1:6">
@@ -10069,17 +10075,17 @@
         <v>322</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E323" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F323" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="324" ht="15" spans="1:6">
@@ -10087,17 +10093,17 @@
         <v>323</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C324" s="8"/>
       <c r="D324" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E324" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F324" s="8" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="325" ht="15" spans="1:6">
@@ -10105,17 +10111,17 @@
         <v>324</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C325" s="8"/>
       <c r="D325" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E325" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F325" s="8" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="326" ht="15" spans="1:6">
@@ -10123,17 +10129,17 @@
         <v>325</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C326" s="8"/>
       <c r="D326" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E326" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F326" s="8" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="327" ht="15" spans="1:6">
@@ -10141,17 +10147,17 @@
         <v>326</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C327" s="8"/>
       <c r="D327" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E327" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F327" s="8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="328" ht="15" spans="1:6">
@@ -10159,17 +10165,17 @@
         <v>327</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C328" s="8"/>
       <c r="D328" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E328" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F328" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="329" ht="15" spans="1:6">
@@ -10177,17 +10183,17 @@
         <v>328</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C329" s="8"/>
       <c r="D329" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E329" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F329" s="8" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="330" ht="15" spans="1:6">
@@ -10195,17 +10201,17 @@
         <v>329</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C330" s="8"/>
       <c r="D330" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E330" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F330" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="331" ht="15" spans="1:6">
@@ -10213,17 +10219,17 @@
         <v>330</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C331" s="8"/>
       <c r="D331" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E331" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F331" s="8" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="332" ht="15" spans="1:6">
@@ -10231,17 +10237,17 @@
         <v>331</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C332" s="8"/>
       <c r="D332" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E332" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F332" s="8" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="333" ht="15" spans="1:6">
@@ -10249,17 +10255,17 @@
         <v>332</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C333" s="8"/>
       <c r="D333" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E333" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F333" s="8" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="334" ht="15" spans="1:6">
@@ -10267,17 +10273,17 @@
         <v>333</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C334" s="8"/>
       <c r="D334" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E334" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F334" s="8" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="335" ht="15" spans="1:6">
@@ -10285,17 +10291,17 @@
         <v>334</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C335" s="8"/>
       <c r="D335" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E335" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F335" s="8" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="336" ht="15" spans="1:6">
@@ -10303,17 +10309,17 @@
         <v>335</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C336" s="8"/>
       <c r="D336" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E336" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F336" s="8" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="337" ht="15" spans="1:6">
@@ -10321,17 +10327,17 @@
         <v>336</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C337" s="8"/>
       <c r="D337" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E337" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F337" s="8" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="338" ht="15" spans="1:6">
@@ -10339,17 +10345,17 @@
         <v>337</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C338" s="8"/>
       <c r="D338" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E338" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F338" s="8" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="339" ht="15" spans="1:6">
@@ -10357,17 +10363,17 @@
         <v>338</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C339" s="8"/>
       <c r="D339" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E339" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F339" s="8" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="340" ht="15" spans="1:6">
@@ -10375,17 +10381,17 @@
         <v>339</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C340" s="8"/>
       <c r="D340" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E340" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F340" s="8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="341" ht="15" spans="1:6">
@@ -10393,17 +10399,17 @@
         <v>340</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C341" s="8"/>
       <c r="D341" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E341" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F341" s="8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="342" ht="15" spans="1:6">
@@ -10411,17 +10417,17 @@
         <v>341</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C342" s="8"/>
       <c r="D342" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E342" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F342" s="8" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="343" ht="15" spans="1:6">
@@ -10429,17 +10435,17 @@
         <v>342</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C343" s="8"/>
       <c r="D343" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E343" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="344" ht="15" spans="1:6">
@@ -10447,19 +10453,19 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C344" s="17" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D344" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E344" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="345" ht="15" spans="1:6">
@@ -10467,16 +10473,16 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D345" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E345" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="346" ht="15" spans="1:6">
@@ -10484,19 +10490,19 @@
         <v>345</v>
       </c>
       <c r="B346" s="18" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C346" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D346" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E346" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F346" s="14" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="347" ht="15" spans="1:6">
@@ -10504,17 +10510,17 @@
         <v>346</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C347" s="8"/>
       <c r="D347" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E347" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F347" s="8" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="348" ht="15" spans="1:6">
@@ -10522,17 +10528,17 @@
         <v>347</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C348" s="8"/>
       <c r="D348" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E348" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F348" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="349" ht="15" spans="1:6">
@@ -10540,17 +10546,17 @@
         <v>348</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C349" s="8"/>
       <c r="D349" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="350" ht="15" spans="1:6">
@@ -10558,17 +10564,17 @@
         <v>349</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C350" s="8"/>
       <c r="D350" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E350" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F350" s="8" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="351" ht="15" spans="1:6">
@@ -10576,17 +10582,17 @@
         <v>350</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C351" s="8"/>
       <c r="D351" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E351" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F351" s="8" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="352" ht="15" spans="1:6">
@@ -10594,17 +10600,17 @@
         <v>351</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C352" s="8"/>
       <c r="D352" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E352" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F352" s="8" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="353" ht="15" spans="1:6">
@@ -10612,17 +10618,17 @@
         <v>352</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C353" s="8"/>
       <c r="D353" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E353" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F353" s="8" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="354" ht="15" spans="1:6">
@@ -10630,17 +10636,17 @@
         <v>353</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C354" s="8"/>
       <c r="D354" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E354" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F354" s="8" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="355" ht="15" spans="1:6">
@@ -10648,17 +10654,17 @@
         <v>354</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C355" s="8"/>
       <c r="D355" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E355" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F355" s="8" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="356" ht="15" spans="1:6">
@@ -10666,17 +10672,17 @@
         <v>355</v>
       </c>
       <c r="B356" s="8" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C356" s="8"/>
       <c r="D356" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E356" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F356" s="8" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="357" ht="15" spans="1:6">
@@ -10684,17 +10690,17 @@
         <v>356</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C357" s="8"/>
       <c r="D357" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E357" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F357" s="8" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="358" ht="15" spans="1:6">
@@ -10702,17 +10708,17 @@
         <v>357</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C358" s="8"/>
       <c r="D358" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E358" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F358" s="8" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="359" ht="15" spans="1:6">
@@ -10720,17 +10726,17 @@
         <v>358</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C359" s="8"/>
       <c r="D359" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E359" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F359" s="8" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="360" ht="15" spans="1:6">
@@ -10738,17 +10744,17 @@
         <v>359</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C360" s="8"/>
       <c r="D360" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E360" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F360" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="361" ht="15" spans="1:6">
@@ -10756,17 +10762,17 @@
         <v>360</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C361" s="8"/>
       <c r="D361" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E361" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F361" s="8" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="362" ht="15" spans="1:6">
@@ -10774,17 +10780,17 @@
         <v>361</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C362" s="8"/>
       <c r="D362" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E362" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F362" s="8" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="363" ht="15" spans="1:6">
@@ -10792,17 +10798,17 @@
         <v>362</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C363" s="8"/>
       <c r="D363" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E363" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F363" s="8" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="364" ht="15" spans="1:6">
@@ -10810,17 +10816,17 @@
         <v>363</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C364" s="8"/>
       <c r="D364" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E364" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F364" s="8" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="365" ht="15" spans="1:6">
@@ -10828,17 +10834,17 @@
         <v>364</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C365" s="8"/>
       <c r="D365" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E365" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F365" s="8" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="366" ht="15" spans="1:6">
@@ -10846,17 +10852,17 @@
         <v>365</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C366" s="8"/>
       <c r="D366" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E366" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F366" s="8" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="367" ht="15" spans="1:6">
@@ -10864,17 +10870,17 @@
         <v>366</v>
       </c>
       <c r="B367" s="8" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C367" s="8"/>
       <c r="D367" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E367" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F367" s="8" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="368" ht="15" spans="1:6">
@@ -10882,17 +10888,17 @@
         <v>367</v>
       </c>
       <c r="B368" s="8" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C368" s="8"/>
       <c r="D368" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E368" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F368" s="8" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="369" ht="15" spans="1:6">
@@ -10900,17 +10906,17 @@
         <v>368</v>
       </c>
       <c r="B369" s="8" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C369" s="8"/>
       <c r="D369" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E369" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F369" s="8" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="370" ht="15" spans="1:6">
@@ -10918,17 +10924,17 @@
         <v>369</v>
       </c>
       <c r="B370" s="8" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C370" s="8"/>
       <c r="D370" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E370" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F370" s="8" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="371" ht="15" spans="1:6">
@@ -10936,17 +10942,17 @@
         <v>370</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C371" s="8"/>
       <c r="D371" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E371" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F371" s="8" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="372" ht="15" spans="1:6">
@@ -10954,17 +10960,17 @@
         <v>371</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C372" s="8"/>
       <c r="D372" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E372" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F372" s="8" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="373" ht="15" spans="1:6">
@@ -10972,17 +10978,17 @@
         <v>372</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C373" s="8"/>
       <c r="D373" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E373" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F373" s="8" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="374" ht="15" spans="1:6">
@@ -10990,17 +10996,17 @@
         <v>373</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C374" s="8"/>
       <c r="D374" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E374" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F374" s="8" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="375" ht="15" spans="1:6">
@@ -11008,17 +11014,17 @@
         <v>374</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C375" s="8"/>
       <c r="D375" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E375" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F375" s="8" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="376" ht="15" spans="1:6">
@@ -11026,17 +11032,17 @@
         <v>375</v>
       </c>
       <c r="B376" s="8" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C376" s="8"/>
       <c r="D376" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E376" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F376" s="8" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="377" ht="15" spans="1:6">
@@ -11044,17 +11050,17 @@
         <v>376</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C377" s="8"/>
       <c r="D377" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E377" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F377" s="8" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="378" ht="15" spans="1:6">
@@ -11062,17 +11068,17 @@
         <v>377</v>
       </c>
       <c r="B378" s="8" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C378" s="8"/>
       <c r="D378" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E378" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F378" s="8" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="379" ht="15" spans="1:6">
@@ -11080,17 +11086,17 @@
         <v>378</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C379" s="8"/>
       <c r="D379" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E379" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F379" s="8" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="380" ht="15" spans="1:6">
@@ -11098,17 +11104,17 @@
         <v>379</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C380" s="8"/>
       <c r="D380" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="381" ht="15" spans="1:6">
@@ -11116,17 +11122,17 @@
         <v>380</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C381" s="8"/>
       <c r="D381" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E381" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F381" s="8" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="382" ht="15" spans="1:6">
@@ -11134,17 +11140,17 @@
         <v>381</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C382" s="8"/>
       <c r="D382" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E382" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F382" s="8" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="383" ht="15" spans="1:6">
@@ -11152,17 +11158,17 @@
         <v>382</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C383" s="8"/>
       <c r="D383" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E383" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F383" s="8" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="384" ht="15" spans="1:6">
@@ -11170,17 +11176,17 @@
         <v>383</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C384" s="8"/>
       <c r="D384" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E384" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F384" s="8" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="385" ht="15" spans="1:6">
@@ -11188,17 +11194,17 @@
         <v>384</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C385" s="8"/>
       <c r="D385" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E385" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F385" s="8" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="386" ht="15" spans="1:6">
@@ -11206,17 +11212,17 @@
         <v>385</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C386" s="8"/>
       <c r="D386" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E386" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F386" s="8" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="387" ht="15" spans="1:6">
@@ -11224,17 +11230,17 @@
         <v>386</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C387" s="8"/>
       <c r="D387" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E387" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F387" s="8" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="388" ht="15" spans="1:6">
@@ -11242,17 +11248,17 @@
         <v>387</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C388" s="8"/>
       <c r="D388" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E388" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F388" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="389" ht="15" spans="1:6">
@@ -11260,17 +11266,17 @@
         <v>388</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C389" s="8"/>
       <c r="D389" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E389" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F389" s="8" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="390" ht="15" spans="1:6">
@@ -11278,17 +11284,17 @@
         <v>389</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C390" s="8"/>
       <c r="D390" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E390" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F390" s="8" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="391" ht="15" spans="1:6">
@@ -11296,17 +11302,17 @@
         <v>390</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C391" s="8"/>
       <c r="D391" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E391" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F391" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="392" ht="15" spans="1:6">
@@ -11314,17 +11320,17 @@
         <v>391</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C392" s="8"/>
       <c r="D392" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E392" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F392" s="8" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="393" ht="15" spans="1:6">
@@ -11332,17 +11338,17 @@
         <v>392</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C393" s="8"/>
       <c r="D393" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E393" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F393" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="394" ht="15" spans="1:6">
@@ -11350,17 +11356,17 @@
         <v>393</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C394" s="8"/>
       <c r="D394" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E394" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F394" s="10" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="395" ht="15" spans="1:6">
@@ -11368,17 +11374,17 @@
         <v>394</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C395" s="8"/>
       <c r="D395" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E395" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F395" s="8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="396" ht="15" spans="1:6">
@@ -11386,17 +11392,17 @@
         <v>395</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C396" s="8"/>
       <c r="D396" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E396" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F396" s="8" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="397" ht="15" spans="1:6">
@@ -11404,17 +11410,17 @@
         <v>396</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C397" s="8"/>
       <c r="D397" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E397" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F397" s="8" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="398" ht="15" spans="1:6">
@@ -11422,17 +11428,17 @@
         <v>397</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C398" s="8"/>
       <c r="D398" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E398" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F398" s="8" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="399" ht="15" spans="1:6">
@@ -11440,17 +11446,17 @@
         <v>398</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C399" s="8"/>
       <c r="D399" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E399" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F399" s="8" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="400" ht="15" spans="1:6">
@@ -11458,17 +11464,17 @@
         <v>399</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C400" s="8"/>
       <c r="D400" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E400" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F400" s="8" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="401" ht="15" spans="1:6">
@@ -11476,17 +11482,17 @@
         <v>400</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C401" s="8"/>
       <c r="D401" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E401" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F401" s="8" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="402" ht="15" spans="1:6">
@@ -11494,17 +11500,17 @@
         <v>401</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C402" s="8"/>
       <c r="D402" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E402" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F402" s="8" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="403" ht="15" spans="1:6">
@@ -11512,17 +11518,17 @@
         <v>402</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C403" s="8"/>
       <c r="D403" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E403" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F403" s="8" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="404" ht="15" spans="1:6">
@@ -11530,17 +11536,17 @@
         <v>403</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C404" s="8"/>
       <c r="D404" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E404" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F404" s="8" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="405" ht="15" spans="1:6">
@@ -11548,17 +11554,17 @@
         <v>404</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C405" s="8"/>
       <c r="D405" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E405" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F405" s="8" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="406" ht="15" spans="1:6">
@@ -11566,17 +11572,17 @@
         <v>405</v>
       </c>
       <c r="B406" s="8" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C406" s="8"/>
       <c r="D406" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E406" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F406" s="8" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="407" ht="15" spans="1:6">
@@ -11584,17 +11590,17 @@
         <v>406</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C407" s="8"/>
       <c r="D407" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E407" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F407" s="8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="408" ht="15" spans="1:6">
@@ -11602,17 +11608,17 @@
         <v>407</v>
       </c>
       <c r="B408" s="8" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C408" s="8"/>
       <c r="D408" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E408" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F408" s="8" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="409" ht="15" spans="1:6">
@@ -11620,17 +11626,17 @@
         <v>408</v>
       </c>
       <c r="B409" s="8" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C409" s="8"/>
       <c r="D409" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F409" s="8" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="410" ht="15" spans="1:6">
@@ -11638,17 +11644,17 @@
         <v>409</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C410" s="8"/>
       <c r="D410" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E410" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F410" s="8" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="411" ht="15" spans="1:6">
@@ -11656,17 +11662,17 @@
         <v>410</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C411" s="8"/>
       <c r="D411" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E411" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F411" s="8" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="412" ht="15" spans="1:6">
@@ -11674,17 +11680,17 @@
         <v>411</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C412" s="8"/>
       <c r="D412" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E412" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F412" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="413" ht="15" spans="1:6">
@@ -11692,17 +11698,17 @@
         <v>412</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C413" s="8"/>
       <c r="D413" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E413" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F413" s="8" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="414" ht="15" spans="1:6">
@@ -11710,17 +11716,17 @@
         <v>413</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C414" s="8"/>
       <c r="D414" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E414" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F414" s="8" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="415" ht="15" spans="1:6">
@@ -11728,17 +11734,17 @@
         <v>414</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C415" s="8"/>
       <c r="D415" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E415" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F415" s="8" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="416" ht="15" spans="1:6">
@@ -11746,17 +11752,17 @@
         <v>415</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C416" s="8"/>
       <c r="D416" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E416" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F416" s="8" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="417" ht="15" spans="1:6">
@@ -11764,17 +11770,17 @@
         <v>416</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C417" s="8"/>
       <c r="D417" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E417" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F417" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="418" ht="15" spans="1:6">
@@ -11782,17 +11788,17 @@
         <v>417</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C418" s="8"/>
       <c r="D418" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E418" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F418" s="8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="419" ht="15" spans="1:6">
@@ -11800,17 +11806,17 @@
         <v>418</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C419" s="8"/>
       <c r="D419" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E419" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F419" s="8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="420" ht="15" spans="1:6">
@@ -11818,17 +11824,17 @@
         <v>419</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C420" s="8"/>
       <c r="D420" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E420" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F420" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="421" ht="15" spans="1:6">
@@ -11836,17 +11842,17 @@
         <v>420</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C421" s="8"/>
       <c r="D421" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E421" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F421" s="8" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="422" ht="15" spans="1:6">
@@ -11854,17 +11860,17 @@
         <v>421</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C422" s="8"/>
       <c r="D422" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E422" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F422" s="8" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="423" ht="15" spans="1:6">
@@ -11872,17 +11878,17 @@
         <v>422</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C423" s="8"/>
       <c r="D423" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E423" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F423" s="8" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="424" ht="15" spans="1:6">
@@ -11890,17 +11896,17 @@
         <v>423</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C424" s="8"/>
       <c r="D424" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E424" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F424" s="8" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="425" ht="15" spans="1:6">
@@ -11908,17 +11914,17 @@
         <v>424</v>
       </c>
       <c r="B425" s="8" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C425" s="8"/>
       <c r="D425" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E425" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F425" s="8" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="426" ht="15" spans="1:6">
@@ -11926,17 +11932,17 @@
         <v>425</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C426" s="8"/>
       <c r="D426" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E426" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F426" s="8" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="427" ht="15" spans="1:6">
@@ -11944,17 +11950,17 @@
         <v>426</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C427" s="8"/>
       <c r="D427" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E427" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F427" s="8" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="428" ht="15" spans="1:6">
@@ -11962,17 +11968,17 @@
         <v>427</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C428" s="8"/>
       <c r="D428" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E428" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F428" s="8" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="429" ht="15" spans="1:6">
@@ -11980,17 +11986,17 @@
         <v>428</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C429" s="8"/>
       <c r="D429" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E429" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F429" s="8" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="430" ht="15" spans="1:6">
@@ -11998,17 +12004,17 @@
         <v>429</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C430" s="8"/>
       <c r="D430" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E430" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F430" s="8" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="431" ht="15" spans="1:6">
@@ -12016,17 +12022,17 @@
         <v>430</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C431" s="8"/>
       <c r="D431" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E431" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F431" s="8" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="432" ht="15" spans="1:6">
@@ -12034,17 +12040,17 @@
         <v>431</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C432" s="8"/>
       <c r="D432" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E432" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F432" s="8" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="433" ht="15" spans="1:6">
@@ -12052,17 +12058,17 @@
         <v>432</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C433" s="8"/>
       <c r="D433" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E433" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F433" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="434" ht="15" spans="1:6">
@@ -12070,17 +12076,17 @@
         <v>433</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C434" s="8"/>
       <c r="D434" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E434" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F434" s="8" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="435" ht="15" spans="1:6">
@@ -12088,17 +12094,17 @@
         <v>434</v>
       </c>
       <c r="B435" s="8" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C435" s="8"/>
       <c r="D435" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E435" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F435" s="8" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="436" ht="15" spans="1:6">
@@ -12106,17 +12112,17 @@
         <v>435</v>
       </c>
       <c r="B436" s="8" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C436" s="8"/>
       <c r="D436" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E436" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F436" s="8" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="437" ht="15" spans="1:6">
@@ -12124,17 +12130,17 @@
         <v>436</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C437" s="8"/>
       <c r="D437" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E437" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F437" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="438" ht="15" spans="1:6">
@@ -12142,17 +12148,17 @@
         <v>437</v>
       </c>
       <c r="B438" s="8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C438" s="8"/>
       <c r="D438" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E438" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F438" s="8" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="439" ht="15" spans="1:6">
@@ -12160,17 +12166,17 @@
         <v>438</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C439" s="8"/>
       <c r="D439" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E439" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F439" s="8" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="440" ht="15" spans="1:6">
@@ -12178,17 +12184,17 @@
         <v>439</v>
       </c>
       <c r="B440" s="8" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C440" s="8"/>
       <c r="D440" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E440" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F440" s="8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="441" ht="15" spans="1:6">
@@ -12196,17 +12202,17 @@
         <v>440</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C441" s="8"/>
       <c r="D441" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E441" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F441" s="8" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="442" ht="15" spans="1:6">
@@ -12214,17 +12220,17 @@
         <v>441</v>
       </c>
       <c r="B442" s="8" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C442" s="8"/>
       <c r="D442" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E442" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F442" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="443" ht="15" spans="1:6">
@@ -12232,17 +12238,17 @@
         <v>442</v>
       </c>
       <c r="B443" s="8" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C443" s="8"/>
       <c r="D443" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E443" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F443" s="8" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="444" ht="15" spans="1:6">
@@ -12250,17 +12256,17 @@
         <v>443</v>
       </c>
       <c r="B444" s="8" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C444" s="8"/>
       <c r="D444" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E444" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F444" s="8" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="445" ht="15" spans="1:6">
@@ -12268,17 +12274,17 @@
         <v>444</v>
       </c>
       <c r="B445" s="8" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C445" s="8"/>
       <c r="D445" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E445" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F445" s="8" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="446" ht="15" spans="1:6">
@@ -12286,17 +12292,17 @@
         <v>445</v>
       </c>
       <c r="B446" s="8" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C446" s="8"/>
       <c r="D446" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E446" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F446" s="8" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="447" ht="15" spans="1:6">
@@ -12304,17 +12310,17 @@
         <v>446</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C447" s="8"/>
       <c r="D447" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E447" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F447" s="8" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="448" ht="15" spans="1:6">
@@ -12322,17 +12328,17 @@
         <v>447</v>
       </c>
       <c r="B448" s="8" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C448" s="8"/>
       <c r="D448" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E448" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F448" s="8" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="449" ht="15" spans="1:6">
@@ -12340,17 +12346,17 @@
         <v>448</v>
       </c>
       <c r="B449" s="8" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C449" s="8"/>
       <c r="D449" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E449" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F449" s="8" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="450" ht="15" spans="1:6">
@@ -12358,17 +12364,17 @@
         <v>449</v>
       </c>
       <c r="B450" s="8" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C450" s="8"/>
       <c r="D450" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E450" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F450" s="8" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="451" ht="15" spans="1:6">
@@ -12376,17 +12382,17 @@
         <v>450</v>
       </c>
       <c r="B451" s="8" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C451" s="8"/>
       <c r="D451" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E451" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F451" s="8" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="452" spans="1:6">
@@ -12394,19 +12400,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="18" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C452" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D452" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E452" t="s">
         <v>14</v>
       </c>
       <c r="F452" s="14" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -12414,16 +12420,16 @@
         <v>452</v>
       </c>
       <c r="B453" s="14" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D453" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E453" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F453" s="14" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="454" spans="1:6">
@@ -12431,19 +12437,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="14" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C454" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D454" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E454" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F454" s="14" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="455" ht="15" spans="1:6">
@@ -12451,17 +12457,17 @@
         <v>454</v>
       </c>
       <c r="B455" s="8" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C455" s="8"/>
       <c r="D455" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E455" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F455" s="10" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="456" ht="15" spans="1:6">
@@ -12469,17 +12475,17 @@
         <v>455</v>
       </c>
       <c r="B456" s="8" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C456" s="8"/>
       <c r="D456" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E456" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F456" s="8" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -12487,16 +12493,16 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D457" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E457" t="s">
         <v>14</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="458" ht="15" spans="1:6">
@@ -12504,17 +12510,17 @@
         <v>457</v>
       </c>
       <c r="B458" s="8" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C458" s="8"/>
       <c r="D458" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E458" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F458" s="8" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="459" ht="15" spans="1:6">
@@ -12522,17 +12528,17 @@
         <v>458</v>
       </c>
       <c r="B459" s="8" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C459" s="8"/>
       <c r="D459" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E459" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F459" s="8" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="460" ht="15" spans="1:6">
@@ -12540,16 +12546,16 @@
         <v>459</v>
       </c>
       <c r="B460" s="14" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D460" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E460" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F460" s="14" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="461" ht="15" spans="1:6">
@@ -12557,16 +12563,16 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D461" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E461" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="462" ht="15" spans="1:6">
@@ -12574,16 +12580,16 @@
         <v>461</v>
       </c>
       <c r="B462" s="14" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D462" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E462" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F462" s="14" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="463" ht="15" spans="1:6">
@@ -12591,16 +12597,16 @@
         <v>462</v>
       </c>
       <c r="B463" s="14" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D463" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E463" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F463" s="14" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="464" ht="15" spans="1:6">
@@ -12608,16 +12614,16 @@
         <v>463</v>
       </c>
       <c r="B464" s="14" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D464" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E464" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F464" s="14" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -12625,16 +12631,16 @@
         <v>464</v>
       </c>
       <c r="B465" s="14" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D465" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E465" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F465" s="14" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -12642,16 +12648,16 @@
         <v>465</v>
       </c>
       <c r="B466" s="14" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D466" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E466" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F466" s="14" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="467" ht="15" spans="1:6">
@@ -12659,17 +12665,17 @@
         <v>466</v>
       </c>
       <c r="B467" s="8" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C467" s="8"/>
       <c r="D467" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E467" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F467" s="10" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="468" ht="15" spans="1:6">
@@ -12677,17 +12683,17 @@
         <v>467</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C468" s="8"/>
       <c r="D468" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E468" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F468" s="8" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="469" ht="15" spans="1:6">
@@ -12695,16 +12701,16 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D469" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E469" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F469" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="470" ht="15" spans="1:6">
@@ -12712,16 +12718,16 @@
         <v>469</v>
       </c>
       <c r="B470" s="14" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D470" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E470" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F470" s="14" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="471" ht="15" spans="1:6">
@@ -12729,16 +12735,16 @@
         <v>470</v>
       </c>
       <c r="B471" s="18" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D471" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E471" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F471" s="14" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="472" ht="15" spans="1:6">
@@ -12746,16 +12752,16 @@
         <v>471</v>
       </c>
       <c r="B472" s="14" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D472" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E472" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F472" s="14" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="473" ht="15" spans="1:6">
@@ -12763,16 +12769,16 @@
         <v>472</v>
       </c>
       <c r="B473" s="14" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D473" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E473" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F473" s="14" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="474" ht="15" spans="1:6">
@@ -12780,16 +12786,16 @@
         <v>473</v>
       </c>
       <c r="B474" s="14" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D474" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E474" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F474" s="14" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="475" ht="15" spans="1:6">
@@ -12797,16 +12803,16 @@
         <v>474</v>
       </c>
       <c r="B475" s="14" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D475" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E475" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F475" s="14" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="476" ht="15" spans="1:6">
@@ -12814,16 +12820,16 @@
         <v>475</v>
       </c>
       <c r="B476" s="14" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D476" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E476" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F476" s="14" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="477" ht="15" spans="1:6">
@@ -12831,16 +12837,16 @@
         <v>476</v>
       </c>
       <c r="B477" s="14" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D477" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E477" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F477" s="14" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="478" ht="15" spans="1:6">
@@ -12848,16 +12854,16 @@
         <v>477</v>
       </c>
       <c r="B478" s="14" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D478" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E478" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F478" s="14" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="479" ht="15" spans="1:6">
@@ -12865,16 +12871,16 @@
         <v>478</v>
       </c>
       <c r="B479" s="14" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D479" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E479" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F479" s="14" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="480" ht="15" spans="1:6">
@@ -12882,16 +12888,16 @@
         <v>479</v>
       </c>
       <c r="B480" s="14" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D480" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E480" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F480" s="14" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="481" ht="15" spans="1:6">
@@ -12899,16 +12905,16 @@
         <v>480</v>
       </c>
       <c r="B481" s="14" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D481" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E481" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F481" s="14" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="482" ht="15" spans="1:6">
@@ -12916,16 +12922,16 @@
         <v>481</v>
       </c>
       <c r="B482" s="14" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D482" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E482" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F482" s="14" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -12933,7 +12939,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="22" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D483" t="s">
         <v>139</v>
@@ -12942,11 +12948,11 @@
         <v>139</v>
       </c>
       <c r="F483" s="22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F482" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F483" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="1096">
   <si>
     <t>id</t>
   </si>
@@ -3246,6 +3246,78 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/796dd609eaad</t>
+  </si>
+  <si>
+    <t>无间道.三部全</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0bfe386169c0</t>
+  </si>
+  <si>
+    <t>肖申克的救赎</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/34a94725c435</t>
+  </si>
+  <si>
+    <t>阿甘正传</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/55b7e3faf361</t>
+  </si>
+  <si>
+    <t>星际穿越</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c35b971e57da</t>
+  </si>
+  <si>
+    <t>楚门的世界</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/42ad1952fca1</t>
+  </si>
+  <si>
+    <t>匿杀</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/2c82fabf962b</t>
+  </si>
+  <si>
+    <t>悬崖绝壁</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e282657cfb3b</t>
+  </si>
+  <si>
+    <t>F1：狂飙飞车</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/bb0fd5ab52af</t>
+  </si>
+  <si>
+    <t>侏罗纪世界：重生</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6ee9f4773f63</t>
+  </si>
+  <si>
+    <t>家弑服务</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e0c07eef150e</t>
+  </si>
+  <si>
+    <t>忠犬八公的故事</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6d90d2856b27</t>
+  </si>
+  <si>
+    <t>风城2</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/73adaa98a4ff</t>
   </si>
 </sst>
 </file>
@@ -3267,11 +3339,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3721,19 +3792,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3742,7 +3813,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3866,8 +3937,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4213,13 +4285,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G484"/>
+  <sheetPr/>
+  <dimension ref="A1:G496"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
     <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="59" customWidth="1"/>
+    <col min="4" max="4" width="35.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4245,7 +4317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4268,7 +4340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4291,7 +4363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:7">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4314,7 +4386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4337,7 +4409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:7">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4360,7 +4432,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:7">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4383,7 +4455,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4406,7 +4478,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4429,7 +4501,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4452,7 +4524,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:7">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4475,7 +4547,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4498,7 +4570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4521,7 +4593,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:7">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4544,7 +4616,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:7">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4567,7 +4639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:7">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4590,7 +4662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4613,7 +4685,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4636,7 +4708,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:7">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4659,7 +4731,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:7">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4682,7 +4754,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:7">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4705,7 +4777,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4728,7 +4800,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4751,7 +4823,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:7">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4774,7 +4846,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:7">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4797,7 +4869,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4820,7 +4892,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:7">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4843,7 +4915,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4866,7 +4938,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:7">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4889,7 +4961,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4912,7 +4984,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:7">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4935,7 +5007,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:7">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4958,7 +5030,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:7">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4981,7 +5053,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:7">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5004,7 +5076,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:7">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5027,7 +5099,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:7">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5050,7 +5122,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:7">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5073,7 +5145,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:7">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5096,7 +5168,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:7">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5119,7 +5191,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:7">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5142,7 +5214,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:7">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5165,7 +5237,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:7">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5188,7 +5260,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:7">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5211,7 +5283,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:7">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5234,7 +5306,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:7">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5257,7 +5329,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:7">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5280,7 +5352,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:7">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5303,7 +5375,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:7">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5326,7 +5398,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:7">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5349,7 +5421,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:7">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5372,7 +5444,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:7">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5395,7 +5467,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:7">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5418,7 +5490,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:7">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5441,7 +5513,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:7">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5464,7 +5536,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:7">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5487,7 +5559,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5510,7 +5582,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:7">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5533,7 +5605,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5556,7 +5628,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:7">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5579,7 +5651,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:7">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5625,7 +5697,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:7">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5648,7 +5720,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:7">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5671,7 +5743,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:7">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5694,7 +5766,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:7">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5717,7 +5789,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:7">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5740,7 +5812,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:7">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5763,7 +5835,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:7">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5786,7 +5858,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:7">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5809,7 +5881,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:7">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5832,7 +5904,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:7">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5855,7 +5927,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:7">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5878,7 +5950,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:7">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5901,7 +5973,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:7">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5924,7 +5996,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:7">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5947,7 +6019,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:7">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5970,7 +6042,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:7">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5993,7 +6065,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:7">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6016,7 +6088,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:7">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6039,7 +6111,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:7">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6062,7 +6134,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:7">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6108,7 +6180,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:7">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6131,7 +6203,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:7">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6154,7 +6226,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:7">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6177,7 +6249,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:7">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6292,7 +6364,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:7">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9788,7 +9860,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="243" hidden="1" spans="1:7">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -9811,7 +9883,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:7">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11490,7 +11562,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:7">
+    <row r="317" spans="1:7">
       <c r="A317">
         <v>316</v>
       </c>
@@ -11513,7 +11585,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:7">
+    <row r="318" spans="1:7">
       <c r="A318">
         <v>317</v>
       </c>
@@ -11536,7 +11608,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:7">
+    <row r="319" spans="1:7">
       <c r="A319">
         <v>318</v>
       </c>
@@ -11559,7 +11631,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:7">
+    <row r="320" spans="1:7">
       <c r="A320">
         <v>319</v>
       </c>
@@ -11582,7 +11654,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:7">
+    <row r="321" spans="1:7">
       <c r="A321">
         <v>320</v>
       </c>
@@ -11605,7 +11677,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:7">
+    <row r="322" spans="1:7">
       <c r="A322">
         <v>321</v>
       </c>
@@ -11628,7 +11700,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:7">
+    <row r="323" spans="1:7">
       <c r="A323">
         <v>322</v>
       </c>
@@ -11651,7 +11723,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:7">
+    <row r="324" spans="1:7">
       <c r="A324">
         <v>323</v>
       </c>
@@ -11674,7 +11746,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:7">
+    <row r="325" spans="1:7">
       <c r="A325">
         <v>324</v>
       </c>
@@ -11697,7 +11769,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:7">
+    <row r="326" spans="1:7">
       <c r="A326">
         <v>325</v>
       </c>
@@ -11720,7 +11792,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:7">
+    <row r="327" spans="1:7">
       <c r="A327">
         <v>326</v>
       </c>
@@ -11743,7 +11815,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:7">
+    <row r="328" spans="1:7">
       <c r="A328">
         <v>327</v>
       </c>
@@ -11766,7 +11838,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:7">
+    <row r="329" spans="1:7">
       <c r="A329">
         <v>328</v>
       </c>
@@ -11789,7 +11861,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:7">
+    <row r="330" spans="1:7">
       <c r="A330">
         <v>329</v>
       </c>
@@ -11812,7 +11884,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:7">
+    <row r="331" spans="1:7">
       <c r="A331">
         <v>330</v>
       </c>
@@ -11835,7 +11907,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:7">
+    <row r="332" spans="1:7">
       <c r="A332">
         <v>331</v>
       </c>
@@ -11858,7 +11930,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:7">
+    <row r="333" spans="1:7">
       <c r="A333">
         <v>332</v>
       </c>
@@ -11881,7 +11953,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:7">
+    <row r="334" spans="1:7">
       <c r="A334">
         <v>333</v>
       </c>
@@ -11904,7 +11976,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:7">
+    <row r="335" spans="1:7">
       <c r="A335">
         <v>334</v>
       </c>
@@ -11927,7 +11999,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:7">
+    <row r="336" spans="1:7">
       <c r="A336">
         <v>335</v>
       </c>
@@ -11950,7 +12022,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:7">
+    <row r="337" spans="1:7">
       <c r="A337">
         <v>336</v>
       </c>
@@ -11973,7 +12045,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:7">
+    <row r="338" spans="1:7">
       <c r="A338">
         <v>337</v>
       </c>
@@ -11996,7 +12068,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="339" hidden="1" spans="1:7">
+    <row r="339" spans="1:7">
       <c r="A339">
         <v>338</v>
       </c>
@@ -12019,7 +12091,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="340" hidden="1" spans="1:7">
+    <row r="340" spans="1:7">
       <c r="A340">
         <v>339</v>
       </c>
@@ -12042,7 +12114,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:7">
+    <row r="341" spans="1:7">
       <c r="A341">
         <v>340</v>
       </c>
@@ -12065,7 +12137,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:7">
+    <row r="342" spans="1:7">
       <c r="A342">
         <v>341</v>
       </c>
@@ -12088,7 +12160,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:7">
+    <row r="343" spans="1:7">
       <c r="A343">
         <v>342</v>
       </c>
@@ -12111,7 +12183,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:7">
+    <row r="344" spans="1:7">
       <c r="A344">
         <v>343</v>
       </c>
@@ -12134,7 +12206,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:7">
+    <row r="345" spans="1:7">
       <c r="A345">
         <v>344</v>
       </c>
@@ -12180,7 +12252,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:7">
+    <row r="347" spans="1:7">
       <c r="A347">
         <v>346</v>
       </c>
@@ -12203,7 +12275,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:7">
+    <row r="348" spans="1:7">
       <c r="A348">
         <v>347</v>
       </c>
@@ -12226,7 +12298,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:7">
+    <row r="349" spans="1:7">
       <c r="A349">
         <v>348</v>
       </c>
@@ -12249,7 +12321,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:7">
+    <row r="350" spans="1:7">
       <c r="A350">
         <v>349</v>
       </c>
@@ -12272,7 +12344,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:7">
+    <row r="351" spans="1:7">
       <c r="A351">
         <v>350</v>
       </c>
@@ -12295,7 +12367,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:7">
+    <row r="352" spans="1:7">
       <c r="A352">
         <v>351</v>
       </c>
@@ -12318,7 +12390,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:7">
+    <row r="353" spans="1:7">
       <c r="A353">
         <v>352</v>
       </c>
@@ -12341,7 +12413,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:7">
+    <row r="354" spans="1:7">
       <c r="A354">
         <v>353</v>
       </c>
@@ -12364,7 +12436,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:7">
+    <row r="355" spans="1:7">
       <c r="A355">
         <v>354</v>
       </c>
@@ -12387,7 +12459,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:7">
+    <row r="356" spans="1:7">
       <c r="A356">
         <v>355</v>
       </c>
@@ -12410,7 +12482,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:7">
+    <row r="357" spans="1:7">
       <c r="A357">
         <v>356</v>
       </c>
@@ -12433,7 +12505,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:7">
+    <row r="358" spans="1:7">
       <c r="A358">
         <v>357</v>
       </c>
@@ -12456,7 +12528,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:7">
+    <row r="359" spans="1:7">
       <c r="A359">
         <v>358</v>
       </c>
@@ -12479,7 +12551,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:7">
+    <row r="360" spans="1:7">
       <c r="A360">
         <v>359</v>
       </c>
@@ -12502,7 +12574,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:7">
+    <row r="361" spans="1:7">
       <c r="A361">
         <v>360</v>
       </c>
@@ -12525,7 +12597,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:7">
+    <row r="362" spans="1:7">
       <c r="A362">
         <v>361</v>
       </c>
@@ -12548,7 +12620,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:7">
+    <row r="363" spans="1:7">
       <c r="A363">
         <v>362</v>
       </c>
@@ -12571,7 +12643,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:7">
+    <row r="364" spans="1:7">
       <c r="A364">
         <v>363</v>
       </c>
@@ -12594,7 +12666,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:7">
+    <row r="365" spans="1:7">
       <c r="A365">
         <v>364</v>
       </c>
@@ -12617,7 +12689,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:7">
+    <row r="366" spans="1:7">
       <c r="A366">
         <v>365</v>
       </c>
@@ -12640,7 +12712,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:7">
+    <row r="367" spans="1:7">
       <c r="A367">
         <v>366</v>
       </c>
@@ -12663,7 +12735,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:7">
+    <row r="368" spans="1:7">
       <c r="A368">
         <v>367</v>
       </c>
@@ -12686,7 +12758,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:7">
+    <row r="369" spans="1:7">
       <c r="A369">
         <v>368</v>
       </c>
@@ -12709,7 +12781,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370">
         <v>369</v>
       </c>
@@ -12732,7 +12804,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:7">
+    <row r="371" spans="1:7">
       <c r="A371">
         <v>370</v>
       </c>
@@ -12755,7 +12827,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:7">
+    <row r="372" spans="1:7">
       <c r="A372">
         <v>371</v>
       </c>
@@ -12778,7 +12850,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:7">
+    <row r="373" spans="1:7">
       <c r="A373">
         <v>372</v>
       </c>
@@ -12801,7 +12873,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:7">
+    <row r="374" spans="1:7">
       <c r="A374">
         <v>373</v>
       </c>
@@ -12824,7 +12896,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:7">
+    <row r="375" spans="1:7">
       <c r="A375">
         <v>374</v>
       </c>
@@ -12847,7 +12919,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:7">
+    <row r="376" spans="1:7">
       <c r="A376">
         <v>375</v>
       </c>
@@ -12870,7 +12942,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:7">
+    <row r="377" spans="1:7">
       <c r="A377">
         <v>376</v>
       </c>
@@ -12893,7 +12965,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:7">
+    <row r="378" spans="1:7">
       <c r="A378">
         <v>377</v>
       </c>
@@ -12916,7 +12988,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:7">
+    <row r="379" spans="1:7">
       <c r="A379">
         <v>378</v>
       </c>
@@ -12939,7 +13011,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:7">
+    <row r="380" spans="1:7">
       <c r="A380">
         <v>379</v>
       </c>
@@ -12962,7 +13034,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:7">
+    <row r="381" spans="1:7">
       <c r="A381">
         <v>380</v>
       </c>
@@ -12985,7 +13057,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:7">
+    <row r="382" spans="1:7">
       <c r="A382">
         <v>381</v>
       </c>
@@ -13008,7 +13080,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:7">
+    <row r="383" spans="1:7">
       <c r="A383">
         <v>382</v>
       </c>
@@ -13031,7 +13103,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384">
         <v>383</v>
       </c>
@@ -13054,7 +13126,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:7">
+    <row r="385" spans="1:7">
       <c r="A385">
         <v>384</v>
       </c>
@@ -13077,7 +13149,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:7">
+    <row r="386" spans="1:7">
       <c r="A386">
         <v>385</v>
       </c>
@@ -13100,7 +13172,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:7">
+    <row r="387" spans="1:7">
       <c r="A387">
         <v>386</v>
       </c>
@@ -13123,7 +13195,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:7">
+    <row r="388" spans="1:7">
       <c r="A388">
         <v>387</v>
       </c>
@@ -13146,7 +13218,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:7">
+    <row r="389" spans="1:7">
       <c r="A389">
         <v>388</v>
       </c>
@@ -13169,7 +13241,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390">
         <v>389</v>
       </c>
@@ -13192,7 +13264,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:7">
+    <row r="391" spans="1:7">
       <c r="A391">
         <v>390</v>
       </c>
@@ -13215,7 +13287,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:7">
+    <row r="392" spans="1:7">
       <c r="A392">
         <v>391</v>
       </c>
@@ -13238,7 +13310,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:7">
+    <row r="393" spans="1:7">
       <c r="A393">
         <v>392</v>
       </c>
@@ -13261,7 +13333,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:7">
+    <row r="394" spans="1:7">
       <c r="A394">
         <v>393</v>
       </c>
@@ -13284,7 +13356,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:7">
+    <row r="395" spans="1:7">
       <c r="A395">
         <v>394</v>
       </c>
@@ -13307,7 +13379,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:7">
+    <row r="396" spans="1:7">
       <c r="A396">
         <v>395</v>
       </c>
@@ -13330,7 +13402,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:7">
+    <row r="397" spans="1:7">
       <c r="A397">
         <v>396</v>
       </c>
@@ -13353,7 +13425,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:7">
+    <row r="398" spans="1:7">
       <c r="A398">
         <v>397</v>
       </c>
@@ -13376,7 +13448,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:7">
+    <row r="399" spans="1:7">
       <c r="A399">
         <v>398</v>
       </c>
@@ -13399,7 +13471,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:7">
+    <row r="400" spans="1:7">
       <c r="A400">
         <v>399</v>
       </c>
@@ -13422,7 +13494,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:7">
+    <row r="401" spans="1:7">
       <c r="A401">
         <v>400</v>
       </c>
@@ -13445,7 +13517,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:7">
+    <row r="402" spans="1:7">
       <c r="A402">
         <v>401</v>
       </c>
@@ -13468,7 +13540,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:7">
+    <row r="403" spans="1:7">
       <c r="A403">
         <v>402</v>
       </c>
@@ -13491,7 +13563,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:7">
+    <row r="404" spans="1:7">
       <c r="A404">
         <v>403</v>
       </c>
@@ -13514,7 +13586,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:7">
+    <row r="405" spans="1:7">
       <c r="A405">
         <v>404</v>
       </c>
@@ -13537,7 +13609,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:7">
+    <row r="406" spans="1:7">
       <c r="A406">
         <v>405</v>
       </c>
@@ -13560,7 +13632,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:7">
+    <row r="407" spans="1:7">
       <c r="A407">
         <v>406</v>
       </c>
@@ -13583,7 +13655,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:7">
+    <row r="408" spans="1:7">
       <c r="A408">
         <v>407</v>
       </c>
@@ -13606,7 +13678,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:7">
+    <row r="409" spans="1:7">
       <c r="A409">
         <v>408</v>
       </c>
@@ -13629,7 +13701,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:7">
+    <row r="410" spans="1:7">
       <c r="A410">
         <v>409</v>
       </c>
@@ -13652,7 +13724,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:7">
+    <row r="411" spans="1:7">
       <c r="A411">
         <v>410</v>
       </c>
@@ -13675,7 +13747,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:7">
+    <row r="412" spans="1:7">
       <c r="A412">
         <v>411</v>
       </c>
@@ -13698,7 +13770,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:7">
+    <row r="413" spans="1:7">
       <c r="A413">
         <v>412</v>
       </c>
@@ -13721,7 +13793,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:7">
+    <row r="414" spans="1:7">
       <c r="A414">
         <v>413</v>
       </c>
@@ -13744,7 +13816,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:7">
+    <row r="415" spans="1:7">
       <c r="A415">
         <v>414</v>
       </c>
@@ -13767,7 +13839,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:7">
+    <row r="416" spans="1:7">
       <c r="A416">
         <v>415</v>
       </c>
@@ -13790,7 +13862,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:7">
+    <row r="417" spans="1:7">
       <c r="A417">
         <v>416</v>
       </c>
@@ -13813,7 +13885,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:7">
+    <row r="418" spans="1:7">
       <c r="A418">
         <v>417</v>
       </c>
@@ -13836,7 +13908,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:7">
+    <row r="419" spans="1:7">
       <c r="A419">
         <v>418</v>
       </c>
@@ -13859,7 +13931,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:7">
+    <row r="420" spans="1:7">
       <c r="A420">
         <v>419</v>
       </c>
@@ -13882,7 +13954,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:7">
+    <row r="421" spans="1:7">
       <c r="A421">
         <v>420</v>
       </c>
@@ -13905,7 +13977,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:7">
+    <row r="422" spans="1:7">
       <c r="A422">
         <v>421</v>
       </c>
@@ -13928,7 +14000,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:7">
+    <row r="423" spans="1:7">
       <c r="A423">
         <v>422</v>
       </c>
@@ -13951,7 +14023,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:7">
+    <row r="424" spans="1:7">
       <c r="A424">
         <v>423</v>
       </c>
@@ -13974,7 +14046,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:7">
+    <row r="425" spans="1:7">
       <c r="A425">
         <v>424</v>
       </c>
@@ -13997,7 +14069,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:7">
+    <row r="426" spans="1:7">
       <c r="A426">
         <v>425</v>
       </c>
@@ -14020,7 +14092,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:7">
+    <row r="427" spans="1:7">
       <c r="A427">
         <v>426</v>
       </c>
@@ -14043,7 +14115,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:7">
+    <row r="428" spans="1:7">
       <c r="A428">
         <v>427</v>
       </c>
@@ -14066,7 +14138,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:7">
+    <row r="429" spans="1:7">
       <c r="A429">
         <v>428</v>
       </c>
@@ -14089,7 +14161,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430">
         <v>429</v>
       </c>
@@ -14112,7 +14184,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:7">
+    <row r="431" spans="1:7">
       <c r="A431">
         <v>430</v>
       </c>
@@ -14135,7 +14207,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:7">
+    <row r="432" spans="1:7">
       <c r="A432">
         <v>431</v>
       </c>
@@ -14158,7 +14230,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:7">
+    <row r="433" spans="1:7">
       <c r="A433">
         <v>432</v>
       </c>
@@ -14181,7 +14253,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:7">
+    <row r="434" spans="1:7">
       <c r="A434">
         <v>433</v>
       </c>
@@ -14204,7 +14276,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:7">
+    <row r="435" spans="1:7">
       <c r="A435">
         <v>434</v>
       </c>
@@ -14227,7 +14299,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:7">
+    <row r="436" spans="1:7">
       <c r="A436">
         <v>435</v>
       </c>
@@ -14250,7 +14322,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:7">
+    <row r="437" spans="1:7">
       <c r="A437">
         <v>436</v>
       </c>
@@ -14273,7 +14345,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:7">
+    <row r="438" spans="1:7">
       <c r="A438">
         <v>437</v>
       </c>
@@ -14296,7 +14368,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439">
         <v>438</v>
       </c>
@@ -14319,7 +14391,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:7">
+    <row r="440" spans="1:7">
       <c r="A440">
         <v>439</v>
       </c>
@@ -14342,7 +14414,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:7">
+    <row r="441" spans="1:7">
       <c r="A441">
         <v>440</v>
       </c>
@@ -14365,7 +14437,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:7">
+    <row r="442" spans="1:7">
       <c r="A442">
         <v>441</v>
       </c>
@@ -14388,7 +14460,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="443" hidden="1" spans="1:7">
+    <row r="443" spans="1:7">
       <c r="A443">
         <v>442</v>
       </c>
@@ -14411,7 +14483,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="444" hidden="1" spans="1:7">
+    <row r="444" spans="1:7">
       <c r="A444">
         <v>443</v>
       </c>
@@ -14434,7 +14506,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:7">
+    <row r="445" spans="1:7">
       <c r="A445">
         <v>444</v>
       </c>
@@ -14457,7 +14529,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446">
         <v>445</v>
       </c>
@@ -14480,7 +14552,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:7">
+    <row r="447" spans="1:7">
       <c r="A447">
         <v>446</v>
       </c>
@@ -14503,7 +14575,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448">
         <v>447</v>
       </c>
@@ -14526,7 +14598,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449">
         <v>448</v>
       </c>
@@ -14549,7 +14621,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:7">
+    <row r="450" spans="1:7">
       <c r="A450">
         <v>449</v>
       </c>
@@ -14572,7 +14644,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:7">
+    <row r="451" spans="1:7">
       <c r="A451">
         <v>450</v>
       </c>
@@ -14595,7 +14667,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="452" hidden="1" spans="1:7">
+    <row r="452" spans="1:7">
       <c r="A452">
         <v>451</v>
       </c>
@@ -14710,7 +14782,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:7">
+    <row r="457" spans="1:7">
       <c r="A457">
         <v>456</v>
       </c>
@@ -14894,7 +14966,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:7">
+    <row r="465" spans="1:7">
       <c r="A465">
         <v>464</v>
       </c>
@@ -14917,7 +14989,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:7">
+    <row r="466" spans="1:7">
       <c r="A466">
         <v>465</v>
       </c>
@@ -15308,7 +15380,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="483" hidden="1" spans="1:7">
+    <row r="483" spans="1:7">
       <c r="A483">
         <v>482</v>
       </c>
@@ -15354,13 +15426,236 @@
         <v>1071</v>
       </c>
     </row>
+    <row r="485" ht="15" spans="1:7">
+      <c r="A485">
+        <v>478</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F485" s="1"/>
+      <c r="G485" s="1" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="486" ht="15" spans="1:7">
+      <c r="A486">
+        <v>476</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F486" s="1"/>
+      <c r="G486" s="1" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="487" ht="15" spans="1:7">
+      <c r="A487">
+        <v>474</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F487" s="1"/>
+      <c r="G487" s="1" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="488" ht="15" spans="1:7">
+      <c r="A488">
+        <v>472</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C488" s="1"/>
+      <c r="D488" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F488" s="1"/>
+      <c r="G488" s="1" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="489" ht="15" spans="1:7">
+      <c r="A489">
+        <v>470</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C489" s="1"/>
+      <c r="D489" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F489" s="1"/>
+      <c r="G489" s="1" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="490" ht="15" spans="1:7">
+      <c r="A490">
+        <v>468</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C490" s="1"/>
+      <c r="D490" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F490" s="1"/>
+      <c r="G490" s="1" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="491" ht="15" spans="1:7">
+      <c r="A491">
+        <v>466</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C491" s="1"/>
+      <c r="D491" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E491" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F491" s="1"/>
+      <c r="G491" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="492" ht="15" spans="1:7">
+      <c r="A492">
+        <v>464</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C492" s="1"/>
+      <c r="D492" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E492" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F492" s="1"/>
+      <c r="G492" s="1" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="493" ht="15" spans="1:7">
+      <c r="A493">
+        <v>462</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C493" s="1"/>
+      <c r="D493" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E493" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F493" s="1"/>
+      <c r="G493" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="494" ht="15" spans="1:7">
+      <c r="A494">
+        <v>460</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C494" s="1"/>
+      <c r="D494" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F494" s="1"/>
+      <c r="G494" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="495" ht="15" spans="1:7">
+      <c r="A495">
+        <v>458</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C495" s="1"/>
+      <c r="D495" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F495" s="1"/>
+      <c r="G495" s="1" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="496" ht="15" spans="1:7">
+      <c r="A496">
+        <v>456</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C496" s="1"/>
+      <c r="D496" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F496" s="1"/>
+      <c r="G496" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G484" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="剧本杀"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -15405,7 +15405,7 @@
     </row>
     <row r="484" spans="1:7">
       <c r="A484">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B484" t="s">
         <v>1070</v>
@@ -15428,7 +15428,7 @@
     </row>
     <row r="485" ht="15" spans="1:7">
       <c r="A485">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>1072</v>
@@ -15447,7 +15447,7 @@
     </row>
     <row r="486" ht="15" spans="1:7">
       <c r="A486">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>1074</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="487" ht="15" spans="1:7">
       <c r="A487">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>1076</v>
@@ -15485,7 +15485,7 @@
     </row>
     <row r="488" ht="15" spans="1:7">
       <c r="A488">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>1078</v>
@@ -15504,7 +15504,7 @@
     </row>
     <row r="489" ht="15" spans="1:7">
       <c r="A489">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>1080</v>
@@ -15523,7 +15523,7 @@
     </row>
     <row r="490" ht="15" spans="1:7">
       <c r="A490">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>1082</v>
@@ -15542,7 +15542,7 @@
     </row>
     <row r="491" ht="15" spans="1:7">
       <c r="A491">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>1084</v>
@@ -15561,7 +15561,7 @@
     </row>
     <row r="492" ht="15" spans="1:7">
       <c r="A492">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>1086</v>
@@ -15580,7 +15580,7 @@
     </row>
     <row r="493" ht="15" spans="1:7">
       <c r="A493">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>1088</v>
@@ -15599,7 +15599,7 @@
     </row>
     <row r="494" ht="15" spans="1:7">
       <c r="A494">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>1090</v>
@@ -15618,7 +15618,7 @@
     </row>
     <row r="495" ht="15" spans="1:7">
       <c r="A495">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>1092</v>
@@ -15637,7 +15637,7 @@
     </row>
     <row r="496" ht="15" spans="1:7">
       <c r="A496">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>1094</v>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2699" uniqueCount="1098">
   <si>
     <t>id</t>
   </si>
@@ -3318,6 +3318,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/73adaa98a4ff</t>
+  </si>
+  <si>
+    <t>请将我深埋</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/aae6cb9bfe41</t>
   </si>
 </sst>
 </file>
@@ -3330,7 +3336,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3342,6 +3348,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3807,16 +3819,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3825,121 +3834,125 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4286,7 +4299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G496"/>
+  <dimension ref="A1:G497"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15654,6 +15667,26 @@
         <v>1095</v>
       </c>
     </row>
+    <row r="497" spans="1:7">
+      <c r="A497">
+        <v>496</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D497" t="s">
+        <v>188</v>
+      </c>
+      <c r="E497" t="s">
+        <v>188</v>
+      </c>
+      <c r="F497">
+        <v>6</v>
+      </c>
+      <c r="G497" s="2" t="s">
+        <v>1097</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G484" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$484</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$497</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3336,7 +3336,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3347,6 +3347,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3819,16 +3825,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3837,122 +3840,126 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -15683,12 +15690,12 @@
       <c r="F497">
         <v>6</v>
       </c>
-      <c r="G497" s="2" t="s">
+      <c r="G497" s="3" t="s">
         <v>1097</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G484" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G497" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -4305,7 +4305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G497"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
@@ -4337,7 +4337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" hidden="1" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" hidden="1" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" hidden="1" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" hidden="1" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" hidden="1" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" hidden="1" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" hidden="1" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" hidden="1" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" hidden="1" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" hidden="1" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" hidden="1" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" hidden="1" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" hidden="1" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" hidden="1" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" hidden="1" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" hidden="1" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" hidden="1" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" hidden="1" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" hidden="1" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" hidden="1" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" hidden="1" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" hidden="1" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" hidden="1" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" hidden="1" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" hidden="1" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" hidden="1" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" hidden="1" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" hidden="1" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" hidden="1" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" hidden="1" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" hidden="1" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" hidden="1" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" hidden="1" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" hidden="1" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" hidden="1" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" hidden="1" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" hidden="1" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" hidden="1" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" hidden="1" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" hidden="1" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" hidden="1" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" hidden="1" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" hidden="1" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" hidden="1" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" hidden="1" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" hidden="1" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" hidden="1" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" hidden="1" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" hidden="1" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" hidden="1" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" hidden="1" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" hidden="1" spans="1:7">
       <c r="A317">
         <v>316</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" hidden="1" spans="1:7">
       <c r="A318">
         <v>317</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" hidden="1" spans="1:7">
       <c r="A319">
         <v>318</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" hidden="1" spans="1:7">
       <c r="A320">
         <v>319</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" hidden="1" spans="1:7">
       <c r="A321">
         <v>320</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" hidden="1" spans="1:7">
       <c r="A322">
         <v>321</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" hidden="1" spans="1:7">
       <c r="A323">
         <v>322</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" hidden="1" spans="1:7">
       <c r="A324">
         <v>323</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" hidden="1" spans="1:7">
       <c r="A325">
         <v>324</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" hidden="1" spans="1:7">
       <c r="A326">
         <v>325</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" hidden="1" spans="1:7">
       <c r="A327">
         <v>326</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" hidden="1" spans="1:7">
       <c r="A328">
         <v>327</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" hidden="1" spans="1:7">
       <c r="A329">
         <v>328</v>
       </c>
@@ -11881,7 +11881,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" hidden="1" spans="1:7">
       <c r="A330">
         <v>329</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331">
         <v>330</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332">
         <v>331</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333">
         <v>332</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" hidden="1" spans="1:7">
       <c r="A334">
         <v>333</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" hidden="1" spans="1:7">
       <c r="A335">
         <v>334</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" hidden="1" spans="1:7">
       <c r="A336">
         <v>335</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" hidden="1" spans="1:7">
       <c r="A337">
         <v>336</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338">
         <v>337</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339">
         <v>338</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340">
         <v>339</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" hidden="1" spans="1:7">
       <c r="A341">
         <v>340</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" hidden="1" spans="1:7">
       <c r="A342">
         <v>341</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" hidden="1" spans="1:7">
       <c r="A343">
         <v>342</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" hidden="1" spans="1:7">
       <c r="A344">
         <v>343</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" hidden="1" spans="1:7">
       <c r="A345">
         <v>344</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" hidden="1" spans="1:7">
       <c r="A347">
         <v>346</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" hidden="1" spans="1:7">
       <c r="A348">
         <v>347</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349">
         <v>348</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" hidden="1" spans="1:7">
       <c r="A350">
         <v>349</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" hidden="1" spans="1:7">
       <c r="A351">
         <v>350</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" hidden="1" spans="1:7">
       <c r="A352">
         <v>351</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" hidden="1" spans="1:7">
       <c r="A353">
         <v>352</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" hidden="1" spans="1:7">
       <c r="A354">
         <v>353</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" hidden="1" spans="1:7">
       <c r="A355">
         <v>354</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" hidden="1" spans="1:7">
       <c r="A356">
         <v>355</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357">
         <v>356</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358">
         <v>357</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359">
         <v>358</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360">
         <v>359</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361">
         <v>360</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362">
         <v>361</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363">
         <v>362</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364">
         <v>363</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365">
         <v>364</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366">
         <v>365</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367">
         <v>366</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368">
         <v>367</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369">
         <v>368</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370">
         <v>369</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371">
         <v>370</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372">
         <v>371</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373">
         <v>372</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" hidden="1" spans="1:7">
       <c r="A374">
         <v>373</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" hidden="1" spans="1:7">
       <c r="A375">
         <v>374</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" hidden="1" spans="1:7">
       <c r="A376">
         <v>375</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" hidden="1" spans="1:7">
       <c r="A377">
         <v>376</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" hidden="1" spans="1:7">
       <c r="A378">
         <v>377</v>
       </c>
@@ -13008,7 +13008,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" hidden="1" spans="1:7">
       <c r="A379">
         <v>378</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380">
         <v>379</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" hidden="1" spans="1:7">
       <c r="A381">
         <v>380</v>
       </c>
@@ -13077,7 +13077,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382">
         <v>381</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383">
         <v>382</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384">
         <v>383</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385">
         <v>384</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386">
         <v>385</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387">
         <v>386</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388">
         <v>387</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389">
         <v>388</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390">
         <v>389</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391">
         <v>390</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392">
         <v>391</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393">
         <v>392</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394">
         <v>393</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395">
         <v>394</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396">
         <v>395</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" hidden="1" spans="1:7">
       <c r="A397">
         <v>396</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398">
         <v>397</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" hidden="1" spans="1:7">
       <c r="A399">
         <v>398</v>
       </c>
@@ -13491,7 +13491,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400">
         <v>399</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401">
         <v>400</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402">
         <v>401</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403">
         <v>402</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" hidden="1" spans="1:7">
       <c r="A404">
         <v>403</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405">
         <v>404</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406">
         <v>405</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" hidden="1" spans="1:7">
       <c r="A407">
         <v>406</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" hidden="1" spans="1:7">
       <c r="A408">
         <v>407</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409">
         <v>408</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410">
         <v>409</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411">
         <v>410</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412">
         <v>411</v>
       </c>
@@ -13790,7 +13790,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413">
         <v>412</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414">
         <v>413</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415">
         <v>414</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416">
         <v>415</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417">
         <v>416</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418">
         <v>417</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419">
         <v>418</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420">
         <v>419</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421">
         <v>420</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422">
         <v>421</v>
       </c>
@@ -14020,7 +14020,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423">
         <v>422</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424">
         <v>423</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425">
         <v>424</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426">
         <v>425</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427">
         <v>426</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428">
         <v>427</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" hidden="1" spans="1:7">
       <c r="A429">
         <v>428</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430">
         <v>429</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431">
         <v>430</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432">
         <v>431</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433">
         <v>432</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434">
         <v>433</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435">
         <v>434</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436">
         <v>435</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437">
         <v>436</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438">
         <v>437</v>
       </c>
@@ -14388,7 +14388,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439">
         <v>438</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440">
         <v>439</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441">
         <v>440</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442">
         <v>441</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" hidden="1" spans="1:7">
       <c r="A443">
         <v>442</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444">
         <v>443</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445">
         <v>444</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446">
         <v>445</v>
       </c>
@@ -14572,7 +14572,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447">
         <v>446</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448">
         <v>447</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449">
         <v>448</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450">
         <v>449</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451">
         <v>450</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" hidden="1" spans="1:7">
       <c r="A452">
         <v>451</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" hidden="1" spans="1:7">
       <c r="A457">
         <v>456</v>
       </c>
@@ -14986,7 +14986,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465">
         <v>464</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" hidden="1" spans="1:7">
       <c r="A466">
         <v>465</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" hidden="1" spans="1:7">
       <c r="A483">
         <v>482</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="485" ht="15" spans="1:7">
+    <row r="485" ht="15" hidden="1" spans="1:7">
       <c r="A485">
         <v>484</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="486" ht="15" spans="1:7">
+    <row r="486" ht="15" hidden="1" spans="1:7">
       <c r="A486">
         <v>485</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="487" ht="15" spans="1:7">
+    <row r="487" ht="15" hidden="1" spans="1:7">
       <c r="A487">
         <v>486</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="488" ht="15" spans="1:7">
+    <row r="488" ht="15" hidden="1" spans="1:7">
       <c r="A488">
         <v>487</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="489" ht="15" spans="1:7">
+    <row r="489" ht="15" hidden="1" spans="1:7">
       <c r="A489">
         <v>488</v>
       </c>
@@ -15541,7 +15541,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="490" ht="15" spans="1:7">
+    <row r="490" ht="15" hidden="1" spans="1:7">
       <c r="A490">
         <v>489</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="491" ht="15" spans="1:7">
+    <row r="491" ht="15" hidden="1" spans="1:7">
       <c r="A491">
         <v>490</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="492" ht="15" spans="1:7">
+    <row r="492" ht="15" hidden="1" spans="1:7">
       <c r="A492">
         <v>491</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="493" ht="15" spans="1:7">
+    <row r="493" ht="15" hidden="1" spans="1:7">
       <c r="A493">
         <v>492</v>
       </c>
@@ -15617,7 +15617,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="494" ht="15" spans="1:7">
+    <row r="494" ht="15" hidden="1" spans="1:7">
       <c r="A494">
         <v>493</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="495" ht="15" spans="1:7">
+    <row r="495" ht="15" hidden="1" spans="1:7">
       <c r="A495">
         <v>494</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="496" ht="15" spans="1:7">
+    <row r="496" ht="15" hidden="1" spans="1:7">
       <c r="A496">
         <v>495</v>
       </c>
@@ -15696,6 +15696,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G497" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="剧本杀"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2699" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1100">
   <si>
     <t>id</t>
   </si>
@@ -3324,6 +3324,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/aae6cb9bfe41</t>
+  </si>
+  <si>
+    <t>江湖夜雨十年灯</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/13554a561c72</t>
   </si>
 </sst>
 </file>
@@ -3345,6 +3351,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -3361,14 +3375,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3825,7 +3831,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3955,11 +3961,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4305,8 +4313,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G497"/>
+  <sheetPr/>
+  <dimension ref="A1:G498"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -4337,7 +4345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4360,7 +4368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4383,7 +4391,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:7">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4406,7 +4414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4429,7 +4437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:7">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4452,7 +4460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:7">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4475,7 +4483,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4498,7 +4506,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4521,7 +4529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4544,7 +4552,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:7">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4567,7 +4575,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4590,7 +4598,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4613,7 +4621,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:7">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4636,7 +4644,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:7">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4659,7 +4667,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:7">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4682,7 +4690,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4705,7 +4713,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4728,7 +4736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:7">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4751,7 +4759,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:7">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4774,7 +4782,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:7">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4797,7 +4805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4820,7 +4828,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4843,7 +4851,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:7">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4866,7 +4874,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:7">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4889,7 +4897,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4912,7 +4920,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:7">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4935,7 +4943,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4958,7 +4966,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:7">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4981,7 +4989,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5004,7 +5012,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:7">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5027,7 +5035,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:7">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5050,7 +5058,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:7">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5073,7 +5081,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:7">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5096,7 +5104,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:7">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5119,7 +5127,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:7">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5142,7 +5150,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:7">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5165,7 +5173,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:7">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5188,7 +5196,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:7">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5211,7 +5219,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:7">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5234,7 +5242,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:7">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5257,7 +5265,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:7">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5280,7 +5288,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:7">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5303,7 +5311,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:7">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5326,7 +5334,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:7">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5349,7 +5357,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:7">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5372,7 +5380,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:7">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5395,7 +5403,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:7">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5418,7 +5426,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:7">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5441,7 +5449,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:7">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5464,7 +5472,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:7">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5487,7 +5495,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:7">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5510,7 +5518,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:7">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5533,7 +5541,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:7">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5556,7 +5564,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:7">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5579,7 +5587,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5602,7 +5610,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:7">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5625,7 +5633,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5648,7 +5656,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:7">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5671,7 +5679,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:7">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5717,7 +5725,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:7">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5740,7 +5748,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:7">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5763,7 +5771,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:7">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5786,7 +5794,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:7">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5809,7 +5817,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:7">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5832,7 +5840,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:7">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5855,7 +5863,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:7">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5878,7 +5886,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:7">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5901,7 +5909,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:7">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5924,7 +5932,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:7">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5943,11 +5951,11 @@
       <c r="F71" t="s">
         <v>8</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:7">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5970,7 +5978,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:7">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5993,7 +6001,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:7">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6016,7 +6024,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:7">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6035,11 +6043,11 @@
       <c r="F75" t="s">
         <v>8</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:7">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6062,7 +6070,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:7">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6085,7 +6093,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:7">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6108,7 +6116,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:7">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6131,7 +6139,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:7">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6154,7 +6162,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:7">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6200,7 +6208,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:7">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6223,7 +6231,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:7">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6246,7 +6254,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:7">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6269,7 +6277,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:7">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6384,7 +6392,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:7">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9880,7 +9888,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="243" hidden="1" spans="1:7">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -9903,7 +9911,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:7">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11582,7 +11590,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:7">
+    <row r="317" spans="1:7">
       <c r="A317">
         <v>316</v>
       </c>
@@ -11605,7 +11613,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:7">
+    <row r="318" spans="1:7">
       <c r="A318">
         <v>317</v>
       </c>
@@ -11628,7 +11636,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:7">
+    <row r="319" spans="1:7">
       <c r="A319">
         <v>318</v>
       </c>
@@ -11651,7 +11659,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:7">
+    <row r="320" spans="1:7">
       <c r="A320">
         <v>319</v>
       </c>
@@ -11674,7 +11682,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:7">
+    <row r="321" spans="1:7">
       <c r="A321">
         <v>320</v>
       </c>
@@ -11697,7 +11705,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:7">
+    <row r="322" spans="1:7">
       <c r="A322">
         <v>321</v>
       </c>
@@ -11720,7 +11728,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:7">
+    <row r="323" spans="1:7">
       <c r="A323">
         <v>322</v>
       </c>
@@ -11743,7 +11751,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:7">
+    <row r="324" spans="1:7">
       <c r="A324">
         <v>323</v>
       </c>
@@ -11766,7 +11774,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:7">
+    <row r="325" spans="1:7">
       <c r="A325">
         <v>324</v>
       </c>
@@ -11789,7 +11797,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:7">
+    <row r="326" spans="1:7">
       <c r="A326">
         <v>325</v>
       </c>
@@ -11812,7 +11820,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:7">
+    <row r="327" spans="1:7">
       <c r="A327">
         <v>326</v>
       </c>
@@ -11835,7 +11843,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:7">
+    <row r="328" spans="1:7">
       <c r="A328">
         <v>327</v>
       </c>
@@ -11858,7 +11866,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:7">
+    <row r="329" spans="1:7">
       <c r="A329">
         <v>328</v>
       </c>
@@ -11881,7 +11889,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:7">
+    <row r="330" spans="1:7">
       <c r="A330">
         <v>329</v>
       </c>
@@ -11904,7 +11912,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:7">
+    <row r="331" spans="1:7">
       <c r="A331">
         <v>330</v>
       </c>
@@ -11927,7 +11935,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:7">
+    <row r="332" spans="1:7">
       <c r="A332">
         <v>331</v>
       </c>
@@ -11950,7 +11958,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:7">
+    <row r="333" spans="1:7">
       <c r="A333">
         <v>332</v>
       </c>
@@ -11973,7 +11981,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:7">
+    <row r="334" spans="1:7">
       <c r="A334">
         <v>333</v>
       </c>
@@ -11996,7 +12004,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:7">
+    <row r="335" spans="1:7">
       <c r="A335">
         <v>334</v>
       </c>
@@ -12019,7 +12027,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:7">
+    <row r="336" spans="1:7">
       <c r="A336">
         <v>335</v>
       </c>
@@ -12042,7 +12050,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:7">
+    <row r="337" spans="1:7">
       <c r="A337">
         <v>336</v>
       </c>
@@ -12065,7 +12073,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:7">
+    <row r="338" spans="1:7">
       <c r="A338">
         <v>337</v>
       </c>
@@ -12088,7 +12096,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="339" hidden="1" spans="1:7">
+    <row r="339" spans="1:7">
       <c r="A339">
         <v>338</v>
       </c>
@@ -12111,7 +12119,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="340" hidden="1" spans="1:7">
+    <row r="340" spans="1:7">
       <c r="A340">
         <v>339</v>
       </c>
@@ -12134,7 +12142,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:7">
+    <row r="341" spans="1:7">
       <c r="A341">
         <v>340</v>
       </c>
@@ -12157,7 +12165,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:7">
+    <row r="342" spans="1:7">
       <c r="A342">
         <v>341</v>
       </c>
@@ -12180,7 +12188,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:7">
+    <row r="343" spans="1:7">
       <c r="A343">
         <v>342</v>
       </c>
@@ -12203,7 +12211,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:7">
+    <row r="344" spans="1:7">
       <c r="A344">
         <v>343</v>
       </c>
@@ -12226,7 +12234,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:7">
+    <row r="345" spans="1:7">
       <c r="A345">
         <v>344</v>
       </c>
@@ -12272,7 +12280,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:7">
+    <row r="347" spans="1:7">
       <c r="A347">
         <v>346</v>
       </c>
@@ -12295,7 +12303,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:7">
+    <row r="348" spans="1:7">
       <c r="A348">
         <v>347</v>
       </c>
@@ -12318,7 +12326,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:7">
+    <row r="349" spans="1:7">
       <c r="A349">
         <v>348</v>
       </c>
@@ -12341,7 +12349,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:7">
+    <row r="350" spans="1:7">
       <c r="A350">
         <v>349</v>
       </c>
@@ -12364,7 +12372,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:7">
+    <row r="351" spans="1:7">
       <c r="A351">
         <v>350</v>
       </c>
@@ -12387,7 +12395,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:7">
+    <row r="352" spans="1:7">
       <c r="A352">
         <v>351</v>
       </c>
@@ -12410,7 +12418,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:7">
+    <row r="353" spans="1:7">
       <c r="A353">
         <v>352</v>
       </c>
@@ -12433,7 +12441,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:7">
+    <row r="354" spans="1:7">
       <c r="A354">
         <v>353</v>
       </c>
@@ -12456,7 +12464,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:7">
+    <row r="355" spans="1:7">
       <c r="A355">
         <v>354</v>
       </c>
@@ -12479,7 +12487,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:7">
+    <row r="356" spans="1:7">
       <c r="A356">
         <v>355</v>
       </c>
@@ -12502,7 +12510,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:7">
+    <row r="357" spans="1:7">
       <c r="A357">
         <v>356</v>
       </c>
@@ -12525,7 +12533,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:7">
+    <row r="358" spans="1:7">
       <c r="A358">
         <v>357</v>
       </c>
@@ -12548,7 +12556,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:7">
+    <row r="359" spans="1:7">
       <c r="A359">
         <v>358</v>
       </c>
@@ -12571,7 +12579,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:7">
+    <row r="360" spans="1:7">
       <c r="A360">
         <v>359</v>
       </c>
@@ -12594,7 +12602,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:7">
+    <row r="361" spans="1:7">
       <c r="A361">
         <v>360</v>
       </c>
@@ -12617,7 +12625,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:7">
+    <row r="362" spans="1:7">
       <c r="A362">
         <v>361</v>
       </c>
@@ -12640,7 +12648,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:7">
+    <row r="363" spans="1:7">
       <c r="A363">
         <v>362</v>
       </c>
@@ -12663,7 +12671,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:7">
+    <row r="364" spans="1:7">
       <c r="A364">
         <v>363</v>
       </c>
@@ -12686,7 +12694,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:7">
+    <row r="365" spans="1:7">
       <c r="A365">
         <v>364</v>
       </c>
@@ -12709,7 +12717,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:7">
+    <row r="366" spans="1:7">
       <c r="A366">
         <v>365</v>
       </c>
@@ -12732,7 +12740,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:7">
+    <row r="367" spans="1:7">
       <c r="A367">
         <v>366</v>
       </c>
@@ -12755,7 +12763,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:7">
+    <row r="368" spans="1:7">
       <c r="A368">
         <v>367</v>
       </c>
@@ -12778,7 +12786,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:7">
+    <row r="369" spans="1:7">
       <c r="A369">
         <v>368</v>
       </c>
@@ -12801,7 +12809,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370">
         <v>369</v>
       </c>
@@ -12824,7 +12832,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:7">
+    <row r="371" spans="1:7">
       <c r="A371">
         <v>370</v>
       </c>
@@ -12847,7 +12855,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:7">
+    <row r="372" spans="1:7">
       <c r="A372">
         <v>371</v>
       </c>
@@ -12870,7 +12878,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:7">
+    <row r="373" spans="1:7">
       <c r="A373">
         <v>372</v>
       </c>
@@ -12893,7 +12901,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:7">
+    <row r="374" spans="1:7">
       <c r="A374">
         <v>373</v>
       </c>
@@ -12916,7 +12924,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:7">
+    <row r="375" spans="1:7">
       <c r="A375">
         <v>374</v>
       </c>
@@ -12939,7 +12947,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:7">
+    <row r="376" spans="1:7">
       <c r="A376">
         <v>375</v>
       </c>
@@ -12962,7 +12970,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:7">
+    <row r="377" spans="1:7">
       <c r="A377">
         <v>376</v>
       </c>
@@ -12985,7 +12993,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:7">
+    <row r="378" spans="1:7">
       <c r="A378">
         <v>377</v>
       </c>
@@ -13008,7 +13016,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:7">
+    <row r="379" spans="1:7">
       <c r="A379">
         <v>378</v>
       </c>
@@ -13031,7 +13039,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:7">
+    <row r="380" spans="1:7">
       <c r="A380">
         <v>379</v>
       </c>
@@ -13054,7 +13062,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:7">
+    <row r="381" spans="1:7">
       <c r="A381">
         <v>380</v>
       </c>
@@ -13077,7 +13085,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:7">
+    <row r="382" spans="1:7">
       <c r="A382">
         <v>381</v>
       </c>
@@ -13100,7 +13108,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:7">
+    <row r="383" spans="1:7">
       <c r="A383">
         <v>382</v>
       </c>
@@ -13123,7 +13131,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384">
         <v>383</v>
       </c>
@@ -13146,7 +13154,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:7">
+    <row r="385" spans="1:7">
       <c r="A385">
         <v>384</v>
       </c>
@@ -13169,7 +13177,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:7">
+    <row r="386" spans="1:7">
       <c r="A386">
         <v>385</v>
       </c>
@@ -13192,7 +13200,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:7">
+    <row r="387" spans="1:7">
       <c r="A387">
         <v>386</v>
       </c>
@@ -13215,7 +13223,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:7">
+    <row r="388" spans="1:7">
       <c r="A388">
         <v>387</v>
       </c>
@@ -13238,7 +13246,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:7">
+    <row r="389" spans="1:7">
       <c r="A389">
         <v>388</v>
       </c>
@@ -13261,7 +13269,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390">
         <v>389</v>
       </c>
@@ -13284,7 +13292,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:7">
+    <row r="391" spans="1:7">
       <c r="A391">
         <v>390</v>
       </c>
@@ -13307,7 +13315,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:7">
+    <row r="392" spans="1:7">
       <c r="A392">
         <v>391</v>
       </c>
@@ -13330,7 +13338,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:7">
+    <row r="393" spans="1:7">
       <c r="A393">
         <v>392</v>
       </c>
@@ -13353,7 +13361,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:7">
+    <row r="394" spans="1:7">
       <c r="A394">
         <v>393</v>
       </c>
@@ -13376,7 +13384,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:7">
+    <row r="395" spans="1:7">
       <c r="A395">
         <v>394</v>
       </c>
@@ -13399,7 +13407,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:7">
+    <row r="396" spans="1:7">
       <c r="A396">
         <v>395</v>
       </c>
@@ -13422,7 +13430,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:7">
+    <row r="397" spans="1:7">
       <c r="A397">
         <v>396</v>
       </c>
@@ -13445,7 +13453,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:7">
+    <row r="398" spans="1:7">
       <c r="A398">
         <v>397</v>
       </c>
@@ -13468,7 +13476,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:7">
+    <row r="399" spans="1:7">
       <c r="A399">
         <v>398</v>
       </c>
@@ -13491,7 +13499,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:7">
+    <row r="400" spans="1:7">
       <c r="A400">
         <v>399</v>
       </c>
@@ -13514,7 +13522,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:7">
+    <row r="401" spans="1:7">
       <c r="A401">
         <v>400</v>
       </c>
@@ -13537,7 +13545,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:7">
+    <row r="402" spans="1:7">
       <c r="A402">
         <v>401</v>
       </c>
@@ -13560,7 +13568,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:7">
+    <row r="403" spans="1:7">
       <c r="A403">
         <v>402</v>
       </c>
@@ -13583,7 +13591,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:7">
+    <row r="404" spans="1:7">
       <c r="A404">
         <v>403</v>
       </c>
@@ -13606,7 +13614,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:7">
+    <row r="405" spans="1:7">
       <c r="A405">
         <v>404</v>
       </c>
@@ -13629,7 +13637,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:7">
+    <row r="406" spans="1:7">
       <c r="A406">
         <v>405</v>
       </c>
@@ -13652,7 +13660,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:7">
+    <row r="407" spans="1:7">
       <c r="A407">
         <v>406</v>
       </c>
@@ -13675,7 +13683,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:7">
+    <row r="408" spans="1:7">
       <c r="A408">
         <v>407</v>
       </c>
@@ -13698,7 +13706,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:7">
+    <row r="409" spans="1:7">
       <c r="A409">
         <v>408</v>
       </c>
@@ -13721,7 +13729,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:7">
+    <row r="410" spans="1:7">
       <c r="A410">
         <v>409</v>
       </c>
@@ -13744,7 +13752,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:7">
+    <row r="411" spans="1:7">
       <c r="A411">
         <v>410</v>
       </c>
@@ -13767,7 +13775,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:7">
+    <row r="412" spans="1:7">
       <c r="A412">
         <v>411</v>
       </c>
@@ -13790,7 +13798,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:7">
+    <row r="413" spans="1:7">
       <c r="A413">
         <v>412</v>
       </c>
@@ -13813,7 +13821,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:7">
+    <row r="414" spans="1:7">
       <c r="A414">
         <v>413</v>
       </c>
@@ -13836,7 +13844,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:7">
+    <row r="415" spans="1:7">
       <c r="A415">
         <v>414</v>
       </c>
@@ -13859,7 +13867,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:7">
+    <row r="416" spans="1:7">
       <c r="A416">
         <v>415</v>
       </c>
@@ -13882,7 +13890,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:7">
+    <row r="417" spans="1:7">
       <c r="A417">
         <v>416</v>
       </c>
@@ -13905,7 +13913,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:7">
+    <row r="418" spans="1:7">
       <c r="A418">
         <v>417</v>
       </c>
@@ -13928,7 +13936,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:7">
+    <row r="419" spans="1:7">
       <c r="A419">
         <v>418</v>
       </c>
@@ -13951,7 +13959,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:7">
+    <row r="420" spans="1:7">
       <c r="A420">
         <v>419</v>
       </c>
@@ -13974,7 +13982,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:7">
+    <row r="421" spans="1:7">
       <c r="A421">
         <v>420</v>
       </c>
@@ -13997,7 +14005,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:7">
+    <row r="422" spans="1:7">
       <c r="A422">
         <v>421</v>
       </c>
@@ -14020,7 +14028,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:7">
+    <row r="423" spans="1:7">
       <c r="A423">
         <v>422</v>
       </c>
@@ -14043,7 +14051,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:7">
+    <row r="424" spans="1:7">
       <c r="A424">
         <v>423</v>
       </c>
@@ -14066,7 +14074,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:7">
+    <row r="425" spans="1:7">
       <c r="A425">
         <v>424</v>
       </c>
@@ -14089,7 +14097,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:7">
+    <row r="426" spans="1:7">
       <c r="A426">
         <v>425</v>
       </c>
@@ -14112,7 +14120,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:7">
+    <row r="427" spans="1:7">
       <c r="A427">
         <v>426</v>
       </c>
@@ -14135,7 +14143,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:7">
+    <row r="428" spans="1:7">
       <c r="A428">
         <v>427</v>
       </c>
@@ -14158,7 +14166,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:7">
+    <row r="429" spans="1:7">
       <c r="A429">
         <v>428</v>
       </c>
@@ -14181,7 +14189,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430">
         <v>429</v>
       </c>
@@ -14204,7 +14212,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:7">
+    <row r="431" spans="1:7">
       <c r="A431">
         <v>430</v>
       </c>
@@ -14227,7 +14235,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:7">
+    <row r="432" spans="1:7">
       <c r="A432">
         <v>431</v>
       </c>
@@ -14250,7 +14258,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:7">
+    <row r="433" spans="1:7">
       <c r="A433">
         <v>432</v>
       </c>
@@ -14273,7 +14281,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:7">
+    <row r="434" spans="1:7">
       <c r="A434">
         <v>433</v>
       </c>
@@ -14296,7 +14304,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:7">
+    <row r="435" spans="1:7">
       <c r="A435">
         <v>434</v>
       </c>
@@ -14319,7 +14327,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:7">
+    <row r="436" spans="1:7">
       <c r="A436">
         <v>435</v>
       </c>
@@ -14342,7 +14350,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:7">
+    <row r="437" spans="1:7">
       <c r="A437">
         <v>436</v>
       </c>
@@ -14365,7 +14373,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:7">
+    <row r="438" spans="1:7">
       <c r="A438">
         <v>437</v>
       </c>
@@ -14388,7 +14396,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439">
         <v>438</v>
       </c>
@@ -14411,7 +14419,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:7">
+    <row r="440" spans="1:7">
       <c r="A440">
         <v>439</v>
       </c>
@@ -14434,7 +14442,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:7">
+    <row r="441" spans="1:7">
       <c r="A441">
         <v>440</v>
       </c>
@@ -14457,7 +14465,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:7">
+    <row r="442" spans="1:7">
       <c r="A442">
         <v>441</v>
       </c>
@@ -14480,7 +14488,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="443" hidden="1" spans="1:7">
+    <row r="443" spans="1:7">
       <c r="A443">
         <v>442</v>
       </c>
@@ -14503,7 +14511,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="444" hidden="1" spans="1:7">
+    <row r="444" spans="1:7">
       <c r="A444">
         <v>443</v>
       </c>
@@ -14526,7 +14534,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:7">
+    <row r="445" spans="1:7">
       <c r="A445">
         <v>444</v>
       </c>
@@ -14549,7 +14557,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446">
         <v>445</v>
       </c>
@@ -14572,7 +14580,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:7">
+    <row r="447" spans="1:7">
       <c r="A447">
         <v>446</v>
       </c>
@@ -14595,7 +14603,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448">
         <v>447</v>
       </c>
@@ -14618,7 +14626,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449">
         <v>448</v>
       </c>
@@ -14641,7 +14649,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:7">
+    <row r="450" spans="1:7">
       <c r="A450">
         <v>449</v>
       </c>
@@ -14664,7 +14672,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:7">
+    <row r="451" spans="1:7">
       <c r="A451">
         <v>450</v>
       </c>
@@ -14687,7 +14695,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="452" hidden="1" spans="1:7">
+    <row r="452" spans="1:7">
       <c r="A452">
         <v>451</v>
       </c>
@@ -14802,7 +14810,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:7">
+    <row r="457" spans="1:7">
       <c r="A457">
         <v>456</v>
       </c>
@@ -14986,7 +14994,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:7">
+    <row r="465" spans="1:7">
       <c r="A465">
         <v>464</v>
       </c>
@@ -15009,7 +15017,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:7">
+    <row r="466" spans="1:7">
       <c r="A466">
         <v>465</v>
       </c>
@@ -15400,7 +15408,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="483" hidden="1" spans="1:7">
+    <row r="483" spans="1:7">
       <c r="A483">
         <v>482</v>
       </c>
@@ -15446,231 +15454,231 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="485" ht="15" hidden="1" spans="1:7">
+    <row r="485" ht="15" spans="1:7">
       <c r="A485">
         <v>484</v>
       </c>
-      <c r="B485" s="1" t="s">
+      <c r="B485" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="C485" s="1"/>
-      <c r="D485" s="1" t="s">
+      <c r="C485" s="2"/>
+      <c r="D485" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E485" s="1" t="s">
+      <c r="E485" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F485" s="1"/>
-      <c r="G485" s="1" t="s">
+      <c r="F485" s="2"/>
+      <c r="G485" s="2" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="486" ht="15" hidden="1" spans="1:7">
+    <row r="486" ht="15" spans="1:7">
       <c r="A486">
         <v>485</v>
       </c>
-      <c r="B486" s="1" t="s">
+      <c r="B486" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="C486" s="1"/>
-      <c r="D486" s="1" t="s">
+      <c r="C486" s="2"/>
+      <c r="D486" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E486" s="1" t="s">
+      <c r="E486" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F486" s="1"/>
-      <c r="G486" s="1" t="s">
+      <c r="F486" s="2"/>
+      <c r="G486" s="2" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="487" ht="15" hidden="1" spans="1:7">
+    <row r="487" ht="15" spans="1:7">
       <c r="A487">
         <v>486</v>
       </c>
-      <c r="B487" s="1" t="s">
+      <c r="B487" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="C487" s="1"/>
-      <c r="D487" s="1" t="s">
+      <c r="C487" s="2"/>
+      <c r="D487" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E487" s="1" t="s">
+      <c r="E487" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F487" s="1"/>
-      <c r="G487" s="1" t="s">
+      <c r="F487" s="2"/>
+      <c r="G487" s="2" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="488" ht="15" hidden="1" spans="1:7">
+    <row r="488" ht="15" spans="1:7">
       <c r="A488">
         <v>487</v>
       </c>
-      <c r="B488" s="1" t="s">
+      <c r="B488" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="C488" s="1"/>
-      <c r="D488" s="1" t="s">
+      <c r="C488" s="2"/>
+      <c r="D488" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E488" s="1" t="s">
+      <c r="E488" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F488" s="1"/>
-      <c r="G488" s="1" t="s">
+      <c r="F488" s="2"/>
+      <c r="G488" s="2" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="489" ht="15" hidden="1" spans="1:7">
+    <row r="489" ht="15" spans="1:7">
       <c r="A489">
         <v>488</v>
       </c>
-      <c r="B489" s="1" t="s">
+      <c r="B489" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="C489" s="1"/>
-      <c r="D489" s="1" t="s">
+      <c r="C489" s="2"/>
+      <c r="D489" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E489" s="1" t="s">
+      <c r="E489" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F489" s="1"/>
-      <c r="G489" s="1" t="s">
+      <c r="F489" s="2"/>
+      <c r="G489" s="2" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="490" ht="15" hidden="1" spans="1:7">
+    <row r="490" ht="15" spans="1:7">
       <c r="A490">
         <v>489</v>
       </c>
-      <c r="B490" s="1" t="s">
+      <c r="B490" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="C490" s="1"/>
-      <c r="D490" s="1" t="s">
+      <c r="C490" s="2"/>
+      <c r="D490" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E490" s="1" t="s">
+      <c r="E490" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F490" s="1"/>
-      <c r="G490" s="1" t="s">
+      <c r="F490" s="2"/>
+      <c r="G490" s="2" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="491" ht="15" hidden="1" spans="1:7">
+    <row r="491" ht="15" spans="1:7">
       <c r="A491">
         <v>490</v>
       </c>
-      <c r="B491" s="1" t="s">
+      <c r="B491" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="C491" s="1"/>
-      <c r="D491" s="1" t="s">
+      <c r="C491" s="2"/>
+      <c r="D491" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E491" s="1" t="s">
+      <c r="E491" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F491" s="1"/>
-      <c r="G491" s="1" t="s">
+      <c r="F491" s="2"/>
+      <c r="G491" s="2" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="492" ht="15" hidden="1" spans="1:7">
+    <row r="492" ht="15" spans="1:7">
       <c r="A492">
         <v>491</v>
       </c>
-      <c r="B492" s="1" t="s">
+      <c r="B492" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="C492" s="1"/>
-      <c r="D492" s="1" t="s">
+      <c r="C492" s="2"/>
+      <c r="D492" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E492" s="1" t="s">
+      <c r="E492" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F492" s="1"/>
-      <c r="G492" s="1" t="s">
+      <c r="F492" s="2"/>
+      <c r="G492" s="2" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="493" ht="15" hidden="1" spans="1:7">
+    <row r="493" ht="15" spans="1:7">
       <c r="A493">
         <v>492</v>
       </c>
-      <c r="B493" s="1" t="s">
+      <c r="B493" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="C493" s="1"/>
-      <c r="D493" s="1" t="s">
+      <c r="C493" s="2"/>
+      <c r="D493" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E493" s="1" t="s">
+      <c r="E493" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F493" s="1"/>
-      <c r="G493" s="1" t="s">
+      <c r="F493" s="2"/>
+      <c r="G493" s="2" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="494" ht="15" hidden="1" spans="1:7">
+    <row r="494" ht="15" spans="1:7">
       <c r="A494">
         <v>493</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="B494" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="C494" s="1"/>
-      <c r="D494" s="1" t="s">
+      <c r="C494" s="2"/>
+      <c r="D494" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E494" s="1" t="s">
+      <c r="E494" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F494" s="1"/>
-      <c r="G494" s="1" t="s">
+      <c r="F494" s="2"/>
+      <c r="G494" s="2" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="495" ht="15" hidden="1" spans="1:7">
+    <row r="495" ht="15" spans="1:7">
       <c r="A495">
         <v>494</v>
       </c>
-      <c r="B495" s="1" t="s">
+      <c r="B495" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="C495" s="1"/>
-      <c r="D495" s="1" t="s">
+      <c r="C495" s="2"/>
+      <c r="D495" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E495" s="1" t="s">
+      <c r="E495" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F495" s="1"/>
-      <c r="G495" s="1" t="s">
+      <c r="F495" s="2"/>
+      <c r="G495" s="2" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="496" ht="15" hidden="1" spans="1:7">
+    <row r="496" ht="15" spans="1:7">
       <c r="A496">
         <v>495</v>
       </c>
-      <c r="B496" s="1" t="s">
+      <c r="B496" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="C496" s="1"/>
-      <c r="D496" s="1" t="s">
+      <c r="C496" s="2"/>
+      <c r="D496" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E496" s="1" t="s">
+      <c r="E496" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F496" s="1"/>
-      <c r="G496" s="1" t="s">
+      <c r="F496" s="2"/>
+      <c r="G496" s="2" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -15678,7 +15686,7 @@
       <c r="A497">
         <v>496</v>
       </c>
-      <c r="B497" s="2" t="s">
+      <c r="B497" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="D497" t="s">
@@ -15690,19 +15698,39 @@
       <c r="F497">
         <v>6</v>
       </c>
-      <c r="G497" s="3" t="s">
+      <c r="G497" s="4" t="s">
         <v>1097</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7">
+      <c r="A498">
+        <v>497</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D498" t="s">
+        <v>188</v>
+      </c>
+      <c r="E498" t="s">
+        <v>188</v>
+      </c>
+      <c r="F498">
+        <v>6</v>
+      </c>
+      <c r="G498" s="5" t="s">
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G497" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="剧本杀"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="G71" r:id="rId1" display="https://pan.quark.cn/s/54ae4c79b6ef"/>
+    <hyperlink ref="G75" r:id="rId2" display="https://pan.quark.cn/s/32466a4d8102"/>
+    <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1102">
   <si>
     <t>id</t>
   </si>
@@ -3330,6 +3330,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/13554a561c72</t>
+  </si>
+  <si>
+    <t>酒大奇迹</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c16bc0af552e</t>
   </si>
 </sst>
 </file>
@@ -4314,7 +4320,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G498"/>
+  <dimension ref="A1:G499"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15720,6 +15726,26 @@
       </c>
       <c r="G498" s="5" t="s">
         <v>1099</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7">
+      <c r="A499">
+        <v>498</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D499" t="s">
+        <v>188</v>
+      </c>
+      <c r="E499" t="s">
+        <v>188</v>
+      </c>
+      <c r="F499">
+        <v>7</v>
+      </c>
+      <c r="G499" t="s">
+        <v>1101</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$497</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$499</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1105">
   <si>
     <t>id</t>
   </si>
@@ -3336,6 +3336,15 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/c16bc0af552e</t>
+  </si>
+  <si>
+    <t>立方馆谋杀始末</t>
+  </si>
+  <si>
+    <t>立方馆谋杀始末,立方馆杀人事件始末</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c6ef2550a3da</t>
   </si>
 </sst>
 </file>
@@ -3967,13 +3976,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4320,7 +4330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G499"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15748,8 +15758,31 @@
         <v>1101</v>
       </c>
     </row>
+    <row r="500" spans="1:7">
+      <c r="A500">
+        <v>499</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D500" t="s">
+        <v>188</v>
+      </c>
+      <c r="E500" t="s">
+        <v>188</v>
+      </c>
+      <c r="F500">
+        <v>6</v>
+      </c>
+      <c r="G500" s="6" t="s">
+        <v>1104</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G497" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G499" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1107">
   <si>
     <t>id</t>
   </si>
@@ -3345,6 +3345,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/c6ef2550a3da</t>
+  </si>
+  <si>
+    <t>安闲领主的愉快领地防卫</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/8d6b85a61cd8</t>
   </si>
 </sst>
 </file>
@@ -3976,13 +3982,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4330,7 +4335,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G501"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15734,7 +15739,7 @@
       <c r="F498">
         <v>6</v>
       </c>
-      <c r="G498" s="5" t="s">
+      <c r="G498" s="1" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -15777,12 +15782,29 @@
       <c r="F500">
         <v>6</v>
       </c>
-      <c r="G500" s="6" t="s">
+      <c r="G500" s="4" t="s">
         <v>1104</v>
       </c>
     </row>
+    <row r="501" spans="1:7">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D501" t="s">
+        <v>141</v>
+      </c>
+      <c r="E501" t="s">
+        <v>141</v>
+      </c>
+      <c r="G501" s="5" t="s">
+        <v>1106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G499" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G500" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$501</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -167,13 +167,13 @@
     <t>https://pan.quark.cn/s/64ac023a320d</t>
   </si>
   <si>
-    <t>权利的游戏系列</t>
+    <t>权利的游戏</t>
   </si>
   <si>
     <t>剧集,美剧,权利的游戏</t>
   </si>
   <si>
-    <t>https://pan.quark.cn/s/4ddac80bdb51</t>
+    <t>https://pan.quark.cn/s/3c4920236e7e</t>
   </si>
   <si>
     <t>斯巴达克斯 全4季 未删减版</t>
@@ -3984,10 +3984,10 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4661,7 +4661,7 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       <c r="F71" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="2" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       <c r="F75" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="2" t="s">
         <v>222</v>
       </c>
     </row>
@@ -15479,18 +15479,18 @@
       <c r="A485">
         <v>484</v>
       </c>
-      <c r="B485" s="2" t="s">
+      <c r="B485" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="C485" s="2"/>
-      <c r="D485" s="2" t="s">
+      <c r="C485" s="3"/>
+      <c r="D485" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E485" s="2" t="s">
+      <c r="E485" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F485" s="2"/>
-      <c r="G485" s="2" t="s">
+      <c r="F485" s="3"/>
+      <c r="G485" s="3" t="s">
         <v>1073</v>
       </c>
     </row>
@@ -15498,18 +15498,18 @@
       <c r="A486">
         <v>485</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="B486" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="C486" s="2"/>
-      <c r="D486" s="2" t="s">
+      <c r="C486" s="3"/>
+      <c r="D486" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E486" s="2" t="s">
+      <c r="E486" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F486" s="2"/>
-      <c r="G486" s="2" t="s">
+      <c r="F486" s="3"/>
+      <c r="G486" s="3" t="s">
         <v>1075</v>
       </c>
     </row>
@@ -15517,18 +15517,18 @@
       <c r="A487">
         <v>486</v>
       </c>
-      <c r="B487" s="2" t="s">
+      <c r="B487" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="C487" s="2"/>
-      <c r="D487" s="2" t="s">
+      <c r="C487" s="3"/>
+      <c r="D487" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E487" s="2" t="s">
+      <c r="E487" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F487" s="2"/>
-      <c r="G487" s="2" t="s">
+      <c r="F487" s="3"/>
+      <c r="G487" s="3" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -15536,18 +15536,18 @@
       <c r="A488">
         <v>487</v>
       </c>
-      <c r="B488" s="2" t="s">
+      <c r="B488" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="C488" s="2"/>
-      <c r="D488" s="2" t="s">
+      <c r="C488" s="3"/>
+      <c r="D488" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E488" s="2" t="s">
+      <c r="E488" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F488" s="2"/>
-      <c r="G488" s="2" t="s">
+      <c r="F488" s="3"/>
+      <c r="G488" s="3" t="s">
         <v>1079</v>
       </c>
     </row>
@@ -15555,18 +15555,18 @@
       <c r="A489">
         <v>488</v>
       </c>
-      <c r="B489" s="2" t="s">
+      <c r="B489" s="3" t="s">
         <v>1080</v>
       </c>
-      <c r="C489" s="2"/>
-      <c r="D489" s="2" t="s">
+      <c r="C489" s="3"/>
+      <c r="D489" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E489" s="2" t="s">
+      <c r="E489" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F489" s="2"/>
-      <c r="G489" s="2" t="s">
+      <c r="F489" s="3"/>
+      <c r="G489" s="3" t="s">
         <v>1081</v>
       </c>
     </row>
@@ -15574,18 +15574,18 @@
       <c r="A490">
         <v>489</v>
       </c>
-      <c r="B490" s="2" t="s">
+      <c r="B490" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="C490" s="2"/>
-      <c r="D490" s="2" t="s">
+      <c r="C490" s="3"/>
+      <c r="D490" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E490" s="2" t="s">
+      <c r="E490" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F490" s="2"/>
-      <c r="G490" s="2" t="s">
+      <c r="F490" s="3"/>
+      <c r="G490" s="3" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -15593,18 +15593,18 @@
       <c r="A491">
         <v>490</v>
       </c>
-      <c r="B491" s="2" t="s">
+      <c r="B491" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="C491" s="2"/>
-      <c r="D491" s="2" t="s">
+      <c r="C491" s="3"/>
+      <c r="D491" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E491" s="2" t="s">
+      <c r="E491" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F491" s="2"/>
-      <c r="G491" s="2" t="s">
+      <c r="F491" s="3"/>
+      <c r="G491" s="3" t="s">
         <v>1085</v>
       </c>
     </row>
@@ -15612,18 +15612,18 @@
       <c r="A492">
         <v>491</v>
       </c>
-      <c r="B492" s="2" t="s">
+      <c r="B492" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="C492" s="2"/>
-      <c r="D492" s="2" t="s">
+      <c r="C492" s="3"/>
+      <c r="D492" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E492" s="2" t="s">
+      <c r="E492" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F492" s="2"/>
-      <c r="G492" s="2" t="s">
+      <c r="F492" s="3"/>
+      <c r="G492" s="3" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -15631,18 +15631,18 @@
       <c r="A493">
         <v>492</v>
       </c>
-      <c r="B493" s="2" t="s">
+      <c r="B493" s="3" t="s">
         <v>1088</v>
       </c>
-      <c r="C493" s="2"/>
-      <c r="D493" s="2" t="s">
+      <c r="C493" s="3"/>
+      <c r="D493" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E493" s="2" t="s">
+      <c r="E493" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F493" s="2"/>
-      <c r="G493" s="2" t="s">
+      <c r="F493" s="3"/>
+      <c r="G493" s="3" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -15650,18 +15650,18 @@
       <c r="A494">
         <v>493</v>
       </c>
-      <c r="B494" s="2" t="s">
+      <c r="B494" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="C494" s="2"/>
-      <c r="D494" s="2" t="s">
+      <c r="C494" s="3"/>
+      <c r="D494" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E494" s="2" t="s">
+      <c r="E494" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F494" s="2"/>
-      <c r="G494" s="2" t="s">
+      <c r="F494" s="3"/>
+      <c r="G494" s="3" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -15669,18 +15669,18 @@
       <c r="A495">
         <v>494</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="B495" s="3" t="s">
         <v>1092</v>
       </c>
-      <c r="C495" s="2"/>
-      <c r="D495" s="2" t="s">
+      <c r="C495" s="3"/>
+      <c r="D495" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E495" s="2" t="s">
+      <c r="E495" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F495" s="2"/>
-      <c r="G495" s="2" t="s">
+      <c r="F495" s="3"/>
+      <c r="G495" s="3" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -15688,18 +15688,18 @@
       <c r="A496">
         <v>495</v>
       </c>
-      <c r="B496" s="2" t="s">
+      <c r="B496" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="C496" s="2"/>
-      <c r="D496" s="2" t="s">
+      <c r="C496" s="3"/>
+      <c r="D496" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E496" s="2" t="s">
+      <c r="E496" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F496" s="2"/>
-      <c r="G496" s="2" t="s">
+      <c r="F496" s="3"/>
+      <c r="G496" s="3" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
       <c r="A497">
         <v>496</v>
       </c>
-      <c r="B497" s="3" t="s">
+      <c r="B497" s="4" t="s">
         <v>1096</v>
       </c>
       <c r="D497" t="s">
@@ -15719,7 +15719,7 @@
       <c r="F497">
         <v>6</v>
       </c>
-      <c r="G497" s="4" t="s">
+      <c r="G497" s="5" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       <c r="F498">
         <v>6</v>
       </c>
-      <c r="G498" s="1" t="s">
+      <c r="G498" s="2" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
       <c r="F500">
         <v>6</v>
       </c>
-      <c r="G500" s="4" t="s">
+      <c r="G500" s="5" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -15804,13 +15804,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G500" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G501" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="G71" r:id="rId1" display="https://pan.quark.cn/s/54ae4c79b6ef"/>
     <hyperlink ref="G75" r:id="rId2" display="https://pan.quark.cn/s/32466a4d8102"/>
     <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
+    <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -167,7 +167,7 @@
     <t>https://pan.quark.cn/s/64ac023a320d</t>
   </si>
   <si>
-    <t>权利的游戏</t>
+    <t>权力的游戏</t>
   </si>
   <si>
     <t>权力的游戏,权利的游戏</t>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="1110">
   <si>
     <t>id</t>
   </si>
@@ -3354,6 +3354,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/8d6b85a61cd8</t>
+  </si>
+  <si>
+    <t>草芥</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6610ed22512e</t>
   </si>
 </sst>
 </file>
@@ -3985,12 +3991,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4338,7 +4345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G501"/>
+  <dimension ref="A1:G502"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15804,6 +15811,26 @@
       </c>
       <c r="G501" s="5" t="s">
         <v>1107</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7">
+      <c r="A502">
+        <v>501</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D502" t="s">
+        <v>189</v>
+      </c>
+      <c r="E502" t="s">
+        <v>189</v>
+      </c>
+      <c r="F502">
+        <v>6</v>
+      </c>
+      <c r="G502" s="6" t="s">
+        <v>1109</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$502</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1112">
   <si>
     <t>id</t>
   </si>
@@ -3360,6 +3360,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/6610ed22512e</t>
+  </si>
+  <si>
+    <t>人魈传说</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1fcb804f0150</t>
   </si>
 </sst>
 </file>
@@ -3991,9 +3997,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4345,7 +4350,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G502"/>
+  <dimension ref="A1:G503"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -5982,7 +5987,7 @@
       <c r="F71" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="1" t="s">
         <v>215</v>
       </c>
     </row>
@@ -6074,7 +6079,7 @@
       <c r="F75" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="1" t="s">
         <v>223</v>
       </c>
     </row>
@@ -15489,18 +15494,18 @@
       <c r="A485">
         <v>484</v>
       </c>
-      <c r="B485" s="3" t="s">
+      <c r="B485" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="C485" s="3"/>
-      <c r="D485" s="3" t="s">
+      <c r="C485" s="2"/>
+      <c r="D485" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E485" s="3" t="s">
+      <c r="E485" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F485" s="3"/>
-      <c r="G485" s="3" t="s">
+      <c r="F485" s="2"/>
+      <c r="G485" s="2" t="s">
         <v>1074</v>
       </c>
     </row>
@@ -15508,18 +15513,18 @@
       <c r="A486">
         <v>485</v>
       </c>
-      <c r="B486" s="3" t="s">
+      <c r="B486" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="C486" s="3"/>
-      <c r="D486" s="3" t="s">
+      <c r="C486" s="2"/>
+      <c r="D486" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E486" s="3" t="s">
+      <c r="E486" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F486" s="3"/>
-      <c r="G486" s="3" t="s">
+      <c r="F486" s="2"/>
+      <c r="G486" s="2" t="s">
         <v>1076</v>
       </c>
     </row>
@@ -15527,18 +15532,18 @@
       <c r="A487">
         <v>486</v>
       </c>
-      <c r="B487" s="3" t="s">
+      <c r="B487" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="C487" s="3"/>
-      <c r="D487" s="3" t="s">
+      <c r="C487" s="2"/>
+      <c r="D487" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E487" s="3" t="s">
+      <c r="E487" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F487" s="3"/>
-      <c r="G487" s="3" t="s">
+      <c r="F487" s="2"/>
+      <c r="G487" s="2" t="s">
         <v>1078</v>
       </c>
     </row>
@@ -15546,18 +15551,18 @@
       <c r="A488">
         <v>487</v>
       </c>
-      <c r="B488" s="3" t="s">
+      <c r="B488" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="C488" s="3"/>
-      <c r="D488" s="3" t="s">
+      <c r="C488" s="2"/>
+      <c r="D488" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E488" s="3" t="s">
+      <c r="E488" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F488" s="3"/>
-      <c r="G488" s="3" t="s">
+      <c r="F488" s="2"/>
+      <c r="G488" s="2" t="s">
         <v>1080</v>
       </c>
     </row>
@@ -15565,18 +15570,18 @@
       <c r="A489">
         <v>488</v>
       </c>
-      <c r="B489" s="3" t="s">
+      <c r="B489" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="C489" s="3"/>
-      <c r="D489" s="3" t="s">
+      <c r="C489" s="2"/>
+      <c r="D489" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E489" s="3" t="s">
+      <c r="E489" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F489" s="3"/>
-      <c r="G489" s="3" t="s">
+      <c r="F489" s="2"/>
+      <c r="G489" s="2" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -15584,18 +15589,18 @@
       <c r="A490">
         <v>489</v>
       </c>
-      <c r="B490" s="3" t="s">
+      <c r="B490" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="C490" s="3"/>
-      <c r="D490" s="3" t="s">
+      <c r="C490" s="2"/>
+      <c r="D490" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E490" s="3" t="s">
+      <c r="E490" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F490" s="3"/>
-      <c r="G490" s="3" t="s">
+      <c r="F490" s="2"/>
+      <c r="G490" s="2" t="s">
         <v>1084</v>
       </c>
     </row>
@@ -15603,18 +15608,18 @@
       <c r="A491">
         <v>490</v>
       </c>
-      <c r="B491" s="3" t="s">
+      <c r="B491" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C491" s="3"/>
-      <c r="D491" s="3" t="s">
+      <c r="C491" s="2"/>
+      <c r="D491" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E491" s="3" t="s">
+      <c r="E491" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F491" s="3"/>
-      <c r="G491" s="3" t="s">
+      <c r="F491" s="2"/>
+      <c r="G491" s="2" t="s">
         <v>1086</v>
       </c>
     </row>
@@ -15622,18 +15627,18 @@
       <c r="A492">
         <v>491</v>
       </c>
-      <c r="B492" s="3" t="s">
+      <c r="B492" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="C492" s="3"/>
-      <c r="D492" s="3" t="s">
+      <c r="C492" s="2"/>
+      <c r="D492" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E492" s="3" t="s">
+      <c r="E492" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F492" s="3"/>
-      <c r="G492" s="3" t="s">
+      <c r="F492" s="2"/>
+      <c r="G492" s="2" t="s">
         <v>1088</v>
       </c>
     </row>
@@ -15641,18 +15646,18 @@
       <c r="A493">
         <v>492</v>
       </c>
-      <c r="B493" s="3" t="s">
+      <c r="B493" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="C493" s="3"/>
-      <c r="D493" s="3" t="s">
+      <c r="C493" s="2"/>
+      <c r="D493" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E493" s="3" t="s">
+      <c r="E493" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F493" s="3"/>
-      <c r="G493" s="3" t="s">
+      <c r="F493" s="2"/>
+      <c r="G493" s="2" t="s">
         <v>1090</v>
       </c>
     </row>
@@ -15660,18 +15665,18 @@
       <c r="A494">
         <v>493</v>
       </c>
-      <c r="B494" s="3" t="s">
+      <c r="B494" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="C494" s="3"/>
-      <c r="D494" s="3" t="s">
+      <c r="C494" s="2"/>
+      <c r="D494" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E494" s="3" t="s">
+      <c r="E494" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F494" s="3"/>
-      <c r="G494" s="3" t="s">
+      <c r="F494" s="2"/>
+      <c r="G494" s="2" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -15679,18 +15684,18 @@
       <c r="A495">
         <v>494</v>
       </c>
-      <c r="B495" s="3" t="s">
+      <c r="B495" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="C495" s="3"/>
-      <c r="D495" s="3" t="s">
+      <c r="C495" s="2"/>
+      <c r="D495" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E495" s="3" t="s">
+      <c r="E495" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F495" s="3"/>
-      <c r="G495" s="3" t="s">
+      <c r="F495" s="2"/>
+      <c r="G495" s="2" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -15698,18 +15703,18 @@
       <c r="A496">
         <v>495</v>
       </c>
-      <c r="B496" s="3" t="s">
+      <c r="B496" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="C496" s="3"/>
-      <c r="D496" s="3" t="s">
+      <c r="C496" s="2"/>
+      <c r="D496" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E496" s="3" t="s">
+      <c r="E496" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F496" s="3"/>
-      <c r="G496" s="3" t="s">
+      <c r="F496" s="2"/>
+      <c r="G496" s="2" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -15717,7 +15722,7 @@
       <c r="A497">
         <v>496</v>
       </c>
-      <c r="B497" s="4" t="s">
+      <c r="B497" s="3" t="s">
         <v>1097</v>
       </c>
       <c r="D497" t="s">
@@ -15729,7 +15734,7 @@
       <c r="F497">
         <v>6</v>
       </c>
-      <c r="G497" s="5" t="s">
+      <c r="G497" s="4" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -15749,7 +15754,7 @@
       <c r="F498">
         <v>6</v>
       </c>
-      <c r="G498" s="2" t="s">
+      <c r="G498" s="1" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -15792,7 +15797,7 @@
       <c r="F500">
         <v>6</v>
       </c>
-      <c r="G500" s="5" t="s">
+      <c r="G500" s="4" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -15809,7 +15814,7 @@
       <c r="E501" t="s">
         <v>142</v>
       </c>
-      <c r="G501" s="5" t="s">
+      <c r="G501" s="4" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -15829,12 +15834,32 @@
       <c r="F502">
         <v>6</v>
       </c>
-      <c r="G502" s="6" t="s">
+      <c r="G502" s="4" t="s">
         <v>1109</v>
       </c>
     </row>
+    <row r="503" spans="1:7">
+      <c r="A503">
+        <v>502</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D503" t="s">
+        <v>189</v>
+      </c>
+      <c r="E503" t="s">
+        <v>189</v>
+      </c>
+      <c r="F503">
+        <v>5</v>
+      </c>
+      <c r="G503" s="5" t="s">
+        <v>1111</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G501" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G502" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$502</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$503</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="1114">
   <si>
     <t>id</t>
   </si>
@@ -3366,6 +3366,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/1fcb804f0150</t>
+  </si>
+  <si>
+    <t>她未能歌颂的明日</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/35428ac34206</t>
   </si>
 </sst>
 </file>
@@ -3395,6 +3401,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -3411,14 +3425,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3870,7 +3876,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -3997,13 +4003,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4350,7 +4357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G503"/>
+  <dimension ref="A1:G504"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -10817,7 +10824,7 @@
       <c r="F281">
         <v>8</v>
       </c>
-      <c r="G281" t="s">
+      <c r="G281" s="2" t="s">
         <v>655</v>
       </c>
     </row>
@@ -15494,18 +15501,18 @@
       <c r="A485">
         <v>484</v>
       </c>
-      <c r="B485" s="2" t="s">
+      <c r="B485" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="C485" s="2"/>
-      <c r="D485" s="2" t="s">
+      <c r="C485" s="3"/>
+      <c r="D485" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E485" s="2" t="s">
+      <c r="E485" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F485" s="2"/>
-      <c r="G485" s="2" t="s">
+      <c r="F485" s="3"/>
+      <c r="G485" s="3" t="s">
         <v>1074</v>
       </c>
     </row>
@@ -15513,18 +15520,18 @@
       <c r="A486">
         <v>485</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="B486" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="C486" s="2"/>
-      <c r="D486" s="2" t="s">
+      <c r="C486" s="3"/>
+      <c r="D486" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E486" s="2" t="s">
+      <c r="E486" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F486" s="2"/>
-      <c r="G486" s="2" t="s">
+      <c r="F486" s="3"/>
+      <c r="G486" s="3" t="s">
         <v>1076</v>
       </c>
     </row>
@@ -15532,18 +15539,18 @@
       <c r="A487">
         <v>486</v>
       </c>
-      <c r="B487" s="2" t="s">
+      <c r="B487" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="C487" s="2"/>
-      <c r="D487" s="2" t="s">
+      <c r="C487" s="3"/>
+      <c r="D487" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E487" s="2" t="s">
+      <c r="E487" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F487" s="2"/>
-      <c r="G487" s="2" t="s">
+      <c r="F487" s="3"/>
+      <c r="G487" s="3" t="s">
         <v>1078</v>
       </c>
     </row>
@@ -15551,18 +15558,18 @@
       <c r="A488">
         <v>487</v>
       </c>
-      <c r="B488" s="2" t="s">
+      <c r="B488" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="C488" s="2"/>
-      <c r="D488" s="2" t="s">
+      <c r="C488" s="3"/>
+      <c r="D488" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E488" s="2" t="s">
+      <c r="E488" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F488" s="2"/>
-      <c r="G488" s="2" t="s">
+      <c r="F488" s="3"/>
+      <c r="G488" s="3" t="s">
         <v>1080</v>
       </c>
     </row>
@@ -15570,18 +15577,18 @@
       <c r="A489">
         <v>488</v>
       </c>
-      <c r="B489" s="2" t="s">
+      <c r="B489" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="C489" s="2"/>
-      <c r="D489" s="2" t="s">
+      <c r="C489" s="3"/>
+      <c r="D489" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E489" s="2" t="s">
+      <c r="E489" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F489" s="2"/>
-      <c r="G489" s="2" t="s">
+      <c r="F489" s="3"/>
+      <c r="G489" s="3" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -15589,18 +15596,18 @@
       <c r="A490">
         <v>489</v>
       </c>
-      <c r="B490" s="2" t="s">
+      <c r="B490" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="C490" s="2"/>
-      <c r="D490" s="2" t="s">
+      <c r="C490" s="3"/>
+      <c r="D490" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E490" s="2" t="s">
+      <c r="E490" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F490" s="2"/>
-      <c r="G490" s="2" t="s">
+      <c r="F490" s="3"/>
+      <c r="G490" s="3" t="s">
         <v>1084</v>
       </c>
     </row>
@@ -15608,18 +15615,18 @@
       <c r="A491">
         <v>490</v>
       </c>
-      <c r="B491" s="2" t="s">
+      <c r="B491" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="C491" s="2"/>
-      <c r="D491" s="2" t="s">
+      <c r="C491" s="3"/>
+      <c r="D491" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E491" s="2" t="s">
+      <c r="E491" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F491" s="2"/>
-      <c r="G491" s="2" t="s">
+      <c r="F491" s="3"/>
+      <c r="G491" s="3" t="s">
         <v>1086</v>
       </c>
     </row>
@@ -15627,18 +15634,18 @@
       <c r="A492">
         <v>491</v>
       </c>
-      <c r="B492" s="2" t="s">
+      <c r="B492" s="3" t="s">
         <v>1087</v>
       </c>
-      <c r="C492" s="2"/>
-      <c r="D492" s="2" t="s">
+      <c r="C492" s="3"/>
+      <c r="D492" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E492" s="2" t="s">
+      <c r="E492" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F492" s="2"/>
-      <c r="G492" s="2" t="s">
+      <c r="F492" s="3"/>
+      <c r="G492" s="3" t="s">
         <v>1088</v>
       </c>
     </row>
@@ -15646,18 +15653,18 @@
       <c r="A493">
         <v>492</v>
       </c>
-      <c r="B493" s="2" t="s">
+      <c r="B493" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="C493" s="2"/>
-      <c r="D493" s="2" t="s">
+      <c r="C493" s="3"/>
+      <c r="D493" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E493" s="2" t="s">
+      <c r="E493" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F493" s="2"/>
-      <c r="G493" s="2" t="s">
+      <c r="F493" s="3"/>
+      <c r="G493" s="3" t="s">
         <v>1090</v>
       </c>
     </row>
@@ -15665,18 +15672,18 @@
       <c r="A494">
         <v>493</v>
       </c>
-      <c r="B494" s="2" t="s">
+      <c r="B494" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="C494" s="2"/>
-      <c r="D494" s="2" t="s">
+      <c r="C494" s="3"/>
+      <c r="D494" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E494" s="2" t="s">
+      <c r="E494" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F494" s="2"/>
-      <c r="G494" s="2" t="s">
+      <c r="F494" s="3"/>
+      <c r="G494" s="3" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -15684,18 +15691,18 @@
       <c r="A495">
         <v>494</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="B495" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="C495" s="2"/>
-      <c r="D495" s="2" t="s">
+      <c r="C495" s="3"/>
+      <c r="D495" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E495" s="2" t="s">
+      <c r="E495" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F495" s="2"/>
-      <c r="G495" s="2" t="s">
+      <c r="F495" s="3"/>
+      <c r="G495" s="3" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -15703,18 +15710,18 @@
       <c r="A496">
         <v>495</v>
       </c>
-      <c r="B496" s="2" t="s">
+      <c r="B496" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="C496" s="2"/>
-      <c r="D496" s="2" t="s">
+      <c r="C496" s="3"/>
+      <c r="D496" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E496" s="2" t="s">
+      <c r="E496" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F496" s="2"/>
-      <c r="G496" s="2" t="s">
+      <c r="F496" s="3"/>
+      <c r="G496" s="3" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -15722,7 +15729,7 @@
       <c r="A497">
         <v>496</v>
       </c>
-      <c r="B497" s="3" t="s">
+      <c r="B497" s="4" t="s">
         <v>1097</v>
       </c>
       <c r="D497" t="s">
@@ -15734,7 +15741,7 @@
       <c r="F497">
         <v>6</v>
       </c>
-      <c r="G497" s="4" t="s">
+      <c r="G497" s="5" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -15797,7 +15804,7 @@
       <c r="F500">
         <v>6</v>
       </c>
-      <c r="G500" s="4" t="s">
+      <c r="G500" s="5" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -15814,7 +15821,7 @@
       <c r="E501" t="s">
         <v>142</v>
       </c>
-      <c r="G501" s="4" t="s">
+      <c r="G501" s="5" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -15834,7 +15841,7 @@
       <c r="F502">
         <v>6</v>
       </c>
-      <c r="G502" s="4" t="s">
+      <c r="G502" s="5" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -15858,8 +15865,28 @@
         <v>1111</v>
       </c>
     </row>
+    <row r="504" spans="1:7">
+      <c r="A504">
+        <v>503</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D504" t="s">
+        <v>189</v>
+      </c>
+      <c r="E504" t="s">
+        <v>189</v>
+      </c>
+      <c r="F504">
+        <v>6</v>
+      </c>
+      <c r="G504" s="6" t="s">
+        <v>1113</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G502" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G503" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -15867,6 +15894,7 @@
     <hyperlink ref="G75" r:id="rId2" display="https://pan.quark.cn/s/32466a4d8102"/>
     <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
     <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
+    <hyperlink ref="G281" r:id="rId5" display="https://pan.quark.cn/s/18f5ee8d2498"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$504</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1116">
   <si>
     <t>id</t>
   </si>
@@ -3372,6 +3372,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/35428ac34206</t>
+  </si>
+  <si>
+    <t>天启诡案</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7d325a5e9c3d</t>
   </si>
 </sst>
 </file>
@@ -4357,7 +4363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G504"/>
+  <dimension ref="A1:G505"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15881,12 +15887,32 @@
       <c r="F504">
         <v>6</v>
       </c>
-      <c r="G504" s="6" t="s">
+      <c r="G504" s="5" t="s">
         <v>1113</v>
       </c>
     </row>
+    <row r="505" spans="1:7">
+      <c r="A505">
+        <v>504</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D505" t="s">
+        <v>189</v>
+      </c>
+      <c r="E505" t="s">
+        <v>189</v>
+      </c>
+      <c r="F505">
+        <v>6</v>
+      </c>
+      <c r="G505" s="6" t="s">
+        <v>1115</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G503" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G504" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$505</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="1120">
   <si>
     <t>id</t>
   </si>
@@ -3378,6 +3378,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/7d325a5e9c3d</t>
+  </si>
+  <si>
+    <t>祝福</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a0c50ac4062d</t>
+  </si>
+  <si>
+    <t>尸乐园</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/28d6b6a2f072</t>
   </si>
 </sst>
 </file>
@@ -4009,7 +4021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4017,6 +4029,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4363,7 +4376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G505"/>
+  <dimension ref="A1:G507"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15907,12 +15920,52 @@
       <c r="F505">
         <v>6</v>
       </c>
-      <c r="G505" s="6" t="s">
+      <c r="G505" s="5" t="s">
         <v>1115</v>
       </c>
     </row>
+    <row r="506" spans="1:7">
+      <c r="A506">
+        <v>505</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D506" t="s">
+        <v>189</v>
+      </c>
+      <c r="E506" t="s">
+        <v>189</v>
+      </c>
+      <c r="F506">
+        <v>6</v>
+      </c>
+      <c r="G506" s="6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7">
+      <c r="A507">
+        <v>506</v>
+      </c>
+      <c r="B507" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D507" t="s">
+        <v>189</v>
+      </c>
+      <c r="E507" t="s">
+        <v>189</v>
+      </c>
+      <c r="F507">
+        <v>6</v>
+      </c>
+      <c r="G507" s="6" t="s">
+        <v>1119</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G504" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G505" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$505</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$507</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1122">
   <si>
     <t>id</t>
   </si>
@@ -3390,6 +3390,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/28d6b6a2f072</t>
+  </si>
+  <si>
+    <t>洗劫伦敦所有的玫瑰</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f7774ffd6157</t>
   </si>
 </sst>
 </file>
@@ -4028,8 +4034,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4376,7 +4382,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G507"/>
+  <dimension ref="A1:G508"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15940,7 +15946,7 @@
       <c r="F506">
         <v>6</v>
       </c>
-      <c r="G506" s="6" t="s">
+      <c r="G506" s="5" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -15948,7 +15954,7 @@
       <c r="A507">
         <v>506</v>
       </c>
-      <c r="B507" s="7" t="s">
+      <c r="B507" s="6" t="s">
         <v>1118</v>
       </c>
       <c r="D507" t="s">
@@ -15960,12 +15966,32 @@
       <c r="F507">
         <v>6</v>
       </c>
-      <c r="G507" s="6" t="s">
+      <c r="G507" s="5" t="s">
         <v>1119</v>
       </c>
     </row>
+    <row r="508" spans="1:7">
+      <c r="A508">
+        <v>507</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D508" t="s">
+        <v>189</v>
+      </c>
+      <c r="E508" t="s">
+        <v>189</v>
+      </c>
+      <c r="F508">
+        <v>6</v>
+      </c>
+      <c r="G508" s="7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G505" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G507" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$508</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="1124">
   <si>
     <t>id</t>
   </si>
@@ -3396,6 +3396,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/f7774ffd6157</t>
+  </si>
+  <si>
+    <t>六角馆的谋杀鉴赏</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/417d7b41d5ce</t>
   </si>
 </sst>
 </file>
@@ -4382,7 +4388,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G508"/>
+  <dimension ref="A1:G509"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -15986,12 +15992,32 @@
       <c r="F508">
         <v>6</v>
       </c>
-      <c r="G508" s="7" t="s">
+      <c r="G508" s="5" t="s">
         <v>1121</v>
       </c>
     </row>
+    <row r="509" spans="1:7">
+      <c r="A509">
+        <v>508</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D509" t="s">
+        <v>189</v>
+      </c>
+      <c r="E509" t="s">
+        <v>189</v>
+      </c>
+      <c r="F509">
+        <v>6</v>
+      </c>
+      <c r="G509" s="7" t="s">
+        <v>1123</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G507" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G508" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$509</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="1128">
   <si>
     <t>id</t>
   </si>
@@ -3402,6 +3402,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/417d7b41d5ce</t>
+  </si>
+  <si>
+    <t>王不见王</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/990b7177392f</t>
+  </si>
+  <si>
+    <t>因火成烟</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/8001e90b0b96</t>
   </si>
 </sst>
 </file>
@@ -4388,7 +4400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G509"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16012,12 +16024,52 @@
       <c r="F509">
         <v>6</v>
       </c>
-      <c r="G509" s="7" t="s">
+      <c r="G509" s="5" t="s">
         <v>1123</v>
       </c>
     </row>
+    <row r="510" spans="1:7">
+      <c r="A510">
+        <v>509</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D510" t="s">
+        <v>189</v>
+      </c>
+      <c r="E510" t="s">
+        <v>189</v>
+      </c>
+      <c r="F510">
+        <v>6</v>
+      </c>
+      <c r="G510" s="7" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7">
+      <c r="A511">
+        <v>510</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D511" t="s">
+        <v>189</v>
+      </c>
+      <c r="E511" t="s">
+        <v>189</v>
+      </c>
+      <c r="F511">
+        <v>6</v>
+      </c>
+      <c r="G511" s="7" t="s">
+        <v>1127</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G508" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G509" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$511</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="1130">
   <si>
     <t>id</t>
   </si>
@@ -3414,6 +3414,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/8001e90b0b96</t>
+  </si>
+  <si>
+    <t>木夕僧之戏</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d1ecb413aaf3</t>
   </si>
 </sst>
 </file>
@@ -4400,7 +4406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G512"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16044,7 +16050,7 @@
       <c r="F510">
         <v>6</v>
       </c>
-      <c r="G510" s="7" t="s">
+      <c r="G510" s="5" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -16064,12 +16070,32 @@
       <c r="F511">
         <v>6</v>
       </c>
-      <c r="G511" s="7" t="s">
+      <c r="G511" s="5" t="s">
         <v>1127</v>
       </c>
     </row>
+    <row r="512" spans="1:7">
+      <c r="A512">
+        <v>511</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D512" t="s">
+        <v>189</v>
+      </c>
+      <c r="E512" t="s">
+        <v>189</v>
+      </c>
+      <c r="F512">
+        <v>7</v>
+      </c>
+      <c r="G512" s="7" t="s">
+        <v>1129</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G509" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G511" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="1133">
   <si>
     <t>id</t>
   </si>
@@ -3423,6 +3423,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/d1ecb413aaf3</t>
+  </si>
+  <si>
+    <t>暗波崖</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4097a88042e9</t>
   </si>
 </sst>
 </file>
@@ -4054,7 +4060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4062,6 +4068,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4408,7 +4415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G512"/>
+  <dimension ref="A1:G513"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16096,6 +16103,26 @@
         <v>1130</v>
       </c>
     </row>
+    <row r="513" spans="1:7">
+      <c r="A513">
+        <v>512</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D513" t="s">
+        <v>190</v>
+      </c>
+      <c r="E513" t="s">
+        <v>190</v>
+      </c>
+      <c r="F513">
+        <v>6</v>
+      </c>
+      <c r="G513" s="7" t="s">
+        <v>1132</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G512" etc:filterBottomFollowUsedRange="0">
     <extLst/>
@@ -16106,6 +16133,7 @@
     <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
     <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
     <hyperlink ref="G281" r:id="rId5" display="https://pan.quark.cn/s/18f5ee8d2498"/>
+    <hyperlink ref="G513" r:id="rId6" display="https://pan.quark.cn/s/4097a88042e9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$513</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="1135">
   <si>
     <t>id</t>
   </si>
@@ -3429,6 +3429,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/4097a88042e9</t>
+  </si>
+  <si>
+    <t>难生恨</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f39f28442fb1</t>
   </si>
 </sst>
 </file>
@@ -4060,7 +4066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4068,7 +4074,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4415,7 +4423,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G513"/>
+  <dimension ref="A1:G514"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16123,8 +16131,28 @@
         <v>1132</v>
       </c>
     </row>
+    <row r="514" spans="1:7">
+      <c r="A514">
+        <v>513</v>
+      </c>
+      <c r="B514" s="8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D514" t="s">
+        <v>190</v>
+      </c>
+      <c r="E514" t="s">
+        <v>190</v>
+      </c>
+      <c r="F514">
+        <v>6</v>
+      </c>
+      <c r="G514" s="9" t="s">
+        <v>1134</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G512" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G513" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$513</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$514</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="1138">
   <si>
     <t>id</t>
   </si>
@@ -3435,6 +3435,26 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/f39f28442fb1</t>
+  </si>
+  <si>
+    <t>大楼里只有谋杀</t>
+  </si>
+  <si>
+    <r>
+      <t>大楼里只有谋杀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,Only Murders,only murder</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/b88785d069e4</t>
   </si>
 </sst>
 </file>
@@ -4066,15 +4086,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -4423,7 +4441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G514"/>
+  <dimension ref="A1:G515"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16127,7 +16145,7 @@
       <c r="F513">
         <v>6</v>
       </c>
-      <c r="G513" s="7" t="s">
+      <c r="G513" s="1" t="s">
         <v>1132</v>
       </c>
     </row>
@@ -16135,7 +16153,7 @@
       <c r="A514">
         <v>513</v>
       </c>
-      <c r="B514" s="8" t="s">
+      <c r="B514" s="6" t="s">
         <v>1133</v>
       </c>
       <c r="D514" t="s">
@@ -16147,12 +16165,32 @@
       <c r="F514">
         <v>6</v>
       </c>
-      <c r="G514" s="9" t="s">
+      <c r="G514" s="5" t="s">
         <v>1134</v>
       </c>
     </row>
+    <row r="515" spans="1:7">
+      <c r="A515">
+        <v>514</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D515" t="s">
+        <v>16</v>
+      </c>
+      <c r="E515" t="s">
+        <v>16</v>
+      </c>
+      <c r="G515" s="7" t="s">
+        <v>1137</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G513" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G514" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$515</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="1140">
   <si>
     <t>id</t>
   </si>
@@ -3441,6 +3441,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>大楼里只有谋杀</t>
     </r>
     <r>
@@ -3455,6 +3461,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/b88785d069e4</t>
+  </si>
+  <si>
+    <t>沃德朴一家</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c3b675d8cc79</t>
   </si>
 </sst>
 </file>
@@ -4441,7 +4453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G515"/>
+  <dimension ref="A1:G516"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16185,12 +16197,29 @@
       <c r="E515" t="s">
         <v>16</v>
       </c>
-      <c r="G515" s="7" t="s">
+      <c r="G515" s="5" t="s">
         <v>1137</v>
       </c>
     </row>
+    <row r="516" spans="1:7">
+      <c r="A516">
+        <v>515</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D516" t="s">
+        <v>143</v>
+      </c>
+      <c r="E516" t="s">
+        <v>143</v>
+      </c>
+      <c r="G516" s="7" t="s">
+        <v>1139</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G514" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G515" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$515</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$516</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="1142">
   <si>
     <t>id</t>
   </si>
@@ -3467,6 +3467,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/c3b675d8cc79</t>
+  </si>
+  <si>
+    <t>阿依达</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3cb81ddaf501</t>
   </si>
 </sst>
 </file>
@@ -4098,13 +4104,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -4453,7 +4460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G516"/>
+  <dimension ref="A1:G517"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16214,12 +16221,32 @@
       <c r="E516" t="s">
         <v>143</v>
       </c>
-      <c r="G516" s="7" t="s">
+      <c r="G516" s="5" t="s">
         <v>1139</v>
       </c>
     </row>
+    <row r="517" spans="1:7">
+      <c r="A517">
+        <v>516</v>
+      </c>
+      <c r="B517" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D517" t="s">
+        <v>190</v>
+      </c>
+      <c r="E517" t="s">
+        <v>190</v>
+      </c>
+      <c r="F517">
+        <v>6</v>
+      </c>
+      <c r="G517" s="8" t="s">
+        <v>1141</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G515" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G516" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$516</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$517</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="1149">
   <si>
     <t>id</t>
   </si>
@@ -3473,6 +3473,27 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/3cb81ddaf501</t>
+  </si>
+  <si>
+    <t>决战洗剪吹</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/90d96d395a84</t>
+  </si>
+  <si>
+    <t>动物监友会</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/256b6bee5294</t>
+  </si>
+  <si>
+    <t>人脑不宜食用</t>
+  </si>
+  <si>
+    <t>人脑,人脑不宜食用</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0b145b0c3c73</t>
   </si>
 </sst>
 </file>
@@ -4112,7 +4133,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4460,7 +4481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G517"/>
+  <dimension ref="A1:G520"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16229,7 +16250,7 @@
       <c r="A517">
         <v>516</v>
       </c>
-      <c r="B517" s="7" t="s">
+      <c r="B517" s="6" t="s">
         <v>1140</v>
       </c>
       <c r="D517" t="s">
@@ -16241,12 +16262,75 @@
       <c r="F517">
         <v>6</v>
       </c>
-      <c r="G517" s="8" t="s">
+      <c r="G517" s="5" t="s">
         <v>1141</v>
       </c>
     </row>
+    <row r="518" spans="1:7">
+      <c r="A518">
+        <v>517</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D518" t="s">
+        <v>190</v>
+      </c>
+      <c r="E518" t="s">
+        <v>190</v>
+      </c>
+      <c r="F518">
+        <v>6</v>
+      </c>
+      <c r="G518" s="7" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7">
+      <c r="A519">
+        <v>518</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D519" t="s">
+        <v>190</v>
+      </c>
+      <c r="E519" t="s">
+        <v>190</v>
+      </c>
+      <c r="F519">
+        <v>5</v>
+      </c>
+      <c r="G519" s="8" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7">
+      <c r="A520">
+        <v>519</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D520" t="s">
+        <v>190</v>
+      </c>
+      <c r="E520" t="s">
+        <v>190</v>
+      </c>
+      <c r="F520">
+        <v>6</v>
+      </c>
+      <c r="G520" s="8" t="s">
+        <v>1148</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G516" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G517" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -16256,6 +16340,7 @@
     <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
     <hyperlink ref="G281" r:id="rId5" display="https://pan.quark.cn/s/18f5ee8d2498"/>
     <hyperlink ref="G513" r:id="rId6" display="https://pan.quark.cn/s/4097a88042e9"/>
+    <hyperlink ref="G518" r:id="rId7" display="https://pan.quark.cn/s/90d96d395a84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$517</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$520</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="1149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="1151">
   <si>
     <t>id</t>
   </si>
@@ -3494,6 +3494,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/0b145b0c3c73</t>
+  </si>
+  <si>
+    <t>不喜</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/66442ff38eb1</t>
   </si>
 </sst>
 </file>
@@ -4125,7 +4131,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4133,7 +4139,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4481,7 +4490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G520"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16302,7 +16311,7 @@
       <c r="F519">
         <v>5</v>
       </c>
-      <c r="G519" s="8" t="s">
+      <c r="G519" s="5" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -16325,12 +16334,32 @@
       <c r="F520">
         <v>6</v>
       </c>
-      <c r="G520" s="8" t="s">
+      <c r="G520" s="5" t="s">
         <v>1148</v>
       </c>
     </row>
+    <row r="521" spans="1:7">
+      <c r="A521">
+        <v>520</v>
+      </c>
+      <c r="B521" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D521" t="s">
+        <v>190</v>
+      </c>
+      <c r="E521" t="s">
+        <v>190</v>
+      </c>
+      <c r="F521">
+        <v>6</v>
+      </c>
+      <c r="G521" s="9" t="s">
+        <v>1150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G517" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G520" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$520</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$521</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1155">
   <si>
     <t>id</t>
   </si>
@@ -3500,6 +3500,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/66442ff38eb1</t>
+  </si>
+  <si>
+    <t>持斧奥夫</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/de855b30b8c7</t>
+  </si>
+  <si>
+    <t>风林火山</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d5f7bb7ec540</t>
   </si>
 </sst>
 </file>
@@ -4131,7 +4143,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4139,11 +4151,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4490,7 +4501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G523"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16291,7 +16302,7 @@
       <c r="F518">
         <v>6</v>
       </c>
-      <c r="G518" s="7" t="s">
+      <c r="G518" s="1" t="s">
         <v>1143</v>
       </c>
     </row>
@@ -16342,7 +16353,7 @@
       <c r="A521">
         <v>520</v>
       </c>
-      <c r="B521" s="8" t="s">
+      <c r="B521" s="7" t="s">
         <v>1149</v>
       </c>
       <c r="D521" t="s">
@@ -16354,12 +16365,52 @@
       <c r="F521">
         <v>6</v>
       </c>
-      <c r="G521" s="9" t="s">
+      <c r="G521" s="5" t="s">
         <v>1150</v>
       </c>
     </row>
+    <row r="522" ht="15" spans="1:7">
+      <c r="A522">
+        <v>521</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D522" t="s">
+        <v>190</v>
+      </c>
+      <c r="E522" t="s">
+        <v>190</v>
+      </c>
+      <c r="F522">
+        <v>6</v>
+      </c>
+      <c r="G522" s="8" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="523" ht="15" spans="1:7">
+      <c r="A523">
+        <v>522</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D523" t="s">
+        <v>190</v>
+      </c>
+      <c r="E523" t="s">
+        <v>190</v>
+      </c>
+      <c r="F523">
+        <v>6</v>
+      </c>
+      <c r="G523" s="8" t="s">
+        <v>1154</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G520" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G521" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$521</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$523</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3505,13 +3505,13 @@
     <t>持斧奥夫</t>
   </si>
   <si>
-    <t>https://pan.quark.cn/s/de855b30b8c7</t>
+    <t>https://pan.quark.cn/s/30e3087f9685</t>
   </si>
   <si>
     <t>风林火山</t>
   </si>
   <si>
-    <t>https://pan.quark.cn/s/d5f7bb7ec540</t>
+    <t>https://pan.quark.cn/s/db1a18bd2f60</t>
   </si>
 </sst>
 </file>
@@ -16410,7 +16410,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G521" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G523" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1156">
   <si>
     <t>id</t>
   </si>
@@ -2142,6 +2142,9 @@
   </si>
   <si>
     <t>漓川怪谈簿</t>
+  </si>
+  <si>
+    <t>漓川怪谈簿,璃川怪谈薄,璃川怪谈簿</t>
   </si>
   <si>
     <t>https://pan.quark.cn/s/333de6750214</t>
@@ -4143,7 +4146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4154,7 +4157,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11486,7 +11488,7 @@
         <v>703</v>
       </c>
       <c r="C304" t="s">
-        <v>8</v>
+        <v>704</v>
       </c>
       <c r="D304" t="s">
         <v>190</v>
@@ -11498,7 +11500,7 @@
         <v>7</v>
       </c>
       <c r="G304" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -11506,7 +11508,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C305" t="s">
         <v>8</v>
@@ -11521,7 +11523,7 @@
         <v>6</v>
       </c>
       <c r="G305" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -11529,7 +11531,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C306" t="s">
         <v>8</v>
@@ -11544,7 +11546,7 @@
         <v>6</v>
       </c>
       <c r="G306" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -11552,7 +11554,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C307" t="s">
         <v>8</v>
@@ -11567,7 +11569,7 @@
         <v>6</v>
       </c>
       <c r="G307" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -11575,7 +11577,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C308" t="s">
         <v>8</v>
@@ -11590,7 +11592,7 @@
         <v>4</v>
       </c>
       <c r="G308" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11598,7 +11600,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C309" t="s">
         <v>8</v>
@@ -11613,7 +11615,7 @@
         <v>5</v>
       </c>
       <c r="G309" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -11621,7 +11623,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C310" t="s">
         <v>8</v>
@@ -11636,7 +11638,7 @@
         <v>7</v>
       </c>
       <c r="G310" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -11644,7 +11646,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C311" t="s">
         <v>8</v>
@@ -11659,7 +11661,7 @@
         <v>4</v>
       </c>
       <c r="G311" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -11667,7 +11669,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C312" t="s">
         <v>8</v>
@@ -11682,7 +11684,7 @@
         <v>4</v>
       </c>
       <c r="G312" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -11690,7 +11692,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C313" t="s">
         <v>8</v>
@@ -11705,7 +11707,7 @@
         <v>6</v>
       </c>
       <c r="G313" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -11713,7 +11715,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C314" t="s">
         <v>8</v>
@@ -11728,7 +11730,7 @@
         <v>6</v>
       </c>
       <c r="G314" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -11736,7 +11738,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C315" t="s">
         <v>8</v>
@@ -11751,7 +11753,7 @@
         <v>8</v>
       </c>
       <c r="G315" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -11759,7 +11761,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C316" t="s">
         <v>8</v>
@@ -11774,7 +11776,7 @@
         <v>6</v>
       </c>
       <c r="G316" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -11782,13 +11784,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C317" t="s">
         <v>8</v>
       </c>
       <c r="D317" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E317" t="s">
         <v>143</v>
@@ -11797,7 +11799,7 @@
         <v>8</v>
       </c>
       <c r="G317" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -11805,13 +11807,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C318" t="s">
         <v>8</v>
       </c>
       <c r="D318" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E318" t="s">
         <v>143</v>
@@ -11820,7 +11822,7 @@
         <v>8</v>
       </c>
       <c r="G318" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -11828,13 +11830,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C319" t="s">
         <v>8</v>
       </c>
       <c r="D319" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E319" t="s">
         <v>143</v>
@@ -11843,7 +11845,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -11851,13 +11853,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C320" t="s">
         <v>8</v>
       </c>
       <c r="D320" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E320" t="s">
         <v>143</v>
@@ -11866,7 +11868,7 @@
         <v>8</v>
       </c>
       <c r="G320" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -11874,13 +11876,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C321" t="s">
         <v>8</v>
       </c>
       <c r="D321" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E321" t="s">
         <v>143</v>
@@ -11889,7 +11891,7 @@
         <v>8</v>
       </c>
       <c r="G321" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -11897,13 +11899,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C322" t="s">
         <v>8</v>
       </c>
       <c r="D322" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E322" t="s">
         <v>143</v>
@@ -11912,7 +11914,7 @@
         <v>8</v>
       </c>
       <c r="G322" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -11920,13 +11922,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C323" t="s">
         <v>8</v>
       </c>
       <c r="D323" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E323" t="s">
         <v>143</v>
@@ -11935,7 +11937,7 @@
         <v>8</v>
       </c>
       <c r="G323" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -11943,13 +11945,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C324" t="s">
         <v>8</v>
       </c>
       <c r="D324" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E324" t="s">
         <v>143</v>
@@ -11958,7 +11960,7 @@
         <v>8</v>
       </c>
       <c r="G324" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -11966,13 +11968,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C325" t="s">
         <v>8</v>
       </c>
       <c r="D325" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E325" t="s">
         <v>143</v>
@@ -11981,7 +11983,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11989,13 +11991,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C326" t="s">
         <v>8</v>
       </c>
       <c r="D326" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E326" t="s">
         <v>143</v>
@@ -12004,7 +12006,7 @@
         <v>8</v>
       </c>
       <c r="G326" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -12012,13 +12014,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C327" t="s">
         <v>8</v>
       </c>
       <c r="D327" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E327" t="s">
         <v>143</v>
@@ -12027,7 +12029,7 @@
         <v>8</v>
       </c>
       <c r="G327" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -12035,13 +12037,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C328" t="s">
         <v>8</v>
       </c>
       <c r="D328" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E328" t="s">
         <v>143</v>
@@ -12050,7 +12052,7 @@
         <v>8</v>
       </c>
       <c r="G328" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -12058,13 +12060,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C329" t="s">
         <v>8</v>
       </c>
       <c r="D329" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E329" t="s">
         <v>143</v>
@@ -12073,7 +12075,7 @@
         <v>8</v>
       </c>
       <c r="G329" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -12081,13 +12083,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C330" t="s">
         <v>8</v>
       </c>
       <c r="D330" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E330" t="s">
         <v>143</v>
@@ -12096,7 +12098,7 @@
         <v>8</v>
       </c>
       <c r="G330" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -12104,13 +12106,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C331" t="s">
         <v>8</v>
       </c>
       <c r="D331" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E331" t="s">
         <v>143</v>
@@ -12119,7 +12121,7 @@
         <v>8</v>
       </c>
       <c r="G331" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -12127,13 +12129,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C332" t="s">
         <v>8</v>
       </c>
       <c r="D332" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E332" t="s">
         <v>143</v>
@@ -12142,7 +12144,7 @@
         <v>8</v>
       </c>
       <c r="G332" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -12150,13 +12152,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C333" t="s">
         <v>8</v>
       </c>
       <c r="D333" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E333" t="s">
         <v>143</v>
@@ -12165,7 +12167,7 @@
         <v>8</v>
       </c>
       <c r="G333" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -12173,13 +12175,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C334" t="s">
         <v>8</v>
       </c>
       <c r="D334" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E334" t="s">
         <v>143</v>
@@ -12188,7 +12190,7 @@
         <v>8</v>
       </c>
       <c r="G334" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -12196,13 +12198,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C335" t="s">
         <v>8</v>
       </c>
       <c r="D335" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E335" t="s">
         <v>143</v>
@@ -12211,7 +12213,7 @@
         <v>8</v>
       </c>
       <c r="G335" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -12219,13 +12221,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C336" t="s">
         <v>8</v>
       </c>
       <c r="D336" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E336" t="s">
         <v>143</v>
@@ -12234,7 +12236,7 @@
         <v>8</v>
       </c>
       <c r="G336" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -12242,13 +12244,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C337" t="s">
         <v>8</v>
       </c>
       <c r="D337" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E337" t="s">
         <v>143</v>
@@ -12257,7 +12259,7 @@
         <v>8</v>
       </c>
       <c r="G337" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -12265,13 +12267,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C338" t="s">
         <v>8</v>
       </c>
       <c r="D338" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E338" t="s">
         <v>143</v>
@@ -12280,7 +12282,7 @@
         <v>8</v>
       </c>
       <c r="G338" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -12288,13 +12290,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C339" t="s">
         <v>8</v>
       </c>
       <c r="D339" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E339" t="s">
         <v>143</v>
@@ -12303,7 +12305,7 @@
         <v>8</v>
       </c>
       <c r="G339" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -12311,13 +12313,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C340" t="s">
         <v>8</v>
       </c>
       <c r="D340" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E340" t="s">
         <v>143</v>
@@ -12326,7 +12328,7 @@
         <v>8</v>
       </c>
       <c r="G340" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -12334,13 +12336,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C341" t="s">
         <v>8</v>
       </c>
       <c r="D341" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E341" t="s">
         <v>143</v>
@@ -12349,7 +12351,7 @@
         <v>8</v>
       </c>
       <c r="G341" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -12357,13 +12359,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C342" t="s">
         <v>8</v>
       </c>
       <c r="D342" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E342" t="s">
         <v>143</v>
@@ -12372,7 +12374,7 @@
         <v>8</v>
       </c>
       <c r="G342" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -12380,13 +12382,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C343" t="s">
         <v>8</v>
       </c>
       <c r="D343" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E343" t="s">
         <v>143</v>
@@ -12395,7 +12397,7 @@
         <v>8</v>
       </c>
       <c r="G343" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -12403,13 +12405,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C344" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D344" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E344" t="s">
         <v>143</v>
@@ -12418,7 +12420,7 @@
         <v>8</v>
       </c>
       <c r="G344" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -12426,13 +12428,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C345" t="s">
         <v>8</v>
       </c>
       <c r="D345" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E345" t="s">
         <v>143</v>
@@ -12441,7 +12443,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -12449,10 +12451,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C346" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D346" t="s">
         <v>190</v>
@@ -12464,7 +12466,7 @@
         <v>7</v>
       </c>
       <c r="G346" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -12472,7 +12474,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C347" t="s">
         <v>8</v>
@@ -12487,7 +12489,7 @@
         <v>8</v>
       </c>
       <c r="G347" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -12495,7 +12497,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C348" t="s">
         <v>8</v>
@@ -12510,7 +12512,7 @@
         <v>8</v>
       </c>
       <c r="G348" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -12518,7 +12520,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C349" t="s">
         <v>8</v>
@@ -12533,7 +12535,7 @@
         <v>8</v>
       </c>
       <c r="G349" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -12541,7 +12543,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C350" t="s">
         <v>8</v>
@@ -12556,7 +12558,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -12564,7 +12566,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C351" t="s">
         <v>8</v>
@@ -12579,7 +12581,7 @@
         <v>8</v>
       </c>
       <c r="G351" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -12587,7 +12589,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C352" t="s">
         <v>8</v>
@@ -12602,7 +12604,7 @@
         <v>8</v>
       </c>
       <c r="G352" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -12610,7 +12612,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C353" t="s">
         <v>8</v>
@@ -12625,7 +12627,7 @@
         <v>8</v>
       </c>
       <c r="G353" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -12633,7 +12635,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C354" t="s">
         <v>8</v>
@@ -12648,7 +12650,7 @@
         <v>8</v>
       </c>
       <c r="G354" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -12656,7 +12658,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C355" t="s">
         <v>8</v>
@@ -12671,7 +12673,7 @@
         <v>8</v>
       </c>
       <c r="G355" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -12679,7 +12681,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C356" t="s">
         <v>8</v>
@@ -12694,7 +12696,7 @@
         <v>8</v>
       </c>
       <c r="G356" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -12702,7 +12704,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C357" t="s">
         <v>8</v>
@@ -12717,7 +12719,7 @@
         <v>8</v>
       </c>
       <c r="G357" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -12725,7 +12727,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C358" t="s">
         <v>8</v>
@@ -12740,7 +12742,7 @@
         <v>8</v>
       </c>
       <c r="G358" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -12748,7 +12750,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C359" t="s">
         <v>8</v>
@@ -12763,7 +12765,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -12771,7 +12773,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C360" t="s">
         <v>8</v>
@@ -12786,7 +12788,7 @@
         <v>8</v>
       </c>
       <c r="G360" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -12794,7 +12796,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C361" t="s">
         <v>8</v>
@@ -12809,7 +12811,7 @@
         <v>8</v>
       </c>
       <c r="G361" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -12817,7 +12819,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C362" t="s">
         <v>8</v>
@@ -12832,7 +12834,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -12840,7 +12842,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C363" t="s">
         <v>8</v>
@@ -12855,7 +12857,7 @@
         <v>8</v>
       </c>
       <c r="G363" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -12863,7 +12865,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C364" t="s">
         <v>8</v>
@@ -12878,7 +12880,7 @@
         <v>8</v>
       </c>
       <c r="G364" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -12886,7 +12888,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C365" t="s">
         <v>8</v>
@@ -12901,7 +12903,7 @@
         <v>8</v>
       </c>
       <c r="G365" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -12909,7 +12911,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C366" t="s">
         <v>8</v>
@@ -12924,7 +12926,7 @@
         <v>8</v>
       </c>
       <c r="G366" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -12932,7 +12934,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C367" t="s">
         <v>8</v>
@@ -12947,7 +12949,7 @@
         <v>8</v>
       </c>
       <c r="G367" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -12955,7 +12957,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C368" t="s">
         <v>8</v>
@@ -12970,7 +12972,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -12978,7 +12980,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C369" t="s">
         <v>8</v>
@@ -12993,7 +12995,7 @@
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -13001,7 +13003,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C370" t="s">
         <v>8</v>
@@ -13016,7 +13018,7 @@
         <v>8</v>
       </c>
       <c r="G370" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -13024,7 +13026,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C371" t="s">
         <v>8</v>
@@ -13039,7 +13041,7 @@
         <v>8</v>
       </c>
       <c r="G371" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -13047,7 +13049,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C372" t="s">
         <v>8</v>
@@ -13062,7 +13064,7 @@
         <v>8</v>
       </c>
       <c r="G372" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -13070,7 +13072,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C373" t="s">
         <v>8</v>
@@ -13085,7 +13087,7 @@
         <v>8</v>
       </c>
       <c r="G373" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -13093,7 +13095,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C374" t="s">
         <v>8</v>
@@ -13108,7 +13110,7 @@
         <v>8</v>
       </c>
       <c r="G374" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -13116,7 +13118,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C375" t="s">
         <v>8</v>
@@ -13131,7 +13133,7 @@
         <v>8</v>
       </c>
       <c r="G375" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -13139,7 +13141,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C376" t="s">
         <v>8</v>
@@ -13154,7 +13156,7 @@
         <v>8</v>
       </c>
       <c r="G376" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -13162,7 +13164,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C377" t="s">
         <v>8</v>
@@ -13177,7 +13179,7 @@
         <v>8</v>
       </c>
       <c r="G377" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -13185,7 +13187,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C378" t="s">
         <v>8</v>
@@ -13200,7 +13202,7 @@
         <v>8</v>
       </c>
       <c r="G378" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -13208,7 +13210,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C379" t="s">
         <v>8</v>
@@ -13223,7 +13225,7 @@
         <v>8</v>
       </c>
       <c r="G379" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -13231,7 +13233,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C380" t="s">
         <v>8</v>
@@ -13246,7 +13248,7 @@
         <v>8</v>
       </c>
       <c r="G380" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -13254,7 +13256,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C381" t="s">
         <v>8</v>
@@ -13269,7 +13271,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -13277,7 +13279,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C382" t="s">
         <v>8</v>
@@ -13292,7 +13294,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -13300,7 +13302,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C383" t="s">
         <v>8</v>
@@ -13315,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -13323,7 +13325,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C384" t="s">
         <v>8</v>
@@ -13338,7 +13340,7 @@
         <v>8</v>
       </c>
       <c r="G384" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -13346,7 +13348,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C385" t="s">
         <v>8</v>
@@ -13361,7 +13363,7 @@
         <v>8</v>
       </c>
       <c r="G385" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -13369,7 +13371,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C386" t="s">
         <v>8</v>
@@ -13384,7 +13386,7 @@
         <v>8</v>
       </c>
       <c r="G386" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -13392,7 +13394,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C387" t="s">
         <v>8</v>
@@ -13407,7 +13409,7 @@
         <v>8</v>
       </c>
       <c r="G387" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -13415,7 +13417,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C388" t="s">
         <v>8</v>
@@ -13430,7 +13432,7 @@
         <v>8</v>
       </c>
       <c r="G388" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -13438,7 +13440,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C389" t="s">
         <v>8</v>
@@ -13453,7 +13455,7 @@
         <v>8</v>
       </c>
       <c r="G389" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -13461,7 +13463,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C390" t="s">
         <v>8</v>
@@ -13476,7 +13478,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -13484,7 +13486,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C391" t="s">
         <v>8</v>
@@ -13499,7 +13501,7 @@
         <v>8</v>
       </c>
       <c r="G391" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -13507,7 +13509,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C392" t="s">
         <v>8</v>
@@ -13522,7 +13524,7 @@
         <v>8</v>
       </c>
       <c r="G392" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -13530,7 +13532,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C393" t="s">
         <v>8</v>
@@ -13545,7 +13547,7 @@
         <v>8</v>
       </c>
       <c r="G393" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -13553,7 +13555,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C394" t="s">
         <v>8</v>
@@ -13568,7 +13570,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -13576,7 +13578,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C395" t="s">
         <v>8</v>
@@ -13591,7 +13593,7 @@
         <v>8</v>
       </c>
       <c r="G395" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -13599,7 +13601,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C396" t="s">
         <v>8</v>
@@ -13614,7 +13616,7 @@
         <v>8</v>
       </c>
       <c r="G396" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -13622,7 +13624,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C397" t="s">
         <v>8</v>
@@ -13637,7 +13639,7 @@
         <v>8</v>
       </c>
       <c r="G397" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -13645,7 +13647,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C398" t="s">
         <v>8</v>
@@ -13660,7 +13662,7 @@
         <v>8</v>
       </c>
       <c r="G398" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -13668,7 +13670,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C399" t="s">
         <v>8</v>
@@ -13683,7 +13685,7 @@
         <v>8</v>
       </c>
       <c r="G399" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -13691,7 +13693,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C400" t="s">
         <v>8</v>
@@ -13706,7 +13708,7 @@
         <v>8</v>
       </c>
       <c r="G400" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -13714,7 +13716,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C401" t="s">
         <v>8</v>
@@ -13729,7 +13731,7 @@
         <v>8</v>
       </c>
       <c r="G401" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -13737,7 +13739,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -13752,7 +13754,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -13760,7 +13762,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C403" t="s">
         <v>8</v>
@@ -13775,7 +13777,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -13783,7 +13785,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C404" t="s">
         <v>8</v>
@@ -13798,7 +13800,7 @@
         <v>8</v>
       </c>
       <c r="G404" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -13806,7 +13808,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C405" t="s">
         <v>8</v>
@@ -13821,7 +13823,7 @@
         <v>8</v>
       </c>
       <c r="G405" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -13829,7 +13831,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C406" t="s">
         <v>8</v>
@@ -13844,7 +13846,7 @@
         <v>8</v>
       </c>
       <c r="G406" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -13852,7 +13854,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C407" t="s">
         <v>8</v>
@@ -13867,7 +13869,7 @@
         <v>8</v>
       </c>
       <c r="G407" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -13875,7 +13877,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C408" t="s">
         <v>8</v>
@@ -13890,7 +13892,7 @@
         <v>8</v>
       </c>
       <c r="G408" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -13898,7 +13900,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C409" t="s">
         <v>8</v>
@@ -13913,7 +13915,7 @@
         <v>8</v>
       </c>
       <c r="G409" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -13921,7 +13923,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C410" t="s">
         <v>8</v>
@@ -13936,7 +13938,7 @@
         <v>8</v>
       </c>
       <c r="G410" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -13944,7 +13946,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C411" t="s">
         <v>8</v>
@@ -13959,7 +13961,7 @@
         <v>8</v>
       </c>
       <c r="G411" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -13967,7 +13969,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C412" t="s">
         <v>8</v>
@@ -13982,7 +13984,7 @@
         <v>8</v>
       </c>
       <c r="G412" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -13990,7 +13992,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C413" t="s">
         <v>8</v>
@@ -14005,7 +14007,7 @@
         <v>8</v>
       </c>
       <c r="G413" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -14013,7 +14015,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C414" t="s">
         <v>8</v>
@@ -14028,7 +14030,7 @@
         <v>8</v>
       </c>
       <c r="G414" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -14036,7 +14038,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C415" t="s">
         <v>8</v>
@@ -14051,7 +14053,7 @@
         <v>8</v>
       </c>
       <c r="G415" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -14059,7 +14061,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C416" t="s">
         <v>8</v>
@@ -14074,7 +14076,7 @@
         <v>8</v>
       </c>
       <c r="G416" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -14082,7 +14084,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C417" t="s">
         <v>8</v>
@@ -14097,7 +14099,7 @@
         <v>8</v>
       </c>
       <c r="G417" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -14105,7 +14107,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C418" t="s">
         <v>8</v>
@@ -14120,7 +14122,7 @@
         <v>8</v>
       </c>
       <c r="G418" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -14128,7 +14130,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C419" t="s">
         <v>8</v>
@@ -14143,7 +14145,7 @@
         <v>8</v>
       </c>
       <c r="G419" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -14151,7 +14153,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C420" t="s">
         <v>8</v>
@@ -14166,7 +14168,7 @@
         <v>8</v>
       </c>
       <c r="G420" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -14174,7 +14176,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C421" t="s">
         <v>8</v>
@@ -14189,7 +14191,7 @@
         <v>8</v>
       </c>
       <c r="G421" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -14197,7 +14199,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C422" t="s">
         <v>8</v>
@@ -14212,7 +14214,7 @@
         <v>8</v>
       </c>
       <c r="G422" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -14220,7 +14222,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C423" t="s">
         <v>8</v>
@@ -14235,7 +14237,7 @@
         <v>8</v>
       </c>
       <c r="G423" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -14243,7 +14245,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C424" t="s">
         <v>8</v>
@@ -14258,7 +14260,7 @@
         <v>8</v>
       </c>
       <c r="G424" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -14266,7 +14268,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C425" t="s">
         <v>8</v>
@@ -14281,7 +14283,7 @@
         <v>8</v>
       </c>
       <c r="G425" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -14289,7 +14291,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C426" t="s">
         <v>8</v>
@@ -14304,7 +14306,7 @@
         <v>8</v>
       </c>
       <c r="G426" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -14312,7 +14314,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C427" t="s">
         <v>8</v>
@@ -14327,7 +14329,7 @@
         <v>8</v>
       </c>
       <c r="G427" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -14335,7 +14337,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C428" t="s">
         <v>8</v>
@@ -14350,7 +14352,7 @@
         <v>8</v>
       </c>
       <c r="G428" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -14358,7 +14360,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C429" t="s">
         <v>8</v>
@@ -14373,7 +14375,7 @@
         <v>8</v>
       </c>
       <c r="G429" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -14381,7 +14383,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C430" t="s">
         <v>8</v>
@@ -14396,7 +14398,7 @@
         <v>8</v>
       </c>
       <c r="G430" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -14404,7 +14406,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C431" t="s">
         <v>8</v>
@@ -14419,7 +14421,7 @@
         <v>8</v>
       </c>
       <c r="G431" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -14427,7 +14429,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C432" t="s">
         <v>8</v>
@@ -14442,7 +14444,7 @@
         <v>8</v>
       </c>
       <c r="G432" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -14450,7 +14452,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C433" t="s">
         <v>8</v>
@@ -14465,7 +14467,7 @@
         <v>8</v>
       </c>
       <c r="G433" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -14473,7 +14475,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C434" t="s">
         <v>8</v>
@@ -14488,7 +14490,7 @@
         <v>8</v>
       </c>
       <c r="G434" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="435" spans="1:7">
@@ -14496,7 +14498,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C435" t="s">
         <v>8</v>
@@ -14511,7 +14513,7 @@
         <v>8</v>
       </c>
       <c r="G435" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -14519,7 +14521,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C436" t="s">
         <v>8</v>
@@ -14534,7 +14536,7 @@
         <v>8</v>
       </c>
       <c r="G436" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -14542,7 +14544,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C437" t="s">
         <v>8</v>
@@ -14557,7 +14559,7 @@
         <v>8</v>
       </c>
       <c r="G437" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -14565,7 +14567,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C438" t="s">
         <v>8</v>
@@ -14580,7 +14582,7 @@
         <v>8</v>
       </c>
       <c r="G438" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -14588,7 +14590,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C439" t="s">
         <v>8</v>
@@ -14603,7 +14605,7 @@
         <v>8</v>
       </c>
       <c r="G439" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -14611,7 +14613,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C440" t="s">
         <v>8</v>
@@ -14626,7 +14628,7 @@
         <v>8</v>
       </c>
       <c r="G440" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -14634,7 +14636,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C441" t="s">
         <v>8</v>
@@ -14649,7 +14651,7 @@
         <v>8</v>
       </c>
       <c r="G441" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="442" spans="1:7">
@@ -14657,7 +14659,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C442" t="s">
         <v>8</v>
@@ -14672,7 +14674,7 @@
         <v>8</v>
       </c>
       <c r="G442" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -14680,7 +14682,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -14695,7 +14697,7 @@
         <v>8</v>
       </c>
       <c r="G443" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="444" spans="1:7">
@@ -14703,7 +14705,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C444" t="s">
         <v>8</v>
@@ -14718,7 +14720,7 @@
         <v>8</v>
       </c>
       <c r="G444" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -14726,7 +14728,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C445" t="s">
         <v>8</v>
@@ -14741,7 +14743,7 @@
         <v>8</v>
       </c>
       <c r="G445" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -14749,7 +14751,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C446" t="s">
         <v>8</v>
@@ -14764,7 +14766,7 @@
         <v>8</v>
       </c>
       <c r="G446" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -14772,7 +14774,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C447" t="s">
         <v>8</v>
@@ -14787,7 +14789,7 @@
         <v>8</v>
       </c>
       <c r="G447" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -14795,7 +14797,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C448" t="s">
         <v>8</v>
@@ -14810,7 +14812,7 @@
         <v>8</v>
       </c>
       <c r="G448" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -14818,7 +14820,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C449" t="s">
         <v>8</v>
@@ -14833,7 +14835,7 @@
         <v>8</v>
       </c>
       <c r="G449" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14841,7 +14843,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C450" t="s">
         <v>8</v>
@@ -14856,7 +14858,7 @@
         <v>8</v>
       </c>
       <c r="G450" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -14864,7 +14866,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C451" t="s">
         <v>8</v>
@@ -14879,7 +14881,7 @@
         <v>8</v>
       </c>
       <c r="G451" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="452" spans="1:7">
@@ -14887,13 +14889,13 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C452" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D452" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E452" t="s">
         <v>16</v>
@@ -14902,7 +14904,7 @@
         <v>8</v>
       </c>
       <c r="G452" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -14910,7 +14912,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C453" t="s">
         <v>8</v>
@@ -14925,7 +14927,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -14933,10 +14935,10 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C454" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D454" t="s">
         <v>190</v>
@@ -14948,7 +14950,7 @@
         <v>6</v>
       </c>
       <c r="G454" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -14956,7 +14958,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C455" t="s">
         <v>8</v>
@@ -14971,7 +14973,7 @@
         <v>4</v>
       </c>
       <c r="G455" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -14979,7 +14981,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C456" t="s">
         <v>8</v>
@@ -14994,7 +14996,7 @@
         <v>7</v>
       </c>
       <c r="G456" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -15002,13 +15004,13 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C457" t="s">
         <v>8</v>
       </c>
       <c r="D457" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E457" t="s">
         <v>16</v>
@@ -15017,7 +15019,7 @@
         <v>8</v>
       </c>
       <c r="G457" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -15025,7 +15027,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C458" t="s">
         <v>8</v>
@@ -15040,7 +15042,7 @@
         <v>7</v>
       </c>
       <c r="G458" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -15048,7 +15050,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C459" t="s">
         <v>8</v>
@@ -15063,7 +15065,7 @@
         <v>7</v>
       </c>
       <c r="G459" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="460" spans="1:7">
@@ -15071,7 +15073,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C460" t="s">
         <v>8</v>
@@ -15086,7 +15088,7 @@
         <v>5</v>
       </c>
       <c r="G460" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="461" spans="1:7">
@@ -15094,7 +15096,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C461" t="s">
         <v>8</v>
@@ -15109,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G461" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -15117,7 +15119,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C462" t="s">
         <v>8</v>
@@ -15132,7 +15134,7 @@
         <v>6</v>
       </c>
       <c r="G462" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="463" spans="1:7">
@@ -15140,7 +15142,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C463" t="s">
         <v>8</v>
@@ -15155,7 +15157,7 @@
         <v>5</v>
       </c>
       <c r="G463" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -15163,7 +15165,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C464" t="s">
         <v>8</v>
@@ -15178,7 +15180,7 @@
         <v>6</v>
       </c>
       <c r="G464" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -15186,7 +15188,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C465" t="s">
         <v>8</v>
@@ -15201,7 +15203,7 @@
         <v>8</v>
       </c>
       <c r="G465" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -15209,7 +15211,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C466" t="s">
         <v>8</v>
@@ -15224,7 +15226,7 @@
         <v>8</v>
       </c>
       <c r="G466" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -15232,7 +15234,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C467" t="s">
         <v>8</v>
@@ -15247,7 +15249,7 @@
         <v>6</v>
       </c>
       <c r="G467" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -15255,7 +15257,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C468" t="s">
         <v>8</v>
@@ -15270,7 +15272,7 @@
         <v>6</v>
       </c>
       <c r="G468" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -15278,7 +15280,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C469" t="s">
         <v>8</v>
@@ -15293,7 +15295,7 @@
         <v>6</v>
       </c>
       <c r="G469" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -15301,7 +15303,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C470" t="s">
         <v>8</v>
@@ -15316,7 +15318,7 @@
         <v>6</v>
       </c>
       <c r="G470" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -15324,7 +15326,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C471" t="s">
         <v>8</v>
@@ -15339,7 +15341,7 @@
         <v>4</v>
       </c>
       <c r="G471" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -15347,7 +15349,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C472" t="s">
         <v>8</v>
@@ -15362,7 +15364,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="473" ht="13" customHeight="1" spans="1:7">
@@ -15370,7 +15372,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C473" t="s">
         <v>8</v>
@@ -15385,7 +15387,7 @@
         <v>4</v>
       </c>
       <c r="G473" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -15393,7 +15395,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C474" t="s">
         <v>8</v>
@@ -15408,7 +15410,7 @@
         <v>4</v>
       </c>
       <c r="G474" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -15416,7 +15418,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C475" t="s">
         <v>8</v>
@@ -15431,7 +15433,7 @@
         <v>6</v>
       </c>
       <c r="G475" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -15439,7 +15441,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C476" t="s">
         <v>8</v>
@@ -15454,7 +15456,7 @@
         <v>4</v>
       </c>
       <c r="G476" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -15462,7 +15464,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C477" t="s">
         <v>8</v>
@@ -15477,7 +15479,7 @@
         <v>7</v>
       </c>
       <c r="G477" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -15485,7 +15487,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C478" t="s">
         <v>8</v>
@@ -15500,7 +15502,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -15508,7 +15510,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C479" t="s">
         <v>8</v>
@@ -15523,7 +15525,7 @@
         <v>6</v>
       </c>
       <c r="G479" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -15531,7 +15533,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C480" t="s">
         <v>8</v>
@@ -15546,7 +15548,7 @@
         <v>6</v>
       </c>
       <c r="G480" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="481" spans="1:7">
@@ -15554,7 +15556,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C481" t="s">
         <v>8</v>
@@ -15569,7 +15571,7 @@
         <v>6</v>
       </c>
       <c r="G481" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="482" spans="1:7">
@@ -15577,7 +15579,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C482" t="s">
         <v>8</v>
@@ -15592,7 +15594,7 @@
         <v>8</v>
       </c>
       <c r="G482" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -15600,7 +15602,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C483" t="s">
         <v>8</v>
@@ -15615,7 +15617,7 @@
         <v>8</v>
       </c>
       <c r="G483" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -15623,7 +15625,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C484" t="s">
         <v>8</v>
@@ -15638,7 +15640,7 @@
         <v>10</v>
       </c>
       <c r="G484" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="485" ht="15" spans="1:7">
@@ -15646,7 +15648,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C485" s="3"/>
       <c r="D485" s="3" t="s">
@@ -15657,7 +15659,7 @@
       </c>
       <c r="F485" s="3"/>
       <c r="G485" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="486" ht="15" spans="1:7">
@@ -15665,7 +15667,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C486" s="3"/>
       <c r="D486" s="3" t="s">
@@ -15676,7 +15678,7 @@
       </c>
       <c r="F486" s="3"/>
       <c r="G486" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="487" ht="15" spans="1:7">
@@ -15684,7 +15686,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C487" s="3"/>
       <c r="D487" s="3" t="s">
@@ -15695,7 +15697,7 @@
       </c>
       <c r="F487" s="3"/>
       <c r="G487" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="488" ht="15" spans="1:7">
@@ -15703,7 +15705,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C488" s="3"/>
       <c r="D488" s="3" t="s">
@@ -15714,7 +15716,7 @@
       </c>
       <c r="F488" s="3"/>
       <c r="G488" s="3" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="489" ht="15" spans="1:7">
@@ -15722,7 +15724,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C489" s="3"/>
       <c r="D489" s="3" t="s">
@@ -15733,7 +15735,7 @@
       </c>
       <c r="F489" s="3"/>
       <c r="G489" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="490" ht="15" spans="1:7">
@@ -15741,7 +15743,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C490" s="3"/>
       <c r="D490" s="3" t="s">
@@ -15752,7 +15754,7 @@
       </c>
       <c r="F490" s="3"/>
       <c r="G490" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="491" ht="15" spans="1:7">
@@ -15760,7 +15762,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C491" s="3"/>
       <c r="D491" s="3" t="s">
@@ -15771,7 +15773,7 @@
       </c>
       <c r="F491" s="3"/>
       <c r="G491" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="492" ht="15" spans="1:7">
@@ -15779,7 +15781,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C492" s="3"/>
       <c r="D492" s="3" t="s">
@@ -15790,7 +15792,7 @@
       </c>
       <c r="F492" s="3"/>
       <c r="G492" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="493" ht="15" spans="1:7">
@@ -15798,7 +15800,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C493" s="3"/>
       <c r="D493" s="3" t="s">
@@ -15809,7 +15811,7 @@
       </c>
       <c r="F493" s="3"/>
       <c r="G493" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="494" ht="15" spans="1:7">
@@ -15817,7 +15819,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C494" s="3"/>
       <c r="D494" s="3" t="s">
@@ -15828,7 +15830,7 @@
       </c>
       <c r="F494" s="3"/>
       <c r="G494" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="495" ht="15" spans="1:7">
@@ -15836,7 +15838,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C495" s="3"/>
       <c r="D495" s="3" t="s">
@@ -15847,7 +15849,7 @@
       </c>
       <c r="F495" s="3"/>
       <c r="G495" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="496" ht="15" spans="1:7">
@@ -15855,7 +15857,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C496" s="3"/>
       <c r="D496" s="3" t="s">
@@ -15866,7 +15868,7 @@
       </c>
       <c r="F496" s="3"/>
       <c r="G496" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="497" spans="1:7">
@@ -15874,7 +15876,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D497" t="s">
         <v>190</v>
@@ -15886,7 +15888,7 @@
         <v>6</v>
       </c>
       <c r="G497" s="5" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -15894,7 +15896,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D498" t="s">
         <v>190</v>
@@ -15906,7 +15908,7 @@
         <v>6</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -15914,7 +15916,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D499" t="s">
         <v>190</v>
@@ -15926,7 +15928,7 @@
         <v>7</v>
       </c>
       <c r="G499" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -15934,10 +15936,10 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C500" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D500" t="s">
         <v>190</v>
@@ -15949,7 +15951,7 @@
         <v>6</v>
       </c>
       <c r="G500" s="5" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="501" spans="1:7">
@@ -15957,7 +15959,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D501" t="s">
         <v>143</v>
@@ -15966,7 +15968,7 @@
         <v>143</v>
       </c>
       <c r="G501" s="5" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="502" spans="1:7">
@@ -15974,7 +15976,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D502" t="s">
         <v>190</v>
@@ -15986,7 +15988,7 @@
         <v>6</v>
       </c>
       <c r="G502" s="5" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -15994,7 +15996,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D503" t="s">
         <v>190</v>
@@ -16006,7 +16008,7 @@
         <v>5</v>
       </c>
       <c r="G503" s="5" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="504" spans="1:7">
@@ -16014,7 +16016,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D504" t="s">
         <v>190</v>
@@ -16026,7 +16028,7 @@
         <v>6</v>
       </c>
       <c r="G504" s="5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -16034,7 +16036,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D505" t="s">
         <v>190</v>
@@ -16046,7 +16048,7 @@
         <v>6</v>
       </c>
       <c r="G505" s="5" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -16054,7 +16056,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D506" t="s">
         <v>190</v>
@@ -16066,7 +16068,7 @@
         <v>6</v>
       </c>
       <c r="G506" s="5" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -16074,7 +16076,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="6" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D507" t="s">
         <v>190</v>
@@ -16086,7 +16088,7 @@
         <v>6</v>
       </c>
       <c r="G507" s="5" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -16094,7 +16096,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D508" t="s">
         <v>190</v>
@@ -16106,7 +16108,7 @@
         <v>6</v>
       </c>
       <c r="G508" s="5" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -16114,7 +16116,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D509" t="s">
         <v>190</v>
@@ -16126,7 +16128,7 @@
         <v>6</v>
       </c>
       <c r="G509" s="5" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -16134,7 +16136,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D510" t="s">
         <v>190</v>
@@ -16146,7 +16148,7 @@
         <v>6</v>
       </c>
       <c r="G510" s="5" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -16154,7 +16156,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D511" t="s">
         <v>190</v>
@@ -16166,7 +16168,7 @@
         <v>6</v>
       </c>
       <c r="G511" s="5" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -16174,7 +16176,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D512" t="s">
         <v>190</v>
@@ -16186,7 +16188,7 @@
         <v>7</v>
       </c>
       <c r="G512" s="5" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -16194,7 +16196,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D513" t="s">
         <v>190</v>
@@ -16206,7 +16208,7 @@
         <v>6</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -16214,7 +16216,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="6" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D514" t="s">
         <v>190</v>
@@ -16226,7 +16228,7 @@
         <v>6</v>
       </c>
       <c r="G514" s="5" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -16234,10 +16236,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D515" t="s">
         <v>16</v>
@@ -16246,7 +16248,7 @@
         <v>16</v>
       </c>
       <c r="G515" s="5" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -16254,7 +16256,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D516" t="s">
         <v>143</v>
@@ -16263,7 +16265,7 @@
         <v>143</v>
       </c>
       <c r="G516" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -16271,7 +16273,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D517" t="s">
         <v>190</v>
@@ -16283,7 +16285,7 @@
         <v>6</v>
       </c>
       <c r="G517" s="5" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -16291,7 +16293,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D518" t="s">
         <v>190</v>
@@ -16303,7 +16305,7 @@
         <v>6</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -16311,7 +16313,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D519" t="s">
         <v>190</v>
@@ -16323,7 +16325,7 @@
         <v>5</v>
       </c>
       <c r="G519" s="5" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -16331,10 +16333,10 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C520" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D520" t="s">
         <v>190</v>
@@ -16346,7 +16348,7 @@
         <v>6</v>
       </c>
       <c r="G520" s="5" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -16354,7 +16356,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="7" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D521" t="s">
         <v>190</v>
@@ -16366,7 +16368,7 @@
         <v>6</v>
       </c>
       <c r="G521" s="5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="522" ht="15" spans="1:7">
@@ -16374,7 +16376,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D522" t="s">
         <v>190</v>
@@ -16385,8 +16387,8 @@
       <c r="F522">
         <v>6</v>
       </c>
-      <c r="G522" s="8" t="s">
-        <v>1152</v>
+      <c r="G522" s="3" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="523" ht="15" spans="1:7">
@@ -16394,7 +16396,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D523" t="s">
         <v>190</v>
@@ -16405,8 +16407,8 @@
       <c r="F523">
         <v>6</v>
       </c>
-      <c r="G523" s="8" t="s">
-        <v>1154</v>
+      <c r="G523" s="3" t="s">
+        <v>1155</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="1157">
   <si>
     <t>id</t>
   </si>
@@ -3399,6 +3399,9 @@
   </si>
   <si>
     <t>洗劫伦敦所有的玫瑰</t>
+  </si>
+  <si>
+    <t>洗劫伦敦所有玫瑰,洗劫伦敦所有的玫瑰</t>
   </si>
   <si>
     <t>https://pan.quark.cn/s/f7774ffd6157</t>
@@ -16098,6 +16101,9 @@
       <c r="B508" t="s">
         <v>1122</v>
       </c>
+      <c r="C508" t="s">
+        <v>1123</v>
+      </c>
       <c r="D508" t="s">
         <v>190</v>
       </c>
@@ -16108,7 +16114,7 @@
         <v>6</v>
       </c>
       <c r="G508" s="5" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -16116,7 +16122,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D509" t="s">
         <v>190</v>
@@ -16128,7 +16134,7 @@
         <v>6</v>
       </c>
       <c r="G509" s="5" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -16136,7 +16142,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D510" t="s">
         <v>190</v>
@@ -16148,7 +16154,7 @@
         <v>6</v>
       </c>
       <c r="G510" s="5" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -16156,7 +16162,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D511" t="s">
         <v>190</v>
@@ -16168,7 +16174,7 @@
         <v>6</v>
       </c>
       <c r="G511" s="5" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -16176,7 +16182,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D512" t="s">
         <v>190</v>
@@ -16188,7 +16194,7 @@
         <v>7</v>
       </c>
       <c r="G512" s="5" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -16196,7 +16202,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D513" t="s">
         <v>190</v>
@@ -16208,7 +16214,7 @@
         <v>6</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -16216,7 +16222,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D514" t="s">
         <v>190</v>
@@ -16228,7 +16234,7 @@
         <v>6</v>
       </c>
       <c r="G514" s="5" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -16236,10 +16242,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D515" t="s">
         <v>16</v>
@@ -16248,7 +16254,7 @@
         <v>16</v>
       </c>
       <c r="G515" s="5" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -16256,7 +16262,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D516" t="s">
         <v>143</v>
@@ -16265,7 +16271,7 @@
         <v>143</v>
       </c>
       <c r="G516" s="5" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -16273,7 +16279,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="6" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D517" t="s">
         <v>190</v>
@@ -16285,7 +16291,7 @@
         <v>6</v>
       </c>
       <c r="G517" s="5" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -16293,7 +16299,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D518" t="s">
         <v>190</v>
@@ -16305,7 +16311,7 @@
         <v>6</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -16313,7 +16319,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D519" t="s">
         <v>190</v>
@@ -16325,7 +16331,7 @@
         <v>5</v>
       </c>
       <c r="G519" s="5" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -16333,10 +16339,10 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C520" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D520" t="s">
         <v>190</v>
@@ -16348,7 +16354,7 @@
         <v>6</v>
       </c>
       <c r="G520" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -16356,7 +16362,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="7" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D521" t="s">
         <v>190</v>
@@ -16368,7 +16374,7 @@
         <v>6</v>
       </c>
       <c r="G521" s="5" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="522" ht="15" spans="1:7">
@@ -16376,7 +16382,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D522" t="s">
         <v>190</v>
@@ -16388,7 +16394,7 @@
         <v>6</v>
       </c>
       <c r="G522" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="523" ht="15" spans="1:7">
@@ -16396,7 +16402,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D523" t="s">
         <v>190</v>
@@ -16408,7 +16414,7 @@
         <v>6</v>
       </c>
       <c r="G523" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2811" uniqueCount="1159">
   <si>
     <t>id</t>
   </si>
@@ -3518,6 +3518,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/db1a18bd2f60</t>
+  </si>
+  <si>
+    <t>甜蜜的家</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/bf8609aea9c7</t>
   </si>
 </sst>
 </file>
@@ -4149,7 +4155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4160,6 +4166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4506,7 +4513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G523"/>
+  <dimension ref="A1:G524"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16415,6 +16422,26 @@
       </c>
       <c r="G523" s="3" t="s">
         <v>1156</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7">
+      <c r="A524">
+        <v>523</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D524" t="s">
+        <v>190</v>
+      </c>
+      <c r="E524" t="s">
+        <v>190</v>
+      </c>
+      <c r="F524">
+        <v>5</v>
+      </c>
+      <c r="G524" s="8" t="s">
+        <v>1158</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$524</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2811" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="1161">
   <si>
     <t>id</t>
   </si>
@@ -3524,6 +3524,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/bf8609aea9c7</t>
+  </si>
+  <si>
+    <t>偷吃</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/59dae98979cd</t>
   </si>
 </sst>
 </file>
@@ -4513,7 +4519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G524"/>
+  <dimension ref="A1:G525"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16440,12 +16446,32 @@
       <c r="F524">
         <v>5</v>
       </c>
-      <c r="G524" s="8" t="s">
+      <c r="G524" s="5" t="s">
         <v>1158</v>
       </c>
     </row>
+    <row r="525" spans="1:7">
+      <c r="A525">
+        <v>524</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D525" t="s">
+        <v>190</v>
+      </c>
+      <c r="E525" t="s">
+        <v>190</v>
+      </c>
+      <c r="F525">
+        <v>6</v>
+      </c>
+      <c r="G525" s="8" t="s">
+        <v>1160</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G523" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G524" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$525</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="1165">
   <si>
     <t>id</t>
   </si>
@@ -3530,6 +3530,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/59dae98979cd</t>
+  </si>
+  <si>
+    <t>如故</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/2acbaeeee408</t>
+  </si>
+  <si>
+    <t>野菩萨</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0c8001b09ec5</t>
   </si>
 </sst>
 </file>
@@ -4161,7 +4173,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4172,7 +4184,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4519,7 +4530,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G525"/>
+  <dimension ref="A1:G527"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16466,12 +16477,52 @@
       <c r="F525">
         <v>6</v>
       </c>
-      <c r="G525" s="8" t="s">
+      <c r="G525" s="5" t="s">
         <v>1160</v>
       </c>
     </row>
+    <row r="526" spans="1:7">
+      <c r="A526">
+        <v>525</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D526" t="s">
+        <v>190</v>
+      </c>
+      <c r="E526" t="s">
+        <v>190</v>
+      </c>
+      <c r="F526">
+        <v>6</v>
+      </c>
+      <c r="G526" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7">
+      <c r="A527">
+        <v>526</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D527" t="s">
+        <v>190</v>
+      </c>
+      <c r="E527" t="s">
+        <v>190</v>
+      </c>
+      <c r="F527">
+        <v>6</v>
+      </c>
+      <c r="G527" t="s">
+        <v>1164</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G524" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G525" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$525</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$527</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="1169">
   <si>
     <t>id</t>
   </si>
@@ -3543,6 +3543,18 @@
   <si>
     <t>https://pan.quark.cn/s/0c8001b09ec5</t>
   </si>
+  <si>
+    <t>继承者</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e371c53d8bbd</t>
+  </si>
+  <si>
+    <t>鬼河怒放</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f9f1a734c277</t>
+  </si>
 </sst>
 </file>
 
@@ -3554,7 +3566,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3594,6 +3606,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4052,128 +4070,128 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4184,6 +4202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4530,7 +4549,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G527"/>
+  <dimension ref="A1:G529"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16521,8 +16540,48 @@
         <v>1164</v>
       </c>
     </row>
+    <row r="528" spans="1:7">
+      <c r="A528">
+        <v>527</v>
+      </c>
+      <c r="B528" s="8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D528" t="s">
+        <v>190</v>
+      </c>
+      <c r="E528" t="s">
+        <v>190</v>
+      </c>
+      <c r="F528">
+        <v>6</v>
+      </c>
+      <c r="G528" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7">
+      <c r="A529">
+        <v>528</v>
+      </c>
+      <c r="B529" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D529" t="s">
+        <v>190</v>
+      </c>
+      <c r="E529" t="s">
+        <v>190</v>
+      </c>
+      <c r="F529">
+        <v>6</v>
+      </c>
+      <c r="G529" t="s">
+        <v>1168</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G525" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G527" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$530</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="1171">
   <si>
     <t>id</t>
   </si>
@@ -3554,6 +3554,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/f9f1a734c277</t>
+  </si>
+  <si>
+    <t>老鼠记者</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/17ad7974e3b7</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4203,6 +4209,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4549,7 +4556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G529"/>
+  <dimension ref="A1:G530"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16580,8 +16587,25 @@
         <v>1168</v>
       </c>
     </row>
+    <row r="530" spans="1:7">
+      <c r="A530">
+        <v>529</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D530" t="s">
+        <v>143</v>
+      </c>
+      <c r="E530" t="s">
+        <v>143</v>
+      </c>
+      <c r="G530" s="9" t="s">
+        <v>1170</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G527" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G530" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="1174">
   <si>
     <t>id</t>
   </si>
@@ -3560,6 +3560,15 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/17ad7974e3b7</t>
+  </si>
+  <si>
+    <t>归昼</t>
+  </si>
+  <si>
+    <t>归昼,Life again</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e8cb872e3bf3</t>
   </si>
 </sst>
 </file>
@@ -4556,7 +4565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G530"/>
+  <dimension ref="A1:G531"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16600,8 +16609,31 @@
       <c r="E530" t="s">
         <v>143</v>
       </c>
-      <c r="G530" s="9" t="s">
+      <c r="G530" s="5" t="s">
         <v>1170</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7">
+      <c r="A531">
+        <v>530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D531" t="s">
+        <v>190</v>
+      </c>
+      <c r="E531" t="s">
+        <v>190</v>
+      </c>
+      <c r="F531">
+        <v>6</v>
+      </c>
+      <c r="G531" s="9" t="s">
+        <v>1173</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$530</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$531</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="1180">
   <si>
     <t>id</t>
   </si>
@@ -3569,6 +3569,24 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/e8cb872e3bf3</t>
+  </si>
+  <si>
+    <t>血色唐人街</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/090f5f5206c5</t>
+  </si>
+  <si>
+    <t>再见苏西</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c5d5fff3ec00</t>
+  </si>
+  <si>
+    <t>女帝攻略</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4bc5ec8b5dee</t>
   </si>
 </sst>
 </file>
@@ -4218,7 +4236,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4565,7 +4583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G531"/>
+  <dimension ref="A1:G534"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16632,12 +16650,72 @@
       <c r="F531">
         <v>6</v>
       </c>
-      <c r="G531" s="9" t="s">
+      <c r="G531" s="5" t="s">
         <v>1173</v>
       </c>
     </row>
+    <row r="532" spans="1:7">
+      <c r="A532">
+        <v>531</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D532" t="s">
+        <v>190</v>
+      </c>
+      <c r="E532" t="s">
+        <v>190</v>
+      </c>
+      <c r="F532">
+        <v>6</v>
+      </c>
+      <c r="G532" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7">
+      <c r="A533">
+        <v>532</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D533" t="s">
+        <v>190</v>
+      </c>
+      <c r="E533" t="s">
+        <v>190</v>
+      </c>
+      <c r="F533">
+        <v>5</v>
+      </c>
+      <c r="G533" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7">
+      <c r="A534">
+        <v>533</v>
+      </c>
+      <c r="B534" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D534" t="s">
+        <v>190</v>
+      </c>
+      <c r="E534" t="s">
+        <v>190</v>
+      </c>
+      <c r="F534">
+        <v>6</v>
+      </c>
+      <c r="G534" t="s">
+        <v>1179</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G530" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G531" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$531</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$534</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1184">
   <si>
     <t>id</t>
   </si>
@@ -3587,6 +3587,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/4bc5ec8b5dee</t>
+  </si>
+  <si>
+    <t>金粉</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7a0fb33da2cc</t>
+  </si>
+  <si>
+    <t>绿洲</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3b7095e9fcf7</t>
   </si>
 </sst>
 </file>
@@ -4236,7 +4248,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4583,7 +4595,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G534"/>
+  <dimension ref="A1:G536"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16698,7 +16710,7 @@
       <c r="A534">
         <v>533</v>
       </c>
-      <c r="B534" s="9" t="s">
+      <c r="B534" s="6" t="s">
         <v>1178</v>
       </c>
       <c r="D534" t="s">
@@ -16714,8 +16726,48 @@
         <v>1179</v>
       </c>
     </row>
+    <row r="535" spans="1:7">
+      <c r="A535">
+        <v>534</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D535" t="s">
+        <v>190</v>
+      </c>
+      <c r="E535" t="s">
+        <v>190</v>
+      </c>
+      <c r="F535">
+        <v>7</v>
+      </c>
+      <c r="G535" s="9" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7">
+      <c r="A536">
+        <v>535</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D536" t="s">
+        <v>190</v>
+      </c>
+      <c r="E536" t="s">
+        <v>190</v>
+      </c>
+      <c r="F536">
+        <v>6</v>
+      </c>
+      <c r="G536" s="9" t="s">
+        <v>1183</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G531" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G534" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\quark-dynamic\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D51E0AC-57E4-47DB-B5DD-AFBEA29B1966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,24 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$534</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="1188">
   <si>
     <t>id</t>
   </si>
@@ -3460,7 +3453,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Segoe UI"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>,Only Murders,only murder</t>
     </r>
@@ -3599,19 +3592,25 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/3b7095e9fcf7</t>
+  </si>
+  <si>
+    <t>游轮谜影</t>
+  </si>
+  <si>
+    <t>疯人塔</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/cbec5b40475d</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f8d67521cedd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3624,7 +3623,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3632,7 +3631,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3651,338 +3650,29 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Roboto"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3990,321 +3680,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4589,21 +3995,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G536"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G538"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="35.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="4" max="4" width="35.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4626,7 +4032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4649,7 +4055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4672,7 +4078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4695,7 +4101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4718,7 +4124,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4741,7 +4147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4764,7 +4170,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4787,7 +4193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4810,7 +4216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4833,7 +4239,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4856,7 +4262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4879,7 +4285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4902,7 +4308,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4925,7 +4331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4948,7 +4354,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4971,7 +4377,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4994,7 +4400,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5017,7 +4423,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5040,7 +4446,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5063,7 +4469,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5086,7 +4492,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5109,7 +4515,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5132,7 +4538,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5155,7 +4561,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5178,7 +4584,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5201,7 +4607,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5224,7 +4630,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5247,7 +4653,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5270,7 +4676,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5293,7 +4699,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5316,7 +4722,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5339,7 +4745,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5362,7 +4768,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5385,7 +4791,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5408,7 +4814,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5431,7 +4837,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5454,7 +4860,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5477,7 +4883,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5500,7 +4906,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5523,7 +4929,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5546,7 +4952,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5569,7 +4975,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5592,7 +4998,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5615,7 +5021,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5638,7 +5044,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5661,7 +5067,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5684,7 +5090,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5707,7 +5113,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5730,7 +5136,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5753,7 +5159,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5776,7 +5182,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5799,7 +5205,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5822,7 +5228,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5845,7 +5251,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5868,7 +5274,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5891,7 +5297,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5914,7 +5320,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5937,7 +5343,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5960,7 +5366,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5983,7 +5389,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6006,7 +5412,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6029,7 +5435,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6052,7 +5458,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6075,7 +5481,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6098,7 +5504,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6121,7 +5527,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6144,7 +5550,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6167,7 +5573,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6190,7 +5596,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6213,7 +5619,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6236,7 +5642,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6259,7 +5665,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6282,7 +5688,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6305,7 +5711,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6328,7 +5734,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6351,7 +5757,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6374,7 +5780,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6397,7 +5803,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6420,7 +5826,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6443,7 +5849,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6466,7 +5872,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6489,7 +5895,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6512,7 +5918,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6535,7 +5941,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6558,7 +5964,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6581,7 +5987,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6604,7 +6010,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6627,7 +6033,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6650,7 +6056,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6673,7 +6079,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6696,7 +6102,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6719,7 +6125,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6742,7 +6148,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6765,7 +6171,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6788,7 +6194,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6811,7 +6217,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6834,7 +6240,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6857,7 +6263,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6880,7 +6286,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6903,7 +6309,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6926,7 +6332,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6949,7 +6355,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6972,7 +6378,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6995,7 +6401,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7018,7 +6424,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7041,7 +6447,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7064,7 +6470,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7087,7 +6493,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7110,7 +6516,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7133,7 +6539,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7156,7 +6562,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7179,7 +6585,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7202,7 +6608,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7225,7 +6631,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7248,7 +6654,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7271,7 +6677,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7294,7 +6700,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7317,7 +6723,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7340,7 +6746,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7363,7 +6769,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7386,7 +6792,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7409,7 +6815,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7432,7 +6838,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7455,7 +6861,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7478,7 +6884,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7501,7 +6907,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7524,7 +6930,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7547,7 +6953,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7570,7 +6976,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7593,7 +6999,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7616,7 +7022,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7639,7 +7045,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7662,7 +7068,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7685,7 +7091,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7708,7 +7114,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7731,7 +7137,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7754,7 +7160,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7777,7 +7183,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7800,7 +7206,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7823,7 +7229,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7846,7 +7252,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7869,7 +7275,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7892,7 +7298,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7915,7 +7321,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7938,7 +7344,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7961,7 +7367,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7984,7 +7390,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8007,7 +7413,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8030,7 +7436,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8053,7 +7459,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8076,7 +7482,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8099,7 +7505,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8122,7 +7528,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8145,7 +7551,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8168,7 +7574,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8191,7 +7597,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8214,7 +7620,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8237,7 +7643,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8260,7 +7666,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8283,7 +7689,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8306,7 +7712,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8329,7 +7735,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8352,7 +7758,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8375,7 +7781,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8398,7 +7804,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8421,7 +7827,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8444,7 +7850,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8467,7 +7873,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8490,7 +7896,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8513,7 +7919,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8536,7 +7942,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8559,7 +7965,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -8582,7 +7988,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8605,7 +8011,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8628,7 +8034,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8651,7 +8057,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8674,7 +8080,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8697,7 +8103,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8720,7 +8126,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8743,7 +8149,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8766,7 +8172,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8789,7 +8195,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8812,7 +8218,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -8835,7 +8241,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -8858,7 +8264,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -8881,7 +8287,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -8904,7 +8310,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -8927,7 +8333,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -8950,7 +8356,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -8973,7 +8379,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -8996,7 +8402,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9019,7 +8425,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9042,7 +8448,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9065,7 +8471,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9088,7 +8494,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9111,7 +8517,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9134,7 +8540,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -9157,7 +8563,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -9180,7 +8586,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -9203,7 +8609,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -9226,7 +8632,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -9249,7 +8655,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -9272,7 +8678,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -9295,7 +8701,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -9318,7 +8724,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -9341,7 +8747,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -9364,7 +8770,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -9387,7 +8793,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -9410,7 +8816,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -9433,7 +8839,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -9456,7 +8862,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -9479,7 +8885,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -9502,7 +8908,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -9525,7 +8931,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -9548,7 +8954,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -9571,7 +8977,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -9594,7 +9000,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -9617,7 +9023,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -9640,7 +9046,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -9663,7 +9069,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -9686,7 +9092,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -9709,7 +9115,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -9732,7 +9138,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -9755,7 +9161,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -9778,7 +9184,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -9801,7 +9207,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -9824,7 +9230,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -9847,7 +9253,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -9870,7 +9276,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -9893,7 +9299,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -9916,7 +9322,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -9939,7 +9345,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -9962,7 +9368,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -9985,7 +9391,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -10008,7 +9414,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -10031,7 +9437,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -10054,7 +9460,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -10077,7 +9483,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -10100,7 +9506,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -10123,7 +9529,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -10146,7 +9552,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -10169,7 +9575,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -10192,7 +9598,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -10215,7 +9621,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -10238,7 +9644,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -10261,7 +9667,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -10284,7 +9690,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -10307,7 +9713,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -10330,7 +9736,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -10353,7 +9759,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -10376,7 +9782,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -10399,7 +9805,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -10422,7 +9828,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -10445,7 +9851,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -10468,7 +9874,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -10491,7 +9897,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -10514,7 +9920,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -10537,7 +9943,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -10560,7 +9966,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -10583,7 +9989,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -10606,7 +10012,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -10629,7 +10035,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -10652,7 +10058,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -10675,7 +10081,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -10698,7 +10104,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -10721,7 +10127,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -10744,7 +10150,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -10767,7 +10173,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -10790,7 +10196,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -10813,7 +10219,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -10836,7 +10242,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -10859,7 +10265,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -10882,7 +10288,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -10905,7 +10311,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -10928,7 +10334,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -10951,7 +10357,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -10974,7 +10380,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -10997,7 +10403,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -11020,7 +10426,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -11043,7 +10449,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -11066,7 +10472,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -11089,7 +10495,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -11112,7 +10518,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -11135,7 +10541,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -11158,7 +10564,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -11181,7 +10587,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -11204,7 +10610,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -11227,7 +10633,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -11250,7 +10656,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -11273,7 +10679,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -11296,7 +10702,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -11319,7 +10725,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -11342,7 +10748,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -11365,7 +10771,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -11388,7 +10794,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -11411,7 +10817,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -11434,7 +10840,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -11457,7 +10863,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -11480,7 +10886,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -11503,7 +10909,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -11526,7 +10932,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -11549,7 +10955,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -11572,7 +10978,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -11595,7 +11001,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -11618,7 +11024,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -11641,7 +11047,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -11664,7 +11070,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -11687,7 +11093,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -11710,7 +11116,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -11733,7 +11139,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -11756,7 +11162,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -11779,7 +11185,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -11802,7 +11208,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -11825,7 +11231,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -11848,7 +11254,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -11871,7 +11277,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -11894,7 +11300,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -11917,7 +11323,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -11940,7 +11346,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -11963,7 +11369,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -11986,7 +11392,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -12009,7 +11415,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -12032,7 +11438,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -12055,7 +11461,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -12078,7 +11484,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -12101,7 +11507,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -12124,7 +11530,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -12147,7 +11553,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -12170,7 +11576,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -12193,7 +11599,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -12216,7 +11622,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -12239,7 +11645,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -12262,7 +11668,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
@@ -12285,7 +11691,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -12308,7 +11714,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -12331,7 +11737,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -12354,7 +11760,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -12377,7 +11783,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -12400,7 +11806,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -12423,7 +11829,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -12446,7 +11852,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -12469,7 +11875,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -12492,7 +11898,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -12515,7 +11921,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -12538,7 +11944,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -12561,7 +11967,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -12584,7 +11990,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -12607,7 +12013,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -12630,7 +12036,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -12653,7 +12059,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -12676,7 +12082,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -12699,7 +12105,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -12722,7 +12128,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -12745,7 +12151,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -12768,7 +12174,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -12791,7 +12197,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -12814,7 +12220,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -12837,7 +12243,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -12860,7 +12266,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -12883,7 +12289,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -12906,7 +12312,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -12929,7 +12335,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -12952,7 +12358,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -12975,7 +12381,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -12998,7 +12404,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -13021,7 +12427,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -13044,7 +12450,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -13067,7 +12473,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -13090,7 +12496,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -13113,7 +12519,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -13136,7 +12542,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -13159,7 +12565,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -13182,7 +12588,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -13205,7 +12611,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -13228,7 +12634,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -13251,7 +12657,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -13274,7 +12680,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -13297,7 +12703,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -13320,7 +12726,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -13343,7 +12749,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -13366,7 +12772,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -13389,7 +12795,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -13412,7 +12818,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -13435,7 +12841,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -13458,7 +12864,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -13481,7 +12887,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -13504,7 +12910,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -13527,7 +12933,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -13550,7 +12956,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -13573,7 +12979,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -13596,7 +13002,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -13619,7 +13025,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -13642,7 +13048,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -13665,7 +13071,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -13688,7 +13094,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -13711,7 +13117,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -13734,7 +13140,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -13757,7 +13163,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -13780,7 +13186,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -13803,7 +13209,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -13826,7 +13232,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -13849,7 +13255,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -13872,7 +13278,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -13895,7 +13301,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -13918,7 +13324,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -13941,7 +13347,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -13964,7 +13370,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -13987,7 +13393,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -14010,7 +13416,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -14033,7 +13439,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -14056,7 +13462,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -14079,7 +13485,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -14102,7 +13508,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -14125,7 +13531,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -14148,7 +13554,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -14171,7 +13577,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -14194,7 +13600,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -14217,7 +13623,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -14240,7 +13646,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -14263,7 +13669,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -14286,7 +13692,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -14309,7 +13715,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -14332,7 +13738,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -14355,7 +13761,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -14378,7 +13784,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -14401,7 +13807,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -14424,7 +13830,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -14447,7 +13853,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -14470,7 +13876,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -14493,7 +13899,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -14516,7 +13922,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -14539,7 +13945,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -14562,7 +13968,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -14585,7 +13991,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -14608,7 +14014,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -14631,7 +14037,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -14654,7 +14060,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -14677,7 +14083,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -14700,7 +14106,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -14723,7 +14129,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -14746,7 +14152,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -14769,7 +14175,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -14792,7 +14198,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -14815,7 +14221,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -14838,7 +14244,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -14861,7 +14267,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -14884,7 +14290,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -14907,7 +14313,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -14930,7 +14336,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -14953,7 +14359,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -14976,7 +14382,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -14999,7 +14405,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -15022,7 +14428,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -15045,7 +14451,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -15068,7 +14474,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -15091,7 +14497,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -15114,7 +14520,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -15137,7 +14543,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -15160,7 +14566,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -15183,7 +14589,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -15206,7 +14612,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -15229,7 +14635,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -15252,7 +14658,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -15275,7 +14681,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -15298,7 +14704,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -15321,7 +14727,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -15344,7 +14750,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -15367,7 +14773,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -15390,7 +14796,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -15413,7 +14819,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -15436,7 +14842,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -15459,7 +14865,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="473" ht="13" customHeight="1" spans="1:7">
+    <row r="473" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -15482,7 +14888,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -15505,7 +14911,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -15528,7 +14934,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -15551,7 +14957,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -15574,7 +14980,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -15597,7 +15003,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -15620,7 +15026,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -15643,7 +15049,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -15666,7 +15072,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -15689,7 +15095,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -15712,7 +15118,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -15735,7 +15141,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="485" ht="15" spans="1:7">
+    <row r="485" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -15754,7 +15160,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="486" ht="15" spans="1:7">
+    <row r="486" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -15773,7 +15179,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="487" ht="15" spans="1:7">
+    <row r="487" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -15792,7 +15198,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="488" ht="15" spans="1:7">
+    <row r="488" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -15811,7 +15217,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="489" ht="15" spans="1:7">
+    <row r="489" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -15830,7 +15236,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="490" ht="15" spans="1:7">
+    <row r="490" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -15849,7 +15255,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="491" ht="15" spans="1:7">
+    <row r="491" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -15868,7 +15274,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="492" ht="15" spans="1:7">
+    <row r="492" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -15887,7 +15293,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="493" ht="15" spans="1:7">
+    <row r="493" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -15906,7 +15312,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="494" ht="15" spans="1:7">
+    <row r="494" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -15925,7 +15331,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="495" ht="15" spans="1:7">
+    <row r="495" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -15944,7 +15350,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="496" ht="15" spans="1:7">
+    <row r="496" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -15963,7 +15369,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A497">
         <v>496</v>
       </c>
@@ -15983,7 +15389,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -16003,7 +15409,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -16023,7 +15429,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A500">
         <v>499</v>
       </c>
@@ -16046,7 +15452,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A501">
         <v>500</v>
       </c>
@@ -16063,7 +15469,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
+    <row r="502" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A502">
         <v>501</v>
       </c>
@@ -16083,7 +15489,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="503" spans="1:7">
+    <row r="503" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A503">
         <v>502</v>
       </c>
@@ -16103,7 +15509,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A504">
         <v>503</v>
       </c>
@@ -16123,7 +15529,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A505">
         <v>504</v>
       </c>
@@ -16143,7 +15549,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A506">
         <v>505</v>
       </c>
@@ -16163,11 +15569,11 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A507">
         <v>506</v>
       </c>
-      <c r="B507" s="6" t="s">
+      <c r="B507" t="s">
         <v>1120</v>
       </c>
       <c r="D507" t="s">
@@ -16183,7 +15589,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A508">
         <v>507</v>
       </c>
@@ -16206,7 +15612,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A509">
         <v>508</v>
       </c>
@@ -16226,7 +15632,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A510">
         <v>509</v>
       </c>
@@ -16246,7 +15652,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A511">
         <v>510</v>
       </c>
@@ -16266,7 +15672,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A512">
         <v>511</v>
       </c>
@@ -16286,7 +15692,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -16306,11 +15712,11 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A514">
         <v>513</v>
       </c>
-      <c r="B514" s="6" t="s">
+      <c r="B514" t="s">
         <v>1135</v>
       </c>
       <c r="D514" t="s">
@@ -16326,7 +15732,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A515">
         <v>514</v>
       </c>
@@ -16346,7 +15752,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="516" spans="1:7">
+    <row r="516" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A516">
         <v>515</v>
       </c>
@@ -16363,11 +15769,11 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="517" spans="1:7">
+    <row r="517" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A517">
         <v>516</v>
       </c>
-      <c r="B517" s="6" t="s">
+      <c r="B517" t="s">
         <v>1142</v>
       </c>
       <c r="D517" t="s">
@@ -16383,7 +15789,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="518" spans="1:7">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -16403,7 +15809,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="519" spans="1:7">
+    <row r="519" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A519">
         <v>518</v>
       </c>
@@ -16423,7 +15829,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A520">
         <v>519</v>
       </c>
@@ -16446,11 +15852,11 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A521">
         <v>520</v>
       </c>
-      <c r="B521" s="7" t="s">
+      <c r="B521" s="6" t="s">
         <v>1151</v>
       </c>
       <c r="D521" t="s">
@@ -16466,7 +15872,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="522" ht="15" spans="1:7">
+    <row r="522" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>521</v>
       </c>
@@ -16486,7 +15892,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="523" ht="15" spans="1:7">
+    <row r="523" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -16506,7 +15912,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A524">
         <v>523</v>
       </c>
@@ -16526,7 +15932,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A525">
         <v>524</v>
       </c>
@@ -16546,7 +15952,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -16566,7 +15972,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="527" spans="1:7">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>526</v>
       </c>
@@ -16586,11 +15992,11 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>527</v>
       </c>
-      <c r="B528" s="8" t="s">
+      <c r="B528" s="7" t="s">
         <v>1165</v>
       </c>
       <c r="D528" t="s">
@@ -16606,11 +16012,11 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>528</v>
       </c>
-      <c r="B529" s="8" t="s">
+      <c r="B529" s="7" t="s">
         <v>1167</v>
       </c>
       <c r="D529" t="s">
@@ -16626,7 +16032,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A530">
         <v>529</v>
       </c>
@@ -16643,7 +16049,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A531">
         <v>530</v>
       </c>
@@ -16666,7 +16072,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="532" spans="1:7">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>531</v>
       </c>
@@ -16686,7 +16092,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="533" spans="1:7">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>532</v>
       </c>
@@ -16706,11 +16112,11 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>533</v>
       </c>
-      <c r="B534" s="6" t="s">
+      <c r="B534" t="s">
         <v>1178</v>
       </c>
       <c r="D534" t="s">
@@ -16726,7 +16132,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="535" spans="1:7">
+    <row r="535" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A535">
         <v>534</v>
       </c>
@@ -16742,11 +16148,11 @@
       <c r="F535">
         <v>7</v>
       </c>
-      <c r="G535" s="9" t="s">
+      <c r="G535" s="5" t="s">
         <v>1181</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
+    <row r="536" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A536">
         <v>535</v>
       </c>
@@ -16762,24 +16168,62 @@
       <c r="F536">
         <v>6</v>
       </c>
-      <c r="G536" s="9" t="s">
+      <c r="G536" s="5" t="s">
         <v>1183</v>
       </c>
     </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>536</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D537" t="s">
+        <v>190</v>
+      </c>
+      <c r="E537" t="s">
+        <v>190</v>
+      </c>
+      <c r="F537">
+        <v>6</v>
+      </c>
+      <c r="G537" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>537</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D538" t="s">
+        <v>190</v>
+      </c>
+      <c r="E538" t="s">
+        <v>190</v>
+      </c>
+      <c r="F538">
+        <v>5</v>
+      </c>
+      <c r="G538" t="s">
+        <v>1187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G534" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:G534" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G71" r:id="rId1" display="https://pan.quark.cn/s/54ae4c79b6ef"/>
-    <hyperlink ref="G75" r:id="rId2" display="https://pan.quark.cn/s/32466a4d8102"/>
-    <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
-    <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
-    <hyperlink ref="G281" r:id="rId5" display="https://pan.quark.cn/s/18f5ee8d2498"/>
-    <hyperlink ref="G513" r:id="rId6" display="https://pan.quark.cn/s/4097a88042e9"/>
-    <hyperlink ref="G518" r:id="rId7" display="https://pan.quark.cn/s/90d96d395a84"/>
+    <hyperlink ref="G71" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G75" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G498" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G281" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G513" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G518" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,29 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\quark-dynamic\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D51E0AC-57E4-47DB-B5DD-AFBEA29B1966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$534</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$538</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="1190">
   <si>
     <t>id</t>
   </si>
@@ -3453,7 +3460,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>,Only Murders,only murder</t>
     </r>
@@ -3597,20 +3604,32 @@
     <t>游轮谜影</t>
   </si>
   <si>
+    <t>https://pan.quark.cn/s/cbec5b40475d</t>
+  </si>
+  <si>
     <t>疯人塔</t>
   </si>
   <si>
-    <t>https://pan.quark.cn/s/cbec5b40475d</t>
-  </si>
-  <si>
     <t>https://pan.quark.cn/s/f8d67521cedd</t>
+  </si>
+  <si>
+    <t>北京爱情图鉴</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5ae04db230de</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3650,29 +3669,346 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Roboto"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3680,17 +4016,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3699,18 +4274,61 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3995,21 +4613,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G538"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G539"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
-    <col min="4" max="4" width="35.36328125" customWidth="1"/>
+    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="35.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4032,7 +4650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4055,7 +4673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4078,7 +4696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4101,7 +4719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4124,7 +4742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4147,7 +4765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4170,7 +4788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4193,7 +4811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4216,7 +4834,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4239,7 +4857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4262,7 +4880,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4285,7 +4903,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4308,7 +4926,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4331,7 +4949,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4354,7 +4972,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4377,7 +4995,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4400,7 +5018,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4423,7 +5041,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4446,7 +5064,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4469,7 +5087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4492,7 +5110,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4515,7 +5133,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4538,7 +5156,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4561,7 +5179,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4584,7 +5202,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4607,7 +5225,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4630,7 +5248,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4653,7 +5271,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4676,7 +5294,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4699,7 +5317,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4722,7 +5340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4745,7 +5363,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4768,7 +5386,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4791,7 +5409,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4814,7 +5432,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4837,7 +5455,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4860,7 +5478,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4883,7 +5501,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4906,7 +5524,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4929,7 +5547,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4952,7 +5570,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4975,7 +5593,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4998,7 +5616,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5021,7 +5639,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5044,7 +5662,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5067,7 +5685,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5090,7 +5708,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5113,7 +5731,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5136,7 +5754,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5159,7 +5777,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5182,7 +5800,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5205,7 +5823,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5228,7 +5846,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5251,7 +5869,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5274,7 +5892,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5297,7 +5915,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5320,7 +5938,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5343,7 +5961,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5366,7 +5984,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5389,7 +6007,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5412,7 +6030,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5435,7 +6053,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5458,7 +6076,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5481,7 +6099,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5504,7 +6122,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5527,7 +6145,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5550,7 +6168,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5573,7 +6191,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5596,7 +6214,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5619,7 +6237,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5642,7 +6260,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5665,7 +6283,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5688,7 +6306,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5711,7 +6329,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5734,7 +6352,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5757,7 +6375,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5780,7 +6398,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5803,7 +6421,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5826,7 +6444,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5849,7 +6467,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5872,7 +6490,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5895,7 +6513,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5918,7 +6536,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5941,7 +6559,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5964,7 +6582,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5987,7 +6605,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6010,7 +6628,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6033,7 +6651,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6056,7 +6674,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6079,7 +6697,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6102,7 +6720,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6125,7 +6743,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6148,7 +6766,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6171,7 +6789,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6194,7 +6812,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6217,7 +6835,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6240,7 +6858,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6263,7 +6881,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6286,7 +6904,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6309,7 +6927,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6332,7 +6950,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6355,7 +6973,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6378,7 +6996,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6401,7 +7019,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6424,7 +7042,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6447,7 +7065,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6470,7 +7088,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6493,7 +7111,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6516,7 +7134,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6539,7 +7157,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6562,7 +7180,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6585,7 +7203,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6608,7 +7226,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6631,7 +7249,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6654,7 +7272,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6677,7 +7295,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6700,7 +7318,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6723,7 +7341,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6746,7 +7364,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6769,7 +7387,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6792,7 +7410,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6815,7 +7433,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6838,7 +7456,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6861,7 +7479,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6884,7 +7502,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6907,7 +7525,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6930,7 +7548,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6953,7 +7571,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6976,7 +7594,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6999,7 +7617,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7022,7 +7640,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7045,7 +7663,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7068,7 +7686,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7091,7 +7709,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7114,7 +7732,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7137,7 +7755,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7160,7 +7778,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7183,7 +7801,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7206,7 +7824,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7229,7 +7847,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7252,7 +7870,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7275,7 +7893,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7298,7 +7916,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7321,7 +7939,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7344,7 +7962,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7367,7 +7985,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7390,7 +8008,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7413,7 +8031,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7436,7 +8054,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7459,7 +8077,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7482,7 +8100,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7505,7 +8123,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7528,7 +8146,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7551,7 +8169,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7574,7 +8192,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7597,7 +8215,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7620,7 +8238,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7643,7 +8261,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7666,7 +8284,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7689,7 +8307,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7712,7 +8330,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>161</v>
       </c>
@@ -7735,7 +8353,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>162</v>
       </c>
@@ -7758,7 +8376,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7781,7 +8399,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>164</v>
       </c>
@@ -7804,7 +8422,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>165</v>
       </c>
@@ -7827,7 +8445,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>166</v>
       </c>
@@ -7850,7 +8468,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>167</v>
       </c>
@@ -7873,7 +8491,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>168</v>
       </c>
@@ -7896,7 +8514,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>169</v>
       </c>
@@ -7919,7 +8537,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>170</v>
       </c>
@@ -7942,7 +8560,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>171</v>
       </c>
@@ -7965,7 +8583,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>172</v>
       </c>
@@ -7988,7 +8606,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8011,7 +8629,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8034,7 +8652,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8057,7 +8675,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8080,7 +8698,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8103,7 +8721,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8126,7 +8744,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8149,7 +8767,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8172,7 +8790,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8195,7 +8813,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8218,7 +8836,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7">
       <c r="A184">
         <v>183</v>
       </c>
@@ -8241,7 +8859,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7">
       <c r="A185">
         <v>184</v>
       </c>
@@ -8264,7 +8882,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7">
       <c r="A186">
         <v>185</v>
       </c>
@@ -8287,7 +8905,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7">
       <c r="A187">
         <v>186</v>
       </c>
@@ -8310,7 +8928,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7">
       <c r="A188">
         <v>187</v>
       </c>
@@ -8333,7 +8951,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7">
       <c r="A189">
         <v>188</v>
       </c>
@@ -8356,7 +8974,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7">
       <c r="A190">
         <v>189</v>
       </c>
@@ -8379,7 +8997,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7">
       <c r="A191">
         <v>190</v>
       </c>
@@ -8402,7 +9020,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7">
       <c r="A192">
         <v>191</v>
       </c>
@@ -8425,7 +9043,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>192</v>
       </c>
@@ -8448,7 +9066,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>193</v>
       </c>
@@ -8471,7 +9089,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>194</v>
       </c>
@@ -8494,7 +9112,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>195</v>
       </c>
@@ -8517,7 +9135,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7">
       <c r="A197">
         <v>196</v>
       </c>
@@ -8540,7 +9158,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7">
       <c r="A198">
         <v>197</v>
       </c>
@@ -8563,7 +9181,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7">
       <c r="A199">
         <v>198</v>
       </c>
@@ -8586,7 +9204,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7">
       <c r="A200">
         <v>199</v>
       </c>
@@ -8609,7 +9227,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7">
       <c r="A201">
         <v>200</v>
       </c>
@@ -8632,7 +9250,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>201</v>
       </c>
@@ -8655,7 +9273,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7">
       <c r="A203">
         <v>202</v>
       </c>
@@ -8678,7 +9296,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7">
       <c r="A204">
         <v>203</v>
       </c>
@@ -8701,7 +9319,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7">
       <c r="A205">
         <v>204</v>
       </c>
@@ -8724,7 +9342,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7">
       <c r="A206">
         <v>205</v>
       </c>
@@ -8747,7 +9365,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7">
       <c r="A207">
         <v>206</v>
       </c>
@@ -8770,7 +9388,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7">
       <c r="A208">
         <v>207</v>
       </c>
@@ -8793,7 +9411,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7">
       <c r="A209">
         <v>208</v>
       </c>
@@ -8816,7 +9434,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7">
       <c r="A210">
         <v>209</v>
       </c>
@@ -8839,7 +9457,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7">
       <c r="A211">
         <v>210</v>
       </c>
@@ -8862,7 +9480,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7">
       <c r="A212">
         <v>211</v>
       </c>
@@ -8885,7 +9503,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7">
       <c r="A213">
         <v>212</v>
       </c>
@@ -8908,7 +9526,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7">
       <c r="A214">
         <v>213</v>
       </c>
@@ -8931,7 +9549,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7">
       <c r="A215">
         <v>214</v>
       </c>
@@ -8954,7 +9572,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7">
       <c r="A216">
         <v>215</v>
       </c>
@@ -8977,7 +9595,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7">
       <c r="A217">
         <v>216</v>
       </c>
@@ -9000,7 +9618,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7">
       <c r="A218">
         <v>217</v>
       </c>
@@ -9023,7 +9641,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7">
       <c r="A219">
         <v>218</v>
       </c>
@@ -9046,7 +9664,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7">
       <c r="A220">
         <v>219</v>
       </c>
@@ -9069,7 +9687,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7">
       <c r="A221">
         <v>220</v>
       </c>
@@ -9092,7 +9710,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7">
       <c r="A222">
         <v>221</v>
       </c>
@@ -9115,7 +9733,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7">
       <c r="A223">
         <v>222</v>
       </c>
@@ -9138,7 +9756,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7">
       <c r="A224">
         <v>223</v>
       </c>
@@ -9161,7 +9779,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7">
       <c r="A225">
         <v>224</v>
       </c>
@@ -9184,7 +9802,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7">
       <c r="A226">
         <v>225</v>
       </c>
@@ -9207,7 +9825,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7">
       <c r="A227">
         <v>226</v>
       </c>
@@ -9230,7 +9848,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7">
       <c r="A228">
         <v>227</v>
       </c>
@@ -9253,7 +9871,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7">
       <c r="A229">
         <v>228</v>
       </c>
@@ -9276,7 +9894,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7">
       <c r="A230">
         <v>229</v>
       </c>
@@ -9299,7 +9917,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7">
       <c r="A231">
         <v>230</v>
       </c>
@@ -9322,7 +9940,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7">
       <c r="A232">
         <v>231</v>
       </c>
@@ -9345,7 +9963,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7">
       <c r="A233">
         <v>232</v>
       </c>
@@ -9368,7 +9986,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7">
       <c r="A234">
         <v>233</v>
       </c>
@@ -9391,7 +10009,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7">
       <c r="A235">
         <v>234</v>
       </c>
@@ -9414,7 +10032,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7">
       <c r="A236">
         <v>235</v>
       </c>
@@ -9437,7 +10055,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7">
       <c r="A237">
         <v>236</v>
       </c>
@@ -9460,7 +10078,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7">
       <c r="A238">
         <v>237</v>
       </c>
@@ -9483,7 +10101,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7">
       <c r="A239">
         <v>238</v>
       </c>
@@ -9506,7 +10124,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7">
       <c r="A240">
         <v>239</v>
       </c>
@@ -9529,7 +10147,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7">
       <c r="A241">
         <v>240</v>
       </c>
@@ -9552,7 +10170,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7">
       <c r="A242">
         <v>241</v>
       </c>
@@ -9575,7 +10193,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -9598,7 +10216,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -9621,7 +10239,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7">
       <c r="A245">
         <v>244</v>
       </c>
@@ -9644,7 +10262,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7">
       <c r="A246">
         <v>245</v>
       </c>
@@ -9667,7 +10285,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7">
       <c r="A247">
         <v>246</v>
       </c>
@@ -9690,7 +10308,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7">
       <c r="A248">
         <v>247</v>
       </c>
@@ -9713,7 +10331,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7">
       <c r="A249">
         <v>248</v>
       </c>
@@ -9736,7 +10354,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7">
       <c r="A250">
         <v>249</v>
       </c>
@@ -9759,7 +10377,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7">
       <c r="A251">
         <v>250</v>
       </c>
@@ -9782,7 +10400,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7">
       <c r="A252">
         <v>251</v>
       </c>
@@ -9805,7 +10423,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7">
       <c r="A253">
         <v>252</v>
       </c>
@@ -9828,7 +10446,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7">
       <c r="A254">
         <v>253</v>
       </c>
@@ -9851,7 +10469,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7">
       <c r="A255">
         <v>254</v>
       </c>
@@ -9874,7 +10492,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7">
       <c r="A256">
         <v>255</v>
       </c>
@@ -9897,7 +10515,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7">
       <c r="A257">
         <v>256</v>
       </c>
@@ -9920,7 +10538,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7">
       <c r="A258">
         <v>257</v>
       </c>
@@ -9943,7 +10561,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7">
       <c r="A259">
         <v>258</v>
       </c>
@@ -9966,7 +10584,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7">
       <c r="A260">
         <v>259</v>
       </c>
@@ -9989,7 +10607,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7">
       <c r="A261">
         <v>260</v>
       </c>
@@ -10012,7 +10630,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7">
       <c r="A262">
         <v>261</v>
       </c>
@@ -10035,7 +10653,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7">
       <c r="A263">
         <v>262</v>
       </c>
@@ -10058,7 +10676,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7">
       <c r="A264">
         <v>263</v>
       </c>
@@ -10081,7 +10699,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7">
       <c r="A265">
         <v>264</v>
       </c>
@@ -10104,7 +10722,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7">
       <c r="A266">
         <v>265</v>
       </c>
@@ -10127,7 +10745,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7">
       <c r="A267">
         <v>266</v>
       </c>
@@ -10150,7 +10768,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7">
       <c r="A268">
         <v>267</v>
       </c>
@@ -10173,7 +10791,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7">
       <c r="A269">
         <v>268</v>
       </c>
@@ -10196,7 +10814,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7">
       <c r="A270">
         <v>269</v>
       </c>
@@ -10219,7 +10837,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7">
       <c r="A271">
         <v>270</v>
       </c>
@@ -10242,7 +10860,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7">
       <c r="A272">
         <v>271</v>
       </c>
@@ -10265,7 +10883,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7">
       <c r="A273">
         <v>272</v>
       </c>
@@ -10288,7 +10906,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7">
       <c r="A274">
         <v>273</v>
       </c>
@@ -10311,7 +10929,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7">
       <c r="A275">
         <v>274</v>
       </c>
@@ -10334,7 +10952,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7">
       <c r="A276">
         <v>275</v>
       </c>
@@ -10357,7 +10975,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7">
       <c r="A277">
         <v>276</v>
       </c>
@@ -10380,7 +10998,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7">
       <c r="A278">
         <v>277</v>
       </c>
@@ -10403,7 +11021,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7">
       <c r="A279">
         <v>278</v>
       </c>
@@ -10426,7 +11044,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7">
       <c r="A280">
         <v>279</v>
       </c>
@@ -10449,7 +11067,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7">
       <c r="A281">
         <v>280</v>
       </c>
@@ -10472,7 +11090,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7">
       <c r="A282">
         <v>281</v>
       </c>
@@ -10495,7 +11113,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7">
       <c r="A283">
         <v>282</v>
       </c>
@@ -10518,7 +11136,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7">
       <c r="A284">
         <v>283</v>
       </c>
@@ -10541,7 +11159,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7">
       <c r="A285">
         <v>284</v>
       </c>
@@ -10564,7 +11182,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7">
       <c r="A286">
         <v>285</v>
       </c>
@@ -10587,7 +11205,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7">
       <c r="A287">
         <v>286</v>
       </c>
@@ -10610,7 +11228,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7">
       <c r="A288">
         <v>287</v>
       </c>
@@ -10633,7 +11251,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7">
       <c r="A289">
         <v>288</v>
       </c>
@@ -10656,7 +11274,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7">
       <c r="A290">
         <v>289</v>
       </c>
@@ -10679,7 +11297,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7">
       <c r="A291">
         <v>290</v>
       </c>
@@ -10702,7 +11320,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7">
       <c r="A292">
         <v>291</v>
       </c>
@@ -10725,7 +11343,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7">
       <c r="A293">
         <v>292</v>
       </c>
@@ -10748,7 +11366,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7">
       <c r="A294">
         <v>293</v>
       </c>
@@ -10771,7 +11389,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7">
       <c r="A295">
         <v>294</v>
       </c>
@@ -10794,7 +11412,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7">
       <c r="A296">
         <v>295</v>
       </c>
@@ -10817,7 +11435,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7">
       <c r="A297">
         <v>296</v>
       </c>
@@ -10840,7 +11458,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7">
       <c r="A298">
         <v>297</v>
       </c>
@@ -10863,7 +11481,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7">
       <c r="A299">
         <v>298</v>
       </c>
@@ -10886,7 +11504,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7">
       <c r="A300">
         <v>299</v>
       </c>
@@ -10909,7 +11527,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7">
       <c r="A301">
         <v>300</v>
       </c>
@@ -10932,7 +11550,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7">
       <c r="A302">
         <v>301</v>
       </c>
@@ -10955,7 +11573,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7">
       <c r="A303">
         <v>302</v>
       </c>
@@ -10978,7 +11596,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7">
       <c r="A304">
         <v>303</v>
       </c>
@@ -11001,7 +11619,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7">
       <c r="A305">
         <v>304</v>
       </c>
@@ -11024,7 +11642,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7">
       <c r="A306">
         <v>305</v>
       </c>
@@ -11047,7 +11665,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7">
       <c r="A307">
         <v>306</v>
       </c>
@@ -11070,7 +11688,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7">
       <c r="A308">
         <v>307</v>
       </c>
@@ -11093,7 +11711,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7">
       <c r="A309">
         <v>308</v>
       </c>
@@ -11116,7 +11734,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7">
       <c r="A310">
         <v>309</v>
       </c>
@@ -11139,7 +11757,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7">
       <c r="A311">
         <v>310</v>
       </c>
@@ -11162,7 +11780,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7">
       <c r="A312">
         <v>311</v>
       </c>
@@ -11185,7 +11803,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7">
       <c r="A313">
         <v>312</v>
       </c>
@@ -11208,7 +11826,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7">
       <c r="A314">
         <v>313</v>
       </c>
@@ -11231,7 +11849,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7">
       <c r="A315">
         <v>314</v>
       </c>
@@ -11254,7 +11872,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7">
       <c r="A316">
         <v>315</v>
       </c>
@@ -11277,7 +11895,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7">
       <c r="A317">
         <v>316</v>
       </c>
@@ -11300,7 +11918,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7">
       <c r="A318">
         <v>317</v>
       </c>
@@ -11323,7 +11941,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7">
       <c r="A319">
         <v>318</v>
       </c>
@@ -11346,7 +11964,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7">
       <c r="A320">
         <v>319</v>
       </c>
@@ -11369,7 +11987,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7">
       <c r="A321">
         <v>320</v>
       </c>
@@ -11392,7 +12010,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7">
       <c r="A322">
         <v>321</v>
       </c>
@@ -11415,7 +12033,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7">
       <c r="A323">
         <v>322</v>
       </c>
@@ -11438,7 +12056,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7">
       <c r="A324">
         <v>323</v>
       </c>
@@ -11461,7 +12079,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7">
       <c r="A325">
         <v>324</v>
       </c>
@@ -11484,7 +12102,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7">
       <c r="A326">
         <v>325</v>
       </c>
@@ -11507,7 +12125,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7">
       <c r="A327">
         <v>326</v>
       </c>
@@ -11530,7 +12148,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7">
       <c r="A328">
         <v>327</v>
       </c>
@@ -11553,7 +12171,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7">
       <c r="A329">
         <v>328</v>
       </c>
@@ -11576,7 +12194,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7">
       <c r="A330">
         <v>329</v>
       </c>
@@ -11599,7 +12217,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7">
       <c r="A331">
         <v>330</v>
       </c>
@@ -11622,7 +12240,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7">
       <c r="A332">
         <v>331</v>
       </c>
@@ -11645,7 +12263,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7">
       <c r="A333">
         <v>332</v>
       </c>
@@ -11668,7 +12286,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7">
       <c r="A334">
         <v>333</v>
       </c>
@@ -11691,7 +12309,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7">
       <c r="A335">
         <v>334</v>
       </c>
@@ -11714,7 +12332,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7">
       <c r="A336">
         <v>335</v>
       </c>
@@ -11737,7 +12355,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7">
       <c r="A337">
         <v>336</v>
       </c>
@@ -11760,7 +12378,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7">
       <c r="A338">
         <v>337</v>
       </c>
@@ -11783,7 +12401,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7">
       <c r="A339">
         <v>338</v>
       </c>
@@ -11806,7 +12424,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7">
       <c r="A340">
         <v>339</v>
       </c>
@@ -11829,7 +12447,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7">
       <c r="A341">
         <v>340</v>
       </c>
@@ -11852,7 +12470,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7">
       <c r="A342">
         <v>341</v>
       </c>
@@ -11875,7 +12493,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7">
       <c r="A343">
         <v>342</v>
       </c>
@@ -11898,7 +12516,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7">
       <c r="A344">
         <v>343</v>
       </c>
@@ -11921,7 +12539,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7">
       <c r="A345">
         <v>344</v>
       </c>
@@ -11944,7 +12562,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7">
       <c r="A346">
         <v>345</v>
       </c>
@@ -11967,7 +12585,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7">
       <c r="A347">
         <v>346</v>
       </c>
@@ -11990,7 +12608,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7">
       <c r="A348">
         <v>347</v>
       </c>
@@ -12013,7 +12631,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7">
       <c r="A349">
         <v>348</v>
       </c>
@@ -12036,7 +12654,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7">
       <c r="A350">
         <v>349</v>
       </c>
@@ -12059,7 +12677,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7">
       <c r="A351">
         <v>350</v>
       </c>
@@ -12082,7 +12700,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7">
       <c r="A352">
         <v>351</v>
       </c>
@@ -12105,7 +12723,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7">
       <c r="A353">
         <v>352</v>
       </c>
@@ -12128,7 +12746,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7">
       <c r="A354">
         <v>353</v>
       </c>
@@ -12151,7 +12769,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7">
       <c r="A355">
         <v>354</v>
       </c>
@@ -12174,7 +12792,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7">
       <c r="A356">
         <v>355</v>
       </c>
@@ -12197,7 +12815,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7">
       <c r="A357">
         <v>356</v>
       </c>
@@ -12220,7 +12838,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7">
       <c r="A358">
         <v>357</v>
       </c>
@@ -12243,7 +12861,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7">
       <c r="A359">
         <v>358</v>
       </c>
@@ -12266,7 +12884,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7">
       <c r="A360">
         <v>359</v>
       </c>
@@ -12289,7 +12907,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7">
       <c r="A361">
         <v>360</v>
       </c>
@@ -12312,7 +12930,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7">
       <c r="A362">
         <v>361</v>
       </c>
@@ -12335,7 +12953,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7">
       <c r="A363">
         <v>362</v>
       </c>
@@ -12358,7 +12976,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7">
       <c r="A364">
         <v>363</v>
       </c>
@@ -12381,7 +12999,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7">
       <c r="A365">
         <v>364</v>
       </c>
@@ -12404,7 +13022,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7">
       <c r="A366">
         <v>365</v>
       </c>
@@ -12427,7 +13045,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7">
       <c r="A367">
         <v>366</v>
       </c>
@@ -12450,7 +13068,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7">
       <c r="A368">
         <v>367</v>
       </c>
@@ -12473,7 +13091,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7">
       <c r="A369">
         <v>368</v>
       </c>
@@ -12496,7 +13114,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7">
       <c r="A370">
         <v>369</v>
       </c>
@@ -12519,7 +13137,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7">
       <c r="A371">
         <v>370</v>
       </c>
@@ -12542,7 +13160,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7">
       <c r="A372">
         <v>371</v>
       </c>
@@ -12565,7 +13183,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7">
       <c r="A373">
         <v>372</v>
       </c>
@@ -12588,7 +13206,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7">
       <c r="A374">
         <v>373</v>
       </c>
@@ -12611,7 +13229,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7">
       <c r="A375">
         <v>374</v>
       </c>
@@ -12634,7 +13252,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7">
       <c r="A376">
         <v>375</v>
       </c>
@@ -12657,7 +13275,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7">
       <c r="A377">
         <v>376</v>
       </c>
@@ -12680,7 +13298,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7">
       <c r="A378">
         <v>377</v>
       </c>
@@ -12703,7 +13321,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7">
       <c r="A379">
         <v>378</v>
       </c>
@@ -12726,7 +13344,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7">
       <c r="A380">
         <v>379</v>
       </c>
@@ -12749,7 +13367,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7">
       <c r="A381">
         <v>380</v>
       </c>
@@ -12772,7 +13390,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7">
       <c r="A382">
         <v>381</v>
       </c>
@@ -12795,7 +13413,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7">
       <c r="A383">
         <v>382</v>
       </c>
@@ -12818,7 +13436,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7">
       <c r="A384">
         <v>383</v>
       </c>
@@ -12841,7 +13459,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7">
       <c r="A385">
         <v>384</v>
       </c>
@@ -12864,7 +13482,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7">
       <c r="A386">
         <v>385</v>
       </c>
@@ -12887,7 +13505,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7">
       <c r="A387">
         <v>386</v>
       </c>
@@ -12910,7 +13528,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7">
       <c r="A388">
         <v>387</v>
       </c>
@@ -12933,7 +13551,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7">
       <c r="A389">
         <v>388</v>
       </c>
@@ -12956,7 +13574,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7">
       <c r="A390">
         <v>389</v>
       </c>
@@ -12979,7 +13597,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7">
       <c r="A391">
         <v>390</v>
       </c>
@@ -13002,7 +13620,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7">
       <c r="A392">
         <v>391</v>
       </c>
@@ -13025,7 +13643,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7">
       <c r="A393">
         <v>392</v>
       </c>
@@ -13048,7 +13666,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7">
       <c r="A394">
         <v>393</v>
       </c>
@@ -13071,7 +13689,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7">
       <c r="A395">
         <v>394</v>
       </c>
@@ -13094,7 +13712,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7">
       <c r="A396">
         <v>395</v>
       </c>
@@ -13117,7 +13735,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7">
       <c r="A397">
         <v>396</v>
       </c>
@@ -13140,7 +13758,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7">
       <c r="A398">
         <v>397</v>
       </c>
@@ -13163,7 +13781,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7">
       <c r="A399">
         <v>398</v>
       </c>
@@ -13186,7 +13804,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7">
       <c r="A400">
         <v>399</v>
       </c>
@@ -13209,7 +13827,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7">
       <c r="A401">
         <v>400</v>
       </c>
@@ -13232,7 +13850,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7">
       <c r="A402">
         <v>401</v>
       </c>
@@ -13255,7 +13873,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7">
       <c r="A403">
         <v>402</v>
       </c>
@@ -13278,7 +13896,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7">
       <c r="A404">
         <v>403</v>
       </c>
@@ -13301,7 +13919,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7">
       <c r="A405">
         <v>404</v>
       </c>
@@ -13324,7 +13942,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7">
       <c r="A406">
         <v>405</v>
       </c>
@@ -13347,7 +13965,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7">
       <c r="A407">
         <v>406</v>
       </c>
@@ -13370,7 +13988,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7">
       <c r="A408">
         <v>407</v>
       </c>
@@ -13393,7 +14011,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7">
       <c r="A409">
         <v>408</v>
       </c>
@@ -13416,7 +14034,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7">
       <c r="A410">
         <v>409</v>
       </c>
@@ -13439,7 +14057,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7">
       <c r="A411">
         <v>410</v>
       </c>
@@ -13462,7 +14080,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7">
       <c r="A412">
         <v>411</v>
       </c>
@@ -13485,7 +14103,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7">
       <c r="A413">
         <v>412</v>
       </c>
@@ -13508,7 +14126,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7">
       <c r="A414">
         <v>413</v>
       </c>
@@ -13531,7 +14149,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7">
       <c r="A415">
         <v>414</v>
       </c>
@@ -13554,7 +14172,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7">
       <c r="A416">
         <v>415</v>
       </c>
@@ -13577,7 +14195,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7">
       <c r="A417">
         <v>416</v>
       </c>
@@ -13600,7 +14218,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7">
       <c r="A418">
         <v>417</v>
       </c>
@@ -13623,7 +14241,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7">
       <c r="A419">
         <v>418</v>
       </c>
@@ -13646,7 +14264,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7">
       <c r="A420">
         <v>419</v>
       </c>
@@ -13669,7 +14287,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7">
       <c r="A421">
         <v>420</v>
       </c>
@@ -13692,7 +14310,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7">
       <c r="A422">
         <v>421</v>
       </c>
@@ -13715,7 +14333,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7">
       <c r="A423">
         <v>422</v>
       </c>
@@ -13738,7 +14356,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7">
       <c r="A424">
         <v>423</v>
       </c>
@@ -13761,7 +14379,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7">
       <c r="A425">
         <v>424</v>
       </c>
@@ -13784,7 +14402,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7">
       <c r="A426">
         <v>425</v>
       </c>
@@ -13807,7 +14425,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7">
       <c r="A427">
         <v>426</v>
       </c>
@@ -13830,7 +14448,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7">
       <c r="A428">
         <v>427</v>
       </c>
@@ -13853,7 +14471,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7">
       <c r="A429">
         <v>428</v>
       </c>
@@ -13876,7 +14494,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7">
       <c r="A430">
         <v>429</v>
       </c>
@@ -13899,7 +14517,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7">
       <c r="A431">
         <v>430</v>
       </c>
@@ -13922,7 +14540,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7">
       <c r="A432">
         <v>431</v>
       </c>
@@ -13945,7 +14563,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7">
       <c r="A433">
         <v>432</v>
       </c>
@@ -13968,7 +14586,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7">
       <c r="A434">
         <v>433</v>
       </c>
@@ -13991,7 +14609,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7">
       <c r="A435">
         <v>434</v>
       </c>
@@ -14014,7 +14632,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7">
       <c r="A436">
         <v>435</v>
       </c>
@@ -14037,7 +14655,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7">
       <c r="A437">
         <v>436</v>
       </c>
@@ -14060,7 +14678,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7">
       <c r="A438">
         <v>437</v>
       </c>
@@ -14083,7 +14701,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7">
       <c r="A439">
         <v>438</v>
       </c>
@@ -14106,7 +14724,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7">
       <c r="A440">
         <v>439</v>
       </c>
@@ -14129,7 +14747,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7">
       <c r="A441">
         <v>440</v>
       </c>
@@ -14152,7 +14770,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7">
       <c r="A442">
         <v>441</v>
       </c>
@@ -14175,7 +14793,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7">
       <c r="A443">
         <v>442</v>
       </c>
@@ -14198,7 +14816,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7">
       <c r="A444">
         <v>443</v>
       </c>
@@ -14221,7 +14839,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7">
       <c r="A445">
         <v>444</v>
       </c>
@@ -14244,7 +14862,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7">
       <c r="A446">
         <v>445</v>
       </c>
@@ -14267,7 +14885,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7">
       <c r="A447">
         <v>446</v>
       </c>
@@ -14290,7 +14908,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7">
       <c r="A448">
         <v>447</v>
       </c>
@@ -14313,7 +14931,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7">
       <c r="A449">
         <v>448</v>
       </c>
@@ -14336,7 +14954,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7">
       <c r="A450">
         <v>449</v>
       </c>
@@ -14359,7 +14977,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7">
       <c r="A451">
         <v>450</v>
       </c>
@@ -14382,7 +15000,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7">
       <c r="A452">
         <v>451</v>
       </c>
@@ -14405,7 +15023,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7">
       <c r="A453">
         <v>452</v>
       </c>
@@ -14428,7 +15046,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7">
       <c r="A454">
         <v>453</v>
       </c>
@@ -14451,7 +15069,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7">
       <c r="A455">
         <v>454</v>
       </c>
@@ -14474,7 +15092,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7">
       <c r="A456">
         <v>455</v>
       </c>
@@ -14497,7 +15115,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7">
       <c r="A457">
         <v>456</v>
       </c>
@@ -14520,7 +15138,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7">
       <c r="A458">
         <v>457</v>
       </c>
@@ -14543,7 +15161,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7">
       <c r="A459">
         <v>458</v>
       </c>
@@ -14566,7 +15184,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7">
       <c r="A460">
         <v>459</v>
       </c>
@@ -14589,7 +15207,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7">
       <c r="A461">
         <v>460</v>
       </c>
@@ -14612,7 +15230,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7">
       <c r="A462">
         <v>461</v>
       </c>
@@ -14635,7 +15253,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7">
       <c r="A463">
         <v>462</v>
       </c>
@@ -14658,7 +15276,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7">
       <c r="A464">
         <v>463</v>
       </c>
@@ -14681,7 +15299,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7">
       <c r="A465">
         <v>464</v>
       </c>
@@ -14704,7 +15322,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7">
       <c r="A466">
         <v>465</v>
       </c>
@@ -14727,7 +15345,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7">
       <c r="A467">
         <v>466</v>
       </c>
@@ -14750,7 +15368,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7">
       <c r="A468">
         <v>467</v>
       </c>
@@ -14773,7 +15391,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7">
       <c r="A469">
         <v>468</v>
       </c>
@@ -14796,7 +15414,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7">
       <c r="A470">
         <v>469</v>
       </c>
@@ -14819,7 +15437,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7">
       <c r="A471">
         <v>470</v>
       </c>
@@ -14842,7 +15460,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7">
       <c r="A472">
         <v>471</v>
       </c>
@@ -14865,7 +15483,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" ht="13" customHeight="1" spans="1:7">
       <c r="A473">
         <v>472</v>
       </c>
@@ -14888,7 +15506,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7">
       <c r="A474">
         <v>473</v>
       </c>
@@ -14911,7 +15529,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7">
       <c r="A475">
         <v>474</v>
       </c>
@@ -14934,7 +15552,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7">
       <c r="A476">
         <v>475</v>
       </c>
@@ -14957,7 +15575,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7">
       <c r="A477">
         <v>476</v>
       </c>
@@ -14980,7 +15598,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7">
       <c r="A478">
         <v>477</v>
       </c>
@@ -15003,7 +15621,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7">
       <c r="A479">
         <v>478</v>
       </c>
@@ -15026,7 +15644,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7">
       <c r="A480">
         <v>479</v>
       </c>
@@ -15049,7 +15667,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7">
       <c r="A481">
         <v>480</v>
       </c>
@@ -15072,7 +15690,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7">
       <c r="A482">
         <v>481</v>
       </c>
@@ -15095,7 +15713,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7">
       <c r="A483">
         <v>482</v>
       </c>
@@ -15118,7 +15736,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7">
       <c r="A484">
         <v>483</v>
       </c>
@@ -15141,7 +15759,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="485" ht="15" spans="1:7">
       <c r="A485">
         <v>484</v>
       </c>
@@ -15160,7 +15778,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="486" ht="15" spans="1:7">
       <c r="A486">
         <v>485</v>
       </c>
@@ -15179,7 +15797,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="487" ht="15" spans="1:7">
       <c r="A487">
         <v>486</v>
       </c>
@@ -15198,7 +15816,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="488" ht="15" spans="1:7">
       <c r="A488">
         <v>487</v>
       </c>
@@ -15217,7 +15835,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="489" ht="15" spans="1:7">
       <c r="A489">
         <v>488</v>
       </c>
@@ -15236,7 +15854,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="490" ht="15" spans="1:7">
       <c r="A490">
         <v>489</v>
       </c>
@@ -15255,7 +15873,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="491" ht="15" spans="1:7">
       <c r="A491">
         <v>490</v>
       </c>
@@ -15274,7 +15892,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="492" ht="15" spans="1:7">
       <c r="A492">
         <v>491</v>
       </c>
@@ -15293,7 +15911,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="493" ht="15" spans="1:7">
       <c r="A493">
         <v>492</v>
       </c>
@@ -15312,7 +15930,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="494" ht="15" spans="1:7">
       <c r="A494">
         <v>493</v>
       </c>
@@ -15331,7 +15949,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="495" ht="15" spans="1:7">
       <c r="A495">
         <v>494</v>
       </c>
@@ -15350,7 +15968,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="496" ht="15" spans="1:7">
       <c r="A496">
         <v>495</v>
       </c>
@@ -15369,7 +15987,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:7">
       <c r="A497">
         <v>496</v>
       </c>
@@ -15389,7 +16007,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7">
       <c r="A498">
         <v>497</v>
       </c>
@@ -15409,7 +16027,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7">
       <c r="A499">
         <v>498</v>
       </c>
@@ -15429,7 +16047,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:7">
       <c r="A500">
         <v>499</v>
       </c>
@@ -15452,7 +16070,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:7">
       <c r="A501">
         <v>500</v>
       </c>
@@ -15469,7 +16087,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:7">
       <c r="A502">
         <v>501</v>
       </c>
@@ -15489,7 +16107,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:7">
       <c r="A503">
         <v>502</v>
       </c>
@@ -15509,7 +16127,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:7">
       <c r="A504">
         <v>503</v>
       </c>
@@ -15529,7 +16147,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:7">
       <c r="A505">
         <v>504</v>
       </c>
@@ -15549,7 +16167,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:7">
       <c r="A506">
         <v>505</v>
       </c>
@@ -15569,7 +16187,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:7">
       <c r="A507">
         <v>506</v>
       </c>
@@ -15589,7 +16207,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:7">
       <c r="A508">
         <v>507</v>
       </c>
@@ -15612,7 +16230,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:7">
       <c r="A509">
         <v>508</v>
       </c>
@@ -15632,7 +16250,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:7">
       <c r="A510">
         <v>509</v>
       </c>
@@ -15652,7 +16270,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:7">
       <c r="A511">
         <v>510</v>
       </c>
@@ -15672,7 +16290,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:7">
       <c r="A512">
         <v>511</v>
       </c>
@@ -15692,7 +16310,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7">
       <c r="A513">
         <v>512</v>
       </c>
@@ -15712,7 +16330,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:7">
       <c r="A514">
         <v>513</v>
       </c>
@@ -15732,7 +16350,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:7">
       <c r="A515">
         <v>514</v>
       </c>
@@ -15752,7 +16370,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:7">
       <c r="A516">
         <v>515</v>
       </c>
@@ -15769,7 +16387,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:7">
       <c r="A517">
         <v>516</v>
       </c>
@@ -15789,7 +16407,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7">
       <c r="A518">
         <v>517</v>
       </c>
@@ -15809,7 +16427,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:7">
       <c r="A519">
         <v>518</v>
       </c>
@@ -15829,7 +16447,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:7">
       <c r="A520">
         <v>519</v>
       </c>
@@ -15852,7 +16470,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:7">
       <c r="A521">
         <v>520</v>
       </c>
@@ -15872,7 +16490,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="522" ht="15" spans="1:7">
       <c r="A522">
         <v>521</v>
       </c>
@@ -15892,7 +16510,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="523" ht="15" spans="1:7">
       <c r="A523">
         <v>522</v>
       </c>
@@ -15912,7 +16530,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:7">
       <c r="A524">
         <v>523</v>
       </c>
@@ -15932,7 +16550,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:7">
       <c r="A525">
         <v>524</v>
       </c>
@@ -15952,7 +16570,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7">
       <c r="A526">
         <v>525</v>
       </c>
@@ -15972,7 +16590,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7">
       <c r="A527">
         <v>526</v>
       </c>
@@ -15992,7 +16610,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7">
       <c r="A528">
         <v>527</v>
       </c>
@@ -16012,7 +16630,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7">
       <c r="A529">
         <v>528</v>
       </c>
@@ -16032,7 +16650,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:7">
       <c r="A530">
         <v>529</v>
       </c>
@@ -16049,7 +16667,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:7">
       <c r="A531">
         <v>530</v>
       </c>
@@ -16072,7 +16690,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7">
       <c r="A532">
         <v>531</v>
       </c>
@@ -16092,7 +16710,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7">
       <c r="A533">
         <v>532</v>
       </c>
@@ -16112,7 +16730,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7">
       <c r="A534">
         <v>533</v>
       </c>
@@ -16132,7 +16750,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:7">
       <c r="A535">
         <v>534</v>
       </c>
@@ -16152,7 +16770,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:7">
       <c r="A536">
         <v>535</v>
       </c>
@@ -16172,7 +16790,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7">
       <c r="A537">
         <v>536</v>
       </c>
@@ -16189,15 +16807,15 @@
         <v>6</v>
       </c>
       <c r="G537" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7">
       <c r="A538">
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D538" t="s">
         <v>190</v>
@@ -16212,18 +16830,40 @@
         <v>1187</v>
       </c>
     </row>
+    <row r="539" spans="1:7">
+      <c r="A539">
+        <v>538</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D539" t="s">
+        <v>190</v>
+      </c>
+      <c r="E539" t="s">
+        <v>190</v>
+      </c>
+      <c r="F539">
+        <v>6</v>
+      </c>
+      <c r="G539" t="s">
+        <v>1189</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G534" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G538" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G71" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G75" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G498" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G281" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G513" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G518" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G71" r:id="rId1" display="https://pan.quark.cn/s/54ae4c79b6ef"/>
+    <hyperlink ref="G75" r:id="rId2" display="https://pan.quark.cn/s/32466a4d8102"/>
+    <hyperlink ref="G498" r:id="rId3" display="https://pan.quark.cn/s/13554a561c72"/>
+    <hyperlink ref="G14" r:id="rId4" display="https://pan.quark.cn/s/3c4920236e7e"/>
+    <hyperlink ref="G281" r:id="rId5" display="https://pan.quark.cn/s/18f5ee8d2498"/>
+    <hyperlink ref="G513" r:id="rId6" display="https://pan.quark.cn/s/4097a88042e9"/>
+    <hyperlink ref="G518" r:id="rId7" display="https://pan.quark.cn/s/90d96d395a84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$538</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$540</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="1194">
   <si>
     <t>id</t>
   </si>
@@ -3617,6 +3617,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/5ae04db230de</t>
+  </si>
+  <si>
+    <t>星火号</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/809c1725495c</t>
+  </si>
+  <si>
+    <t>魔女的考验</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3afdca922c20</t>
   </si>
 </sst>
 </file>
@@ -4619,7 +4631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G539"/>
+  <dimension ref="A1:G541"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16850,8 +16862,45 @@
         <v>1189</v>
       </c>
     </row>
+    <row r="540" spans="1:7">
+      <c r="A540">
+        <v>539</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D540" t="s">
+        <v>190</v>
+      </c>
+      <c r="E540" t="s">
+        <v>190</v>
+      </c>
+      <c r="F540">
+        <v>5</v>
+      </c>
+      <c r="G540" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7">
+      <c r="A541">
+        <v>540</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D541" t="s">
+        <v>143</v>
+      </c>
+      <c r="E541" t="s">
+        <v>143</v>
+      </c>
+      <c r="G541" t="s">
+        <v>1193</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G538" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G540" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$541</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="1196">
   <si>
     <t>id</t>
   </si>
@@ -3629,6 +3629,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/3afdca922c20</t>
+  </si>
+  <si>
+    <t>窃云台</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/8d60329b9400</t>
   </si>
 </sst>
 </file>
@@ -4274,7 +4280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4285,6 +4291,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4631,7 +4638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G541"/>
+  <dimension ref="A1:G542"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16899,8 +16906,28 @@
         <v>1193</v>
       </c>
     </row>
+    <row r="542" spans="1:7">
+      <c r="A542">
+        <v>541</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D542" t="s">
+        <v>190</v>
+      </c>
+      <c r="E542" t="s">
+        <v>190</v>
+      </c>
+      <c r="F542">
+        <v>6</v>
+      </c>
+      <c r="G542" s="8" t="s">
+        <v>1195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G540" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G541" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="1198">
   <si>
     <t>id</t>
   </si>
@@ -3635,6 +3635,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/8d60329b9400</t>
+  </si>
+  <si>
+    <t>塑料温室</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/b91f58b83a77</t>
   </si>
 </sst>
 </file>
@@ -4638,7 +4644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G543"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16924,6 +16930,26 @@
       </c>
       <c r="G542" s="8" t="s">
         <v>1195</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7">
+      <c r="A543">
+        <v>542</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D543" t="s">
+        <v>190</v>
+      </c>
+      <c r="E543" t="s">
+        <v>190</v>
+      </c>
+      <c r="F543">
+        <v>6</v>
+      </c>
+      <c r="G543" s="8" t="s">
+        <v>1197</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$541</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$543</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1201">
   <si>
     <t>id</t>
   </si>
@@ -3642,6 +3642,46 @@
   <si>
     <t>https://pan.quark.cn/s/b91f58b83a77</t>
   </si>
+  <si>
+    <r>
+      <t>二流货色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>二流货色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>青花</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4a630320eb91</t>
+  </si>
 </sst>
 </file>
 
@@ -3653,7 +3693,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3699,6 +3739,12 @@
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Roboto"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3836,6 +3882,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4159,13 +4211,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4174,119 +4223,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4297,6 +4349,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4644,7 +4697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G543"/>
+  <dimension ref="A1:G544"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -16928,7 +16981,7 @@
       <c r="F542">
         <v>6</v>
       </c>
-      <c r="G542" s="8" t="s">
+      <c r="G542" s="5" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -16948,12 +17001,35 @@
       <c r="F543">
         <v>6</v>
       </c>
-      <c r="G543" s="8" t="s">
+      <c r="G543" s="5" t="s">
         <v>1197</v>
       </c>
     </row>
+    <row r="544" spans="1:7">
+      <c r="A544">
+        <v>543</v>
+      </c>
+      <c r="B544" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C544" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D544" t="s">
+        <v>190</v>
+      </c>
+      <c r="E544" t="s">
+        <v>190</v>
+      </c>
+      <c r="F544">
+        <v>6</v>
+      </c>
+      <c r="G544" s="9" t="s">
+        <v>1200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G541" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G543" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$543</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$544</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1204">
   <si>
     <t>id</t>
   </si>
@@ -3644,6 +3644,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>二流货色</t>
     </r>
     <r>
@@ -3658,6 +3664,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>二流货色</t>
     </r>
     <r>
@@ -3681,6 +3693,35 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/4a630320eb91</t>
+  </si>
+  <si>
+    <t>白昼2如果长夜无明</t>
+  </si>
+  <si>
+    <r>
+      <t>白昼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果长夜无明</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/bbd1269dee05</t>
   </si>
 </sst>
 </file>
@@ -4697,7 +4738,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G544"/>
+  <dimension ref="A1:G545"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17024,12 +17065,35 @@
       <c r="F544">
         <v>6</v>
       </c>
-      <c r="G544" s="9" t="s">
+      <c r="G544" s="5" t="s">
         <v>1200</v>
       </c>
     </row>
+    <row r="545" spans="1:7">
+      <c r="A545">
+        <v>544</v>
+      </c>
+      <c r="B545" s="9" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D545" t="s">
+        <v>190</v>
+      </c>
+      <c r="E545" t="s">
+        <v>190</v>
+      </c>
+      <c r="F545">
+        <v>6</v>
+      </c>
+      <c r="G545" s="9" t="s">
+        <v>1203</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G543" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G544" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$544</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$545</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="1206">
   <si>
     <t>id</t>
   </si>
@@ -3699,6 +3699,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>白昼</t>
     </r>
     <r>
@@ -3722,6 +3728,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/bbd1269dee05</t>
+  </si>
+  <si>
+    <t>流芳</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/fa0b8ca2c1c2</t>
   </si>
 </sst>
 </file>
@@ -4738,7 +4750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G545"/>
+  <dimension ref="A1:G546"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17073,7 +17085,7 @@
       <c r="A545">
         <v>544</v>
       </c>
-      <c r="B545" s="9" t="s">
+      <c r="B545" s="5" t="s">
         <v>1201</v>
       </c>
       <c r="C545" s="4" t="s">
@@ -17088,12 +17100,32 @@
       <c r="F545">
         <v>6</v>
       </c>
-      <c r="G545" s="9" t="s">
+      <c r="G545" s="5" t="s">
         <v>1203</v>
       </c>
     </row>
+    <row r="546" spans="1:7">
+      <c r="A546">
+        <v>545</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D546" t="s">
+        <v>190</v>
+      </c>
+      <c r="E546" t="s">
+        <v>190</v>
+      </c>
+      <c r="F546">
+        <v>6</v>
+      </c>
+      <c r="G546" s="9" t="s">
+        <v>1205</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G544" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G545" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$545</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$546</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="1208">
   <si>
     <t>id</t>
   </si>
@@ -3734,6 +3734,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/fa0b8ca2c1c2</t>
+  </si>
+  <si>
+    <t>壁上观</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d477ab363f5b</t>
   </si>
 </sst>
 </file>
@@ -4750,7 +4756,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G546"/>
+  <dimension ref="A1:G547"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17120,12 +17126,32 @@
       <c r="F546">
         <v>6</v>
       </c>
-      <c r="G546" s="9" t="s">
+      <c r="G546" s="5" t="s">
         <v>1205</v>
       </c>
     </row>
+    <row r="547" spans="1:7">
+      <c r="A547">
+        <v>546</v>
+      </c>
+      <c r="B547" s="9" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D547" t="s">
+        <v>190</v>
+      </c>
+      <c r="E547" t="s">
+        <v>190</v>
+      </c>
+      <c r="F547">
+        <v>6</v>
+      </c>
+      <c r="G547" s="9" t="s">
+        <v>1207</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G545" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G546" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$546</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$547</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1210">
   <si>
     <t>id</t>
   </si>
@@ -3740,6 +3740,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/d477ab363f5b</t>
+  </si>
+  <si>
+    <t>同流合屋</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/9eea94d2021f</t>
   </si>
 </sst>
 </file>
@@ -4756,7 +4762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G547"/>
+  <dimension ref="A1:G548"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17134,7 +17140,7 @@
       <c r="A547">
         <v>546</v>
       </c>
-      <c r="B547" s="9" t="s">
+      <c r="B547" s="5" t="s">
         <v>1206</v>
       </c>
       <c r="D547" t="s">
@@ -17146,12 +17152,32 @@
       <c r="F547">
         <v>6</v>
       </c>
-      <c r="G547" s="9" t="s">
+      <c r="G547" s="5" t="s">
         <v>1207</v>
       </c>
     </row>
+    <row r="548" spans="1:7">
+      <c r="A548">
+        <v>547</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D548" t="s">
+        <v>190</v>
+      </c>
+      <c r="E548" t="s">
+        <v>190</v>
+      </c>
+      <c r="F548">
+        <v>6</v>
+      </c>
+      <c r="G548" s="9" t="s">
+        <v>1209</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G546" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G547" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$547</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$548</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="1214">
   <si>
     <t>id</t>
   </si>
@@ -3746,6 +3746,18 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/9eea94d2021f</t>
+  </si>
+  <si>
+    <t>头颅们的失眠夜</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/98217a80acf2</t>
+  </si>
+  <si>
+    <t>葡萄不是幸福的水果</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5ed7f8c04c1a</t>
   </si>
 </sst>
 </file>
@@ -4415,7 +4427,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4762,7 +4774,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G548"/>
+  <dimension ref="A1:G550"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17172,12 +17184,52 @@
       <c r="F548">
         <v>6</v>
       </c>
-      <c r="G548" s="9" t="s">
+      <c r="G548" s="5" t="s">
         <v>1209</v>
       </c>
     </row>
+    <row r="549" spans="1:7">
+      <c r="A549">
+        <v>548</v>
+      </c>
+      <c r="B549" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D549" t="s">
+        <v>190</v>
+      </c>
+      <c r="E549" t="s">
+        <v>190</v>
+      </c>
+      <c r="F549">
+        <v>6</v>
+      </c>
+      <c r="G549" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7">
+      <c r="A550">
+        <v>549</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D550" t="s">
+        <v>190</v>
+      </c>
+      <c r="E550" t="s">
+        <v>190</v>
+      </c>
+      <c r="F550">
+        <v>6</v>
+      </c>
+      <c r="G550" t="s">
+        <v>1213</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G547" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G548" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$548</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$550</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="1216">
   <si>
     <t>id</t>
   </si>
@@ -3758,6 +3758,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/5ed7f8c04c1a</t>
+  </si>
+  <si>
+    <t>疯兔子，白又白，砍下脑袋飞起来</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/010744a54042</t>
   </si>
 </sst>
 </file>
@@ -4415,7 +4421,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4428,6 +4434,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4774,7 +4784,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G550"/>
+  <dimension ref="A1:G551"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17228,8 +17238,28 @@
         <v>1213</v>
       </c>
     </row>
+    <row r="551" spans="1:7">
+      <c r="A551">
+        <v>550</v>
+      </c>
+      <c r="B551" s="10" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D551" t="s">
+        <v>190</v>
+      </c>
+      <c r="E551" t="s">
+        <v>190</v>
+      </c>
+      <c r="F551">
+        <v>6</v>
+      </c>
+      <c r="G551" s="11" t="s">
+        <v>1215</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G548" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G550" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$550</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$551</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="1218">
   <si>
     <t>id</t>
   </si>
@@ -3764,6 +3764,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/010744a54042</t>
+  </si>
+  <si>
+    <t>野狗不需要墓碑2：天生坏种</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/b106935fd45d</t>
   </si>
 </sst>
 </file>
@@ -4784,7 +4790,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G551"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17254,12 +17260,32 @@
       <c r="F551">
         <v>6</v>
       </c>
-      <c r="G551" s="11" t="s">
+      <c r="G551" s="5" t="s">
         <v>1215</v>
       </c>
     </row>
+    <row r="552" spans="1:7">
+      <c r="A552">
+        <v>551</v>
+      </c>
+      <c r="B552" s="11" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D552" t="s">
+        <v>190</v>
+      </c>
+      <c r="E552" t="s">
+        <v>190</v>
+      </c>
+      <c r="F552">
+        <v>6</v>
+      </c>
+      <c r="G552" s="11" t="s">
+        <v>1217</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G550" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G551" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$551</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$552</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="1243">
   <si>
     <t>id</t>
   </si>
@@ -3771,6 +3771,141 @@
   <si>
     <t>https://pan.quark.cn/s/b106935fd45d</t>
   </si>
+  <si>
+    <t>蜘蛛侠：平行宇宙</t>
+  </si>
+  <si>
+    <t>蜘蛛侠,平行宇宙</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1c0190227981</t>
+  </si>
+  <si>
+    <t>蜘蛛侠：纵横宇宙</t>
+  </si>
+  <si>
+    <t>蜘蛛侠,纵横宇宙</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/75cadb877855</t>
+  </si>
+  <si>
+    <t>超凡蜘蛛侠</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5d2a1264ba83</t>
+  </si>
+  <si>
+    <t>蜘蛛侠 托比·马奎尔版</t>
+  </si>
+  <si>
+    <t>蜘蛛侠,托比马奎尔</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/aade5716656e</t>
+  </si>
+  <si>
+    <t>蜘蛛侠：英雄归来</t>
+  </si>
+  <si>
+    <r>
+      <t>蜘蛛侠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>英雄归来</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/24a0d6c0e996</t>
+  </si>
+  <si>
+    <t>蜘蛛侠：英雄远征</t>
+  </si>
+  <si>
+    <r>
+      <t>蜘蛛侠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>英雄远征</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/aa7b37d235f8</t>
+  </si>
+  <si>
+    <t>蜘蛛侠：英雄无归</t>
+  </si>
+  <si>
+    <r>
+      <t>蜘蛛侠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>英雄无归</t>
+    </r>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/fb53407f76a8</t>
+  </si>
+  <si>
+    <t>蜘蛛侠：崭新之日</t>
+  </si>
+  <si>
+    <t>蜘蛛侠,崭新之日</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ca8720c4543d</t>
+  </si>
+  <si>
+    <t>终极蜘蛛侠</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0a86c2095bd4</t>
+  </si>
 </sst>
 </file>
 
@@ -3782,7 +3917,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3833,6 +3968,18 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4300,134 +4447,134 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4444,6 +4591,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4790,7 +4939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G561"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17268,7 +17417,7 @@
       <c r="A552">
         <v>551</v>
       </c>
-      <c r="B552" s="11" t="s">
+      <c r="B552" s="5" t="s">
         <v>1216</v>
       </c>
       <c r="D552" t="s">
@@ -17280,12 +17429,186 @@
       <c r="F552">
         <v>6</v>
       </c>
-      <c r="G552" s="11" t="s">
+      <c r="G552" s="5" t="s">
         <v>1217</v>
       </c>
     </row>
+    <row r="553" spans="1:7">
+      <c r="A553">
+        <v>552</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D553" t="s">
+        <v>143</v>
+      </c>
+      <c r="E553" t="s">
+        <v>143</v>
+      </c>
+      <c r="G553" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7">
+      <c r="A554">
+        <v>553</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C554" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D554" t="s">
+        <v>143</v>
+      </c>
+      <c r="E554" t="s">
+        <v>143</v>
+      </c>
+      <c r="G554" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7">
+      <c r="A555">
+        <v>554</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D555" t="s">
+        <v>143</v>
+      </c>
+      <c r="E555" t="s">
+        <v>143</v>
+      </c>
+      <c r="G555" s="11" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7">
+      <c r="A556">
+        <v>555</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D556" t="s">
+        <v>143</v>
+      </c>
+      <c r="E556" t="s">
+        <v>143</v>
+      </c>
+      <c r="G556" s="11" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="557" ht="15.5" spans="1:7">
+      <c r="A557">
+        <v>556</v>
+      </c>
+      <c r="B557" s="12" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C557" s="13" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D557" t="s">
+        <v>143</v>
+      </c>
+      <c r="E557" t="s">
+        <v>143</v>
+      </c>
+      <c r="G557" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="558" ht="15.5" spans="1:7">
+      <c r="A558">
+        <v>557</v>
+      </c>
+      <c r="B558" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C558" s="13" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D558" t="s">
+        <v>143</v>
+      </c>
+      <c r="E558" t="s">
+        <v>143</v>
+      </c>
+      <c r="G558" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="559" ht="15.5" spans="1:7">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559" s="13" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C559" s="13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D559" t="s">
+        <v>143</v>
+      </c>
+      <c r="E559" t="s">
+        <v>143</v>
+      </c>
+      <c r="G559" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D560" t="s">
+        <v>143</v>
+      </c>
+      <c r="E560" t="s">
+        <v>143</v>
+      </c>
+      <c r="G560" s="11" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7">
+      <c r="A561">
+        <v>560</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D561" t="s">
+        <v>143</v>
+      </c>
+      <c r="E561" t="s">
+        <v>143</v>
+      </c>
+      <c r="G561" s="11" t="s">
+        <v>1242</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G551" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G552" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$552</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$561</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2974" uniqueCount="1246">
   <si>
     <t>id</t>
   </si>
@@ -3809,6 +3809,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>蜘蛛侠</t>
     </r>
     <r>
@@ -3838,6 +3844,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>蜘蛛侠</t>
     </r>
     <r>
@@ -3867,6 +3879,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>蜘蛛侠</t>
     </r>
     <r>
@@ -3906,6 +3924,15 @@
   <si>
     <t>https://pan.quark.cn/s/0a86c2095bd4</t>
   </si>
+  <si>
+    <t>东京恐怖故事：如月车站</t>
+  </si>
+  <si>
+    <t>东京恐怖故事,如月车站</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/41c56905a332</t>
+  </si>
 </sst>
 </file>
 
@@ -3917,7 +3944,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3982,6 +4009,13 @@
       <color rgb="FF333333"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -4447,13 +4481,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4462,119 +4493,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4590,9 +4624,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4939,7 +4976,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G561"/>
+  <dimension ref="A1:G562"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17486,7 +17523,7 @@
       <c r="E555" t="s">
         <v>143</v>
       </c>
-      <c r="G555" s="11" t="s">
+      <c r="G555" s="5" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -17506,7 +17543,7 @@
       <c r="E556" t="s">
         <v>143</v>
       </c>
-      <c r="G556" s="11" t="s">
+      <c r="G556" s="5" t="s">
         <v>1228</v>
       </c>
     </row>
@@ -17514,10 +17551,10 @@
       <c r="A557">
         <v>556</v>
       </c>
-      <c r="B557" s="12" t="s">
+      <c r="B557" s="11" t="s">
         <v>1229</v>
       </c>
-      <c r="C557" s="13" t="s">
+      <c r="C557" s="12" t="s">
         <v>1230</v>
       </c>
       <c r="D557" t="s">
@@ -17534,10 +17571,10 @@
       <c r="A558">
         <v>557</v>
       </c>
-      <c r="B558" s="12" t="s">
+      <c r="B558" s="11" t="s">
         <v>1232</v>
       </c>
-      <c r="C558" s="13" t="s">
+      <c r="C558" s="12" t="s">
         <v>1233</v>
       </c>
       <c r="D558" t="s">
@@ -17554,10 +17591,10 @@
       <c r="A559">
         <v>558</v>
       </c>
-      <c r="B559" s="13" t="s">
+      <c r="B559" s="12" t="s">
         <v>1235</v>
       </c>
-      <c r="C559" s="13" t="s">
+      <c r="C559" s="12" t="s">
         <v>1236</v>
       </c>
       <c r="D559" t="s">
@@ -17586,7 +17623,7 @@
       <c r="E560" t="s">
         <v>143</v>
       </c>
-      <c r="G560" s="11" t="s">
+      <c r="G560" s="5" t="s">
         <v>1240</v>
       </c>
     </row>
@@ -17603,12 +17640,35 @@
       <c r="E561" t="s">
         <v>143</v>
       </c>
-      <c r="G561" s="11" t="s">
+      <c r="G561" s="5" t="s">
         <v>1242</v>
       </c>
     </row>
+    <row r="562" spans="1:7">
+      <c r="A562">
+        <v>561</v>
+      </c>
+      <c r="B562" s="13" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D562" t="s">
+        <v>190</v>
+      </c>
+      <c r="E562" t="s">
+        <v>190</v>
+      </c>
+      <c r="F562">
+        <v>7</v>
+      </c>
+      <c r="G562" s="14" t="s">
+        <v>1245</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G552" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G561" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$561</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$562</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2974" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1248">
   <si>
     <t>id</t>
   </si>
@@ -3932,6 +3932,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/41c56905a332</t>
+  </si>
+  <si>
+    <t>体温</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/eebbc27e7ac2</t>
   </si>
 </sst>
 </file>
@@ -4976,7 +4982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G562"/>
+  <dimension ref="A1:G563"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17663,12 +17669,32 @@
       <c r="F562">
         <v>7</v>
       </c>
-      <c r="G562" s="14" t="s">
+      <c r="G562" s="5" t="s">
         <v>1245</v>
       </c>
     </row>
+    <row r="563" spans="1:7">
+      <c r="A563">
+        <v>562</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D563" t="s">
+        <v>190</v>
+      </c>
+      <c r="E563" t="s">
+        <v>190</v>
+      </c>
+      <c r="F563">
+        <v>6</v>
+      </c>
+      <c r="G563" s="14" t="s">
+        <v>1247</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G561" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G562" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$563</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="1256">
   <si>
     <t>id</t>
   </si>
@@ -3938,6 +3938,30 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/eebbc27e7ac2</t>
+  </si>
+  <si>
+    <t>【2026考研英语】石雷鹏橙啦全程班</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4438a68d866c</t>
+  </si>
+  <si>
+    <t>橙啦六级全程班[石雷鹏]</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5caf4219ac1c</t>
+  </si>
+  <si>
+    <t>408计算机统考历年真题</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4ffa8ce9b42f</t>
+  </si>
+  <si>
+    <t>1980-2025考研英语学习资料合集</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/35f57081c370</t>
   </si>
 </sst>
 </file>
@@ -4614,7 +4638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4635,7 +4659,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4982,7 +5005,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G563"/>
+  <dimension ref="A1:G567"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17689,12 +17712,80 @@
       <c r="F563">
         <v>6</v>
       </c>
-      <c r="G563" s="14" t="s">
+      <c r="G563" s="5" t="s">
         <v>1247</v>
       </c>
     </row>
+    <row r="564" spans="1:7">
+      <c r="A564">
+        <v>563</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D564" t="s">
+        <v>10</v>
+      </c>
+      <c r="E564" t="s">
+        <v>10</v>
+      </c>
+      <c r="G564" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7">
+      <c r="A565">
+        <v>564</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D565" t="s">
+        <v>10</v>
+      </c>
+      <c r="E565" t="s">
+        <v>10</v>
+      </c>
+      <c r="G565" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7">
+      <c r="A566">
+        <v>565</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D566" t="s">
+        <v>10</v>
+      </c>
+      <c r="E566" t="s">
+        <v>10</v>
+      </c>
+      <c r="G566" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7">
+      <c r="A567">
+        <v>566</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D567" t="s">
+        <v>10</v>
+      </c>
+      <c r="E567" t="s">
+        <v>10</v>
+      </c>
+      <c r="G567" t="s">
+        <v>1255</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G562" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G563" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$563</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$567</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -17547,10 +17547,10 @@
         <v>1224</v>
       </c>
       <c r="D555" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E555" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G555" s="5" t="s">
         <v>1225</v>
@@ -17567,10 +17567,10 @@
         <v>1227</v>
       </c>
       <c r="D556" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E556" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G556" s="5" t="s">
         <v>1228</v>
@@ -17587,10 +17587,10 @@
         <v>1230</v>
       </c>
       <c r="D557" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E557" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G557" t="s">
         <v>1231</v>
@@ -17607,10 +17607,10 @@
         <v>1233</v>
       </c>
       <c r="D558" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E558" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G558" t="s">
         <v>1234</v>
@@ -17627,10 +17627,10 @@
         <v>1236</v>
       </c>
       <c r="D559" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E559" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G559" t="s">
         <v>1237</v>
@@ -17647,10 +17647,10 @@
         <v>1239</v>
       </c>
       <c r="D560" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="E560" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="G560" s="5" t="s">
         <v>1240</v>
@@ -17785,7 +17785,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G563" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G567" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="1258">
   <si>
     <t>id</t>
   </si>
@@ -3962,6 +3962,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/35f57081c370</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海2苦夏</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6b6be0d93ec9</t>
   </si>
 </sst>
 </file>
@@ -4638,7 +4644,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4659,6 +4665,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5005,7 +5012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G567"/>
+  <dimension ref="A1:G568"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17782,6 +17789,26 @@
       </c>
       <c r="G567" t="s">
         <v>1255</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7">
+      <c r="A568">
+        <v>567</v>
+      </c>
+      <c r="B568" s="14" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D568" t="s">
+        <v>190</v>
+      </c>
+      <c r="E568" t="s">
+        <v>190</v>
+      </c>
+      <c r="F568">
+        <v>6</v>
+      </c>
+      <c r="G568" s="14" t="s">
+        <v>1257</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$567</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$568</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1260">
   <si>
     <t>id</t>
   </si>
@@ -3968,6 +3968,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/6b6be0d93ec9</t>
+  </si>
+  <si>
+    <t>2027考研英语课程资源大全</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/869c0d46cdbb</t>
   </si>
 </sst>
 </file>
@@ -5012,7 +5018,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G568"/>
+  <dimension ref="A1:G569"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17795,7 +17801,7 @@
       <c r="A568">
         <v>567</v>
       </c>
-      <c r="B568" s="14" t="s">
+      <c r="B568" s="5" t="s">
         <v>1256</v>
       </c>
       <c r="D568" t="s">
@@ -17807,12 +17813,29 @@
       <c r="F568">
         <v>6</v>
       </c>
-      <c r="G568" s="14" t="s">
+      <c r="G568" s="5" t="s">
         <v>1257</v>
       </c>
     </row>
+    <row r="569" spans="1:7">
+      <c r="A569">
+        <v>568</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D569" t="s">
+        <v>10</v>
+      </c>
+      <c r="E569" t="s">
+        <v>10</v>
+      </c>
+      <c r="G569" s="14" t="s">
+        <v>1259</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G567" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G568" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$568</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$569</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4650,7 +4650,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4671,7 +4671,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -17830,12 +17829,12 @@
       <c r="E569" t="s">
         <v>10</v>
       </c>
-      <c r="G569" s="14" t="s">
+      <c r="G569" s="5" t="s">
         <v>1259</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G568" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G569" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3006" uniqueCount="1262">
   <si>
     <t>id</t>
   </si>
@@ -3974,6 +3974,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/869c0d46cdbb</t>
+  </si>
+  <si>
+    <t>飞哥与小佛</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/51df7e9e2745</t>
   </si>
 </sst>
 </file>
@@ -4650,7 +4656,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
@@ -4671,6 +4677,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5017,7 +5024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G569"/>
+  <dimension ref="A1:G570"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -17831,6 +17838,23 @@
       </c>
       <c r="G569" s="5" t="s">
         <v>1259</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7">
+      <c r="A570">
+        <v>569</v>
+      </c>
+      <c r="B570" s="14" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D570" t="s">
+        <v>143</v>
+      </c>
+      <c r="E570" t="s">
+        <v>143</v>
+      </c>
+      <c r="G570" s="14" t="s">
+        <v>1261</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1175,7 +1175,6 @@
           <t>《女王带你唱读Raz》(340集) [幼儿分级英语启蒙动画]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>启蒙英语</t>
@@ -1186,7 +1185,6 @@
           <t>学习资料</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/47fa7de74af7</t>
@@ -1202,7 +1200,6 @@
           <t>SSS儿歌及配套合集</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>启蒙英语</t>
@@ -1213,7 +1210,6 @@
           <t>学习资料</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f0a378f45f0b</t>
@@ -1229,7 +1225,6 @@
           <t>监狱风云</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>剧集,美剧,监狱风云</t>
@@ -1240,7 +1235,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/98da7aed43e2</t>
@@ -1256,7 +1250,6 @@
           <t>传奇办公室</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>剧集,美剧,传奇办公室</t>
@@ -1267,7 +1260,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c9e9cf4ef725</t>
@@ -1283,7 +1275,6 @@
           <t>大西洋帝国</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>剧集,美剧,大西洋帝国</t>
@@ -1294,7 +1285,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2b6ec19ca1ef</t>
@@ -1310,7 +1300,6 @@
           <t>飞天大盗</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>剧集,美剧,飞天大盗</t>
@@ -1321,7 +1310,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a32ba31162a1</t>
@@ -1337,7 +1325,6 @@
           <t>国土安全</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>剧集,美剧,国土安全</t>
@@ -1348,7 +1335,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/cae446202571</t>
@@ -1364,7 +1350,6 @@
           <t>黄石</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>剧集,美剧,黄石</t>
@@ -1375,7 +1360,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fcb925340306</t>
@@ -1391,7 +1375,6 @@
           <t>火线 The Wire 1-5季全集 中英双字</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>剧集,美剧,火线</t>
@@ -1402,7 +1385,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ef3d7bea1b0f</t>
@@ -1418,7 +1400,6 @@
           <t>绝命毒师 1-5季全集+电影</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>剧集,美剧,绝命毒师</t>
@@ -1429,7 +1410,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7af9af1faaf3</t>
@@ -1445,7 +1425,6 @@
           <t>良医</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>剧集,美剧,良医</t>
@@ -1456,7 +1435,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/91b146f2bc7f</t>
@@ -1472,7 +1450,6 @@
           <t>老友记 S01-S10（1994-2003）1080P蓝光 内封简英特效字幕</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>剧集,美剧,老友记</t>
@@ -1483,7 +1460,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/64ac023a320d</t>
@@ -1514,7 +1490,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" s="1" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3c4920236e7e</t>
@@ -1530,7 +1505,6 @@
           <t>斯巴达克斯 全4季 未删减版</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>剧集,美剧,斯巴达克斯</t>
@@ -1541,7 +1515,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/da6168e6a62c</t>
@@ -1557,7 +1530,6 @@
           <t>生活大爆炸</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>剧集,美剧,生活大爆炸</t>
@@ -1568,7 +1540,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e28b54f51959</t>
@@ -1584,7 +1555,6 @@
           <t>唐顿庄园 1-6季</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>剧集,美剧,唐顿庄园</t>
@@ -1595,7 +1565,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/845a7fda1f52</t>
@@ -1611,7 +1580,6 @@
           <t>无耻之徒 全1-11季</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>剧集,美剧,无耻之徒</t>
@@ -1622,7 +1590,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/84039429fbe2</t>
@@ -1638,7 +1605,6 @@
           <t>兄弟连 (2001) 1080P 蓝光 国英音轨 特效字幕</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>剧集,美剧,兄弟连</t>
@@ -1649,7 +1615,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/eb0018f17d2c</t>
@@ -1665,7 +1630,6 @@
           <t>行尸走肉 11季全+2部番外无删减 1080P</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>剧集,美剧,行尸走肉</t>
@@ -1676,7 +1640,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/141068ddd275</t>
@@ -1692,7 +1655,6 @@
           <t>浴血黑帮</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>剧集,美剧,浴血黑帮</t>
@@ -1703,7 +1665,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e42ee1fa3786</t>
@@ -1719,7 +1680,6 @@
           <t>越狱</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>剧集,美剧,越狱</t>
@@ -1730,7 +1690,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b389c835fba5</t>
@@ -1746,7 +1705,6 @@
           <t>纸牌屋 (1-6季) 豆瓣9.3分</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>剧集,美剧,纸牌屋</t>
@@ -1757,7 +1715,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b23c1ee89e81</t>
@@ -1773,7 +1730,6 @@
           <t>《风骚律师》1-6季 4K 全集 内嵌简英字幕</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>剧集,美剧,风骚律师</t>
@@ -1784,7 +1740,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/60666ee04fe1</t>
@@ -1800,7 +1755,6 @@
           <t>《破产姐妹》1-6季全 4K超清无删减</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>剧集,美剧,破产姐妹</t>
@@ -1811,7 +1765,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6a8880143dee</t>
@@ -1827,7 +1780,6 @@
           <t>【美剧】黑吃黑.全4季.中英双字.1080P</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>剧集,美剧,黑吃黑</t>
@@ -1838,7 +1790,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b03f39790294</t>
@@ -1854,7 +1805,6 @@
           <t>黑钱胜地</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>剧集,美剧,黑钱胜地</t>
@@ -1865,7 +1815,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/00f31baf0b52</t>
@@ -1896,7 +1845,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2d8fe11a64f6</t>
@@ -1912,7 +1860,6 @@
           <t>黑袍纠察队</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>剧集,美剧,黑袍纠察队</t>
@@ -1923,7 +1870,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ac9dbacc3a8a</t>
@@ -1939,7 +1885,6 @@
           <t>请回答1988 4K</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>剧集,韩剧,请回答1988</t>
@@ -1950,7 +1895,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1c26d1bceb53</t>
@@ -1966,7 +1910,6 @@
           <t>我的大叔</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>剧集,韩剧,我的大叔</t>
@@ -1977,7 +1920,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/aa1b07232473</t>
@@ -1993,7 +1935,6 @@
           <t>秘密森林 1-2季</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>剧集,韩剧,秘密森林</t>
@@ -2004,7 +1945,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4f593f8ecb99</t>
@@ -2020,7 +1960,6 @@
           <t>信号（2016）全16集</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>剧集,韩剧,信号</t>
@@ -2031,7 +1970,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ae72792dfbe0</t>
@@ -2062,7 +2000,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/215166a7f55d</t>
@@ -2078,7 +2015,6 @@
           <t>浪漫的体质</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>剧集,韩剧,浪漫的体质</t>
@@ -2089,7 +2025,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/66c18b025584</t>
@@ -2105,7 +2040,6 @@
           <t>棒球大联盟</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>剧集,韩剧,棒球大联盟</t>
@@ -2116,7 +2050,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5c494118590a</t>
@@ -2132,7 +2065,6 @@
           <t>搞笑一家人</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>剧集,韩剧,搞笑一家人</t>
@@ -2143,7 +2075,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d698cdcde69e</t>
@@ -2159,7 +2090,6 @@
           <t>第五共和国</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>剧集,韩剧,第五共和国</t>
@@ -2170,7 +2100,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/114f841f4acf</t>
@@ -2186,7 +2115,6 @@
           <t>顺风妇产科</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>剧集,韩剧,顺风妇产科</t>
@@ -2197,7 +2125,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9d1c3ff0b45b</t>
@@ -2213,7 +2140,6 @@
           <t>模范出租车</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>剧集,韩剧,模范出租车</t>
@@ -2224,7 +2150,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c927c73b9c3d</t>
@@ -2240,7 +2165,6 @@
           <t>背着善宰跑</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>剧集,韩剧,背着善宰跑</t>
@@ -2251,7 +2175,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c9e6ea1c5a78</t>
@@ -2267,7 +2190,6 @@
           <t>超异能族</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>剧集,韩剧,超异能族</t>
@@ -2278,7 +2200,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4f5448bae0bc</t>
@@ -2294,7 +2215,6 @@
           <t>好久没做</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>剧集,韩剧,好久没做</t>
@@ -2305,7 +2225,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/662c139bb03e</t>
@@ -2321,7 +2240,6 @@
           <t>我的出走日记</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>剧集,韩剧,我的出走日记</t>
@@ -2332,7 +2250,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b28353c9de59</t>
@@ -2348,7 +2265,6 @@
           <t>飞出个未来[1-13季+大电影合集][ 动漫 喜剧]</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>动漫,飞出个未来</t>
@@ -2359,7 +2275,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3e71231c34e8</t>
@@ -2375,7 +2290,6 @@
           <t>怪诞小镇 1-2季全集 特别篇 中英双字</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>动漫,怪诞小镇</t>
@@ -2386,7 +2300,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ea6aa5d35d21</t>
@@ -2402,7 +2315,6 @@
           <t>怪诞小镇.1-2季全合集+番外+特辑</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>动漫,怪诞小镇</t>
@@ -2413,7 +2325,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/87cfb16d0ad5</t>
@@ -2429,7 +2340,6 @@
           <t>幻灭 全五季</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>动漫,幻灭</t>
@@ -2440,7 +2350,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/905326fb51ce</t>
@@ -2456,7 +2365,6 @@
           <t>猫头鹰魔法社 S1-S3 合集</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>动漫,猫头鹰魔法社</t>
@@ -2467,7 +2375,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5be9090d10a5</t>
@@ -2483,7 +2390,6 @@
           <t>探险活宝S1-S10 十季</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>动漫,探险活宝</t>
@@ -2494,7 +2400,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c776f07d4c71</t>
@@ -2510,7 +2415,6 @@
           <t>外星也难民 1-6季 1080P</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>动漫,外星也难民</t>
@@ -2521,7 +2425,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/91ce7f35bfe9</t>
@@ -2537,7 +2440,6 @@
           <t>希尔达（1-3季全+剧场版）Hilda</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>动漫,希尔达</t>
@@ -2548,7 +2450,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/bc18ef0da559</t>
@@ -2564,7 +2465,6 @@
           <t>《海底小纵队》(1-9季) [趣学英语][117G]</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>动漫,海底小纵队</t>
@@ -2575,7 +2475,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5763243263de</t>
@@ -2591,7 +2490,6 @@
           <t>【恶搞之家】S1-S22季 1080P 中英字幕未删减收藏版</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>动漫,恶搞之家</t>
@@ -2602,7 +2500,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e44fa038ef9e</t>
@@ -2618,7 +2515,6 @@
           <t>《小马宝莉》(1-9季) [经典儿童动画故事]</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>动漫,小马宝莉</t>
@@ -2629,7 +2525,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/63da9a407f26</t>
@@ -2645,7 +2540,6 @@
           <t>马男波杰克</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>动漫,马男波杰克</t>
@@ -2656,7 +2550,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/017511f52017</t>
@@ -2672,7 +2565,6 @@
           <t>拽妹儿</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>动漫,拽妹儿</t>
@@ -2683,7 +2575,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a0b7918bf26b</t>
@@ -2699,7 +2590,6 @@
           <t>尼克频道英语启蒙动画《喧闹一家亲 The Loud use (1-4季) 》</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>动漫,喧闹一家亲</t>
@@ -2710,7 +2600,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e4849b8d2115</t>
@@ -2726,7 +2615,6 @@
           <t>奇幻沼泽</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>动漫,奇幻沼泽</t>
@@ -2737,7 +2625,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f3bcdb716267</t>
@@ -2753,7 +2640,6 @@
           <t>亲子情境英语学习资料包 (视频+音频+图片)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>启蒙英语</t>
@@ -2764,7 +2650,6 @@
           <t>学习资料</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/07acc9b06384</t>
@@ -2803,6 +2688,11 @@
           <t>https://pan.quark.cn/s/3a3303e54e4a</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>欢乐</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2813,7 +2703,6 @@
           <t>从优质生活到巴士乡村生活</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>综艺,真人秀</t>
@@ -2824,7 +2713,6 @@
           <t>综艺</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/68678b493510</t>
@@ -2840,7 +2728,6 @@
           <t>选美皇后遇见乡村皇后</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>综艺,真人秀</t>
@@ -2851,7 +2738,6 @@
           <t>综艺</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/807cd82a720d</t>
@@ -2867,7 +2753,6 @@
           <t>50个陌生人互相滑动</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>综艺,真人秀</t>
@@ -2878,7 +2763,6 @@
           <t>综艺</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/75463a265bfd</t>
@@ -2894,7 +2778,6 @@
           <t>简历模板个性模板40个</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>简历模板</t>
@@ -2905,7 +2788,6 @@
           <t>模板</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5fd8a6e8c830</t>
@@ -2921,7 +2803,6 @@
           <t>简历模板表格模板50个</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>简历模板</t>
@@ -2932,7 +2813,6 @@
           <t>模板</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4fee740d83c1</t>
@@ -2948,7 +2828,6 @@
           <t>简历模板各专业简历67个</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>简历模板</t>
@@ -2959,7 +2838,6 @@
           <t>模板</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f367685cfefc</t>
@@ -2975,7 +2853,6 @@
           <t>好一个乖乖女</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -2986,7 +2863,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0da2e70e236f</t>
@@ -3002,7 +2878,6 @@
           <t>玫瑰冠冕</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3013,7 +2888,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/72fad0d6fd78</t>
@@ -3029,7 +2903,6 @@
           <t>家里家外</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3040,7 +2913,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b08d1d32782d</t>
@@ -3056,7 +2928,6 @@
           <t>深情诱引</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3067,7 +2938,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" s="1" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/54ae4c79b6ef</t>
@@ -3083,7 +2953,6 @@
           <t>我在八零年代当后妈</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3094,7 +2963,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e1e91ab28d0c</t>
@@ -3110,7 +2978,6 @@
           <t>步步为营</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3121,7 +2988,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e9a0505d423a</t>
@@ -3137,7 +3003,6 @@
           <t>声色犬马</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3148,7 +3013,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6fa3ba822a52</t>
@@ -3164,7 +3028,6 @@
           <t>请君入瓮</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3175,7 +3038,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" s="1" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/32466a4d8102</t>
@@ -3191,7 +3053,6 @@
           <t>美国往事</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>电影</t>
@@ -3202,7 +3063,6 @@
           <t>电影</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ff5a85744c5d</t>
@@ -3218,7 +3078,6 @@
           <t>穆赫兰跳</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>电影</t>
@@ -3229,7 +3088,6 @@
           <t>电影</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6ccb09286f58</t>
@@ -3245,7 +3103,6 @@
           <t>盛夏芬德拉</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>短剧</t>
@@ -3256,7 +3113,6 @@
           <t>短剧</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5b1b6c2a4735</t>
@@ -3272,7 +3128,6 @@
           <t>2025抖音网红歌曲</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>抖音,网红,歌曲</t>
@@ -3283,7 +3138,6 @@
           <t>音乐</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dc9d400da273</t>
@@ -3299,7 +3153,6 @@
           <t>爱尔兰人</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>电影,黑帮电影</t>
@@ -3310,7 +3163,6 @@
           <t>电影</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7abdc28d5d78</t>
@@ -3326,7 +3178,6 @@
           <t>匹兹堡医护前线 The Pitt 第一季</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>剧集,美剧,匹兹堡医护前线</t>
@@ -3337,7 +3188,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e7921a23213d</t>
@@ -3353,7 +3203,6 @@
           <t>马丁内斯死在惊奇馆</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3387,7 +3236,6 @@
           <t>堕落街传奇(S01-S03合集)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>剧集,美剧,堕落街传奇</t>
@@ -3398,7 +3246,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/294cfd0559d9</t>
@@ -3414,7 +3261,6 @@
           <t>嗜血法医1-8季[附杀魔新生][美国悬疑犯罪]</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>剧集,美剧,嗜血法医</t>
@@ -3425,7 +3271,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c9202cab2164</t>
@@ -3441,7 +3286,6 @@
           <t>都铎王朝</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>剧集,美剧,都铎王朝</t>
@@ -3452,7 +3296,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4c9a8a3dd24a</t>
@@ -3468,7 +3311,6 @@
           <t>亢奋S1-S2+特别集</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>剧集,美剧,亢奋</t>
@@ -3479,7 +3321,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d09674d89e0e</t>
@@ -3495,7 +3336,6 @@
           <t>一点半</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3529,7 +3369,6 @@
           <t>流氓叙事</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3563,7 +3402,6 @@
           <t>人吃人 4-5人开放</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3580,6 +3418,11 @@
       <c r="G89" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/75df5b4bb02e</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3435,6 @@
           <t>告别诗</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3626,7 +3468,6 @@
           <t>黑道家族</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>剧集,美剧,黑道家族</t>
@@ -3637,7 +3478,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c01736bb9d87</t>
@@ -3676,6 +3516,11 @@
           <t>https://pan.quark.cn/s/95e2b562166b</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>欢乐</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3686,7 +3531,6 @@
           <t>红影 5-6人开放本</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3703,6 +3547,11 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/663e837c08ee</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3564,6 @@
           <t>诛心太平间 5-6人开放</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3732,6 +3580,11 @@
       <c r="G94" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e380547efdca</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3597,6 @@
           <t>办公室谋杀案 4-5人封闭</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3761,6 +3613,11 @@
       <c r="G95" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0c67d09fc0eb</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3630,6 @@
           <t>大明星最后的演出 2人半开放</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3790,6 +3646,11 @@
       <c r="G96" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/affbfdf5c09b</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3663,6 @@
           <t>西游记降魔之莲花精 4人封闭</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3819,6 +3679,11 @@
       <c r="G97" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/48b8370c77f2</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -3854,6 +3719,11 @@
           <t>https://pan.quark.cn/s/d47624bd9832</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>古风</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3887,6 +3757,11 @@
           <t>https://pan.quark.cn/s/4e04a07074cd</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>古风</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3897,7 +3772,6 @@
           <t>名捕1-铁鸡帮 4人开放</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3914,6 +3788,11 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3ca6c1226788</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3805,6 @@
           <t>名捕2-千门宫 4人开放</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3943,6 +3821,11 @@
       <c r="G101" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4e95f87ae65c</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3838,6 @@
           <t>名捕3-龙门客栈 4人开放</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -3972,6 +3854,11 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0c8af7f4b898</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3871,6 @@
           <t>江湖客栈开放 4人开放</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4001,6 +3887,11 @@
       <c r="G103" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/18081e8c3875</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>武侠</t>
         </is>
       </c>
     </row>
@@ -4013,7 +3904,6 @@
           <t>病毒 4-5人开放本</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4030,6 +3920,11 @@
       <c r="G104" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/cb0d8c38ffa0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>科幻</t>
         </is>
       </c>
     </row>
@@ -4042,7 +3937,6 @@
           <t>致命喷泉 4-5人开放</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4059,6 +3953,11 @@
       <c r="G105" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/bbfe2b45f3a7</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4071,7 +3970,6 @@
           <t>无间旅途 4-5人开放</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4088,6 +3986,11 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e08d16cf0c0d</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4003,6 @@
           <t>绝命阳光号 4-5人开放</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4117,6 +4019,11 @@
       <c r="G107" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ee00659579e2</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4036,6 @@
           <t>人生考场 4-5人开放</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4146,6 +4052,11 @@
       <c r="G108" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/53b501724102</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4069,6 @@
           <t>巴德将军的信 5人封闭</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4175,6 +4085,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a0531133a800</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>谍战</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4102,6 @@
           <t>上海滩杀人事件 5人封闭</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4204,6 +4118,11 @@
       <c r="G110" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dfee302903ea</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4135,6 @@
           <t>致命圣诞节5人封闭</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4233,6 +4151,11 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d5c479fe3d09</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4168,6 @@
           <t>华丽的背后 5人开放</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4262,6 +4184,11 @@
       <c r="G112" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a5a9207629f7</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4201,6 @@
           <t>魔盗之殇 5人开放</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4291,6 +4217,11 @@
       <c r="G113" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/07c947e8866d</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4234,6 @@
           <t>东方之星号游轮事件 5人开放</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4320,6 +4250,11 @@
       <c r="G114" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ebb5a7c4b626</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4267,6 @@
           <t>东方之星游轮续集 5人开放</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4349,6 +4283,11 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/896f9421277f</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4300,6 @@
           <t>十年 5人开放</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4378,6 +4316,11 @@
       <c r="G116" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f88b3d74a9c5</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4333,6 @@
           <t>女演员之死 5-6人封闭</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4407,6 +4349,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4787837e9d45</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4366,6 @@
           <t>军师1 望明路 5-6人封闭</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4436,6 +4382,11 @@
       <c r="G118" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fb5a45a2f239</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>机制</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4399,6 @@
           <t>天命 5-6人封闭</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4465,6 +4415,11 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/df13c700276d</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>仙侠/机制</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4432,6 @@
           <t>夜袭 5-6人封闭</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4494,6 +4448,11 @@
       <c r="G120" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/bcaaeb247783</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4465,6 @@
           <t>乐声 5-6人封闭</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4523,6 +4481,11 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5c8986db2e1d</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4498,6 @@
           <t>惊魂首映 5-6人封闭</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4552,6 +4514,11 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d89df5658a16</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4531,6 @@
           <t>漫画家之死 5-6开放</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4581,6 +4547,11 @@
       <c r="G123" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/11650976f13a</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4564,6 @@
           <t>禁止入内 5-6人</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4610,6 +4580,11 @@
       <c r="G124" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/467f755bb18c</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4597,6 @@
           <t>滴血之瞳 5-6人开放</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4639,6 +4613,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5f80a12a2d94</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4630,6 @@
           <t>传说中的故事 5-6人开放</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4668,6 +4646,11 @@
       <c r="G126" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2ad16c92c895</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4663,6 @@
           <t>红楼梦中人 5-6人开放</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4697,6 +4679,11 @@
       <c r="G127" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6bac467eb6f6</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4696,6 @@
           <t>富豪之死 5-6人开放</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4726,6 +4712,11 @@
       <c r="G128" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/69c424fcb540</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4729,6 @@
           <t>长生门 5-6人</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4755,6 +4745,11 @@
       <c r="G129" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d57753b80c6b</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4762,6 @@
           <t>雪玉山 5-6人开放</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4784,6 +4778,11 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f048cf2afecd</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4795,6 @@
           <t>西门变 5-6人开放</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4813,6 +4811,11 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5ed70f07839d</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4828,6 @@
           <t>江夏劫 5-6人开放</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4842,6 +4844,11 @@
       <c r="G132" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/be28eb7fece7</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4861,6 @@
           <t>渡厄 5-6人开放</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4871,6 +4877,11 @@
       <c r="G133" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/68fe850f8581</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>仙侠/情感</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4894,6 @@
           <t>颍汝流风 5-6人开放</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4900,6 +4910,11 @@
       <c r="G134" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3ddb8d4e4498</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>古风/情感</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4927,6 @@
           <t>庆典前夜5-6人开放</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4929,6 +4943,11 @@
       <c r="G135" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ba5a12d37c67</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4960,6 @@
           <t>校园不可思议事件 5-6人开放</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4958,6 +4976,11 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0535d2bc2a02</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4993,6 @@
           <t>和平饭店 5-6人开放</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -4987,6 +5009,11 @@
       <c r="G137" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/96575dcf411d</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5026,6 @@
           <t>血海无涯 5-6人开放</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5016,6 +5042,11 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d6e25f171eab</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5059,6 @@
           <t>马戏团事件 6人封闭</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5045,6 +5075,11 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/044e806025b6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5092,6 @@
           <t>致命倒计时 6人封闭</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5074,6 +5108,11 @@
       <c r="G140" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/97f47aaf77a4</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5125,6 @@
           <t>愤怒的葡萄 6人封闭</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5103,6 +5141,11 @@
       <c r="G141" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4769ed2da63d</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5158,6 @@
           <t>老烟枪 6人封闭本</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5132,6 +5174,11 @@
       <c r="G142" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d2ba4178b779</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5191,6 @@
           <t>夜总会杀人夜 6人封闭本</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5161,6 +5207,11 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9a1075abd5c2</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5224,6 @@
           <t>米兰凶杀案 6人封闭式</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5190,6 +5240,11 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a500574eaa6f</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5257,6 @@
           <t>电梯恶魔 6人封闭</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5219,6 +5273,11 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f9f646a6371f</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5290,6 @@
           <t>美术室杀人事件 6人开放</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5248,6 +5306,11 @@
       <c r="G146" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9c3d18f3f8aa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5323,6 @@
           <t>死亡致意 6人开放</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5277,6 +5339,11 @@
       <c r="G147" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/32d51b1f3360</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,6 @@
           <t>怒海余生 6人开放</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5306,6 +5372,11 @@
       <c r="G148" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/14ede8796f8b</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5389,6 @@
           <t>傀儡的记忆 6人开放</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5335,6 +5405,11 @@
       <c r="G149" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9cdb5d7c3433</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5422,6 @@
           <t>神秘研究所 6人开放</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5364,6 +5438,11 @@
       <c r="G150" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/511ffaf7be2e</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5455,6 @@
           <t>塞西尔迷雾 6人开放</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5393,6 +5471,11 @@
       <c r="G151" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/aaf952f578f9</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5488,6 @@
           <t>怪病侵袭 6人开放</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5422,6 +5504,11 @@
       <c r="G152" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9f19b563af95</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5521,6 @@
           <t>中央贸易公司杀人事件 6人开放</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5451,6 +5537,11 @@
       <c r="G153" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/783a0303e936</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5554,6 @@
           <t>电梯惊魂 6人开放</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5480,6 +5570,11 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fbab44a468e9</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5587,6 @@
           <t>穿越时空的爱 6人半开放</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5509,6 +5603,11 @@
       <c r="G155" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c4e17bf12479</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>科幻</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5620,6 @@
           <t>光棍节血案 6人开放</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5538,6 +5636,11 @@
       <c r="G156" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1b541ae369f2</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5653,6 @@
           <t>人间 6-7人封闭</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5567,6 +5669,11 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/57c226791e5f</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5686,6 @@
           <t>死去的女儿 6~7开放</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5596,6 +5702,11 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2eaf114cd60f</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5719,6 @@
           <t>大名青龙街 6~7开放</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5625,6 +5735,11 @@
       <c r="G159" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/72e39948fc7e</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5752,6 @@
           <t>雨中的钟楼 6-7人开放</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5654,6 +5768,11 @@
       <c r="G160" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a7abe651d760</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5785,6 @@
           <t>兽心 6-7人开放</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5683,6 +5801,11 @@
       <c r="G161" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0a1354a2063e</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5818,6 @@
           <t>生死道 6-7人开放</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5712,6 +5834,11 @@
       <c r="G162" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e30cfa1c3b2d</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>仙侠</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5851,6 @@
           <t>古堡迷踪 6-7人开放</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5741,6 +5867,11 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/bdd9df4b0009</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5884,6 @@
           <t>凝视深渊 6-7人开放</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5770,6 +5900,11 @@
       <c r="G164" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/de11f38e54ea</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5917,6 @@
           <t>万灵血6-7人开放</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5799,6 +5933,11 @@
       <c r="G165" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d6478b54b440</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5950,6 @@
           <t>酒红色的谋杀6-8人封闭</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5828,6 +5966,11 @@
       <c r="G166" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/37f976a6eee0</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5983,6 @@
           <t>致命遗嘱 6-11开放</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5857,6 +5999,11 @@
       <c r="G167" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ab9cf71e6da1</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5869,7 +6016,6 @@
           <t>奥伯利庄园 7人封闭</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5886,6 +6032,11 @@
       <c r="G168" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/56a84a3efb1f</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5898,7 +6049,6 @@
           <t>南瓜投毒者 7人封闭</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5915,6 +6065,11 @@
       <c r="G169" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9914159ffa05</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6082,6 @@
           <t>加勒比海悲剧 7人封闭本</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5944,6 +6098,11 @@
       <c r="G170" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/db3ef8601f4e</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -5956,7 +6115,6 @@
           <t>绝命派对 7人封闭</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -5973,6 +6131,11 @@
       <c r="G171" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b80461156691</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -5985,7 +6148,6 @@
           <t>修玛疑案 7人半开放</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6002,6 +6164,11 @@
       <c r="G172" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f72450a06201</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6181,6 @@
           <t>禁锢之塔 7人半开放</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6031,6 +6197,11 @@
       <c r="G173" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c76439c6fd11</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6214,6 @@
           <t>津门遗云 7人开放</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6060,6 +6230,11 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/54659c21c37b</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>机制</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6247,6 @@
           <t>血色牌局 7人开放</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6089,6 +6263,11 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a743344f480e</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6280,6 @@
           <t>弈剑诀 7人开放</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6118,6 +6296,11 @@
       <c r="G176" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f8d2c6a7b8eb</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6313,6 @@
           <t>丹水山庄 7人开放</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6147,6 +6329,11 @@
       <c r="G177" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b52efda1e829</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6346,6 @@
           <t>未完结的爱 7人开放</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6176,6 +6362,11 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/b5fdd85cca72</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6379,6 @@
           <t>幽灵特快 7人开放</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6205,6 +6395,11 @@
       <c r="G179" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/002290f44ba3</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6412,6 @@
           <t>青龙山精神病院 7人开放</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6234,6 +6428,11 @@
       <c r="G180" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/67cef72f5746</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6445,6 @@
           <t>名捕4-皇宫 7人开放</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6263,6 +6461,11 @@
       <c r="G181" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5e01843a34e5</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6478,6 @@
           <t>临终遗言 7-8人封闭</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6292,6 +6494,11 @@
       <c r="G182" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/06ab3f36069b</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6511,6 @@
           <t>幽灵复仇 7-8人开放</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6321,6 +6527,11 @@
       <c r="G183" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/41720495da45</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6544,6 @@
           <t>图纹窃案 8人封闭</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6350,6 +6560,11 @@
       <c r="G184" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/961334e5b6ac</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6577,6 @@
           <t>神秘岛 8人封闭</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6379,6 +6593,11 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/163c483c7028</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6610,6 @@
           <t>沃特顿庄园 8人封闭</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6408,6 +6626,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/8084a297fcf4</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6643,6 @@
           <t>狂欢节的悲剧 8人封闭</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6437,6 +6659,11 @@
       <c r="G187" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3ae05e69b308</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6676,6 @@
           <t>校园七大不可思议之谜杀人事件 8人封闭</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6466,6 +6692,11 @@
       <c r="G188" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0241f4af20c1</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6709,6 @@
           <t>飞弹机关宅邸杀人事件 8人封闭本</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6495,6 +6725,11 @@
       <c r="G189" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d4059b41d6ef</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6742,6 @@
           <t>年轮（5人开放）</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6524,6 +6758,11 @@
       <c r="G190" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/201ffd1f45b4</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6775,6 @@
           <t>孽岛疑云完整版（5人半开放）</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6553,6 +6791,11 @@
       <c r="G191" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/87eaa33b5866</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6808,6 @@
           <t>窗边的女人</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6599,7 +6841,6 @@
           <t>不能说的秘密</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6633,7 +6874,6 @@
           <t>彩虹酒吧</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6667,7 +6907,6 @@
           <t>神乐汤</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6701,7 +6940,6 @@
           <t>收藏馆怪谈夜</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6735,7 +6973,6 @@
           <t>月落洼</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6769,7 +7006,6 @@
           <t>中彩票</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6786,6 +7022,11 @@
       <c r="G198" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d9c4cf0b4066</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -6798,7 +7039,6 @@
           <t>来电</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6870,7 +7110,6 @@
           <t>月光下的持刀者</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6904,7 +7143,6 @@
           <t>唐人街捉妖</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6938,7 +7176,6 @@
           <t>谁与争疯</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6972,7 +7209,6 @@
           <t>窥镜</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -6989,6 +7225,11 @@
       <c r="G204" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a5f57e15428e</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7242,6 @@
           <t>一座城</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7035,7 +7275,6 @@
           <t>搞钱</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7069,7 +7308,6 @@
           <t>诡楼异事</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7103,7 +7341,6 @@
           <t>上路</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7120,6 +7357,11 @@
       <c r="G208" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d314b8afab24</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7412,6 @@
           <t>桔梗物语</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7204,7 +7445,6 @@
           <t>桐花中路私立协济医院怪谈</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7221,6 +7461,11 @@
       <c r="G211" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3acf12cb40ce</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7478,6 @@
           <t>冥婚</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7267,7 +7511,6 @@
           <t>下课后</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7284,6 +7527,11 @@
       <c r="G213" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5e0b3ac31f4c</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>校园</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7544,6 @@
           <t>前男友的100种死法（5人开放）</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7313,6 +7560,11 @@
       <c r="G214" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fed1f575fbcc</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7577,6 @@
           <t>伟大的一生</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7359,7 +7610,6 @@
           <t>双生探案</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7393,7 +7643,6 @@
           <t>归途</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7427,7 +7676,6 @@
           <t>宇宙奇点</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7444,6 +7692,11 @@
       <c r="G218" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2f53a947ddd3</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>科幻</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7709,6 @@
           <t>我亲爱的侦探小姐</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7490,7 +7742,6 @@
           <t>天衣无缝</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7524,7 +7775,6 @@
           <t>消失的兔尾巴</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7558,7 +7808,6 @@
           <t>记忆碎片</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7575,6 +7824,11 @@
       <c r="G222" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/254afea42a52</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7841,6 @@
           <t>西游记降魔之莲花精 4人封闭</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7604,6 +7857,11 @@
       <c r="G223" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ac750687a1f4</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7874,6 @@
           <t>江湖客栈 4人开放</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7633,6 +7890,11 @@
       <c r="G224" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3d6d703a1772</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>武侠</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7907,6 @@
           <t>第二十二条校规2 返校</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7679,7 +7940,6 @@
           <t>赌王之王</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7713,7 +7973,6 @@
           <t>梭哈监狱</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7747,7 +8006,6 @@
           <t>古木吟</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7781,7 +8039,6 @@
           <t>无间追凶</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7815,7 +8072,6 @@
           <t>陶宅夜话</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7849,7 +8105,6 @@
           <t>无限逃亡噩梦</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7883,7 +8138,6 @@
           <t>死亡回响</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7940,6 +8194,11 @@
           <t>https://pan.quark.cn/s/1d663430e5d8</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>古风</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7950,7 +8209,6 @@
           <t>阿姐鼓</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -7984,7 +8242,6 @@
           <t>双生 6人开放</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8001,6 +8258,11 @@
       <c r="G235" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9a6eaef2bd04</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8275,6 @@
           <t>青楼 7人开放</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8030,6 +8291,11 @@
       <c r="G236" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/134f9933fcc4</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8308,6 @@
           <t>摸鱼</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8076,7 +8341,6 @@
           <t>觉醒</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8093,6 +8357,11 @@
       <c r="G238" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/86bad56f21ba</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8374,6 @@
           <t>雾起云浮</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8139,7 +8407,6 @@
           <t>银子那点事</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8173,7 +8440,6 @@
           <t>一出好戏</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8207,7 +8473,6 @@
           <t>大疫</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8241,7 +8506,6 @@
           <t>那些回不去的年少时光</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>剧集,国剧,电视剧,那些回不去的年少时光</t>
@@ -8252,7 +8516,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0430293ba257</t>
@@ -8268,7 +8531,6 @@
           <t>那些回不去的年少时光</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>小说,那些回不去的年少时光</t>
@@ -8279,7 +8541,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/450745a17172</t>
@@ -8295,7 +8556,6 @@
           <t>大唐风华录</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8329,7 +8589,6 @@
           <t>森林派对</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8363,7 +8622,6 @@
           <t>逢山遇鬼</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8397,7 +8655,6 @@
           <t>万国来朝</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8431,7 +8688,6 @@
           <t>鲸鱼马戏团</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8465,7 +8721,6 @@
           <t>山之神</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8499,7 +8754,6 @@
           <t>消失的学号</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8533,7 +8787,6 @@
           <t>娘娘千岁</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8567,7 +8820,6 @@
           <t>校规2返校 开放6人</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8584,6 +8836,11 @@
       <c r="G253" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6f57d9c810ee</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8853,6 @@
           <t>海龟浓汤</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8668,7 +8924,6 @@
           <t>消失的红宝石</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8702,7 +8957,6 @@
           <t>余香</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8736,7 +8990,6 @@
           <t>幻方馆谋杀奇境</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8770,7 +9023,6 @@
           <t>疯人院</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8787,6 +9039,11 @@
       <c r="G259" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4f3716054c34</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -8799,7 +9056,6 @@
           <t>消失的第五人</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8833,7 +9089,6 @@
           <t>恋物癖罪恶之花</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8867,7 +9122,6 @@
           <t>二流货色</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8884,6 +9138,11 @@
       <c r="G262" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/de5789df34f2</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9155,6 @@
           <t>群星落幕时</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8930,7 +9188,6 @@
           <t>隔墙有眼</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8964,7 +9221,6 @@
           <t>雪夜城谜案</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -8998,7 +9254,6 @@
           <t>加个v呗</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9015,6 +9270,11 @@
       <c r="G266" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9135afbb1fc2</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -9050,6 +9310,11 @@
           <t>https://pan.quark.cn/s/bc237772d620</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>推理</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -9060,7 +9325,6 @@
           <t>躲猫猫</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9077,6 +9341,11 @@
       <c r="G268" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/aeba1716a49f</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9358,6 @@
           <t>诡寓实录</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9123,7 +9391,6 @@
           <t>不要回答</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9140,6 +9407,11 @@
       <c r="G270" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c04cbc664ff3</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>科幻</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9424,6 @@
           <t>黑色星期五</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9169,6 +9440,11 @@
       <c r="G271" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/717e7a680862</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9204,6 +9480,11 @@
           <t>https://pan.quark.cn/s/7238bd7db544</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>恐怖</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9214,7 +9495,6 @@
           <t>双影共秀</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9231,6 +9511,11 @@
       <c r="G273" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a984f9feb600</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9528,6 @@
           <t>与恶为邻的她</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9260,6 +9544,11 @@
       <c r="G274" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/38cee15eeaa1</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9561,6 @@
           <t>59分钟推理守则</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9289,6 +9577,11 @@
       <c r="G275" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ca355a2c0c37</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9594,6 @@
           <t>珠帘异梦</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9335,7 +9627,6 @@
           <t>生死道</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9369,7 +9660,6 @@
           <t>万灵血</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9403,7 +9693,6 @@
           <t>杀马特驾到通通闪开</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9420,6 +9709,11 @@
       <c r="G279" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dbda09ef8a4d</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9726,6 @@
           <t>别在派对搞谋杀</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9449,6 +9742,11 @@
       <c r="G280" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9808803ed573</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9759,6 @@
           <t>爱幼妇产医院</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9478,6 +9775,11 @@
       <c r="G281" s="2" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/18f5ee8d2498</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9792,6 @@
           <t>东京恐怖故事铃兰女校</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9507,6 +9808,11 @@
       <c r="G282" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/739751d100b3</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9825,6 @@
           <t>拆迁</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9536,6 +9841,11 @@
       <c r="G283" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0ec092a63e5e</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9858,6 @@
           <t>当海风吹过我的坟墓</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9582,7 +9891,6 @@
           <t>叫爸爸</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9616,7 +9924,6 @@
           <t>雨夜感染者</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9633,6 +9940,11 @@
       <c r="G286" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a23e007c6e4f</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9957,6 @@
           <t>草台班子</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9662,6 +9973,11 @@
       <c r="G287" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/71f801cf1e36</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9990,6 @@
           <t>野狗不需要墓碑</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9708,7 +10023,6 @@
           <t>人皮灯笼</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9742,7 +10056,6 @@
           <t>科举</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9759,6 +10072,11 @@
       <c r="G290" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d5c015c8daba</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -9794,6 +10112,11 @@
           <t>https://pan.quark.cn/s/931d63f66899</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>推理</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9804,7 +10127,6 @@
           <t>惊魂青金村</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9821,6 +10143,11 @@
       <c r="G292" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/45f3d9d03966</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9833,7 +10160,6 @@
           <t>雪嫁娘</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9850,6 +10176,11 @@
       <c r="G293" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/031a62b5bddb</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9862,7 +10193,6 @@
           <t>守夜人</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9879,6 +10209,11 @@
       <c r="G294" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4597878098b7</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -9891,7 +10226,6 @@
           <t>献祭者</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9908,6 +10242,11 @@
       <c r="G295" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/eb0e96e86371</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9920,7 +10259,6 @@
           <t>一座城2</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9937,6 +10275,11 @@
       <c r="G296" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f4ac3e17be93</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -9949,7 +10292,6 @@
           <t>胎屋</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -9966,6 +10308,11 @@
       <c r="G297" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/35d06c92a74d</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -9978,7 +10325,6 @@
           <t>食梦女</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10012,7 +10358,6 @@
           <t>刺杀肯尼迪</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10029,6 +10374,11 @@
       <c r="G299" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/50b0fd7e36d8</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>谍战</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10391,6 @@
           <t>璃火</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10058,6 +10407,11 @@
       <c r="G300" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5aa68b8028ef</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>仙侠</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10424,6 @@
           <t>第四栋教学楼</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10087,6 +10440,11 @@
       <c r="G301" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/533b7a27586f</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10457,6 @@
           <t>雪松郡公立医院</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10156,6 +10513,11 @@
           <t>https://pan.quark.cn/s/cd4d3d16c835</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>推理</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -10204,7 +10566,6 @@
           <t>凶手的小酒酒</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10221,6 +10582,11 @@
       <c r="G305" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fa309bb07bc3</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -10233,7 +10599,6 @@
           <t>月光酒馆2大浪</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10250,6 +10615,11 @@
       <c r="G306" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/75f3751136fe</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10632,6 @@
           <t>装病</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10279,6 +10648,11 @@
       <c r="G307" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/eea39c867e51</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10665,6 @@
           <t>惊人院：怪胎公馆</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10308,6 +10681,11 @@
       <c r="G308" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e32180ab226c</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10698,6 @@
           <t>国立第七中学（骑马钉版）</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10337,6 +10714,11 @@
       <c r="G309" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/8c4bd81d7048</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10731,6 @@
           <t>谁偷了朕的外卖</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10366,6 +10747,11 @@
       <c r="G310" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/189448e0713a</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10764,6 @@
           <t>不死之徒</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10395,6 +10780,11 @@
       <c r="G311" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d90c92c53f39</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10797,6 @@
           <t>失魂</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10424,6 +10813,11 @@
       <c r="G312" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/05fb2cc9db0a</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10830,6 @@
           <t>屋魂</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10453,6 +10846,11 @@
       <c r="G313" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7be3029319dc</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10863,6 @@
           <t>未完待续</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10482,6 +10879,11 @@
       <c r="G314" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c928c080711b</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10896,6 @@
           <t>月光下的诅咒</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10528,7 +10929,6 @@
           <t>牛鬼蛇神</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -10545,6 +10945,11 @@
       <c r="G316" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e920c9e24c3a</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10962,6 @@
           <t>红辣椒</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10568,7 +10972,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/23cd9f7c6e8a</t>
@@ -10584,7 +10987,6 @@
           <t>阿雅与魔女</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10595,7 +10997,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9effd40ba0f4</t>
@@ -10611,7 +11012,6 @@
           <t>侧耳倾听.1995.豆瓣评分8.9</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10622,7 +11022,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d46796ca8f30</t>
@@ -10638,7 +11037,6 @@
           <t>苍鹭AND少年.2023</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10649,7 +11047,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1f4c53fed9aa</t>
@@ -10665,7 +11062,6 @@
           <t>地海战记</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10676,7 +11072,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4cd570805a6a</t>
@@ -10692,7 +11087,6 @@
           <t>风之谷.1984.豆瓣评分8.9</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10703,7 +11097,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/446c48afc197</t>
@@ -10719,7 +11112,6 @@
           <t>哈尔的移动城堡.2004.豆瓣评分9.1</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10730,7 +11122,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/311eaa66645c</t>
@@ -10746,7 +11137,6 @@
           <t>红海龟</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10757,7 +11147,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0bed5f99c992</t>
@@ -10773,7 +11162,6 @@
           <t>辉夜姬物语</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10784,7 +11172,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d0ad2be20939</t>
@@ -10800,7 +11187,6 @@
           <t>红猪1992</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10811,7 +11197,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f6ca8b00ed73</t>
@@ -10827,7 +11212,6 @@
           <t>借东西的小人阿莉埃蒂.2010.豆瓣评分8.9</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10838,7 +11222,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/36a79af266f6</t>
@@ -10854,7 +11237,6 @@
           <t>记忆中的玛妮</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10865,7 +11247,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3dded1bb60a6</t>
@@ -10881,7 +11262,6 @@
           <t>鲁邦三世：卡里奥斯特罗城1979</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10892,7 +11272,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e0395568a37c</t>
@@ -10908,7 +11287,6 @@
           <t>龙猫.1998.豆瓣评分9.2</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10919,7 +11297,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/cc83537f511c</t>
@@ -10935,7 +11312,6 @@
           <t>猫的报恩</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10946,7 +11322,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/01e2825ff163</t>
@@ -10962,7 +11337,6 @@
           <t>魔女宅急便.1989.豆瓣评分8.7</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -10973,7 +11347,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/505f9564fcdd</t>
@@ -10989,7 +11362,6 @@
           <t>平成狸合战</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11000,7 +11372,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4c884e7e9d98</t>
@@ -11016,7 +11387,6 @@
           <t>起风了2013</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11027,7 +11397,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f8861d74be87</t>
@@ -11043,7 +11412,6 @@
           <t>千与千寻.2021.4K.豆瓣评分9.4</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11054,7 +11422,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5ed2f856c515</t>
@@ -11070,7 +11437,6 @@
           <t>岁月的童话</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11081,7 +11447,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dca4dc06096c</t>
@@ -11097,7 +11462,6 @@
           <t>听到涛声</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11108,7 +11472,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6d732a0ab5aa</t>
@@ -11124,7 +11487,6 @@
           <t>天空之城.1986.豆瓣评分9.2</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11135,7 +11497,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/565e385b9919</t>
@@ -11151,7 +11512,6 @@
           <t>我的邻居山田君</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11162,7 +11522,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e75e27e4b8ea</t>
@@ -11178,7 +11537,6 @@
           <t>萤火虫之墓</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11189,7 +11547,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/20776b6f00cb</t>
@@ -11205,7 +11562,6 @@
           <t>幽灵公主.1997.豆瓣评分8.9</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11216,7 +11572,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f038e52f0b48</t>
@@ -11232,7 +11587,6 @@
           <t>虞美人盛开的山坡</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11243,7 +11597,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/53a415d73fde</t>
@@ -11259,7 +11612,6 @@
           <t>崖上的波妞.2008.豆瓣评分8.6</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>动漫,宫崎骏</t>
@@ -11270,7 +11622,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fc6f18916582</t>
@@ -11301,7 +11652,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e005f7eab755</t>
@@ -11317,7 +11667,6 @@
           <t>冰雪奇缘</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>动漫,冰雪奇缘</t>
@@ -11328,7 +11677,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/79dd474cb6bb</t>
@@ -11367,6 +11715,11 @@
           <t>https://pan.quark.cn/s/c675e7514d1a</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>恐怖</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11377,7 +11730,6 @@
           <t>《十六年无穷日》作者：夏日勿苇</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11388,7 +11740,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f8867443f692</t>
@@ -11404,7 +11755,6 @@
           <t>《被曾经的金丝雀反向圈养了》作者：墨泊洲</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11415,7 +11765,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f140a8d03b3f</t>
@@ -11431,7 +11780,6 @@
           <t>《被竹马的表兄觊觎后》作者：抱帚忘雪</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11442,7 +11790,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4bc68383e4a7</t>
@@ -11458,7 +11805,6 @@
           <t>《穿进狗血文后和男主的命运交换了[快穿gb]》作者：姜沉漾</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11469,7 +11815,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0a181c0e6fba</t>
@@ -11485,7 +11830,6 @@
           <t>《从签到开始修仙成圣》作者：缇卡</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11496,7 +11840,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4d78409bb045</t>
@@ -11512,7 +11855,6 @@
           <t>《掺水酒不会梦到黑皮巧克力》作者：岫夕</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11523,7 +11865,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3d3d6f38c059</t>
@@ -11539,7 +11880,6 @@
           <t>《大美人甜蜜再婚生活[七零]》作者：春池星</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11550,7 +11890,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/cfeecb7ee244</t>
@@ -11566,7 +11905,6 @@
           <t>《大魔头他养大了死对头》作者：墨弦青</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11577,7 +11915,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ff364bbd6ae7</t>
@@ -11593,7 +11930,6 @@
           <t>《都市怪谈拆迁办（第一诡异拆迁办）》作者：撕枕犹眠</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11604,7 +11940,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e3af1f65fcfd</t>
@@ -11620,7 +11955,6 @@
           <t>《当我错刷你的校园卡之后》作者：周在川</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11631,7 +11965,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/482b8161a979</t>
@@ -11647,7 +11980,6 @@
           <t>《奋斗的金丝雀》</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11658,7 +11990,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/63d40d123952</t>
@@ -11674,7 +12005,6 @@
           <t>《古言短篇4：囡囡》作者：袖侧</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11685,7 +12015,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a782cbd8996f</t>
@@ -11701,7 +12030,6 @@
           <t>《怀了主母兄长的孩子后》作者：不落言笙</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11712,7 +12040,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/64613639cd9a</t>
@@ -11728,7 +12055,6 @@
           <t>《捡到一只小狐狸O！[全息]》作者：沉缄</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11739,7 +12065,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1956a451801e</t>
@@ -11755,7 +12080,6 @@
           <t>《将军太傲娇》作者：苏有仪</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11766,7 +12090,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2bfe95745f87</t>
@@ -11782,7 +12105,6 @@
           <t>《假千金身份曝光后被迫万人迷了》作者：待我温酒</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11793,7 +12115,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/36b6271022b6</t>
@@ -11809,7 +12130,6 @@
           <t>《九十三个红绿灯》作者：樾杉木</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11820,7 +12140,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6686c7ffa0ee</t>
@@ -11836,7 +12155,6 @@
           <t>《锦书散落星河》宋锦书 顾瑾珩</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11847,7 +12165,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0e85973b25e5</t>
@@ -11863,7 +12180,6 @@
           <t>《救赎文但与黑化男主互演》作者：酒酿汤圆W</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11874,7 +12190,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f58655bfbce1</t>
@@ -11890,7 +12205,6 @@
           <t>《巨星只想卖鞋和贴贴[娱乐圈]》作者：支野</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11901,7 +12215,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/08454139a9ee</t>
@@ -11917,7 +12230,6 @@
           <t>《开局一朵向日葵》作者：文梦呓</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11928,7 +12240,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e07a7a754007</t>
@@ -11944,7 +12255,6 @@
           <t>《没错，我是大反派[轮回末世]》作者：焚轮吹梦</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11955,7 +12265,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2fa4be453ecd</t>
@@ -11971,7 +12280,6 @@
           <t>《满级富婆，潇洒九零》作者：金面佛</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>小说</t>
@@ -11982,7 +12290,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e4b2d3f18610</t>
@@ -11998,7 +12305,6 @@
           <t>《末日领主种番薯日志[基建]》作者：甜饼喂猪</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12009,7 +12315,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6b5c613e600f</t>
@@ -12025,7 +12330,6 @@
           <t>《毛绒绒带我进厂》作者：春和景明一号</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12036,7 +12340,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0cdea0127956</t>
@@ -12052,7 +12355,6 @@
           <t>《明月不曾奔我而来》林舒苒 傅庭深</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12063,7 +12365,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0981cf7326b7</t>
@@ -12079,7 +12380,6 @@
           <t>《妈，救命!》作者：红刺北</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12090,7 +12390,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ce546aec935d</t>
@@ -12106,7 +12405,6 @@
           <t>《年代大佬的报恩小娇妻[八零]》作者：金湘语</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12117,7 +12415,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d9439264c38f</t>
@@ -12133,7 +12430,6 @@
           <t>《南风若知我意》谢瑶 裴瑾南</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12144,7 +12440,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4c9283f0e472</t>
@@ -12160,7 +12455,6 @@
           <t>《犬系陷阱》作者：韩肆夏</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12171,7 +12465,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1f8464d03eb1</t>
@@ -12187,7 +12480,6 @@
           <t>《清云鉴》作者：烬天翼</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12198,7 +12490,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/64c41e2c8c8f</t>
@@ -12214,7 +12505,6 @@
           <t>《全宇宙都在觊觎我的基因》作者：鹿衔灯</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12225,7 +12515,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/099bc0290e64</t>
@@ -12241,7 +12530,6 @@
           <t>《如懿传进忠同人之穿越时空奔向你》作者：进忠公公的迷妹</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12252,7 +12540,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/62efb3dfcc54</t>
@@ -12268,7 +12555,6 @@
           <t>《少阁主今天也没有死》作者：嵊灵</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12279,7 +12565,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/6a758e390481</t>
@@ -12295,7 +12580,6 @@
           <t>《世界更新中》作者：烛萤舟</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12306,7 +12590,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/43b85a883caa</t>
@@ -12322,7 +12605,6 @@
           <t>《随老公进城的乡下小媳妇重生了》</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12333,7 +12615,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/820eacb3194b</t>
@@ -12349,7 +12630,6 @@
           <t>《守陵娘子山食纪》作者：绿豆红汤</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12360,7 +12640,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fa49fc0c0f95</t>
@@ -12376,7 +12655,6 @@
           <t>《谁说分手后不能暗恋前任》作者：陶格</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12387,7 +12665,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0ef3713d4a3c</t>
@@ -12403,7 +12680,6 @@
           <t>《首席她又吐血了[星际机甲]》作者：仿生八爪鱼</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12414,7 +12690,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a26f853b0682</t>
@@ -12430,7 +12705,6 @@
           <t>《师祖为何还不飞升》作者：海盐芝士卷</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12441,7 +12715,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d69a0acd3e96</t>
@@ -12457,7 +12730,6 @@
           <t>《丧葬直播后暴富了》作者：达不溜蓝</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12468,7 +12740,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1368e1ea0cab</t>
@@ -12484,7 +12755,6 @@
           <t>《退!我老公尾巴在响!》作者：椰椰不打烊</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12495,7 +12765,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0f0e14b02765</t>
@@ -12511,7 +12780,6 @@
           <t>《她有惑人美貌2[快穿]》作者：玥滢</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12522,7 +12790,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/670d5495b1f4</t>
@@ -12538,7 +12805,6 @@
           <t>《为你打开时间的门[网络版]》作者：皎皎</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12549,7 +12815,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/2efb921bae6b</t>
@@ -12565,7 +12830,6 @@
           <t>《亡妻的第八年》作者：浅困</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12576,7 +12840,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3c6297954de3</t>
@@ -12592,7 +12855,6 @@
           <t>《我听见海棠花落》江晚吟 周砚白</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12603,7 +12865,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1d1b9ad7d03a</t>
@@ -12619,7 +12880,6 @@
           <t>《小巷烟火[八零]》作者：秋凌</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12630,7 +12890,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ccf8fc90be25</t>
@@ -12646,7 +12905,6 @@
           <t>《御兽：从天灾降临开始》作者：金彩</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12657,7 +12915,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e90ebe569558</t>
@@ -12673,7 +12930,6 @@
           <t>《纯白恶魔》作者：priest</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12684,7 +12940,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/022714ae032d</t>
@@ -12700,7 +12955,6 @@
           <t>《春风沉醉的夜晚》作者：鲤鲤鲤</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12711,7 +12965,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/97d3517f3181</t>
@@ -12727,7 +12980,6 @@
           <t>《穿进真假少爷文，我成恋综背景板》</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12738,7 +12990,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a851f0d05c25</t>
@@ -12754,7 +13005,6 @@
           <t>《纯情金主和他的金丝雀大哥》作者：布布里</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12765,7 +13015,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ff8cea42c6be</t>
@@ -12781,7 +13030,6 @@
           <t>《顶级恋爱脑，但装的》作者：祝辞酒</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12792,7 +13040,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/3a739975c3f7</t>
@@ -12808,7 +13055,6 @@
           <t>《当他分手后》作者：雾苏台</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12819,7 +13065,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/224914d3532f</t>
@@ -12835,7 +13080,6 @@
           <t>《烦人上司竟是我的家奴？！》作者：勤恳牛马</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12846,7 +13090,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0841d607b49a</t>
@@ -12862,7 +13105,6 @@
           <t>《分手》作者：冷山就木</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12873,7 +13115,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a43b0ac43ac7</t>
@@ -12889,7 +13130,6 @@
           <t>《寡夫郎有喜了》作者：猛嚼酸菜鱼</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12900,7 +13140,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/84f97a540914</t>
@@ -12916,7 +13155,6 @@
           <t>《顾总，夫人他又去相亲啦！》作者：楚君山</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12927,7 +13165,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/762657b4b30a</t>
@@ -12943,7 +13180,6 @@
           <t>《荒岛求生后揣了宿敌的崽》作者：日月一明</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12954,7 +13190,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c9a0823e7eab</t>
@@ -12970,7 +13205,6 @@
           <t>《和死对头的异界冒险[基建]》作者：木兰竹</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
           <t>小说</t>
@@ -12981,7 +13215,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/40585eff661f</t>
@@ -12997,7 +13230,6 @@
           <t>《禁欲系顶流被强取豪夺后》作者：付萌萌</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13008,7 +13240,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/933c97a68084</t>
@@ -13024,7 +13255,6 @@
           <t>《快穿硬核管家，专治霸总癫公》</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13035,7 +13265,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/15b08ea06645</t>
@@ -13051,7 +13280,6 @@
           <t>《凌晨三点熬夜会被随机拉进怪谈故事会》作者：石头羊</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13062,7 +13290,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/62243c60a6a9</t>
@@ -13078,7 +13305,6 @@
           <t>《荔枝煮茶》作者：静沚</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13089,7 +13315,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/edf623756613</t>
@@ -13105,7 +13330,6 @@
           <t>《摩擦生热》作者：一院</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13116,7 +13340,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5101cd34980b</t>
@@ -13132,7 +13355,6 @@
           <t>《梦里看见昨天》作者：不执灯</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13143,7 +13365,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1c2a11368396</t>
@@ -13159,7 +13380,6 @@
           <t>《男团选秀里的祭天皇族》作者：颓废大带鱼</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13170,7 +13390,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f763483fe001</t>
@@ -13186,7 +13405,6 @@
           <t>《破产霸总：兵王司机别太会宠</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13197,7 +13415,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/9b5a7cc1def6</t>
@@ -13213,7 +13430,6 @@
           <t>《漂亮宝贝不养了？》作者：杳杳一言</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13224,7 +13440,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ec1324328ded</t>
@@ -13240,7 +13455,6 @@
           <t>《什刹海是海吗》作者：晏灼宁</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13251,7 +13465,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/a7b409de2c77</t>
@@ -13267,7 +13480,6 @@
           <t>《死对头误食吐真剂后》作者：查理小羊</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13278,7 +13490,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fe07af9cd0de</t>
@@ -13294,7 +13505,6 @@
           <t>《丧尸也可以打网球》作者：左木茶茶君</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13305,7 +13515,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dc4c5e85b752</t>
@@ -13321,7 +13530,6 @@
           <t>《死亡万花筒》 作者：西子绪【补福利番】</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13332,7 +13540,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/895a7f71a9b6</t>
@@ -13348,7 +13555,6 @@
           <t>《伤心绿苹果》作者：下一天雨</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13359,7 +13565,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/cc4a46d54c2c</t>
@@ -13375,7 +13580,6 @@
           <t>《同僚们都有病啊！》作者：甜来哉</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13386,7 +13590,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dbb1998382b5</t>
@@ -13402,7 +13605,6 @@
           <t>《我靠天道系统带领宗门致富》</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13413,7 +13615,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/4ce5b4487a56</t>
@@ -13429,7 +13630,6 @@
           <t>《为了多活几年我闪婚了》作者：言六册</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13440,7 +13640,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/555709453c4a</t>
@@ -13456,7 +13655,6 @@
           <t>《误撩高岭之花后他黑化了》作者：深海鲤</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13467,7 +13665,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/675d96b714f9</t>
@@ -13483,7 +13680,6 @@
           <t>《万人嫌军校o，但钓系美人！》作者：一枕孤舟</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13494,7 +13690,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7d304028184e</t>
@@ -13510,7 +13705,6 @@
           <t>《易感期的顶A黏上舔狗beta了》作者：月下莲客</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13521,7 +13715,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/85b74c7d27d9</t>
@@ -13537,7 +13730,6 @@
           <t>《诱惑》作者：冥月鬼姬／鬼姬·溟</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13548,7 +13740,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/eb8104eb1785</t>
@@ -13564,7 +13755,6 @@
           <t>《作精假少爷失忆后攻略养兄》作者：脉脉春风</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13575,7 +13765,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7b6c6e87bc4a</t>
@@ -13591,7 +13780,6 @@
           <t>《竹马每天都在钓我》作者：橙三月</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13602,7 +13790,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/37c3261ca8ac</t>
@@ -13618,7 +13805,6 @@
           <t>《直男的自我攻略》作者：落回</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13629,7 +13815,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7e4bceb98040</t>
@@ -13645,7 +13830,6 @@
           <t>《真实遗愿清单》作者：卡比丘</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13656,7 +13840,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/53d1bb667dfa</t>
@@ -13672,7 +13855,6 @@
           <t>《重生之豁然》作者：缘何故</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13683,7 +13865,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/5da1fc0f0d5a</t>
@@ -13699,7 +13880,6 @@
           <t>《重生之至尊仙侣》作者：冰糖莲子羹</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13710,7 +13890,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d859100214e2</t>
@@ -13726,7 +13905,6 @@
           <t>《重新救赎偏执反派后（快穿）》作者：糖晚</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13737,7 +13915,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ea5bce8e8a94</t>
@@ -13753,7 +13930,6 @@
           <t>《穿成绝嗣皇帝早死的崽》作者：闻鹊语</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13764,7 +13940,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/f20fae829a05</t>
@@ -13780,7 +13955,6 @@
           <t>《九殿下究竟何时登基》作者：骨漏呱闻</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13791,7 +13965,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/612e51dd4b9e</t>
@@ -13807,7 +13980,6 @@
           <t>《快穿：大佬又穿成恶毒女配啦！》作者：暮十七</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13818,7 +13990,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/efb48ceeee98</t>
@@ -13834,7 +14005,6 @@
           <t>《末世降临：我的随身空间无限大！》作者：卿阿卿</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13845,7 +14015,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1c3cdaf6d56e</t>
@@ -13861,7 +14030,6 @@
           <t>《末世小店：我带系统搞经营》作者：榴莲肠粉</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13872,7 +14040,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0b64680b1485</t>
@@ -13888,7 +14055,6 @@
           <t>《骑自行车逛遍各位面》作者：蒜冰激凌香</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13899,7 +14065,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d9f0fb0e7d3a</t>
@@ -13915,7 +14080,6 @@
           <t>《傻女归来》作者：小寒将至</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13926,7 +14090,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1aa3c8677929</t>
@@ -13942,7 +14105,6 @@
           <t>《逃荒，我全家都是重生的》作者：墨墨是墨爷</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13953,7 +14115,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/194d0b3064f7</t>
@@ -13969,7 +14130,6 @@
           <t>《心声泄露后：满朝文武爱上吃瓜》作者：甜玉米汁</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
           <t>小说</t>
@@ -13980,7 +14140,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c4b2d592a21c</t>
@@ -13996,7 +14155,6 @@
           <t>《直播：摇出霍去病做代打》作者：酒神葡萄绿</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14007,7 +14165,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1d7fb390a435</t>
@@ -14023,7 +14180,6 @@
           <t>《败给格格＆别吵，前任的大佬小叔在宠了》景格 厉牧时 作者：灯下不黑黑</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14034,7 +14190,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/48d88efb4a8e</t>
@@ -14050,7 +14205,6 @@
           <t>《别人修仙我捡漏，卷王们破防了》凤青禾 作者：一人派对</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14061,7 +14215,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ac430a3f3cb6</t>
@@ -14077,7 +14230,6 @@
           <t>《白月光回京，夜夜被太子爷亲红温》贺雨棠 周宴泽 作者：野火不熄</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14088,7 +14240,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/21ed9b227073</t>
@@ -14104,7 +14255,6 @@
           <t>《春望山楹》云菅 周婆子 作者：庄大刀</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14115,7 +14265,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c148f9eb8dae</t>
@@ -14131,7 +14280,6 @@
           <t>《热恋从新婚开始＆婚既钟情》林序秋 周望津 作者：暴躁小红</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14142,7 +14290,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/30aceb039b93</t>
@@ -14158,7 +14305,6 @@
           <t>《越夜越熟＆玩玩而已，他怎么上瘾了》诗悦 秦昭 作者：玛格绿特</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14169,7 +14315,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/142fee39cf5f</t>
@@ -14185,7 +14330,6 @@
           <t>《真千金她断亲修道＆玄学大佬断亲后，和酆都大帝锁了》酆烬 沈月魄 作者：脾气暴躁的吼吼</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14196,7 +14340,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0c78700a9b55</t>
@@ -14227,7 +14370,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fb10f2c52bb1</t>
@@ -14243,7 +14385,6 @@
           <t>季风吹过橘色的海</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14260,6 +14401,11 @@
       <c r="G453" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/1344ec35ccd0</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -14295,6 +14441,11 @@
           <t>https://pan.quark.cn/s/5d694cff834e</t>
         </is>
       </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>推理</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -14305,7 +14456,6 @@
           <t>豆大点事物语</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14339,7 +14489,6 @@
           <t>盒子先生的秘密商店</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14356,6 +14505,11 @@
       <c r="G456" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/7ffada50549b</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14522,6 @@
           <t>豺狼的日子</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
           <t>剧集,豺狼的日子</t>
@@ -14379,7 +14532,6 @@
           <t>剧集</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/8f1dba4c0f68</t>
@@ -14395,7 +14547,6 @@
           <t>孤城</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14429,7 +14580,6 @@
           <t>刀鞘</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14446,6 +14596,11 @@
       <c r="G459" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c00a82990679</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>谍战</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14613,6 @@
           <t>精神病院4</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14475,6 +14629,11 @@
       <c r="G460" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/19127453dd73</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>恐怖</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14646,6 @@
           <t>最后的晚餐</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14504,6 +14662,11 @@
       <c r="G461" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ff2903564234</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14679,6 @@
           <t>青白</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14533,6 +14695,11 @@
       <c r="G462" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/0a7827db09f3</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>古风</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14712,6 @@
           <t>蓝色大丽花</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14579,7 +14745,6 @@
           <t>此时彼刻之人</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14596,6 +14761,11 @@
       <c r="G464" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/dd840fcb4e06</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>推理</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14778,6 @@
           <t>长安秘案录</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14619,7 +14788,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/ec0a3f96df64</t>
@@ -14635,7 +14803,6 @@
           <t>亡瘾</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
           <t>小说</t>
@@ -14646,7 +14813,6 @@
           <t>小说</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/c006323e4119</t>
@@ -14662,7 +14828,6 @@
           <t>我与我诀别</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14679,6 +14844,11 @@
       <c r="G467" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/d0bd4ce4f9fe</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14861,6 @@
           <t>红豆</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14725,7 +14894,6 @@
           <t>大宴之上</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14759,7 +14927,6 @@
           <t>家宴</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14776,6 +14943,11 @@
       <c r="G470" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/302f10500dff</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14960,6 @@
           <t>阴明寺</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14822,7 +14993,6 @@
           <t>死者在幻夜中醒来</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14856,7 +15026,6 @@
           <t>刑侦现场雪夜追凶</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14890,7 +15059,6 @@
           <t>生还之日</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14924,7 +15092,6 @@
           <t>一个死去的朋友</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14958,7 +15125,6 @@
           <t>生门</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -14992,7 +15158,6 @@
           <t>东京恐怖故事：加藤病院</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15026,7 +15191,6 @@
           <t>三界之下</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15060,7 +15224,6 @@
           <t>猫岛2犬山谋杀循环</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15094,7 +15257,6 @@
           <t>声声慢</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15128,7 +15290,6 @@
           <t>声声慢2</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15162,7 +15323,6 @@
           <t>我滴家在东北</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -15179,6 +15339,11 @@
       <c r="G482" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/74291074815b</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>欢乐</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15356,6 @@
           <t>花牌情缘</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
           <t>动漫</t>
@@ -15202,7 +15366,6 @@
           <t>动漫</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/e53c5370ea1c</t>
@@ -15218,7 +15381,6 @@
           <t>花田喜事</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
           <t>剧本杀</t>
@@ -16124,6 +16286,11 @@
           <t>https://pan.quark.cn/s/4097a88042e9</t>
         </is>
       </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>恐怖</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -16443,6 +16610,11 @@
           <t>https://pan.quark.cn/s/db1a18bd2f60</t>
         </is>
       </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>古风</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -17194,6 +17366,11 @@
       <c r="G546" s="14" t="inlineStr">
         <is>
           <t>https://pan.quark.cn/s/fa0b8ca2c1c2</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>情感</t>
         </is>
       </c>
     </row>
